--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>14.09.2026 08:50:18</t>
+    <t>14.09.2026 10:25:11</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -10999,7 +10999,7 @@
     <t>VCD</t>
   </si>
   <si>
-    <t>AZİMUT PORTFÖY İKİNCİ SERBEST FON</t>
+    <t>AZİMUT PORTFÖY PARA PİYASASI KATILIM SERBEST FON</t>
   </si>
   <si>
     <t>VCG</t>
@@ -12818,7 +12818,7 @@
         <v>46279</v>
       </c>
       <c r="D7" s="7">
-        <v>12.917674</v>
+        <v>12.915785</v>
       </c>
       <c r="E7" s="8">
         <v>1380684</v>
@@ -12827,7 +12827,7 @@
         <v>155</v>
       </c>
       <c r="G7" s="8">
-        <v>17835226.34</v>
+        <v>17832617.05</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -12863,17 +12863,17 @@
       <c r="C9" s="6">
         <v>46279</v>
       </c>
-      <c r="D9" s="8">
-        <v>0</v>
+      <c r="D9" s="7">
+        <v>133.801563</v>
       </c>
       <c r="E9" s="8">
-        <v>0</v>
+        <v>130681131</v>
       </c>
       <c r="F9" s="9">
         <v>180</v>
       </c>
       <c r="G9" s="8">
-        <v>0</v>
+        <v>17485339537.95</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -13346,17 +13346,17 @@
       <c r="C30" s="6">
         <v>46279</v>
       </c>
-      <c r="D30" s="8">
-        <v>0</v>
+      <c r="D30" s="7">
+        <v>1.328777</v>
       </c>
       <c r="E30" s="8">
-        <v>0</v>
+        <v>14368444249</v>
       </c>
       <c r="F30" s="9">
         <v>81536</v>
       </c>
       <c r="G30" s="8">
-        <v>0</v>
+        <v>19092455753.12</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -13416,7 +13416,7 @@
         <v>46279</v>
       </c>
       <c r="D33" s="7">
-        <v>0.601046</v>
+        <v>0.601081</v>
       </c>
       <c r="E33" s="8">
         <v>2035767048</v>
@@ -13425,7 +13425,7 @@
         <v>14823</v>
       </c>
       <c r="G33" s="8">
-        <v>1223590532.68</v>
+        <v>1223661411.16</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -13508,7 +13508,7 @@
         <v>46279</v>
       </c>
       <c r="D37" s="7">
-        <v>70.217039</v>
+        <v>70.132058</v>
       </c>
       <c r="E37" s="8">
         <v>479502</v>
@@ -13517,7 +13517,7 @@
         <v>102</v>
       </c>
       <c r="G37" s="8">
-        <v>33669210.78</v>
+        <v>33628461.87</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -13554,7 +13554,7 @@
         <v>46279</v>
       </c>
       <c r="D39" s="7">
-        <v>22.106788</v>
+        <v>22.187563</v>
       </c>
       <c r="E39" s="8">
         <v>6221880</v>
@@ -13563,7 +13563,7 @@
         <v>206</v>
       </c>
       <c r="G39" s="8">
-        <v>137545784.04</v>
+        <v>138048356.8</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13577,7 +13577,7 @@
         <v>46279</v>
       </c>
       <c r="D40" s="7">
-        <v>32.091681</v>
+        <v>32.185699</v>
       </c>
       <c r="E40" s="8">
         <v>3162820</v>
@@ -13586,7 +13586,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="8">
-        <v>101500210.89</v>
+        <v>101797572.89</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -13968,7 +13968,7 @@
         <v>46279</v>
       </c>
       <c r="D57" s="7">
-        <v>54.647855</v>
+        <v>54.647252</v>
       </c>
       <c r="E57" s="8">
         <v>247955185</v>
@@ -13977,7 +13977,7 @@
         <v>2340</v>
       </c>
       <c r="G57" s="8">
-        <v>13550218965.35</v>
+        <v>13550069428.44</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -14197,17 +14197,17 @@
       <c r="C67" s="6">
         <v>46279</v>
       </c>
-      <c r="D67" s="8">
-        <v>0</v>
+      <c r="D67" s="7">
+        <v>3.081075</v>
       </c>
       <c r="E67" s="8">
-        <v>0</v>
+        <v>279216621</v>
       </c>
       <c r="F67" s="9">
         <v>33</v>
       </c>
       <c r="G67" s="8">
-        <v>0</v>
+        <v>860287348.96</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -14612,7 +14612,7 @@
         <v>46279</v>
       </c>
       <c r="D85" s="7">
-        <v>49.964594</v>
+        <v>49.964407</v>
       </c>
       <c r="E85" s="8">
         <v>7781781</v>
@@ -14621,7 +14621,7 @@
         <v>522</v>
       </c>
       <c r="G85" s="8">
-        <v>388813528.49</v>
+        <v>388812074.3</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -14634,17 +14634,17 @@
       <c r="C86" s="6">
         <v>46279</v>
       </c>
-      <c r="D86" s="8">
-        <v>0</v>
+      <c r="D86" s="7">
+        <v>128.248639</v>
       </c>
       <c r="E86" s="8">
-        <v>0</v>
+        <v>2028702</v>
       </c>
       <c r="F86" s="9">
         <v>12</v>
       </c>
       <c r="G86" s="8">
-        <v>0</v>
+        <v>260178270.2</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -14727,7 +14727,7 @@
         <v>46279</v>
       </c>
       <c r="D90" s="7">
-        <v>1.728815</v>
+        <v>1.729855</v>
       </c>
       <c r="E90" s="8">
         <v>189103512</v>
@@ -14736,7 +14736,7 @@
         <v>12</v>
       </c>
       <c r="G90" s="8">
-        <v>326924987.82</v>
+        <v>327121660.54</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -15186,17 +15186,17 @@
       <c r="C110" s="6">
         <v>46279</v>
       </c>
-      <c r="D110" s="8">
-        <v>0</v>
+      <c r="D110" s="10">
+        <v>79.79043</v>
       </c>
       <c r="E110" s="8">
-        <v>0</v>
+        <v>41712119</v>
       </c>
       <c r="F110" s="9">
         <v>3</v>
       </c>
       <c r="G110" s="8">
-        <v>0</v>
+        <v>3328227924.95</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -15394,7 +15394,7 @@
         <v>46279</v>
       </c>
       <c r="D119" s="7">
-        <v>1.847571</v>
+        <v>1.853902</v>
       </c>
       <c r="E119" s="8">
         <v>5601605</v>
@@ -15403,7 +15403,7 @@
         <v>56</v>
       </c>
       <c r="G119" s="8">
-        <v>10349364.88</v>
+        <v>10384824.3</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -15440,7 +15440,7 @@
         <v>46279</v>
       </c>
       <c r="D121" s="7">
-        <v>1.173814</v>
+        <v>1.109878</v>
       </c>
       <c r="E121" s="8">
         <v>24988165</v>
@@ -15449,7 +15449,7 @@
         <v>319</v>
       </c>
       <c r="G121" s="8">
-        <v>29331457.33</v>
+        <v>27733826.07</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -16406,7 +16406,7 @@
         <v>46279</v>
       </c>
       <c r="D163" s="7">
-        <v>1.645313</v>
+        <v>1.650647</v>
       </c>
       <c r="E163" s="8">
         <v>53771518</v>
@@ -16415,7 +16415,7 @@
         <v>1143</v>
       </c>
       <c r="G163" s="8">
-        <v>88470970.33</v>
+        <v>88757772.64</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -16520,17 +16520,17 @@
       <c r="C168" s="6">
         <v>46279</v>
       </c>
-      <c r="D168" s="8">
-        <v>0</v>
+      <c r="D168" s="10">
+        <v>55.73661</v>
       </c>
       <c r="E168" s="8">
-        <v>0</v>
+        <v>28212700</v>
       </c>
       <c r="F168" s="9">
         <v>5</v>
       </c>
       <c r="G168" s="8">
-        <v>0</v>
+        <v>1572480258.58</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -17257,7 +17257,7 @@
         <v>46279</v>
       </c>
       <c r="D200" s="7">
-        <v>5.721023</v>
+        <v>5.721196</v>
       </c>
       <c r="E200" s="8">
         <v>3745267</v>
@@ -17266,7 +17266,7 @@
         <v>10</v>
       </c>
       <c r="G200" s="8">
-        <v>21426759.05</v>
+        <v>21427405.93</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -17349,7 +17349,7 @@
         <v>46279</v>
       </c>
       <c r="D204" s="7">
-        <v>1.272115</v>
+        <v>1.272331</v>
       </c>
       <c r="E204" s="8">
         <v>12439701</v>
@@ -17358,7 +17358,7 @@
         <v>190</v>
       </c>
       <c r="G204" s="8">
-        <v>15824733.6</v>
+        <v>15827412.96</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -17463,17 +17463,17 @@
       <c r="C209" s="6">
         <v>46279</v>
       </c>
-      <c r="D209" s="8">
-        <v>0</v>
+      <c r="D209" s="7">
+        <v>2.580702</v>
       </c>
       <c r="E209" s="8">
-        <v>0</v>
+        <v>747348590</v>
       </c>
       <c r="F209" s="9">
         <v>460</v>
       </c>
       <c r="G209" s="8">
-        <v>0</v>
+        <v>1928683833.84</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -17739,17 +17739,17 @@
       <c r="C221" s="6">
         <v>46279</v>
       </c>
-      <c r="D221" s="8">
-        <v>0</v>
+      <c r="D221" s="10">
+        <v>3.84331</v>
       </c>
       <c r="E221" s="8">
-        <v>0</v>
+        <v>247191395</v>
       </c>
       <c r="F221" s="9">
         <v>13908</v>
       </c>
       <c r="G221" s="8">
-        <v>0</v>
+        <v>950033048.14</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -18981,17 +18981,17 @@
       <c r="C275" s="6">
         <v>46279</v>
       </c>
-      <c r="D275" s="8">
-        <v>0</v>
+      <c r="D275" s="7">
+        <v>6.486006</v>
       </c>
       <c r="E275" s="8">
-        <v>0</v>
+        <v>4930836234</v>
       </c>
       <c r="F275" s="9">
         <v>47612</v>
       </c>
       <c r="G275" s="8">
-        <v>0</v>
+        <v>31981435370.21</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -19004,17 +19004,17 @@
       <c r="C276" s="6">
         <v>46279</v>
       </c>
-      <c r="D276" s="8">
-        <v>0</v>
+      <c r="D276" s="10">
+        <v>4.06882</v>
       </c>
       <c r="E276" s="8">
-        <v>0</v>
+        <v>295635450</v>
       </c>
       <c r="F276" s="9">
         <v>2</v>
       </c>
       <c r="G276" s="8">
-        <v>0</v>
+        <v>1202887482.28</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -19073,17 +19073,17 @@
       <c r="C279" s="6">
         <v>46279</v>
       </c>
-      <c r="D279" s="8">
-        <v>0</v>
+      <c r="D279" s="7">
+        <v>0.436411</v>
       </c>
       <c r="E279" s="8">
-        <v>0</v>
+        <v>5285672299</v>
       </c>
       <c r="F279" s="9">
         <v>46</v>
       </c>
       <c r="G279" s="8">
-        <v>0</v>
+        <v>2306723955.95</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -19120,7 +19120,7 @@
         <v>46279</v>
       </c>
       <c r="D281" s="7">
-        <v>5.403679</v>
+        <v>5.420333</v>
       </c>
       <c r="E281" s="8">
         <v>4731309</v>
@@ -19129,7 +19129,7 @@
         <v>1111</v>
       </c>
       <c r="G281" s="8">
-        <v>25566477.01</v>
+        <v>25645272.63</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -19189,7 +19189,7 @@
         <v>46279</v>
       </c>
       <c r="D284" s="7">
-        <v>1.144673</v>
+        <v>1.144694</v>
       </c>
       <c r="E284" s="8">
         <v>63100620</v>
@@ -19198,7 +19198,7 @@
         <v>767</v>
       </c>
       <c r="G284" s="8">
-        <v>72229576.86</v>
+        <v>72230884.06</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -19326,17 +19326,17 @@
       <c r="C290" s="6">
         <v>46279</v>
       </c>
-      <c r="D290" s="8">
-        <v>0</v>
+      <c r="D290" s="7">
+        <v>1.513126</v>
       </c>
       <c r="E290" s="8">
-        <v>0</v>
+        <v>2184624983</v>
       </c>
       <c r="F290" s="9">
         <v>70</v>
       </c>
       <c r="G290" s="8">
-        <v>0</v>
+        <v>3305613553.26</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -19373,7 +19373,7 @@
         <v>46279</v>
       </c>
       <c r="D292" s="7">
-        <v>48.484941</v>
+        <v>48.485011</v>
       </c>
       <c r="E292" s="8">
         <v>50978831</v>
@@ -19382,7 +19382,7 @@
         <v>239</v>
       </c>
       <c r="G292" s="8">
-        <v>2471705613.97</v>
+        <v>2471709194.49</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -19672,7 +19672,7 @@
         <v>46279</v>
       </c>
       <c r="D305" s="7">
-        <v>6.869401</v>
+        <v>6.865021</v>
       </c>
       <c r="E305" s="8">
         <v>437308991</v>
@@ -19681,7 +19681,7 @@
         <v>15157</v>
       </c>
       <c r="G305" s="8">
-        <v>3004050978.08</v>
+        <v>3002135355.59</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -19878,8 +19878,8 @@
       <c r="C314" s="6">
         <v>46279</v>
       </c>
-      <c r="D314" s="7">
-        <v>52.944037</v>
+      <c r="D314" s="10">
+        <v>52.87235</v>
       </c>
       <c r="E314" s="8">
         <v>27299529</v>
@@ -19888,7 +19888,7 @@
         <v>1058</v>
       </c>
       <c r="G314" s="8">
-        <v>1445347264.51</v>
+        <v>1443390260.77</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -20178,7 +20178,7 @@
         <v>46279</v>
       </c>
       <c r="D327" s="7">
-        <v>75.734816</v>
+        <v>75.743315</v>
       </c>
       <c r="E327" s="8">
         <v>7294243</v>
@@ -20187,7 +20187,7 @@
         <v>3</v>
       </c>
       <c r="G327" s="8">
-        <v>552428153.16</v>
+        <v>552490146.48</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -20431,7 +20431,7 @@
         <v>46279</v>
       </c>
       <c r="D338" s="7">
-        <v>103.683705</v>
+        <v>103.685139</v>
       </c>
       <c r="E338" s="8">
         <v>22490084</v>
@@ -20440,7 +20440,7 @@
         <v>1</v>
       </c>
       <c r="G338" s="8">
-        <v>2331855238.45</v>
+        <v>2331887489.48</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -20546,7 +20546,7 @@
         <v>46279</v>
       </c>
       <c r="D343" s="7">
-        <v>1.255093</v>
+        <v>1.256924</v>
       </c>
       <c r="E343" s="8">
         <v>32636305</v>
@@ -20555,7 +20555,7 @@
         <v>42</v>
       </c>
       <c r="G343" s="8">
-        <v>40961582.06</v>
+        <v>41021354.7</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -20707,7 +20707,7 @@
         <v>46279</v>
       </c>
       <c r="D350" s="7">
-        <v>15.027448</v>
+        <v>15.049422</v>
       </c>
       <c r="E350" s="8">
         <v>9836053</v>
@@ -20716,7 +20716,7 @@
         <v>1215</v>
       </c>
       <c r="G350" s="8">
-        <v>147810771.25</v>
+        <v>148026911.16</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -20959,17 +20959,17 @@
       <c r="C361" s="6">
         <v>46279</v>
       </c>
-      <c r="D361" s="8">
-        <v>0</v>
+      <c r="D361" s="7">
+        <v>1.106019</v>
       </c>
       <c r="E361" s="8">
-        <v>0</v>
+        <v>130440010</v>
       </c>
       <c r="F361" s="9">
         <v>438</v>
       </c>
       <c r="G361" s="8">
-        <v>0</v>
+        <v>144269145.15</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -21581,7 +21581,7 @@
         <v>46279</v>
       </c>
       <c r="D388" s="7">
-        <v>1.167498</v>
+        <v>1.167503</v>
       </c>
       <c r="E388" s="8">
         <v>25305317</v>
@@ -21590,7 +21590,7 @@
         <v>958</v>
       </c>
       <c r="G388" s="8">
-        <v>29543898.08</v>
+        <v>29544023.4</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -21902,17 +21902,17 @@
       <c r="C402" s="6">
         <v>46279</v>
       </c>
-      <c r="D402" s="8">
-        <v>0</v>
+      <c r="D402" s="7">
+        <v>1.865821</v>
       </c>
       <c r="E402" s="8">
-        <v>0</v>
+        <v>1165587248</v>
       </c>
       <c r="F402" s="9">
         <v>1275</v>
       </c>
       <c r="G402" s="8">
-        <v>0</v>
+        <v>2174777187.45</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
@@ -21995,7 +21995,7 @@
         <v>46279</v>
       </c>
       <c r="D406" s="7">
-        <v>1.169175</v>
+        <v>1.169189</v>
       </c>
       <c r="E406" s="8">
         <v>37525004</v>
@@ -22004,7 +22004,7 @@
         <v>1753</v>
       </c>
       <c r="G406" s="8">
-        <v>43873283.48</v>
+        <v>43873809.84</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
@@ -22041,7 +22041,7 @@
         <v>46279</v>
       </c>
       <c r="D408" s="7">
-        <v>49.142603</v>
+        <v>49.144234</v>
       </c>
       <c r="E408" s="8">
         <v>1577692</v>
@@ -22050,7 +22050,7 @@
         <v>117</v>
       </c>
       <c r="G408" s="8">
-        <v>77531892.08</v>
+        <v>77534464.67</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
@@ -22087,7 +22087,7 @@
         <v>46279</v>
       </c>
       <c r="D410" s="7">
-        <v>1.224692</v>
+        <v>1.224801</v>
       </c>
       <c r="E410" s="8">
         <v>34518430</v>
@@ -22096,7 +22096,7 @@
         <v>1810</v>
       </c>
       <c r="G410" s="8">
-        <v>42274445.39</v>
+        <v>42278210.37</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
@@ -22454,17 +22454,17 @@
       <c r="C426" s="6">
         <v>46279</v>
       </c>
-      <c r="D426" s="8">
-        <v>0</v>
+      <c r="D426" s="7">
+        <v>45.026207</v>
       </c>
       <c r="E426" s="8">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F426" s="9">
         <v>1</v>
       </c>
       <c r="G426" s="8">
-        <v>0</v>
+        <v>4502620.67</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
@@ -22616,7 +22616,7 @@
         <v>46279</v>
       </c>
       <c r="D433" s="7">
-        <v>4.759259</v>
+        <v>4.759256</v>
       </c>
       <c r="E433" s="8">
         <v>62460113</v>
@@ -22625,7 +22625,7 @@
         <v>396</v>
       </c>
       <c r="G433" s="8">
-        <v>297263830.45</v>
+        <v>297263648.4</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
@@ -22915,7 +22915,7 @@
         <v>46279</v>
       </c>
       <c r="D446" s="7">
-        <v>7.876077</v>
+        <v>7.886609</v>
       </c>
       <c r="E446" s="8">
         <v>254819233</v>
@@ -22924,7 +22924,7 @@
         <v>2398</v>
       </c>
       <c r="G446" s="8">
-        <v>2006975816.83</v>
+        <v>2009659763.08</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
@@ -23444,7 +23444,7 @@
         <v>46279</v>
       </c>
       <c r="D469" s="7">
-        <v>0.208439</v>
+        <v>0.208518</v>
       </c>
       <c r="E469" s="8">
         <v>52393870132.04</v>
@@ -23453,7 +23453,7 @@
         <v>6521</v>
       </c>
       <c r="G469" s="8">
-        <v>10920907465.24</v>
+        <v>10925052692.64</v>
       </c>
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.25">
@@ -23466,17 +23466,17 @@
       <c r="C470" s="6">
         <v>46279</v>
       </c>
-      <c r="D470" s="8">
-        <v>0</v>
+      <c r="D470" s="7">
+        <v>2.130506</v>
       </c>
       <c r="E470" s="8">
-        <v>0</v>
+        <v>194703301</v>
       </c>
       <c r="F470" s="9">
         <v>1708</v>
       </c>
       <c r="G470" s="8">
-        <v>0</v>
+        <v>414816524.94</v>
       </c>
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.25">
@@ -23835,7 +23835,7 @@
         <v>46279</v>
       </c>
       <c r="D486" s="7">
-        <v>0.908005</v>
+        <v>0.907974</v>
       </c>
       <c r="E486" s="8">
         <v>513376841</v>
@@ -23844,7 +23844,7 @@
         <v>20</v>
       </c>
       <c r="G486" s="8">
-        <v>466148692.27</v>
+        <v>466133036.41</v>
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
@@ -23950,7 +23950,7 @@
         <v>46279</v>
       </c>
       <c r="D491" s="7">
-        <v>4.838432</v>
+        <v>4.863138</v>
       </c>
       <c r="E491" s="8">
         <v>76682656</v>
@@ -23959,7 +23959,7 @@
         <v>522</v>
       </c>
       <c r="G491" s="8">
-        <v>371023782.35</v>
+        <v>372918367.37</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
@@ -24064,17 +24064,17 @@
       <c r="C496" s="6">
         <v>46279</v>
       </c>
-      <c r="D496" s="8">
-        <v>0</v>
+      <c r="D496" s="7">
+        <v>1.508088</v>
       </c>
       <c r="E496" s="8">
-        <v>0</v>
+        <v>1796932937</v>
       </c>
       <c r="F496" s="9">
         <v>11472</v>
       </c>
       <c r="G496" s="8">
-        <v>0</v>
+        <v>2709933229.9</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
@@ -24295,7 +24295,7 @@
         <v>46279</v>
       </c>
       <c r="D506" s="7">
-        <v>0.055344</v>
+        <v>0.055343</v>
       </c>
       <c r="E506" s="8">
         <v>28277659875.69</v>
@@ -24304,7 +24304,7 @@
         <v>144</v>
       </c>
       <c r="G506" s="8">
-        <v>1565010056.29</v>
+        <v>1564961869.82</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
@@ -24547,8 +24547,8 @@
       <c r="C517" s="6">
         <v>46279</v>
       </c>
-      <c r="D517" s="7">
-        <v>5.780586</v>
+      <c r="D517" s="10">
+        <v>5.79735</v>
       </c>
       <c r="E517" s="8">
         <v>201989273.63</v>
@@ -24557,7 +24557,7 @@
         <v>2119</v>
       </c>
       <c r="G517" s="8">
-        <v>1167616424.1</v>
+        <v>1171002559.35</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
@@ -24616,17 +24616,17 @@
       <c r="C520" s="6">
         <v>46279</v>
       </c>
-      <c r="D520" s="8">
-        <v>0</v>
+      <c r="D520" s="7">
+        <v>78.145471</v>
       </c>
       <c r="E520" s="8">
-        <v>0</v>
+        <v>5527677</v>
       </c>
       <c r="F520" s="9">
         <v>1</v>
       </c>
       <c r="G520" s="8">
-        <v>0</v>
+        <v>431962923.87</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.25">
@@ -24708,17 +24708,17 @@
       <c r="C524" s="6">
         <v>46279</v>
       </c>
-      <c r="D524" s="8">
-        <v>0</v>
+      <c r="D524" s="7">
+        <v>12.888813</v>
       </c>
       <c r="E524" s="8">
-        <v>0</v>
+        <v>27913127</v>
       </c>
       <c r="F524" s="9">
         <v>2691</v>
       </c>
       <c r="G524" s="8">
-        <v>0</v>
+        <v>359767067.28</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
@@ -24731,17 +24731,17 @@
       <c r="C525" s="6">
         <v>46279</v>
       </c>
-      <c r="D525" s="8">
-        <v>0</v>
+      <c r="D525" s="7">
+        <v>63.985374</v>
       </c>
       <c r="E525" s="8">
-        <v>0</v>
+        <v>7935068</v>
       </c>
       <c r="F525" s="9">
         <v>1</v>
       </c>
       <c r="G525" s="8">
-        <v>0</v>
+        <v>507728291.05</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.25">
@@ -24823,17 +24823,17 @@
       <c r="C529" s="6">
         <v>46279</v>
       </c>
-      <c r="D529" s="8">
-        <v>0</v>
+      <c r="D529" s="7">
+        <v>67.779739</v>
       </c>
       <c r="E529" s="8">
-        <v>0</v>
+        <v>32360328</v>
       </c>
       <c r="F529" s="9">
         <v>5</v>
       </c>
       <c r="G529" s="8">
-        <v>0</v>
+        <v>2193374577.52</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
@@ -24846,17 +24846,17 @@
       <c r="C530" s="6">
         <v>46279</v>
       </c>
-      <c r="D530" s="8">
-        <v>0</v>
+      <c r="D530" s="7">
+        <v>62.901786</v>
       </c>
       <c r="E530" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F530" s="9">
         <v>1</v>
       </c>
       <c r="G530" s="8">
-        <v>0</v>
+        <v>247895939.18</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
@@ -25007,17 +25007,17 @@
       <c r="C537" s="6">
         <v>46279</v>
       </c>
-      <c r="D537" s="8">
-        <v>0</v>
+      <c r="D537" s="7">
+        <v>71.295524</v>
       </c>
       <c r="E537" s="8">
-        <v>0</v>
+        <v>53983981</v>
       </c>
       <c r="F537" s="9">
         <v>2</v>
       </c>
       <c r="G537" s="8">
-        <v>0</v>
+        <v>3848816188.06</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
@@ -25030,17 +25030,17 @@
       <c r="C538" s="6">
         <v>46279</v>
       </c>
-      <c r="D538" s="8">
-        <v>0</v>
+      <c r="D538" s="7">
+        <v>13.602493</v>
       </c>
       <c r="E538" s="8">
-        <v>0</v>
+        <v>165461008</v>
       </c>
       <c r="F538" s="9">
         <v>21813</v>
       </c>
       <c r="G538" s="8">
-        <v>0</v>
+        <v>2250682121.42</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
@@ -25053,8 +25053,8 @@
       <c r="C539" s="6">
         <v>46279</v>
       </c>
-      <c r="D539" s="11">
-        <v>3.6157</v>
+      <c r="D539" s="10">
+        <v>3.61858</v>
       </c>
       <c r="E539" s="8">
         <v>335545831</v>
@@ -25063,7 +25063,7 @@
         <v>3245</v>
       </c>
       <c r="G539" s="8">
-        <v>1213233066.93</v>
+        <v>1214199530.11</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -25076,17 +25076,17 @@
       <c r="C540" s="6">
         <v>46279</v>
       </c>
-      <c r="D540" s="8">
-        <v>0</v>
+      <c r="D540" s="10">
+        <v>72.08076</v>
       </c>
       <c r="E540" s="8">
-        <v>0</v>
+        <v>11517383</v>
       </c>
       <c r="F540" s="9">
         <v>2</v>
       </c>
       <c r="G540" s="8">
-        <v>0</v>
+        <v>830181723.32</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
@@ -25099,17 +25099,17 @@
       <c r="C541" s="6">
         <v>46279</v>
       </c>
-      <c r="D541" s="8">
-        <v>0</v>
+      <c r="D541" s="7">
+        <v>6.021665</v>
       </c>
       <c r="E541" s="8">
-        <v>0</v>
+        <v>222060386</v>
       </c>
       <c r="F541" s="9">
         <v>2</v>
       </c>
       <c r="G541" s="8">
-        <v>0</v>
+        <v>1337173149.41</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
@@ -25122,17 +25122,17 @@
       <c r="C542" s="6">
         <v>46279</v>
       </c>
-      <c r="D542" s="8">
-        <v>0</v>
+      <c r="D542" s="7">
+        <v>4.033957</v>
       </c>
       <c r="E542" s="8">
-        <v>0</v>
+        <v>253720603</v>
       </c>
       <c r="F542" s="9">
         <v>20</v>
       </c>
       <c r="G542" s="8">
-        <v>0</v>
+        <v>1023498026.92</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
@@ -25145,17 +25145,17 @@
       <c r="C543" s="6">
         <v>46279</v>
       </c>
-      <c r="D543" s="8">
-        <v>0</v>
+      <c r="D543" s="7">
+        <v>65.280266</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>3425896</v>
       </c>
       <c r="F543" s="9">
         <v>3</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>223643402.6</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25168,17 +25168,17 @@
       <c r="C544" s="6">
         <v>46279</v>
       </c>
-      <c r="D544" s="8">
-        <v>0</v>
+      <c r="D544" s="7">
+        <v>61.633499</v>
       </c>
       <c r="E544" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F544" s="9">
         <v>1</v>
       </c>
       <c r="G544" s="8">
-        <v>0</v>
+        <v>12000966.83</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -25191,17 +25191,17 @@
       <c r="C545" s="6">
         <v>46279</v>
       </c>
-      <c r="D545" s="8">
-        <v>0</v>
+      <c r="D545" s="7">
+        <v>62.742251</v>
       </c>
       <c r="E545" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F545" s="9">
         <v>4</v>
       </c>
       <c r="G545" s="8">
-        <v>0</v>
+        <v>508301826.93</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -25214,17 +25214,17 @@
       <c r="C546" s="6">
         <v>46279</v>
       </c>
-      <c r="D546" s="8">
-        <v>0</v>
+      <c r="D546" s="7">
+        <v>67.488805</v>
       </c>
       <c r="E546" s="8">
-        <v>0</v>
+        <v>23236050</v>
       </c>
       <c r="F546" s="9">
         <v>1</v>
       </c>
       <c r="G546" s="8">
-        <v>0</v>
+        <v>1568173250.46</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -25237,17 +25237,17 @@
       <c r="C547" s="6">
         <v>46279</v>
       </c>
-      <c r="D547" s="8">
-        <v>0</v>
+      <c r="D547" s="7">
+        <v>77.006906</v>
       </c>
       <c r="E547" s="8">
-        <v>0</v>
+        <v>2099501</v>
       </c>
       <c r="F547" s="9">
         <v>2</v>
       </c>
       <c r="G547" s="8">
-        <v>0</v>
+        <v>161676075.11</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -25283,17 +25283,17 @@
       <c r="C549" s="6">
         <v>46279</v>
       </c>
-      <c r="D549" s="8">
-        <v>0</v>
+      <c r="D549" s="7">
+        <v>62.216232</v>
       </c>
       <c r="E549" s="8">
-        <v>0</v>
+        <v>6634456</v>
       </c>
       <c r="F549" s="9">
         <v>1</v>
       </c>
       <c r="G549" s="8">
-        <v>0</v>
+        <v>412770853.02</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -25306,17 +25306,17 @@
       <c r="C550" s="6">
         <v>46279</v>
       </c>
-      <c r="D550" s="8">
-        <v>0</v>
+      <c r="D550" s="10">
+        <v>71.06425</v>
       </c>
       <c r="E550" s="8">
-        <v>0</v>
+        <v>5961167</v>
       </c>
       <c r="F550" s="9">
         <v>4</v>
       </c>
       <c r="G550" s="8">
-        <v>0</v>
+        <v>423625861.02</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
@@ -25329,17 +25329,17 @@
       <c r="C551" s="6">
         <v>46279</v>
       </c>
-      <c r="D551" s="8">
-        <v>0</v>
+      <c r="D551" s="7">
+        <v>70.964916</v>
       </c>
       <c r="E551" s="8">
-        <v>0</v>
+        <v>1533442</v>
       </c>
       <c r="F551" s="9">
         <v>2</v>
       </c>
       <c r="G551" s="8">
-        <v>0</v>
+        <v>108820582.12</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -25352,17 +25352,17 @@
       <c r="C552" s="6">
         <v>46279</v>
       </c>
-      <c r="D552" s="8">
-        <v>0</v>
+      <c r="D552" s="7">
+        <v>54.454243</v>
       </c>
       <c r="E552" s="8">
-        <v>0</v>
+        <v>30698413</v>
       </c>
       <c r="F552" s="9">
         <v>3</v>
       </c>
       <c r="G552" s="8">
-        <v>0</v>
+        <v>1671658833.25</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -25375,17 +25375,17 @@
       <c r="C553" s="6">
         <v>46279</v>
       </c>
-      <c r="D553" s="8">
-        <v>0</v>
+      <c r="D553" s="7">
+        <v>11.441429</v>
       </c>
       <c r="E553" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F553" s="9">
         <v>1</v>
       </c>
       <c r="G553" s="8">
-        <v>0</v>
+        <v>337372581.99</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -25398,17 +25398,17 @@
       <c r="C554" s="6">
         <v>46279</v>
       </c>
-      <c r="D554" s="8">
-        <v>0</v>
+      <c r="D554" s="7">
+        <v>80.247441</v>
       </c>
       <c r="E554" s="8">
-        <v>0</v>
+        <v>11573436</v>
       </c>
       <c r="F554" s="9">
         <v>3</v>
       </c>
       <c r="G554" s="8">
-        <v>0</v>
+        <v>928738627.34</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -25421,17 +25421,17 @@
       <c r="C555" s="6">
         <v>46279</v>
       </c>
-      <c r="D555" s="8">
-        <v>0</v>
+      <c r="D555" s="11">
+        <v>70.9952</v>
       </c>
       <c r="E555" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F555" s="9">
         <v>3</v>
       </c>
       <c r="G555" s="8">
-        <v>0</v>
+        <v>413391347.75</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -25444,17 +25444,17 @@
       <c r="C556" s="6">
         <v>46279</v>
       </c>
-      <c r="D556" s="8">
-        <v>0</v>
+      <c r="D556" s="10">
+        <v>67.98955</v>
       </c>
       <c r="E556" s="8">
-        <v>0</v>
+        <v>121942198</v>
       </c>
       <c r="F556" s="9">
         <v>3</v>
       </c>
       <c r="G556" s="8">
-        <v>0</v>
+        <v>8290795219.63</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
@@ -25490,17 +25490,17 @@
       <c r="C558" s="6">
         <v>46279</v>
       </c>
-      <c r="D558" s="8">
-        <v>0</v>
+      <c r="D558" s="7">
+        <v>66.758879</v>
       </c>
       <c r="E558" s="8">
-        <v>0</v>
+        <v>90240169</v>
       </c>
       <c r="F558" s="9">
         <v>2</v>
       </c>
       <c r="G558" s="8">
-        <v>0</v>
+        <v>6024332529.29</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -25536,17 +25536,17 @@
       <c r="C560" s="6">
         <v>46279</v>
       </c>
-      <c r="D560" s="8">
-        <v>0</v>
+      <c r="D560" s="10">
+        <v>8.68657</v>
       </c>
       <c r="E560" s="8">
-        <v>0</v>
+        <v>342290935</v>
       </c>
       <c r="F560" s="9">
         <v>1</v>
       </c>
       <c r="G560" s="8">
-        <v>0</v>
+        <v>2973334217.94</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -25559,17 +25559,17 @@
       <c r="C561" s="6">
         <v>46279</v>
       </c>
-      <c r="D561" s="8">
-        <v>0</v>
+      <c r="D561" s="7">
+        <v>70.516171</v>
       </c>
       <c r="E561" s="8">
-        <v>0</v>
+        <v>6963426</v>
       </c>
       <c r="F561" s="9">
         <v>4</v>
       </c>
       <c r="G561" s="8">
-        <v>0</v>
+        <v>491034135.61</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
@@ -25582,17 +25582,17 @@
       <c r="C562" s="6">
         <v>46279</v>
       </c>
-      <c r="D562" s="8">
-        <v>0</v>
+      <c r="D562" s="7">
+        <v>8.094062</v>
       </c>
       <c r="E562" s="8">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="F562" s="9">
         <v>1</v>
       </c>
       <c r="G562" s="8">
-        <v>0</v>
+        <v>56067.57</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -25605,17 +25605,17 @@
       <c r="C563" s="6">
         <v>46279</v>
       </c>
-      <c r="D563" s="8">
-        <v>0</v>
+      <c r="D563" s="7">
+        <v>69.017704</v>
       </c>
       <c r="E563" s="8">
-        <v>0</v>
+        <v>23548896</v>
       </c>
       <c r="F563" s="9">
         <v>3</v>
       </c>
       <c r="G563" s="8">
-        <v>0</v>
+        <v>1625290744.35</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
@@ -25651,17 +25651,17 @@
       <c r="C565" s="6">
         <v>46279</v>
       </c>
-      <c r="D565" s="8">
-        <v>0</v>
+      <c r="D565" s="7">
+        <v>1.687098</v>
       </c>
       <c r="E565" s="8">
-        <v>0</v>
+        <v>22525911</v>
       </c>
       <c r="F565" s="9">
         <v>1921</v>
       </c>
       <c r="G565" s="8">
-        <v>0</v>
+        <v>38003421.5</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -25720,17 +25720,17 @@
       <c r="C568" s="6">
         <v>46279</v>
       </c>
-      <c r="D568" s="8">
-        <v>0</v>
+      <c r="D568" s="7">
+        <v>67.424987</v>
       </c>
       <c r="E568" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F568" s="9">
         <v>3</v>
       </c>
       <c r="G568" s="8">
-        <v>0</v>
+        <v>961706587.88</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
@@ -25766,17 +25766,17 @@
       <c r="C570" s="6">
         <v>46279</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="7">
+        <v>65.182503</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>6323702</v>
       </c>
       <c r="F570" s="9">
         <v>3</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>412194723.79</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25789,17 +25789,17 @@
       <c r="C571" s="6">
         <v>46279</v>
       </c>
-      <c r="D571" s="8">
-        <v>0</v>
+      <c r="D571" s="7">
+        <v>64.432466</v>
       </c>
       <c r="E571" s="8">
-        <v>0</v>
+        <v>2316713</v>
       </c>
       <c r="F571" s="9">
         <v>2</v>
       </c>
       <c r="G571" s="8">
-        <v>0</v>
+        <v>149271531.87</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -25812,17 +25812,17 @@
       <c r="C572" s="6">
         <v>46279</v>
       </c>
-      <c r="D572" s="8">
-        <v>0</v>
+      <c r="D572" s="7">
+        <v>64.632933</v>
       </c>
       <c r="E572" s="8">
-        <v>0</v>
+        <v>3647864</v>
       </c>
       <c r="F572" s="9">
         <v>2</v>
       </c>
       <c r="G572" s="8">
-        <v>0</v>
+        <v>235772151.28</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
@@ -25881,17 +25881,17 @@
       <c r="C575" s="6">
         <v>46279</v>
       </c>
-      <c r="D575" s="8">
-        <v>0</v>
+      <c r="D575" s="7">
+        <v>60.440715</v>
       </c>
       <c r="E575" s="8">
-        <v>0</v>
+        <v>9779449</v>
       </c>
       <c r="F575" s="9">
         <v>1</v>
       </c>
       <c r="G575" s="8">
-        <v>0</v>
+        <v>591076886.07</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
@@ -25996,17 +25996,17 @@
       <c r="C580" s="6">
         <v>46279</v>
       </c>
-      <c r="D580" s="8">
-        <v>0</v>
+      <c r="D580" s="7">
+        <v>66.597671</v>
       </c>
       <c r="E580" s="8">
-        <v>0</v>
+        <v>30617607</v>
       </c>
       <c r="F580" s="9">
         <v>2</v>
       </c>
       <c r="G580" s="8">
-        <v>0</v>
+        <v>2039061314.1</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.25">
@@ -26180,17 +26180,17 @@
       <c r="C588" s="6">
         <v>46279</v>
       </c>
-      <c r="D588" s="8">
-        <v>0</v>
+      <c r="D588" s="7">
+        <v>1.016547</v>
       </c>
       <c r="E588" s="8">
-        <v>0</v>
+        <v>9142074</v>
       </c>
       <c r="F588" s="9">
         <v>41</v>
       </c>
       <c r="G588" s="8">
-        <v>0</v>
+        <v>9293345.24</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -26226,17 +26226,17 @@
       <c r="C590" s="6">
         <v>46279</v>
       </c>
-      <c r="D590" s="8">
-        <v>0</v>
+      <c r="D590" s="7">
+        <v>69.666696</v>
       </c>
       <c r="E590" s="8">
-        <v>0</v>
+        <v>8202021</v>
       </c>
       <c r="F590" s="9">
         <v>4</v>
       </c>
       <c r="G590" s="8">
-        <v>0</v>
+        <v>571407703.45</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
@@ -26479,17 +26479,17 @@
       <c r="C601" s="6">
         <v>46279</v>
       </c>
-      <c r="D601" s="8">
-        <v>0</v>
+      <c r="D601" s="7">
+        <v>62.911906</v>
       </c>
       <c r="E601" s="8">
-        <v>0</v>
+        <v>25439462</v>
       </c>
       <c r="F601" s="9">
         <v>1</v>
       </c>
       <c r="G601" s="8">
-        <v>0</v>
+        <v>1600445033.09</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.25">
@@ -26617,17 +26617,17 @@
       <c r="C607" s="6">
         <v>46279</v>
       </c>
-      <c r="D607" s="8">
-        <v>0</v>
+      <c r="D607" s="11">
+        <v>62.1831</v>
       </c>
       <c r="E607" s="8">
-        <v>0</v>
+        <v>28454944</v>
       </c>
       <c r="F607" s="9">
         <v>3</v>
       </c>
       <c r="G607" s="8">
-        <v>0</v>
+        <v>1769416614.72</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
@@ -26779,7 +26779,7 @@
         <v>46279</v>
       </c>
       <c r="D614" s="7">
-        <v>4.368803</v>
+        <v>4.369138</v>
       </c>
       <c r="E614" s="8">
         <v>1114426365</v>
@@ -26788,7 +26788,7 @@
         <v>3993</v>
       </c>
       <c r="G614" s="8">
-        <v>4868709458.7</v>
+        <v>4869082764.22</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
@@ -26824,17 +26824,17 @@
       <c r="C616" s="6">
         <v>46279</v>
       </c>
-      <c r="D616" s="8">
-        <v>0</v>
+      <c r="D616" s="7">
+        <v>53.439161</v>
       </c>
       <c r="E616" s="8">
-        <v>0</v>
+        <v>7914345</v>
       </c>
       <c r="F616" s="9">
         <v>339</v>
       </c>
       <c r="G616" s="8">
-        <v>0</v>
+        <v>422935957.43</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
@@ -26870,17 +26870,17 @@
       <c r="C618" s="6">
         <v>46279</v>
       </c>
-      <c r="D618" s="8">
-        <v>0</v>
+      <c r="D618" s="7">
+        <v>1.014533</v>
       </c>
       <c r="E618" s="8">
-        <v>0</v>
+        <v>52924067</v>
       </c>
       <c r="F618" s="9">
         <v>19</v>
       </c>
       <c r="G618" s="8">
-        <v>0</v>
+        <v>53693196.49</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
@@ -26916,17 +26916,17 @@
       <c r="C620" s="6">
         <v>46279</v>
       </c>
-      <c r="D620" s="8">
-        <v>0</v>
+      <c r="D620" s="7">
+        <v>1.248945</v>
       </c>
       <c r="E620" s="8">
-        <v>0</v>
+        <v>595283766</v>
       </c>
       <c r="F620" s="9">
         <v>1366</v>
       </c>
       <c r="G620" s="8">
-        <v>0</v>
+        <v>743476676.47</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
@@ -26962,17 +26962,17 @@
       <c r="C622" s="6">
         <v>46279</v>
       </c>
-      <c r="D622" s="8">
-        <v>0</v>
+      <c r="D622" s="7">
+        <v>63.912331</v>
       </c>
       <c r="E622" s="8">
-        <v>0</v>
+        <v>11218134</v>
       </c>
       <c r="F622" s="9">
         <v>477</v>
       </c>
       <c r="G622" s="8">
-        <v>0</v>
+        <v>716977095.48</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
@@ -27008,17 +27008,17 @@
       <c r="C624" s="6">
         <v>46279</v>
       </c>
-      <c r="D624" s="8">
-        <v>0</v>
+      <c r="D624" s="7">
+        <v>12.464862</v>
       </c>
       <c r="E624" s="8">
-        <v>0</v>
+        <v>102516135</v>
       </c>
       <c r="F624" s="9">
         <v>9573</v>
       </c>
       <c r="G624" s="8">
-        <v>0</v>
+        <v>1277849456.84</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
@@ -27100,17 +27100,17 @@
       <c r="C628" s="6">
         <v>46279</v>
       </c>
-      <c r="D628" s="8">
-        <v>0</v>
+      <c r="D628" s="7">
+        <v>45.738457</v>
       </c>
       <c r="E628" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F628" s="9">
         <v>1</v>
       </c>
       <c r="G628" s="8">
-        <v>0</v>
+        <v>2681965.91</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
@@ -27123,17 +27123,17 @@
       <c r="C629" s="6">
         <v>46279</v>
       </c>
-      <c r="D629" s="8">
-        <v>0</v>
+      <c r="D629" s="7">
+        <v>18.861291</v>
       </c>
       <c r="E629" s="8">
-        <v>0</v>
+        <v>39444290</v>
       </c>
       <c r="F629" s="9">
         <v>2793</v>
       </c>
       <c r="G629" s="8">
-        <v>0</v>
+        <v>743970226.59</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
@@ -27146,17 +27146,17 @@
       <c r="C630" s="6">
         <v>46279</v>
       </c>
-      <c r="D630" s="8">
-        <v>0</v>
+      <c r="D630" s="7">
+        <v>58.869297</v>
       </c>
       <c r="E630" s="8">
-        <v>0</v>
+        <v>14772170</v>
       </c>
       <c r="F630" s="9">
         <v>2</v>
       </c>
       <c r="G630" s="8">
-        <v>0</v>
+        <v>869627262.86</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -27192,17 +27192,17 @@
       <c r="C632" s="6">
         <v>46279</v>
       </c>
-      <c r="D632" s="8">
-        <v>0</v>
+      <c r="D632" s="7">
+        <v>63.027665</v>
       </c>
       <c r="E632" s="8">
-        <v>0</v>
+        <v>20837078</v>
       </c>
       <c r="F632" s="9">
         <v>2</v>
       </c>
       <c r="G632" s="8">
-        <v>0</v>
+        <v>1313312379.34</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
@@ -27239,16 +27239,16 @@
         <v>46279</v>
       </c>
       <c r="D634" s="7">
-        <v>2.835231</v>
+        <v>2.850128</v>
       </c>
       <c r="E634" s="8">
-        <v>35557155</v>
+        <v>35478117</v>
       </c>
       <c r="F634" s="9">
         <v>3096</v>
       </c>
       <c r="G634" s="8">
-        <v>100812746.26</v>
+        <v>101117176.8</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
@@ -27261,17 +27261,17 @@
       <c r="C635" s="6">
         <v>46279</v>
       </c>
-      <c r="D635" s="8">
-        <v>0</v>
+      <c r="D635" s="10">
+        <v>21.52881</v>
       </c>
       <c r="E635" s="8">
-        <v>0</v>
+        <v>16695880</v>
       </c>
       <c r="F635" s="9">
         <v>2453</v>
       </c>
       <c r="G635" s="8">
-        <v>0</v>
+        <v>359442427.7</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.25">
@@ -27331,7 +27331,7 @@
         <v>46279</v>
       </c>
       <c r="D638" s="7">
-        <v>1.834473</v>
+        <v>1.828577</v>
       </c>
       <c r="E638" s="8">
         <v>209679547</v>
@@ -27340,7 +27340,7 @@
         <v>286</v>
       </c>
       <c r="G638" s="8">
-        <v>384651386.3</v>
+        <v>383415166.58</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.25">
@@ -27468,17 +27468,17 @@
       <c r="C644" s="6">
         <v>46279</v>
       </c>
-      <c r="D644" s="8">
-        <v>0</v>
+      <c r="D644" s="7">
+        <v>15.681249</v>
       </c>
       <c r="E644" s="8">
-        <v>0</v>
+        <v>3359152821</v>
       </c>
       <c r="F644" s="9">
         <v>8</v>
       </c>
       <c r="G644" s="8">
-        <v>0</v>
+        <v>52675711225.19</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
@@ -27514,17 +27514,17 @@
       <c r="C646" s="6">
         <v>46279</v>
       </c>
-      <c r="D646" s="8">
-        <v>0</v>
+      <c r="D646" s="7">
+        <v>58.104319</v>
       </c>
       <c r="E646" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F646" s="9">
         <v>2</v>
       </c>
       <c r="G646" s="8">
-        <v>0</v>
+        <v>269787649.41</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
@@ -27629,17 +27629,17 @@
       <c r="C651" s="6">
         <v>46279</v>
       </c>
-      <c r="D651" s="8">
-        <v>0</v>
+      <c r="D651" s="7">
+        <v>7.167279</v>
       </c>
       <c r="E651" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F651" s="9">
         <v>1</v>
       </c>
       <c r="G651" s="8">
-        <v>0</v>
+        <v>28880315713.06</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
@@ -27698,17 +27698,17 @@
       <c r="C654" s="6">
         <v>46279</v>
       </c>
-      <c r="D654" s="8">
-        <v>0</v>
+      <c r="D654" s="7">
+        <v>52.972617</v>
       </c>
       <c r="E654" s="8">
-        <v>0</v>
+        <v>28012535</v>
       </c>
       <c r="F654" s="9">
         <v>2</v>
       </c>
       <c r="G654" s="8">
-        <v>0</v>
+        <v>1483897277.96</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
@@ -27721,17 +27721,17 @@
       <c r="C655" s="6">
         <v>46279</v>
       </c>
-      <c r="D655" s="8">
-        <v>0</v>
+      <c r="D655" s="7">
+        <v>6.475778</v>
       </c>
       <c r="E655" s="8">
-        <v>0</v>
+        <v>63231340</v>
       </c>
       <c r="F655" s="9">
         <v>506</v>
       </c>
       <c r="G655" s="8">
-        <v>0</v>
+        <v>409472133.13</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
@@ -27744,17 +27744,17 @@
       <c r="C656" s="6">
         <v>46279</v>
       </c>
-      <c r="D656" s="8">
-        <v>0</v>
+      <c r="D656" s="7">
+        <v>11.759365</v>
       </c>
       <c r="E656" s="8">
-        <v>0</v>
+        <v>1046819197</v>
       </c>
       <c r="F656" s="9">
         <v>61480</v>
       </c>
       <c r="G656" s="8">
-        <v>0</v>
+        <v>12309928922.05</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
@@ -27767,17 +27767,17 @@
       <c r="C657" s="6">
         <v>46279</v>
       </c>
-      <c r="D657" s="8">
-        <v>0</v>
+      <c r="D657" s="7">
+        <v>6.091294</v>
       </c>
       <c r="E657" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F657" s="9">
         <v>1</v>
       </c>
       <c r="G657" s="8">
-        <v>0</v>
+        <v>2082374737.38</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
@@ -27859,17 +27859,17 @@
       <c r="C661" s="6">
         <v>46279</v>
       </c>
-      <c r="D661" s="8">
-        <v>0</v>
+      <c r="D661" s="7">
+        <v>0.462557</v>
       </c>
       <c r="E661" s="8">
-        <v>0</v>
+        <v>10718093989</v>
       </c>
       <c r="F661" s="9">
         <v>38536</v>
       </c>
       <c r="G661" s="8">
-        <v>0</v>
+        <v>4957729565.07</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.25">
@@ -27882,17 +27882,17 @@
       <c r="C662" s="6">
         <v>46279</v>
       </c>
-      <c r="D662" s="8">
-        <v>0</v>
+      <c r="D662" s="7">
+        <v>1.421392</v>
       </c>
       <c r="E662" s="8">
-        <v>0</v>
+        <v>789011361</v>
       </c>
       <c r="F662" s="9">
         <v>2581</v>
       </c>
       <c r="G662" s="8">
-        <v>0</v>
+        <v>1121494142.79</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
@@ -27951,17 +27951,17 @@
       <c r="C665" s="6">
         <v>46279</v>
       </c>
-      <c r="D665" s="8">
-        <v>0</v>
+      <c r="D665" s="7">
+        <v>4.145789</v>
       </c>
       <c r="E665" s="8">
-        <v>0</v>
+        <v>22503536</v>
       </c>
       <c r="F665" s="9">
         <v>3375</v>
       </c>
       <c r="G665" s="8">
-        <v>0</v>
+        <v>93294912.86</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -27974,17 +27974,17 @@
       <c r="C666" s="6">
         <v>46279</v>
       </c>
-      <c r="D666" s="8">
-        <v>0</v>
+      <c r="D666" s="7">
+        <v>68.661325</v>
       </c>
       <c r="E666" s="8">
-        <v>0</v>
+        <v>52499640</v>
       </c>
       <c r="F666" s="9">
         <v>3</v>
       </c>
       <c r="G666" s="8">
-        <v>0</v>
+        <v>3604694870.52</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
@@ -27997,17 +27997,17 @@
       <c r="C667" s="6">
         <v>46279</v>
       </c>
-      <c r="D667" s="8">
-        <v>0</v>
+      <c r="D667" s="7">
+        <v>65.080424</v>
       </c>
       <c r="E667" s="8">
-        <v>0</v>
+        <v>4739268</v>
       </c>
       <c r="F667" s="9">
         <v>1</v>
       </c>
       <c r="G667" s="8">
-        <v>0</v>
+        <v>308433570.94</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -28020,17 +28020,17 @@
       <c r="C668" s="6">
         <v>46279</v>
       </c>
-      <c r="D668" s="8">
-        <v>0</v>
+      <c r="D668" s="7">
+        <v>18.414066</v>
       </c>
       <c r="E668" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F668" s="9">
         <v>1</v>
       </c>
       <c r="G668" s="8">
-        <v>0</v>
+        <v>407227.06</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -28043,17 +28043,17 @@
       <c r="C669" s="6">
         <v>46279</v>
       </c>
-      <c r="D669" s="8">
-        <v>0</v>
+      <c r="D669" s="7">
+        <v>5.709944</v>
       </c>
       <c r="E669" s="8">
-        <v>0</v>
+        <v>203936993</v>
       </c>
       <c r="F669" s="9">
         <v>4556</v>
       </c>
       <c r="G669" s="8">
-        <v>0</v>
+        <v>1164468719.51</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -28066,17 +28066,17 @@
       <c r="C670" s="6">
         <v>46279</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="7">
+        <v>67.497168</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F670" s="9">
         <v>3</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>531345404.54</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28089,17 +28089,17 @@
       <c r="C671" s="6">
         <v>46279</v>
       </c>
-      <c r="D671" s="8">
-        <v>0</v>
+      <c r="D671" s="10">
+        <v>73.94745</v>
       </c>
       <c r="E671" s="8">
-        <v>0</v>
+        <v>5533354</v>
       </c>
       <c r="F671" s="9">
         <v>2</v>
       </c>
       <c r="G671" s="8">
-        <v>0</v>
+        <v>409177417.38</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -28112,17 +28112,17 @@
       <c r="C672" s="6">
         <v>46279</v>
       </c>
-      <c r="D672" s="8">
-        <v>0</v>
+      <c r="D672" s="7">
+        <v>4.175219</v>
       </c>
       <c r="E672" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F672" s="9">
         <v>1</v>
       </c>
       <c r="G672" s="8">
-        <v>0</v>
+        <v>20959944872.91</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -28135,17 +28135,17 @@
       <c r="C673" s="6">
         <v>46279</v>
       </c>
-      <c r="D673" s="8">
-        <v>0</v>
+      <c r="D673" s="7">
+        <v>72.078293</v>
       </c>
       <c r="E673" s="8">
-        <v>0</v>
+        <v>7036272</v>
       </c>
       <c r="F673" s="9">
         <v>4</v>
       </c>
       <c r="G673" s="8">
-        <v>0</v>
+        <v>507162471.89</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -28204,17 +28204,17 @@
       <c r="C676" s="6">
         <v>46279</v>
       </c>
-      <c r="D676" s="8">
-        <v>0</v>
+      <c r="D676" s="7">
+        <v>69.356312</v>
       </c>
       <c r="E676" s="8">
-        <v>0</v>
+        <v>20613565</v>
       </c>
       <c r="F676" s="9">
         <v>1</v>
       </c>
       <c r="G676" s="8">
-        <v>0</v>
+        <v>1429680850.72</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
@@ -28227,17 +28227,17 @@
       <c r="C677" s="6">
         <v>46279</v>
       </c>
-      <c r="D677" s="8">
-        <v>0</v>
+      <c r="D677" s="7">
+        <v>64.127416</v>
       </c>
       <c r="E677" s="8">
-        <v>0</v>
+        <v>9307247</v>
       </c>
       <c r="F677" s="9">
         <v>5</v>
       </c>
       <c r="G677" s="8">
-        <v>0</v>
+        <v>596849701.59</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
@@ -28250,17 +28250,17 @@
       <c r="C678" s="6">
         <v>46279</v>
       </c>
-      <c r="D678" s="8">
-        <v>0</v>
+      <c r="D678" s="7">
+        <v>7.729561</v>
       </c>
       <c r="E678" s="8">
-        <v>0</v>
+        <v>190000000</v>
       </c>
       <c r="F678" s="9">
         <v>1</v>
       </c>
       <c r="G678" s="8">
-        <v>0</v>
+        <v>1468616660.06</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -28273,17 +28273,17 @@
       <c r="C679" s="6">
         <v>46279</v>
       </c>
-      <c r="D679" s="8">
-        <v>0</v>
+      <c r="D679" s="7">
+        <v>62.670121</v>
       </c>
       <c r="E679" s="8">
-        <v>0</v>
+        <v>876698</v>
       </c>
       <c r="F679" s="9">
         <v>3</v>
       </c>
       <c r="G679" s="8">
-        <v>0</v>
+        <v>54942769.59</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
@@ -28296,17 +28296,17 @@
       <c r="C680" s="6">
         <v>46279</v>
       </c>
-      <c r="D680" s="8">
-        <v>0</v>
+      <c r="D680" s="7">
+        <v>8.094455</v>
       </c>
       <c r="E680" s="8">
-        <v>0</v>
+        <v>181423801</v>
       </c>
       <c r="F680" s="9">
         <v>4126</v>
       </c>
       <c r="G680" s="8">
-        <v>0</v>
+        <v>1468526704.79</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -28319,17 +28319,17 @@
       <c r="C681" s="6">
         <v>46279</v>
       </c>
-      <c r="D681" s="8">
-        <v>0</v>
+      <c r="D681" s="7">
+        <v>7.469139</v>
       </c>
       <c r="E681" s="8">
-        <v>0</v>
+        <v>57436044</v>
       </c>
       <c r="F681" s="9">
         <v>4575</v>
       </c>
       <c r="G681" s="8">
-        <v>0</v>
+        <v>428997801.04</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
@@ -28342,17 +28342,17 @@
       <c r="C682" s="6">
         <v>46279</v>
       </c>
-      <c r="D682" s="8">
-        <v>0</v>
+      <c r="D682" s="7">
+        <v>4.857937</v>
       </c>
       <c r="E682" s="8">
-        <v>0</v>
+        <v>74369614</v>
       </c>
       <c r="F682" s="9">
         <v>5463</v>
       </c>
       <c r="G682" s="8">
-        <v>0</v>
+        <v>361282877.58</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -28365,17 +28365,17 @@
       <c r="C683" s="6">
         <v>46279</v>
       </c>
-      <c r="D683" s="8">
-        <v>0</v>
+      <c r="D683" s="7">
+        <v>8.839186</v>
       </c>
       <c r="E683" s="8">
-        <v>0</v>
+        <v>196431029</v>
       </c>
       <c r="F683" s="9">
         <v>5200</v>
       </c>
       <c r="G683" s="8">
-        <v>0</v>
+        <v>1736290448.85</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -28388,17 +28388,17 @@
       <c r="C684" s="6">
         <v>46279</v>
       </c>
-      <c r="D684" s="8">
-        <v>0</v>
+      <c r="D684" s="7">
+        <v>5.807781</v>
       </c>
       <c r="E684" s="8">
-        <v>0</v>
+        <v>67523628</v>
       </c>
       <c r="F684" s="9">
         <v>6434</v>
       </c>
       <c r="G684" s="8">
-        <v>0</v>
+        <v>392162444.18</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -28457,17 +28457,17 @@
       <c r="C687" s="6">
         <v>46279</v>
       </c>
-      <c r="D687" s="8">
-        <v>0</v>
+      <c r="D687" s="7">
+        <v>70.146563</v>
       </c>
       <c r="E687" s="8">
-        <v>0</v>
+        <v>1210798</v>
       </c>
       <c r="F687" s="9">
         <v>1</v>
       </c>
       <c r="G687" s="8">
-        <v>0</v>
+        <v>84933317.73</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.25">
@@ -28480,17 +28480,17 @@
       <c r="C688" s="6">
         <v>46279</v>
       </c>
-      <c r="D688" s="8">
-        <v>0</v>
+      <c r="D688" s="7">
+        <v>7.828697</v>
       </c>
       <c r="E688" s="8">
-        <v>0</v>
+        <v>500778594</v>
       </c>
       <c r="F688" s="9">
         <v>10327</v>
       </c>
       <c r="G688" s="8">
-        <v>0</v>
+        <v>3920443679.49</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
@@ -28526,17 +28526,17 @@
       <c r="C690" s="6">
         <v>46279</v>
       </c>
-      <c r="D690" s="8">
-        <v>0</v>
+      <c r="D690" s="7">
+        <v>68.491182</v>
       </c>
       <c r="E690" s="8">
-        <v>0</v>
+        <v>6829649</v>
       </c>
       <c r="F690" s="9">
         <v>2</v>
       </c>
       <c r="G690" s="8">
-        <v>0</v>
+        <v>467770735.17</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
@@ -28549,17 +28549,17 @@
       <c r="C691" s="6">
         <v>46279</v>
       </c>
-      <c r="D691" s="8">
-        <v>0</v>
+      <c r="D691" s="7">
+        <v>8.745357</v>
       </c>
       <c r="E691" s="8">
-        <v>0</v>
+        <v>11383613</v>
       </c>
       <c r="F691" s="9">
         <v>1377</v>
       </c>
       <c r="G691" s="8">
-        <v>0</v>
+        <v>99553758.12</v>
       </c>
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.25">
@@ -28572,17 +28572,17 @@
       <c r="C692" s="6">
         <v>46279</v>
       </c>
-      <c r="D692" s="8">
-        <v>0</v>
+      <c r="D692" s="7">
+        <v>7.514059</v>
       </c>
       <c r="E692" s="8">
-        <v>0</v>
+        <v>8503570</v>
       </c>
       <c r="F692" s="9">
         <v>2249</v>
       </c>
       <c r="G692" s="8">
-        <v>0</v>
+        <v>63896327.24</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
@@ -28595,17 +28595,17 @@
       <c r="C693" s="6">
         <v>46279</v>
       </c>
-      <c r="D693" s="8">
-        <v>0</v>
+      <c r="D693" s="7">
+        <v>7.067784</v>
       </c>
       <c r="E693" s="8">
-        <v>0</v>
+        <v>9189971</v>
       </c>
       <c r="F693" s="9">
         <v>1237</v>
       </c>
       <c r="G693" s="8">
-        <v>0</v>
+        <v>64952726.64</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
@@ -28687,17 +28687,17 @@
       <c r="C697" s="6">
         <v>46279</v>
       </c>
-      <c r="D697" s="8">
-        <v>0</v>
+      <c r="D697" s="7">
+        <v>3.105039</v>
       </c>
       <c r="E697" s="8">
-        <v>0</v>
+        <v>498905972</v>
       </c>
       <c r="F697" s="9">
         <v>7455</v>
       </c>
       <c r="G697" s="8">
-        <v>0</v>
+        <v>1549122371.57</v>
       </c>
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.25">
@@ -28733,17 +28733,17 @@
       <c r="C699" s="6">
         <v>46279</v>
       </c>
-      <c r="D699" s="8">
-        <v>0</v>
+      <c r="D699" s="7">
+        <v>1.873504</v>
       </c>
       <c r="E699" s="8">
-        <v>0</v>
+        <v>1704573</v>
       </c>
       <c r="F699" s="9">
         <v>80</v>
       </c>
       <c r="G699" s="8">
-        <v>0</v>
+        <v>3193523.87</v>
       </c>
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.25">
@@ -28848,17 +28848,17 @@
       <c r="C704" s="6">
         <v>46279</v>
       </c>
-      <c r="D704" s="8">
-        <v>0</v>
+      <c r="D704" s="7">
+        <v>4.382556</v>
       </c>
       <c r="E704" s="8">
-        <v>0</v>
+        <v>122049185</v>
       </c>
       <c r="F704" s="9">
         <v>1061</v>
       </c>
       <c r="G704" s="8">
-        <v>0</v>
+        <v>534887388.59</v>
       </c>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.25">
@@ -28894,17 +28894,17 @@
       <c r="C706" s="6">
         <v>46279</v>
       </c>
-      <c r="D706" s="8">
-        <v>0</v>
+      <c r="D706" s="7">
+        <v>20.320783</v>
       </c>
       <c r="E706" s="8">
-        <v>0</v>
+        <v>57550088</v>
       </c>
       <c r="F706" s="9">
         <v>17</v>
       </c>
       <c r="G706" s="8">
-        <v>0</v>
+        <v>1169462830.55</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
@@ -28917,17 +28917,17 @@
       <c r="C707" s="6">
         <v>46279</v>
       </c>
-      <c r="D707" s="8">
-        <v>0</v>
+      <c r="D707" s="7">
+        <v>1.008957</v>
       </c>
       <c r="E707" s="8">
-        <v>0</v>
+        <v>146651047</v>
       </c>
       <c r="F707" s="9">
         <v>611</v>
       </c>
       <c r="G707" s="8">
-        <v>0</v>
+        <v>147964658.55</v>
       </c>
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.25">
@@ -28940,17 +28940,17 @@
       <c r="C708" s="6">
         <v>46279</v>
       </c>
-      <c r="D708" s="8">
-        <v>0</v>
+      <c r="D708" s="7">
+        <v>3.173333</v>
       </c>
       <c r="E708" s="8">
-        <v>0</v>
+        <v>29176988</v>
       </c>
       <c r="F708" s="9">
         <v>500</v>
       </c>
       <c r="G708" s="8">
-        <v>0</v>
+        <v>92588303.65</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.25">
@@ -29009,17 +29009,17 @@
       <c r="C711" s="6">
         <v>46279</v>
       </c>
-      <c r="D711" s="8">
-        <v>0</v>
+      <c r="D711" s="7">
+        <v>3890.533017</v>
       </c>
       <c r="E711" s="8">
-        <v>0</v>
+        <v>3698336</v>
       </c>
       <c r="F711" s="9">
         <v>17</v>
       </c>
       <c r="G711" s="8">
-        <v>0</v>
+        <v>14388498317.25</v>
       </c>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.25">
@@ -29032,17 +29032,17 @@
       <c r="C712" s="6">
         <v>46279</v>
       </c>
-      <c r="D712" s="8">
-        <v>0</v>
+      <c r="D712" s="7">
+        <v>6.758037</v>
       </c>
       <c r="E712" s="8">
-        <v>0</v>
+        <v>2420170</v>
       </c>
       <c r="F712" s="9">
         <v>11</v>
       </c>
       <c r="G712" s="8">
-        <v>0</v>
+        <v>16355599.11</v>
       </c>
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.25">
@@ -29055,17 +29055,17 @@
       <c r="C713" s="6">
         <v>46279</v>
       </c>
-      <c r="D713" s="8">
-        <v>0</v>
+      <c r="D713" s="7">
+        <v>3.044274</v>
       </c>
       <c r="E713" s="8">
-        <v>0</v>
+        <v>3924624</v>
       </c>
       <c r="F713" s="9">
         <v>126</v>
       </c>
       <c r="G713" s="8">
-        <v>0</v>
+        <v>11947632.48</v>
       </c>
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.25">
@@ -29078,17 +29078,17 @@
       <c r="C714" s="6">
         <v>46279</v>
       </c>
-      <c r="D714" s="8">
-        <v>0</v>
+      <c r="D714" s="7">
+        <v>17.352318</v>
       </c>
       <c r="E714" s="8">
-        <v>0</v>
+        <v>91221799</v>
       </c>
       <c r="F714" s="9">
         <v>13</v>
       </c>
       <c r="G714" s="8">
-        <v>0</v>
+        <v>1582909647.03</v>
       </c>
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.25">
@@ -29124,17 +29124,17 @@
       <c r="C716" s="6">
         <v>46279</v>
       </c>
-      <c r="D716" s="8">
-        <v>0</v>
+      <c r="D716" s="7">
+        <v>3.343551</v>
       </c>
       <c r="E716" s="8">
-        <v>0</v>
+        <v>117517471</v>
       </c>
       <c r="F716" s="9">
         <v>1397</v>
       </c>
       <c r="G716" s="8">
-        <v>0</v>
+        <v>392925614.39</v>
       </c>
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.25">
@@ -29170,17 +29170,17 @@
       <c r="C718" s="6">
         <v>46279</v>
       </c>
-      <c r="D718" s="8">
-        <v>0</v>
+      <c r="D718" s="7">
+        <v>1.844644</v>
       </c>
       <c r="E718" s="8">
-        <v>0</v>
+        <v>34125259</v>
       </c>
       <c r="F718" s="9">
         <v>128</v>
       </c>
       <c r="G718" s="8">
-        <v>0</v>
+        <v>62948966.11</v>
       </c>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.25">
@@ -29308,17 +29308,17 @@
       <c r="C724" s="6">
         <v>46279</v>
       </c>
-      <c r="D724" s="8">
-        <v>0</v>
+      <c r="D724" s="7">
+        <v>1.786074</v>
       </c>
       <c r="E724" s="8">
-        <v>0</v>
+        <v>572445</v>
       </c>
       <c r="F724" s="9">
         <v>19</v>
       </c>
       <c r="G724" s="8">
-        <v>0</v>
+        <v>1022429.17</v>
       </c>
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.25">
@@ -29331,17 +29331,17 @@
       <c r="C725" s="6">
         <v>46279</v>
       </c>
-      <c r="D725" s="8">
-        <v>0</v>
+      <c r="D725" s="7">
+        <v>12.371493</v>
       </c>
       <c r="E725" s="8">
-        <v>0</v>
+        <v>109096943</v>
       </c>
       <c r="F725" s="9">
         <v>12</v>
       </c>
       <c r="G725" s="8">
-        <v>0</v>
+        <v>1349692039.99</v>
       </c>
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.25">
@@ -29354,17 +29354,17 @@
       <c r="C726" s="6">
         <v>46279</v>
       </c>
-      <c r="D726" s="8">
-        <v>0</v>
+      <c r="D726" s="7">
+        <v>4.262049</v>
       </c>
       <c r="E726" s="8">
-        <v>0</v>
+        <v>37532249.35</v>
       </c>
       <c r="F726" s="9">
         <v>1777</v>
       </c>
       <c r="G726" s="8">
-        <v>0</v>
+        <v>159964269.64</v>
       </c>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.25">
@@ -29377,17 +29377,17 @@
       <c r="C727" s="6">
         <v>46279</v>
       </c>
-      <c r="D727" s="8">
-        <v>0</v>
+      <c r="D727" s="7">
+        <v>1.367613</v>
       </c>
       <c r="E727" s="8">
-        <v>0</v>
+        <v>21876195</v>
       </c>
       <c r="F727" s="9">
         <v>147</v>
       </c>
       <c r="G727" s="8">
-        <v>0</v>
+        <v>29918177.45</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.25">
@@ -29446,17 +29446,17 @@
       <c r="C730" s="6">
         <v>46279</v>
       </c>
-      <c r="D730" s="8">
-        <v>0</v>
+      <c r="D730" s="10">
+        <v>4.51916</v>
       </c>
       <c r="E730" s="8">
-        <v>0</v>
+        <v>11164687</v>
       </c>
       <c r="F730" s="9">
         <v>352</v>
       </c>
       <c r="G730" s="8">
-        <v>0</v>
+        <v>50455011.26</v>
       </c>
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.25">
@@ -29469,17 +29469,17 @@
       <c r="C731" s="6">
         <v>46279</v>
       </c>
-      <c r="D731" s="8">
-        <v>0</v>
+      <c r="D731" s="7">
+        <v>1.581612</v>
       </c>
       <c r="E731" s="8">
-        <v>0</v>
+        <v>767876612</v>
       </c>
       <c r="F731" s="9">
         <v>243</v>
       </c>
       <c r="G731" s="8">
-        <v>0</v>
+        <v>1214483228.36</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.25">
@@ -29492,17 +29492,17 @@
       <c r="C732" s="6">
         <v>46279</v>
       </c>
-      <c r="D732" s="8">
-        <v>0</v>
+      <c r="D732" s="7">
+        <v>0.528217</v>
       </c>
       <c r="E732" s="8">
-        <v>0</v>
+        <v>21102124</v>
       </c>
       <c r="F732" s="9">
         <v>51</v>
       </c>
       <c r="G732" s="8">
-        <v>0</v>
+        <v>11146494.5</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.25">
@@ -29561,17 +29561,17 @@
       <c r="C735" s="6">
         <v>46279</v>
       </c>
-      <c r="D735" s="8">
-        <v>0</v>
+      <c r="D735" s="7">
+        <v>4.053735</v>
       </c>
       <c r="E735" s="8">
-        <v>0</v>
+        <v>70079687</v>
       </c>
       <c r="F735" s="9">
         <v>205</v>
       </c>
       <c r="G735" s="8">
-        <v>0</v>
+        <v>284084455.46</v>
       </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.25">
@@ -29607,17 +29607,17 @@
       <c r="C737" s="6">
         <v>46279</v>
       </c>
-      <c r="D737" s="8">
-        <v>0</v>
+      <c r="D737" s="7">
+        <v>3.023865</v>
       </c>
       <c r="E737" s="8">
-        <v>0</v>
+        <v>440177</v>
       </c>
       <c r="F737" s="9">
         <v>13</v>
       </c>
       <c r="G737" s="8">
-        <v>0</v>
+        <v>1331036.01</v>
       </c>
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.25">
@@ -29676,17 +29676,17 @@
       <c r="C740" s="6">
         <v>46279</v>
       </c>
-      <c r="D740" s="8">
-        <v>0</v>
+      <c r="D740" s="7">
+        <v>4.822285</v>
       </c>
       <c r="E740" s="8">
-        <v>0</v>
+        <v>22643028</v>
       </c>
       <c r="F740" s="9">
         <v>1505</v>
       </c>
       <c r="G740" s="8">
-        <v>0</v>
+        <v>109191143.32</v>
       </c>
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.25">
@@ -29722,17 +29722,17 @@
       <c r="C742" s="6">
         <v>46279</v>
       </c>
-      <c r="D742" s="8">
-        <v>0</v>
+      <c r="D742" s="7">
+        <v>8.948411</v>
       </c>
       <c r="E742" s="8">
-        <v>0</v>
+        <v>87173916</v>
       </c>
       <c r="F742" s="9">
         <v>13160</v>
       </c>
       <c r="G742" s="8">
-        <v>0</v>
+        <v>780068051.43</v>
       </c>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.25">
@@ -29745,17 +29745,17 @@
       <c r="C743" s="6">
         <v>46279</v>
       </c>
-      <c r="D743" s="8">
-        <v>0</v>
+      <c r="D743" s="7">
+        <v>1.444191</v>
       </c>
       <c r="E743" s="8">
-        <v>0</v>
+        <v>10288199418</v>
       </c>
       <c r="F743" s="9">
         <v>2444</v>
       </c>
       <c r="G743" s="8">
-        <v>0</v>
+        <v>14858124505.44</v>
       </c>
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.25">
@@ -29768,17 +29768,17 @@
       <c r="C744" s="6">
         <v>46279</v>
       </c>
-      <c r="D744" s="8">
-        <v>0</v>
+      <c r="D744" s="7">
+        <v>3.941425</v>
       </c>
       <c r="E744" s="8">
-        <v>0</v>
+        <v>11294689</v>
       </c>
       <c r="F744" s="9">
         <v>850</v>
       </c>
       <c r="G744" s="8">
-        <v>0</v>
+        <v>44517164.68</v>
       </c>
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.25">
@@ -29791,17 +29791,17 @@
       <c r="C745" s="6">
         <v>46279</v>
       </c>
-      <c r="D745" s="8">
-        <v>0</v>
+      <c r="D745" s="7">
+        <v>5.974256</v>
       </c>
       <c r="E745" s="8">
-        <v>0</v>
+        <v>25242931</v>
       </c>
       <c r="F745" s="9">
         <v>66</v>
       </c>
       <c r="G745" s="8">
-        <v>0</v>
+        <v>150807731.04</v>
       </c>
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.25">
@@ -29906,17 +29906,17 @@
       <c r="C750" s="6">
         <v>46279</v>
       </c>
-      <c r="D750" s="8">
-        <v>0</v>
+      <c r="D750" s="7">
+        <v>115.350489</v>
       </c>
       <c r="E750" s="8">
-        <v>0</v>
+        <v>28660839</v>
       </c>
       <c r="F750" s="9">
         <v>13</v>
       </c>
       <c r="G750" s="8">
-        <v>0</v>
+        <v>3306041806.63</v>
       </c>
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.25">
@@ -29929,17 +29929,17 @@
       <c r="C751" s="6">
         <v>46279</v>
       </c>
-      <c r="D751" s="8">
-        <v>0</v>
+      <c r="D751" s="7">
+        <v>8.977664</v>
       </c>
       <c r="E751" s="8">
-        <v>0</v>
+        <v>946705</v>
       </c>
       <c r="F751" s="9">
         <v>105</v>
       </c>
       <c r="G751" s="8">
-        <v>0</v>
+        <v>8499199.22</v>
       </c>
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.25">
@@ -29998,17 +29998,17 @@
       <c r="C754" s="6">
         <v>46279</v>
       </c>
-      <c r="D754" s="8">
-        <v>0</v>
+      <c r="D754" s="7">
+        <v>286.846802</v>
       </c>
       <c r="E754" s="8">
-        <v>0</v>
+        <v>251404</v>
       </c>
       <c r="F754" s="9">
         <v>39</v>
       </c>
       <c r="G754" s="8">
-        <v>0</v>
+        <v>72114433.29</v>
       </c>
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.25">
@@ -30021,17 +30021,17 @@
       <c r="C755" s="6">
         <v>46279</v>
       </c>
-      <c r="D755" s="8">
-        <v>0</v>
+      <c r="D755" s="7">
+        <v>48.506396</v>
       </c>
       <c r="E755" s="8">
-        <v>0</v>
+        <v>1606849</v>
       </c>
       <c r="F755" s="9">
         <v>41</v>
       </c>
       <c r="G755" s="8">
-        <v>0</v>
+        <v>77942453.51</v>
       </c>
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.25">
@@ -30090,17 +30090,17 @@
       <c r="C758" s="6">
         <v>46279</v>
       </c>
-      <c r="D758" s="8">
-        <v>0</v>
+      <c r="D758" s="7">
+        <v>16.996787</v>
       </c>
       <c r="E758" s="8">
-        <v>0</v>
+        <v>887234531</v>
       </c>
       <c r="F758" s="9">
         <v>13</v>
       </c>
       <c r="G758" s="8">
-        <v>0</v>
+        <v>15080136096.24</v>
       </c>
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.25">
@@ -30160,7 +30160,7 @@
         <v>46279</v>
       </c>
       <c r="D761" s="7">
-        <v>0.368245</v>
+        <v>0.368241</v>
       </c>
       <c r="E761" s="8">
         <v>3715933596</v>
@@ -30169,7 +30169,7 @@
         <v>2541</v>
       </c>
       <c r="G761" s="8">
-        <v>1368373189.9</v>
+        <v>1368359753.73</v>
       </c>
     </row>
     <row r="762" spans="1:7" x14ac:dyDescent="0.25">
@@ -30182,17 +30182,17 @@
       <c r="C762" s="6">
         <v>46279</v>
       </c>
-      <c r="D762" s="8">
-        <v>0</v>
+      <c r="D762" s="7">
+        <v>59.529245</v>
       </c>
       <c r="E762" s="8">
-        <v>0</v>
+        <v>12299533</v>
       </c>
       <c r="F762" s="9">
         <v>171</v>
       </c>
       <c r="G762" s="8">
-        <v>0</v>
+        <v>732181910.37</v>
       </c>
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.25">
@@ -30251,17 +30251,17 @@
       <c r="C765" s="6">
         <v>46279</v>
       </c>
-      <c r="D765" s="8">
-        <v>0</v>
+      <c r="D765" s="7">
+        <v>20.335656</v>
       </c>
       <c r="E765" s="8">
-        <v>0</v>
+        <v>43149120</v>
       </c>
       <c r="F765" s="9">
         <v>12</v>
       </c>
       <c r="G765" s="8">
-        <v>0</v>
+        <v>877465647.85</v>
       </c>
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.25">
@@ -30274,17 +30274,17 @@
       <c r="C766" s="6">
         <v>46279</v>
       </c>
-      <c r="D766" s="8">
-        <v>0</v>
+      <c r="D766" s="7">
+        <v>2.430223</v>
       </c>
       <c r="E766" s="8">
-        <v>0</v>
+        <v>2516028144</v>
       </c>
       <c r="F766" s="9">
         <v>8992</v>
       </c>
       <c r="G766" s="8">
-        <v>0</v>
+        <v>6114510194.7</v>
       </c>
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.25">
@@ -30297,17 +30297,17 @@
       <c r="C767" s="6">
         <v>46279</v>
       </c>
-      <c r="D767" s="8">
-        <v>0</v>
+      <c r="D767" s="7">
+        <v>4.407781</v>
       </c>
       <c r="E767" s="8">
-        <v>0</v>
+        <v>34414080</v>
       </c>
       <c r="F767" s="9">
         <v>14</v>
       </c>
       <c r="G767" s="8">
-        <v>0</v>
+        <v>151689716.76</v>
       </c>
     </row>
     <row r="768" spans="1:7" x14ac:dyDescent="0.25">
@@ -30343,17 +30343,17 @@
       <c r="C769" s="6">
         <v>46279</v>
       </c>
-      <c r="D769" s="8">
-        <v>0</v>
+      <c r="D769" s="7">
+        <v>0.610023</v>
       </c>
       <c r="E769" s="8">
-        <v>0</v>
+        <v>291815213</v>
       </c>
       <c r="F769" s="9">
         <v>24</v>
       </c>
       <c r="G769" s="8">
-        <v>0</v>
+        <v>178014059.85</v>
       </c>
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.25">
@@ -30435,17 +30435,17 @@
       <c r="C773" s="6">
         <v>46279</v>
       </c>
-      <c r="D773" s="8">
-        <v>0</v>
+      <c r="D773" s="7">
+        <v>556.618018</v>
       </c>
       <c r="E773" s="8">
-        <v>0</v>
+        <v>9674</v>
       </c>
       <c r="F773" s="9">
         <v>18</v>
       </c>
       <c r="G773" s="8">
-        <v>0</v>
+        <v>5384722.71</v>
       </c>
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.25">
@@ -30596,17 +30596,17 @@
       <c r="C780" s="6">
         <v>46279</v>
       </c>
-      <c r="D780" s="8">
-        <v>0</v>
+      <c r="D780" s="7">
+        <v>2.026067</v>
       </c>
       <c r="E780" s="8">
-        <v>0</v>
+        <v>22468650</v>
       </c>
       <c r="F780" s="9">
         <v>250</v>
       </c>
       <c r="G780" s="8">
-        <v>0</v>
+        <v>45522988.47</v>
       </c>
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.25">
@@ -30665,17 +30665,17 @@
       <c r="C783" s="6">
         <v>46279</v>
       </c>
-      <c r="D783" s="8">
-        <v>0</v>
+      <c r="D783" s="7">
+        <v>11.600286</v>
       </c>
       <c r="E783" s="8">
-        <v>0</v>
+        <v>6936066</v>
       </c>
       <c r="F783" s="9">
         <v>13</v>
       </c>
       <c r="G783" s="8">
-        <v>0</v>
+        <v>80460349.92</v>
       </c>
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.25">
@@ -30711,17 +30711,17 @@
       <c r="C785" s="6">
         <v>46279</v>
       </c>
-      <c r="D785" s="8">
-        <v>0</v>
+      <c r="D785" s="7">
+        <v>0.003502</v>
       </c>
       <c r="E785" s="8">
-        <v>0</v>
+        <v>568993837</v>
       </c>
       <c r="F785" s="9">
         <v>12</v>
       </c>
       <c r="G785" s="8">
-        <v>0</v>
+        <v>1992367.15</v>
       </c>
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.25">
@@ -30734,17 +30734,17 @@
       <c r="C786" s="6">
         <v>46279</v>
       </c>
-      <c r="D786" s="8">
-        <v>0</v>
+      <c r="D786" s="7">
+        <v>121.418624</v>
       </c>
       <c r="E786" s="8">
-        <v>0</v>
+        <v>538488</v>
       </c>
       <c r="F786" s="9">
         <v>16</v>
       </c>
       <c r="G786" s="8">
-        <v>0</v>
+        <v>65382472.15</v>
       </c>
     </row>
     <row r="787" spans="1:7" x14ac:dyDescent="0.25">
@@ -30757,17 +30757,17 @@
       <c r="C787" s="6">
         <v>46279</v>
       </c>
-      <c r="D787" s="8">
-        <v>0</v>
+      <c r="D787" s="7">
+        <v>1.122616</v>
       </c>
       <c r="E787" s="8">
-        <v>0</v>
+        <v>1151128347</v>
       </c>
       <c r="F787" s="9">
         <v>13</v>
       </c>
       <c r="G787" s="8">
-        <v>0</v>
+        <v>1292274931.05</v>
       </c>
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.25">
@@ -30780,17 +30780,17 @@
       <c r="C788" s="6">
         <v>46279</v>
       </c>
-      <c r="D788" s="8">
-        <v>0</v>
+      <c r="D788" s="7">
+        <v>26.500543</v>
       </c>
       <c r="E788" s="8">
-        <v>0</v>
+        <v>2727730</v>
       </c>
       <c r="F788" s="9">
         <v>16</v>
       </c>
       <c r="G788" s="8">
-        <v>0</v>
+        <v>72286326.7</v>
       </c>
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.25">
@@ -30826,17 +30826,17 @@
       <c r="C790" s="6">
         <v>46279</v>
       </c>
-      <c r="D790" s="8">
-        <v>0</v>
+      <c r="D790" s="7">
+        <v>4.945797</v>
       </c>
       <c r="E790" s="8">
-        <v>0</v>
+        <v>81685317</v>
       </c>
       <c r="F790" s="9">
         <v>1275</v>
       </c>
       <c r="G790" s="8">
-        <v>0</v>
+        <v>403998995.4</v>
       </c>
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.25">
@@ -30849,17 +30849,17 @@
       <c r="C791" s="6">
         <v>46279</v>
       </c>
-      <c r="D791" s="8">
-        <v>0</v>
+      <c r="D791" s="7">
+        <v>20.555292</v>
       </c>
       <c r="E791" s="8">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="F791" s="9">
         <v>11</v>
       </c>
       <c r="G791" s="8">
-        <v>0</v>
+        <v>2885962.99</v>
       </c>
     </row>
     <row r="792" spans="1:7" x14ac:dyDescent="0.25">
@@ -30872,17 +30872,17 @@
       <c r="C792" s="6">
         <v>46279</v>
       </c>
-      <c r="D792" s="8">
-        <v>0</v>
+      <c r="D792" s="7">
+        <v>5.937806</v>
       </c>
       <c r="E792" s="8">
-        <v>0</v>
+        <v>997109</v>
       </c>
       <c r="F792" s="9">
         <v>12</v>
       </c>
       <c r="G792" s="8">
-        <v>0</v>
+        <v>5920639.38</v>
       </c>
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.25">
@@ -31010,17 +31010,17 @@
       <c r="C798" s="6">
         <v>46279</v>
       </c>
-      <c r="D798" s="8">
-        <v>0</v>
+      <c r="D798" s="7">
+        <v>11.860684</v>
       </c>
       <c r="E798" s="8">
-        <v>0</v>
+        <v>18384812</v>
       </c>
       <c r="F798" s="9">
         <v>35</v>
       </c>
       <c r="G798" s="8">
-        <v>0</v>
+        <v>218056436.63</v>
       </c>
     </row>
     <row r="799" spans="1:7" x14ac:dyDescent="0.25">
@@ -31079,17 +31079,17 @@
       <c r="C801" s="6">
         <v>46279</v>
       </c>
-      <c r="D801" s="8">
-        <v>0</v>
+      <c r="D801" s="7">
+        <v>6.486869</v>
       </c>
       <c r="E801" s="8">
-        <v>0</v>
+        <v>963141092</v>
       </c>
       <c r="F801" s="9">
         <v>6443</v>
       </c>
       <c r="G801" s="8">
-        <v>0</v>
+        <v>6247770358.58</v>
       </c>
     </row>
     <row r="802" spans="1:7" x14ac:dyDescent="0.25">
@@ -32045,17 +32045,17 @@
       <c r="C843" s="6">
         <v>46279</v>
       </c>
-      <c r="D843" s="8">
-        <v>0</v>
+      <c r="D843" s="7">
+        <v>0.240085</v>
       </c>
       <c r="E843" s="8">
-        <v>0</v>
+        <v>2247860453.13</v>
       </c>
       <c r="F843" s="9">
         <v>2468</v>
       </c>
       <c r="G843" s="8">
-        <v>0</v>
+        <v>539677405.19</v>
       </c>
     </row>
     <row r="844" spans="1:7" x14ac:dyDescent="0.25">
@@ -32344,17 +32344,17 @@
       <c r="C856" s="6">
         <v>46279</v>
       </c>
-      <c r="D856" s="8">
-        <v>0</v>
+      <c r="D856" s="7">
+        <v>0.959734</v>
       </c>
       <c r="E856" s="8">
-        <v>0</v>
+        <v>190863406</v>
       </c>
       <c r="F856" s="9">
         <v>100</v>
       </c>
       <c r="G856" s="8">
-        <v>0</v>
+        <v>183178109.74</v>
       </c>
     </row>
     <row r="857" spans="1:7" x14ac:dyDescent="0.25">
@@ -32552,7 +32552,7 @@
         <v>46279</v>
       </c>
       <c r="D865" s="7">
-        <v>3.822396</v>
+        <v>3.822362</v>
       </c>
       <c r="E865" s="8">
         <v>382831186</v>
@@ -32561,7 +32561,7 @@
         <v>11</v>
       </c>
       <c r="G865" s="8">
-        <v>1463332577.73</v>
+        <v>1463319453.12</v>
       </c>
     </row>
     <row r="866" spans="1:7" x14ac:dyDescent="0.25">
@@ -32644,7 +32644,7 @@
         <v>46279</v>
       </c>
       <c r="D869" s="7">
-        <v>34.147029</v>
+        <v>34.146718</v>
       </c>
       <c r="E869" s="8">
         <v>52325347</v>
@@ -32653,7 +32653,7 @@
         <v>21210</v>
       </c>
       <c r="G869" s="8">
-        <v>1786755154.11</v>
+        <v>1786738863.58</v>
       </c>
     </row>
     <row r="870" spans="1:7" x14ac:dyDescent="0.25">
@@ -32689,8 +32689,8 @@
       <c r="C871" s="6">
         <v>46279</v>
       </c>
-      <c r="D871" s="10">
-        <v>36.36727</v>
+      <c r="D871" s="7">
+        <v>36.362943</v>
       </c>
       <c r="E871" s="8">
         <v>31363464.25</v>
@@ -32699,7 +32699,7 @@
         <v>134</v>
       </c>
       <c r="G871" s="8">
-        <v>1140603579.48</v>
+        <v>1140467850.54</v>
       </c>
     </row>
     <row r="872" spans="1:7" x14ac:dyDescent="0.25">
@@ -33311,7 +33311,7 @@
         <v>46279</v>
       </c>
       <c r="D898" s="7">
-        <v>5.744834</v>
+        <v>5.744754</v>
       </c>
       <c r="E898" s="8">
         <v>66550045</v>
@@ -33320,7 +33320,7 @@
         <v>19</v>
       </c>
       <c r="G898" s="8">
-        <v>382318963.57</v>
+        <v>382313622.25</v>
       </c>
     </row>
     <row r="899" spans="1:7" x14ac:dyDescent="0.25">
@@ -33517,17 +33517,17 @@
       <c r="C907" s="6">
         <v>46279</v>
       </c>
-      <c r="D907" s="8">
-        <v>0</v>
+      <c r="D907" s="7">
+        <v>15.134117</v>
       </c>
       <c r="E907" s="8">
-        <v>0</v>
+        <v>15071740</v>
       </c>
       <c r="F907" s="9">
         <v>376</v>
       </c>
       <c r="G907" s="8">
-        <v>0</v>
+        <v>228097481.16</v>
       </c>
     </row>
     <row r="908" spans="1:7" x14ac:dyDescent="0.25">
@@ -33909,7 +33909,7 @@
         <v>46279</v>
       </c>
       <c r="D924" s="7">
-        <v>0.124791</v>
+        <v>0.124706</v>
       </c>
       <c r="E924" s="8">
         <v>1105011730</v>
@@ -33918,7 +33918,7 @@
         <v>22</v>
       </c>
       <c r="G924" s="8">
-        <v>137895214.44</v>
+        <v>137802026.51</v>
       </c>
     </row>
     <row r="925" spans="1:7" x14ac:dyDescent="0.25">
@@ -34024,7 +34024,7 @@
         <v>46279</v>
       </c>
       <c r="D929" s="7">
-        <v>0.184421</v>
+        <v>0.184404</v>
       </c>
       <c r="E929" s="8">
         <v>38099772863</v>
@@ -34033,7 +34033,7 @@
         <v>161</v>
       </c>
       <c r="G929" s="8">
-        <v>7026414403.27</v>
+        <v>7025737248.1</v>
       </c>
     </row>
     <row r="930" spans="1:7" x14ac:dyDescent="0.25">
@@ -34116,7 +34116,7 @@
         <v>46279</v>
       </c>
       <c r="D933" s="7">
-        <v>1.343245</v>
+        <v>1.343236</v>
       </c>
       <c r="E933" s="8">
         <v>944301545</v>
@@ -34125,7 +34125,7 @@
         <v>728</v>
       </c>
       <c r="G933" s="8">
-        <v>1268428538.93</v>
+        <v>1268420135.44</v>
       </c>
     </row>
     <row r="934" spans="1:7" x14ac:dyDescent="0.25">
@@ -34161,17 +34161,17 @@
       <c r="C935" s="6">
         <v>46279</v>
       </c>
-      <c r="D935" s="8">
-        <v>0</v>
+      <c r="D935" s="7">
+        <v>7.592615</v>
       </c>
       <c r="E935" s="8">
-        <v>0</v>
+        <v>68268978</v>
       </c>
       <c r="F935" s="9">
         <v>1933</v>
       </c>
       <c r="G935" s="8">
-        <v>0</v>
+        <v>518340093.26</v>
       </c>
     </row>
     <row r="936" spans="1:7" x14ac:dyDescent="0.25">
@@ -34346,16 +34346,16 @@
         <v>46279</v>
       </c>
       <c r="D943" s="7">
-        <v>0.199537</v>
+        <v>0.199577</v>
       </c>
       <c r="E943" s="8">
-        <v>10104739160.13</v>
+        <v>9474660752.01</v>
       </c>
       <c r="F943" s="9">
         <v>3089</v>
       </c>
       <c r="G943" s="8">
-        <v>2016265296.24</v>
+        <v>1890923905.13</v>
       </c>
     </row>
     <row r="944" spans="1:7" x14ac:dyDescent="0.25">
@@ -34898,7 +34898,7 @@
         <v>46279</v>
       </c>
       <c r="D967" s="7">
-        <v>6.017777</v>
+        <v>6.017391</v>
       </c>
       <c r="E967" s="8">
         <v>33950722.29</v>
@@ -34907,7 +34907,7 @@
         <v>25</v>
       </c>
       <c r="G967" s="8">
-        <v>204307878.42</v>
+        <v>204294756.59</v>
       </c>
     </row>
     <row r="968" spans="1:7" x14ac:dyDescent="0.25">
@@ -35219,8 +35219,8 @@
       <c r="C981" s="6">
         <v>46279</v>
       </c>
-      <c r="D981" s="7">
-        <v>2.263602</v>
+      <c r="D981" s="10">
+        <v>2.26873</v>
       </c>
       <c r="E981" s="8">
         <v>213134691</v>
@@ -35229,7 +35229,7 @@
         <v>16687</v>
       </c>
       <c r="G981" s="8">
-        <v>482452138.46</v>
+        <v>483544979.49</v>
       </c>
     </row>
     <row r="982" spans="1:7" x14ac:dyDescent="0.25">
@@ -35311,17 +35311,17 @@
       <c r="C985" s="6">
         <v>46279</v>
       </c>
-      <c r="D985" s="8">
-        <v>0</v>
+      <c r="D985" s="7">
+        <v>6881.720585</v>
       </c>
       <c r="E985" s="8">
-        <v>0</v>
+        <v>791524</v>
       </c>
       <c r="F985" s="9">
         <v>36</v>
       </c>
       <c r="G985" s="8">
-        <v>0</v>
+        <v>5447047004.18</v>
       </c>
     </row>
     <row r="986" spans="1:7" x14ac:dyDescent="0.25">
@@ -35334,17 +35334,17 @@
       <c r="C986" s="6">
         <v>46279</v>
       </c>
-      <c r="D986" s="8">
-        <v>0</v>
+      <c r="D986" s="7">
+        <v>58.330665</v>
       </c>
       <c r="E986" s="8">
-        <v>0</v>
+        <v>309507840</v>
       </c>
       <c r="F986" s="9">
         <v>5680</v>
       </c>
       <c r="G986" s="8">
-        <v>0</v>
+        <v>18053798154.73</v>
       </c>
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.25">
@@ -35380,17 +35380,17 @@
       <c r="C988" s="6">
         <v>46279</v>
       </c>
-      <c r="D988" s="8">
-        <v>0</v>
+      <c r="D988" s="10">
+        <v>1.78919</v>
       </c>
       <c r="E988" s="8">
-        <v>0</v>
+        <v>189321082</v>
       </c>
       <c r="F988" s="9">
         <v>5</v>
       </c>
       <c r="G988" s="8">
-        <v>0</v>
+        <v>338731400.77</v>
       </c>
     </row>
     <row r="989" spans="1:7" x14ac:dyDescent="0.25">
@@ -35403,17 +35403,17 @@
       <c r="C989" s="6">
         <v>46279</v>
       </c>
-      <c r="D989" s="8">
-        <v>0</v>
+      <c r="D989" s="7">
+        <v>52.516493</v>
       </c>
       <c r="E989" s="8">
-        <v>0</v>
+        <v>3094492</v>
       </c>
       <c r="F989" s="9">
         <v>1</v>
       </c>
       <c r="G989" s="8">
-        <v>0</v>
+        <v>162511866.47</v>
       </c>
     </row>
     <row r="990" spans="1:7" x14ac:dyDescent="0.25">
@@ -35426,17 +35426,17 @@
       <c r="C990" s="6">
         <v>46279</v>
       </c>
-      <c r="D990" s="8">
-        <v>0</v>
+      <c r="D990" s="7">
+        <v>1.792011</v>
       </c>
       <c r="E990" s="8">
-        <v>0</v>
+        <v>6312160</v>
       </c>
       <c r="F990" s="9">
         <v>169</v>
       </c>
       <c r="G990" s="8">
-        <v>0</v>
+        <v>11311457.7</v>
       </c>
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
@@ -35472,17 +35472,17 @@
       <c r="C992" s="6">
         <v>46279</v>
       </c>
-      <c r="D992" s="8">
-        <v>0</v>
+      <c r="D992" s="7">
+        <v>5.330329</v>
       </c>
       <c r="E992" s="8">
-        <v>0</v>
+        <v>568918973</v>
       </c>
       <c r="F992" s="9">
         <v>13470</v>
       </c>
       <c r="G992" s="8">
-        <v>0</v>
+        <v>3032525426.2</v>
       </c>
     </row>
     <row r="993" spans="1:7" x14ac:dyDescent="0.25">
@@ -35495,17 +35495,17 @@
       <c r="C993" s="6">
         <v>46279</v>
       </c>
-      <c r="D993" s="8">
-        <v>0</v>
+      <c r="D993" s="7">
+        <v>1.821169</v>
       </c>
       <c r="E993" s="8">
-        <v>0</v>
+        <v>401020160</v>
       </c>
       <c r="F993" s="9">
         <v>4001</v>
       </c>
       <c r="G993" s="8">
-        <v>0</v>
+        <v>730325393.07</v>
       </c>
     </row>
     <row r="994" spans="1:7" x14ac:dyDescent="0.25">
@@ -35518,17 +35518,17 @@
       <c r="C994" s="6">
         <v>46279</v>
       </c>
-      <c r="D994" s="8">
-        <v>0</v>
+      <c r="D994" s="7">
+        <v>56.842852</v>
       </c>
       <c r="E994" s="8">
-        <v>0</v>
+        <v>248900</v>
       </c>
       <c r="F994" s="9">
         <v>12</v>
       </c>
       <c r="G994" s="8">
-        <v>0</v>
+        <v>14148185.88</v>
       </c>
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.25">
@@ -35541,17 +35541,17 @@
       <c r="C995" s="6">
         <v>46279</v>
       </c>
-      <c r="D995" s="8">
-        <v>0</v>
+      <c r="D995" s="7">
+        <v>15.751633</v>
       </c>
       <c r="E995" s="8">
-        <v>0</v>
+        <v>3147787</v>
       </c>
       <c r="F995" s="9">
         <v>1</v>
       </c>
       <c r="G995" s="8">
-        <v>0</v>
+        <v>49582784.84</v>
       </c>
     </row>
     <row r="996" spans="1:7" x14ac:dyDescent="0.25">
@@ -35564,17 +35564,17 @@
       <c r="C996" s="6">
         <v>46279</v>
       </c>
-      <c r="D996" s="8">
-        <v>0</v>
+      <c r="D996" s="7">
+        <v>53.282722</v>
       </c>
       <c r="E996" s="8">
-        <v>0</v>
+        <v>480675829</v>
       </c>
       <c r="F996" s="9">
         <v>7033</v>
       </c>
       <c r="G996" s="8">
-        <v>0</v>
+        <v>25611716581.8</v>
       </c>
     </row>
     <row r="997" spans="1:7" x14ac:dyDescent="0.25">
@@ -35610,17 +35610,17 @@
       <c r="C998" s="6">
         <v>46279</v>
       </c>
-      <c r="D998" s="8">
-        <v>0</v>
+      <c r="D998" s="10">
+        <v>55.39189</v>
       </c>
       <c r="E998" s="8">
-        <v>0</v>
+        <v>497075544</v>
       </c>
       <c r="F998" s="9">
         <v>1381</v>
       </c>
       <c r="G998" s="8">
-        <v>0</v>
+        <v>27533954048.42</v>
       </c>
     </row>
     <row r="999" spans="1:7" x14ac:dyDescent="0.25">
@@ -35656,17 +35656,17 @@
       <c r="C1000" s="6">
         <v>46279</v>
       </c>
-      <c r="D1000" s="8">
-        <v>0</v>
+      <c r="D1000" s="7">
+        <v>49.529638</v>
       </c>
       <c r="E1000" s="8">
-        <v>0</v>
+        <v>477136380</v>
       </c>
       <c r="F1000" s="9">
         <v>225</v>
       </c>
       <c r="G1000" s="8">
-        <v>0</v>
+        <v>23632392272.55</v>
       </c>
     </row>
     <row r="1001" spans="1:7" x14ac:dyDescent="0.25">
@@ -35679,17 +35679,17 @@
       <c r="C1001" s="6">
         <v>46279</v>
       </c>
-      <c r="D1001" s="8">
-        <v>0</v>
+      <c r="D1001" s="7">
+        <v>49.608588</v>
       </c>
       <c r="E1001" s="8">
-        <v>0</v>
+        <v>82386965</v>
       </c>
       <c r="F1001" s="9">
         <v>806</v>
       </c>
       <c r="G1001" s="8">
-        <v>0</v>
+        <v>4087100997.45</v>
       </c>
     </row>
     <row r="1002" spans="1:7" x14ac:dyDescent="0.25">
@@ -35702,17 +35702,17 @@
       <c r="C1002" s="6">
         <v>46279</v>
       </c>
-      <c r="D1002" s="8">
-        <v>0</v>
+      <c r="D1002" s="10">
+        <v>1.93082</v>
       </c>
       <c r="E1002" s="8">
-        <v>0</v>
+        <v>179618321</v>
       </c>
       <c r="F1002" s="9">
         <v>1</v>
       </c>
       <c r="G1002" s="8">
-        <v>0</v>
+        <v>346810618.72</v>
       </c>
     </row>
     <row r="1003" spans="1:7" x14ac:dyDescent="0.25">
@@ -35725,17 +35725,17 @@
       <c r="C1003" s="6">
         <v>46279</v>
       </c>
-      <c r="D1003" s="8">
-        <v>0</v>
+      <c r="D1003" s="7">
+        <v>1.851587</v>
       </c>
       <c r="E1003" s="8">
-        <v>0</v>
+        <v>39442409</v>
       </c>
       <c r="F1003" s="9">
         <v>1</v>
       </c>
       <c r="G1003" s="8">
-        <v>0</v>
+        <v>73031050.44</v>
       </c>
     </row>
     <row r="1004" spans="1:7" x14ac:dyDescent="0.25">
@@ -35748,17 +35748,17 @@
       <c r="C1004" s="6">
         <v>46279</v>
       </c>
-      <c r="D1004" s="8">
-        <v>0</v>
+      <c r="D1004" s="7">
+        <v>53.939343</v>
       </c>
       <c r="E1004" s="8">
-        <v>0</v>
+        <v>96297860</v>
       </c>
       <c r="F1004" s="9">
         <v>62</v>
       </c>
       <c r="G1004" s="8">
-        <v>0</v>
+        <v>5194243302.5</v>
       </c>
     </row>
     <row r="1005" spans="1:7" x14ac:dyDescent="0.25">
@@ -35771,17 +35771,17 @@
       <c r="C1005" s="6">
         <v>46279</v>
       </c>
-      <c r="D1005" s="8">
-        <v>0</v>
+      <c r="D1005" s="7">
+        <v>4.579833</v>
       </c>
       <c r="E1005" s="8">
-        <v>0</v>
+        <v>82683881</v>
       </c>
       <c r="F1005" s="9">
         <v>1</v>
       </c>
       <c r="G1005" s="8">
-        <v>0</v>
+        <v>378678393.49</v>
       </c>
     </row>
     <row r="1006" spans="1:7" x14ac:dyDescent="0.25">
@@ -35794,17 +35794,17 @@
       <c r="C1006" s="6">
         <v>46279</v>
       </c>
-      <c r="D1006" s="8">
-        <v>0</v>
+      <c r="D1006" s="7">
+        <v>2.958902</v>
       </c>
       <c r="E1006" s="8">
-        <v>0</v>
+        <v>987490836</v>
       </c>
       <c r="F1006" s="9">
         <v>30421</v>
       </c>
       <c r="G1006" s="8">
-        <v>0</v>
+        <v>2921888317.01</v>
       </c>
     </row>
     <row r="1007" spans="1:7" x14ac:dyDescent="0.25">
@@ -35863,17 +35863,17 @@
       <c r="C1009" s="6">
         <v>46279</v>
       </c>
-      <c r="D1009" s="8">
-        <v>0</v>
+      <c r="D1009" s="7">
+        <v>1.583379</v>
       </c>
       <c r="E1009" s="8">
-        <v>0</v>
+        <v>8945273</v>
       </c>
       <c r="F1009" s="9">
         <v>234</v>
       </c>
       <c r="G1009" s="8">
-        <v>0</v>
+        <v>14163758.78</v>
       </c>
     </row>
     <row r="1010" spans="1:7" x14ac:dyDescent="0.25">
@@ -35978,17 +35978,17 @@
       <c r="C1014" s="6">
         <v>46279</v>
       </c>
-      <c r="D1014" s="8">
-        <v>0</v>
+      <c r="D1014" s="7">
+        <v>1.239677</v>
       </c>
       <c r="E1014" s="8">
-        <v>0</v>
+        <v>16503368026</v>
       </c>
       <c r="F1014" s="9">
         <v>1327</v>
       </c>
       <c r="G1014" s="8">
-        <v>0</v>
+        <v>20458841299.38</v>
       </c>
     </row>
     <row r="1015" spans="1:7" x14ac:dyDescent="0.25">
@@ -36024,17 +36024,17 @@
       <c r="C1016" s="6">
         <v>46279</v>
       </c>
-      <c r="D1016" s="8">
-        <v>0</v>
+      <c r="D1016" s="7">
+        <v>37.028071</v>
       </c>
       <c r="E1016" s="8">
-        <v>0</v>
+        <v>95518</v>
       </c>
       <c r="F1016" s="9">
         <v>1</v>
       </c>
       <c r="G1016" s="8">
-        <v>0</v>
+        <v>3536847.33</v>
       </c>
     </row>
     <row r="1017" spans="1:7" x14ac:dyDescent="0.25">
@@ -36070,8 +36070,8 @@
       <c r="C1018" s="6">
         <v>46279</v>
       </c>
-      <c r="D1018" s="7">
-        <v>4.413625</v>
+      <c r="D1018" s="10">
+        <v>4.41672</v>
       </c>
       <c r="E1018" s="8">
         <v>2524738</v>
@@ -36080,7 +36080,7 @@
         <v>1073</v>
       </c>
       <c r="G1018" s="8">
-        <v>11143245.7</v>
+        <v>11151060.52</v>
       </c>
     </row>
     <row r="1019" spans="1:7" x14ac:dyDescent="0.25">
@@ -36116,17 +36116,17 @@
       <c r="C1020" s="6">
         <v>46279</v>
       </c>
-      <c r="D1020" s="8">
-        <v>0</v>
+      <c r="D1020" s="10">
+        <v>1.57106</v>
       </c>
       <c r="E1020" s="8">
-        <v>0</v>
+        <v>38685206</v>
       </c>
       <c r="F1020" s="9">
         <v>26</v>
       </c>
       <c r="G1020" s="8">
-        <v>0</v>
+        <v>60776770.11</v>
       </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.25">
@@ -36139,17 +36139,17 @@
       <c r="C1021" s="6">
         <v>46279</v>
       </c>
-      <c r="D1021" s="8">
-        <v>0</v>
+      <c r="D1021" s="7">
+        <v>1.457613</v>
       </c>
       <c r="E1021" s="8">
-        <v>0</v>
+        <v>110217331</v>
       </c>
       <c r="F1021" s="9">
         <v>1374</v>
       </c>
       <c r="G1021" s="8">
-        <v>0</v>
+        <v>160654258.18</v>
       </c>
     </row>
     <row r="1022" spans="1:7" x14ac:dyDescent="0.25">
@@ -36185,17 +36185,17 @@
       <c r="C1023" s="6">
         <v>46279</v>
       </c>
-      <c r="D1023" s="8">
-        <v>0</v>
+      <c r="D1023" s="7">
+        <v>0.002296</v>
       </c>
       <c r="E1023" s="8">
-        <v>0</v>
+        <v>21405755952</v>
       </c>
       <c r="F1023" s="9">
         <v>1</v>
       </c>
       <c r="G1023" s="8">
-        <v>0</v>
+        <v>49150243.38</v>
       </c>
     </row>
     <row r="1024" spans="1:7" x14ac:dyDescent="0.25">
@@ -36208,17 +36208,17 @@
       <c r="C1024" s="6">
         <v>46279</v>
       </c>
-      <c r="D1024" s="8">
-        <v>0</v>
+      <c r="D1024" s="7">
+        <v>62.554857</v>
       </c>
       <c r="E1024" s="8">
-        <v>0</v>
+        <v>41940</v>
       </c>
       <c r="F1024" s="9">
         <v>1</v>
       </c>
       <c r="G1024" s="8">
-        <v>0</v>
+        <v>2623550.69</v>
       </c>
     </row>
     <row r="1025" spans="1:7" x14ac:dyDescent="0.25">
@@ -36231,17 +36231,17 @@
       <c r="C1025" s="6">
         <v>46279</v>
       </c>
-      <c r="D1025" s="8">
-        <v>0</v>
+      <c r="D1025" s="7">
+        <v>58.282007</v>
       </c>
       <c r="E1025" s="8">
-        <v>0</v>
+        <v>790086</v>
       </c>
       <c r="F1025" s="9">
         <v>52</v>
       </c>
       <c r="G1025" s="8">
-        <v>0</v>
+        <v>46047797.68</v>
       </c>
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.25">
@@ -36254,17 +36254,17 @@
       <c r="C1026" s="6">
         <v>46279</v>
       </c>
-      <c r="D1026" s="8">
-        <v>0</v>
+      <c r="D1026" s="7">
+        <v>52.738036</v>
       </c>
       <c r="E1026" s="8">
-        <v>0</v>
+        <v>1726780</v>
       </c>
       <c r="F1026" s="9">
         <v>2</v>
       </c>
       <c r="G1026" s="8">
-        <v>0</v>
+        <v>91066985.64</v>
       </c>
     </row>
     <row r="1027" spans="1:7" x14ac:dyDescent="0.25">
@@ -36369,17 +36369,17 @@
       <c r="C1031" s="6">
         <v>46279</v>
       </c>
-      <c r="D1031" s="8">
-        <v>0</v>
+      <c r="D1031" s="7">
+        <v>3.201899</v>
       </c>
       <c r="E1031" s="8">
-        <v>0</v>
+        <v>10799662838</v>
       </c>
       <c r="F1031" s="9">
         <v>392</v>
       </c>
       <c r="G1031" s="8">
-        <v>0</v>
+        <v>34579429077.83</v>
       </c>
     </row>
     <row r="1032" spans="1:7" x14ac:dyDescent="0.25">
@@ -36438,17 +36438,17 @@
       <c r="C1034" s="6">
         <v>46279</v>
       </c>
-      <c r="D1034" s="8">
-        <v>0</v>
+      <c r="D1034" s="7">
+        <v>58.488017</v>
       </c>
       <c r="E1034" s="8">
-        <v>0</v>
+        <v>196370</v>
       </c>
       <c r="F1034" s="9">
         <v>1</v>
       </c>
       <c r="G1034" s="8">
-        <v>0</v>
+        <v>11485291.81</v>
       </c>
     </row>
     <row r="1035" spans="1:7" x14ac:dyDescent="0.25">
@@ -36507,17 +36507,17 @@
       <c r="C1037" s="6">
         <v>46279</v>
       </c>
-      <c r="D1037" s="8">
-        <v>0</v>
+      <c r="D1037" s="7">
+        <v>4.956165</v>
       </c>
       <c r="E1037" s="8">
-        <v>0</v>
+        <v>18778769647</v>
       </c>
       <c r="F1037" s="9">
         <v>108976</v>
       </c>
       <c r="G1037" s="8">
-        <v>0</v>
+        <v>93070677115.47</v>
       </c>
     </row>
     <row r="1038" spans="1:7" x14ac:dyDescent="0.25">
@@ -36530,17 +36530,17 @@
       <c r="C1038" s="6">
         <v>46279</v>
       </c>
-      <c r="D1038" s="8">
-        <v>0</v>
+      <c r="D1038" s="7">
+        <v>170.949039</v>
       </c>
       <c r="E1038" s="8">
-        <v>0</v>
+        <v>74818</v>
       </c>
       <c r="F1038" s="9">
         <v>1</v>
       </c>
       <c r="G1038" s="8">
-        <v>0</v>
+        <v>12790065.22</v>
       </c>
     </row>
     <row r="1039" spans="1:7" x14ac:dyDescent="0.25">
@@ -36553,17 +36553,17 @@
       <c r="C1039" s="6">
         <v>46279</v>
       </c>
-      <c r="D1039" s="8">
-        <v>0</v>
+      <c r="D1039" s="7">
+        <v>1.637763</v>
       </c>
       <c r="E1039" s="8">
-        <v>0</v>
+        <v>87053490</v>
       </c>
       <c r="F1039" s="9">
         <v>1229</v>
       </c>
       <c r="G1039" s="8">
-        <v>0</v>
+        <v>142572963.83</v>
       </c>
     </row>
     <row r="1040" spans="1:7" x14ac:dyDescent="0.25">
@@ -36622,17 +36622,17 @@
       <c r="C1042" s="6">
         <v>46279</v>
       </c>
-      <c r="D1042" s="8">
-        <v>0</v>
+      <c r="D1042" s="7">
+        <v>2.866806</v>
       </c>
       <c r="E1042" s="8">
-        <v>0</v>
+        <v>24785369</v>
       </c>
       <c r="F1042" s="9">
         <v>1</v>
       </c>
       <c r="G1042" s="8">
-        <v>0</v>
+        <v>71054833.92</v>
       </c>
     </row>
     <row r="1043" spans="1:7" x14ac:dyDescent="0.25">
@@ -36691,17 +36691,17 @@
       <c r="C1045" s="6">
         <v>46279</v>
       </c>
-      <c r="D1045" s="8">
-        <v>0</v>
+      <c r="D1045" s="7">
+        <v>2.136459</v>
       </c>
       <c r="E1045" s="8">
-        <v>0</v>
+        <v>557271331</v>
       </c>
       <c r="F1045" s="9">
         <v>15770</v>
       </c>
       <c r="G1045" s="8">
-        <v>0</v>
+        <v>1190587425.9</v>
       </c>
     </row>
     <row r="1046" spans="1:7" x14ac:dyDescent="0.25">
@@ -36760,17 +36760,17 @@
       <c r="C1048" s="6">
         <v>46279</v>
       </c>
-      <c r="D1048" s="8">
-        <v>0</v>
+      <c r="D1048" s="7">
+        <v>4.585678</v>
       </c>
       <c r="E1048" s="8">
-        <v>0</v>
+        <v>1127191620</v>
       </c>
       <c r="F1048" s="9">
         <v>1</v>
       </c>
       <c r="G1048" s="8">
-        <v>0</v>
+        <v>5168937744.41</v>
       </c>
     </row>
     <row r="1049" spans="1:7" x14ac:dyDescent="0.25">
@@ -36875,17 +36875,17 @@
       <c r="C1053" s="6">
         <v>46279</v>
       </c>
-      <c r="D1053" s="8">
-        <v>0</v>
+      <c r="D1053" s="7">
+        <v>1.454675</v>
       </c>
       <c r="E1053" s="8">
-        <v>0</v>
+        <v>1939081722</v>
       </c>
       <c r="F1053" s="9">
         <v>80</v>
       </c>
       <c r="G1053" s="8">
-        <v>0</v>
+        <v>2820733908.58</v>
       </c>
     </row>
     <row r="1054" spans="1:7" x14ac:dyDescent="0.25">
@@ -36990,17 +36990,17 @@
       <c r="C1058" s="6">
         <v>46279</v>
       </c>
-      <c r="D1058" s="8">
-        <v>0</v>
+      <c r="D1058" s="7">
+        <v>53.660678</v>
       </c>
       <c r="E1058" s="8">
-        <v>0</v>
+        <v>264284</v>
       </c>
       <c r="F1058" s="9">
         <v>10</v>
       </c>
       <c r="G1058" s="8">
-        <v>0</v>
+        <v>14181658.62</v>
       </c>
     </row>
     <row r="1059" spans="1:7" x14ac:dyDescent="0.25">
@@ -37013,17 +37013,17 @@
       <c r="C1059" s="6">
         <v>46279</v>
       </c>
-      <c r="D1059" s="8">
-        <v>0</v>
+      <c r="D1059" s="7">
+        <v>1.742474</v>
       </c>
       <c r="E1059" s="8">
-        <v>0</v>
+        <v>324552705</v>
       </c>
       <c r="F1059" s="9">
         <v>14105</v>
       </c>
       <c r="G1059" s="8">
-        <v>0</v>
+        <v>565524619.91</v>
       </c>
     </row>
     <row r="1060" spans="1:7" x14ac:dyDescent="0.25">
@@ -37059,17 +37059,17 @@
       <c r="C1061" s="6">
         <v>46279</v>
       </c>
-      <c r="D1061" s="8">
-        <v>0</v>
+      <c r="D1061" s="7">
+        <v>22.097731</v>
       </c>
       <c r="E1061" s="8">
-        <v>0</v>
+        <v>223936957</v>
       </c>
       <c r="F1061" s="9">
         <v>24605</v>
       </c>
       <c r="G1061" s="8">
-        <v>0</v>
+        <v>4948498742.89</v>
       </c>
     </row>
     <row r="1062" spans="1:7" x14ac:dyDescent="0.25">
@@ -37082,17 +37082,17 @@
       <c r="C1062" s="6">
         <v>46279</v>
       </c>
-      <c r="D1062" s="8">
-        <v>0</v>
+      <c r="D1062" s="7">
+        <v>49.094128</v>
       </c>
       <c r="E1062" s="8">
-        <v>0</v>
+        <v>6397294</v>
       </c>
       <c r="F1062" s="9">
         <v>543</v>
       </c>
       <c r="G1062" s="8">
-        <v>0</v>
+        <v>314069572.19</v>
       </c>
     </row>
     <row r="1063" spans="1:7" x14ac:dyDescent="0.25">
@@ -37197,17 +37197,17 @@
       <c r="C1067" s="6">
         <v>46279</v>
       </c>
-      <c r="D1067" s="8">
-        <v>0</v>
+      <c r="D1067" s="7">
+        <v>1.045171</v>
       </c>
       <c r="E1067" s="8">
-        <v>0</v>
+        <v>1508400</v>
       </c>
       <c r="F1067" s="9">
         <v>16</v>
       </c>
       <c r="G1067" s="8">
-        <v>0</v>
+        <v>1576535.29</v>
       </c>
     </row>
     <row r="1068" spans="1:7" x14ac:dyDescent="0.25">
@@ -37220,17 +37220,17 @@
       <c r="C1068" s="6">
         <v>46279</v>
       </c>
-      <c r="D1068" s="8">
-        <v>0</v>
+      <c r="D1068" s="7">
+        <v>3.240783</v>
       </c>
       <c r="E1068" s="8">
-        <v>0</v>
+        <v>127546084</v>
       </c>
       <c r="F1068" s="9">
         <v>667</v>
       </c>
       <c r="G1068" s="8">
-        <v>0</v>
+        <v>413349169.86</v>
       </c>
     </row>
     <row r="1069" spans="1:7" x14ac:dyDescent="0.25">
@@ -37243,17 +37243,17 @@
       <c r="C1069" s="6">
         <v>46279</v>
       </c>
-      <c r="D1069" s="8">
-        <v>0</v>
+      <c r="D1069" s="7">
+        <v>1.919938</v>
       </c>
       <c r="E1069" s="8">
-        <v>0</v>
+        <v>26003550520</v>
       </c>
       <c r="F1069" s="9">
         <v>1090</v>
       </c>
       <c r="G1069" s="8">
-        <v>0</v>
+        <v>49925200479.38</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.25">
@@ -37289,17 +37289,17 @@
       <c r="C1071" s="6">
         <v>46279</v>
       </c>
-      <c r="D1071" s="8">
-        <v>0</v>
+      <c r="D1071" s="7">
+        <v>4.062268</v>
       </c>
       <c r="E1071" s="8">
-        <v>0</v>
+        <v>148481324</v>
       </c>
       <c r="F1071" s="9">
         <v>6077</v>
       </c>
       <c r="G1071" s="8">
-        <v>0</v>
+        <v>603170956.98</v>
       </c>
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.25">
@@ -37312,17 +37312,17 @@
       <c r="C1072" s="6">
         <v>46279</v>
       </c>
-      <c r="D1072" s="8">
-        <v>0</v>
+      <c r="D1072" s="7">
+        <v>0.149514</v>
       </c>
       <c r="E1072" s="8">
-        <v>0</v>
+        <v>204147320</v>
       </c>
       <c r="F1072" s="9">
         <v>146</v>
       </c>
       <c r="G1072" s="8">
-        <v>0</v>
+        <v>30522930.86</v>
       </c>
     </row>
     <row r="1073" spans="1:7" x14ac:dyDescent="0.25">
@@ -37335,17 +37335,17 @@
       <c r="C1073" s="6">
         <v>46279</v>
       </c>
-      <c r="D1073" s="8">
-        <v>0</v>
+      <c r="D1073" s="7">
+        <v>22.072608</v>
       </c>
       <c r="E1073" s="8">
-        <v>0</v>
+        <v>2330165</v>
       </c>
       <c r="F1073" s="9">
         <v>587</v>
       </c>
       <c r="G1073" s="8">
-        <v>0</v>
+        <v>51432817.79</v>
       </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.25">
@@ -37427,17 +37427,17 @@
       <c r="C1077" s="6">
         <v>46279</v>
       </c>
-      <c r="D1077" s="8">
-        <v>0</v>
+      <c r="D1077" s="7">
+        <v>0.530334</v>
       </c>
       <c r="E1077" s="8">
-        <v>0</v>
+        <v>2746834298</v>
       </c>
       <c r="F1077" s="9">
         <v>1089</v>
       </c>
       <c r="G1077" s="8">
-        <v>0</v>
+        <v>1456739198.8</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.25">
@@ -37450,17 +37450,17 @@
       <c r="C1078" s="6">
         <v>46279</v>
       </c>
-      <c r="D1078" s="8">
-        <v>0</v>
+      <c r="D1078" s="7">
+        <v>75.785157</v>
       </c>
       <c r="E1078" s="8">
-        <v>0</v>
+        <v>10567632</v>
       </c>
       <c r="F1078" s="9">
         <v>168</v>
       </c>
       <c r="G1078" s="8">
-        <v>0</v>
+        <v>800869649.09</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.25">
@@ -37496,17 +37496,17 @@
       <c r="C1080" s="6">
         <v>46279</v>
       </c>
-      <c r="D1080" s="8">
-        <v>0</v>
+      <c r="D1080" s="7">
+        <v>4.226791</v>
       </c>
       <c r="E1080" s="8">
-        <v>0</v>
+        <v>3819960833</v>
       </c>
       <c r="F1080" s="9">
         <v>4266</v>
       </c>
       <c r="G1080" s="8">
-        <v>0</v>
+        <v>16146175076.63</v>
       </c>
     </row>
     <row r="1081" spans="1:7" x14ac:dyDescent="0.25">
@@ -37519,17 +37519,17 @@
       <c r="C1081" s="6">
         <v>46279</v>
       </c>
-      <c r="D1081" s="8">
-        <v>0</v>
+      <c r="D1081" s="7">
+        <v>50.200345</v>
       </c>
       <c r="E1081" s="8">
-        <v>0</v>
+        <v>495470</v>
       </c>
       <c r="F1081" s="9">
         <v>1</v>
       </c>
       <c r="G1081" s="8">
-        <v>0</v>
+        <v>24872764.77</v>
       </c>
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.25">
@@ -37589,7 +37589,7 @@
         <v>46279</v>
       </c>
       <c r="D1084" s="7">
-        <v>52.327337</v>
+        <v>52.325686</v>
       </c>
       <c r="E1084" s="8">
         <v>306928344</v>
@@ -37598,7 +37598,7 @@
         <v>737</v>
       </c>
       <c r="G1084" s="8">
-        <v>16060742936.24</v>
+        <v>16060236040.5</v>
       </c>
     </row>
     <row r="1085" spans="1:7" x14ac:dyDescent="0.25">
@@ -37634,17 +37634,17 @@
       <c r="C1086" s="6">
         <v>46279</v>
       </c>
-      <c r="D1086" s="8">
-        <v>0</v>
+      <c r="D1086" s="7">
+        <v>5.213037</v>
       </c>
       <c r="E1086" s="8">
-        <v>0</v>
+        <v>39058460</v>
       </c>
       <c r="F1086" s="9">
         <v>3814</v>
       </c>
       <c r="G1086" s="8">
-        <v>0</v>
+        <v>203613203.12</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.25">
@@ -37680,17 +37680,17 @@
       <c r="C1088" s="6">
         <v>46279</v>
       </c>
-      <c r="D1088" s="8">
-        <v>0</v>
+      <c r="D1088" s="10">
+        <v>5.86465</v>
       </c>
       <c r="E1088" s="8">
-        <v>0</v>
+        <v>8223872782</v>
       </c>
       <c r="F1088" s="9">
         <v>9733</v>
       </c>
       <c r="G1088" s="8">
-        <v>0</v>
+        <v>48230133693.34</v>
       </c>
     </row>
     <row r="1089" spans="1:7" x14ac:dyDescent="0.25">
@@ -37726,17 +37726,17 @@
       <c r="C1090" s="6">
         <v>46279</v>
       </c>
-      <c r="D1090" s="8">
-        <v>0</v>
+      <c r="D1090" s="7">
+        <v>46.421145</v>
       </c>
       <c r="E1090" s="8">
-        <v>0</v>
+        <v>2310590</v>
       </c>
       <c r="F1090" s="9">
         <v>1</v>
       </c>
       <c r="G1090" s="8">
-        <v>0</v>
+        <v>107260233.47</v>
       </c>
     </row>
     <row r="1091" spans="1:7" x14ac:dyDescent="0.25">
@@ -37772,17 +37772,17 @@
       <c r="C1092" s="6">
         <v>46279</v>
       </c>
-      <c r="D1092" s="8">
-        <v>0</v>
+      <c r="D1092" s="10">
+        <v>2.67421</v>
       </c>
       <c r="E1092" s="8">
-        <v>0</v>
+        <v>617773589</v>
       </c>
       <c r="F1092" s="9">
         <v>21296</v>
       </c>
       <c r="G1092" s="8">
-        <v>0</v>
+        <v>1652056223.93</v>
       </c>
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.25">
@@ -37795,17 +37795,17 @@
       <c r="C1093" s="6">
         <v>46279</v>
       </c>
-      <c r="D1093" s="8">
-        <v>0</v>
+      <c r="D1093" s="7">
+        <v>23.119276</v>
       </c>
       <c r="E1093" s="8">
-        <v>0</v>
+        <v>31139822</v>
       </c>
       <c r="F1093" s="9">
         <v>5882</v>
       </c>
       <c r="G1093" s="8">
-        <v>0</v>
+        <v>719930135.75</v>
       </c>
     </row>
     <row r="1094" spans="1:7" x14ac:dyDescent="0.25">
@@ -37818,17 +37818,17 @@
       <c r="C1094" s="6">
         <v>46279</v>
       </c>
-      <c r="D1094" s="8">
-        <v>0</v>
+      <c r="D1094" s="7">
+        <v>8.213443</v>
       </c>
       <c r="E1094" s="8">
-        <v>0</v>
+        <v>51196481</v>
       </c>
       <c r="F1094" s="9">
         <v>4257</v>
       </c>
       <c r="G1094" s="8">
-        <v>0</v>
+        <v>420499379.35</v>
       </c>
     </row>
     <row r="1095" spans="1:7" x14ac:dyDescent="0.25">
@@ -37841,17 +37841,17 @@
       <c r="C1095" s="6">
         <v>46279</v>
       </c>
-      <c r="D1095" s="8">
-        <v>0</v>
+      <c r="D1095" s="7">
+        <v>10.839038</v>
       </c>
       <c r="E1095" s="8">
-        <v>0</v>
+        <v>2300294627</v>
       </c>
       <c r="F1095" s="9">
         <v>621</v>
       </c>
       <c r="G1095" s="8">
-        <v>0</v>
+        <v>24932980162.14</v>
       </c>
     </row>
     <row r="1096" spans="1:7" x14ac:dyDescent="0.25">
@@ -37864,17 +37864,17 @@
       <c r="C1096" s="6">
         <v>46279</v>
       </c>
-      <c r="D1096" s="8">
-        <v>0</v>
+      <c r="D1096" s="7">
+        <v>15.729803</v>
       </c>
       <c r="E1096" s="8">
-        <v>0</v>
+        <v>9409268</v>
       </c>
       <c r="F1096" s="9">
         <v>801</v>
       </c>
       <c r="G1096" s="8">
-        <v>0</v>
+        <v>148005933.62</v>
       </c>
     </row>
     <row r="1097" spans="1:7" x14ac:dyDescent="0.25">
@@ -37887,17 +37887,17 @@
       <c r="C1097" s="6">
         <v>46279</v>
       </c>
-      <c r="D1097" s="8">
-        <v>0</v>
+      <c r="D1097" s="7">
+        <v>71.535542</v>
       </c>
       <c r="E1097" s="8">
-        <v>0</v>
+        <v>75012090</v>
       </c>
       <c r="F1097" s="9">
         <v>1450</v>
       </c>
       <c r="G1097" s="8">
-        <v>0</v>
+        <v>5366030506.02</v>
       </c>
     </row>
     <row r="1098" spans="1:7" x14ac:dyDescent="0.25">
@@ -37910,17 +37910,17 @@
       <c r="C1098" s="6">
         <v>46279</v>
       </c>
-      <c r="D1098" s="8">
-        <v>0</v>
+      <c r="D1098" s="7">
+        <v>30.624191</v>
       </c>
       <c r="E1098" s="8">
-        <v>0</v>
+        <v>32515349</v>
       </c>
       <c r="F1098" s="9">
         <v>1</v>
       </c>
       <c r="G1098" s="8">
-        <v>0</v>
+        <v>995756270.76</v>
       </c>
     </row>
     <row r="1099" spans="1:7" x14ac:dyDescent="0.25">
@@ -37933,17 +37933,17 @@
       <c r="C1099" s="6">
         <v>46279</v>
       </c>
-      <c r="D1099" s="8">
-        <v>0</v>
+      <c r="D1099" s="10">
+        <v>7.87331</v>
       </c>
       <c r="E1099" s="8">
-        <v>0</v>
+        <v>5344105514</v>
       </c>
       <c r="F1099" s="9">
         <v>47030</v>
       </c>
       <c r="G1099" s="8">
-        <v>0</v>
+        <v>42075799209.07</v>
       </c>
     </row>
     <row r="1100" spans="1:7" x14ac:dyDescent="0.25">
@@ -37956,17 +37956,17 @@
       <c r="C1100" s="6">
         <v>46279</v>
       </c>
-      <c r="D1100" s="8">
-        <v>0</v>
+      <c r="D1100" s="7">
+        <v>1.183437</v>
       </c>
       <c r="E1100" s="8">
-        <v>0</v>
+        <v>236892870</v>
       </c>
       <c r="F1100" s="9">
         <v>2854</v>
       </c>
       <c r="G1100" s="8">
-        <v>0</v>
+        <v>280347722.43</v>
       </c>
     </row>
     <row r="1101" spans="1:7" x14ac:dyDescent="0.25">
@@ -37979,17 +37979,17 @@
       <c r="C1101" s="6">
         <v>46279</v>
       </c>
-      <c r="D1101" s="8">
-        <v>0</v>
+      <c r="D1101" s="10">
+        <v>1.47049</v>
       </c>
       <c r="E1101" s="8">
-        <v>0</v>
+        <v>68590507</v>
       </c>
       <c r="F1101" s="9">
         <v>2064</v>
       </c>
       <c r="G1101" s="8">
-        <v>0</v>
+        <v>100861647.43</v>
       </c>
     </row>
     <row r="1102" spans="1:7" x14ac:dyDescent="0.25">
@@ -38002,17 +38002,17 @@
       <c r="C1102" s="6">
         <v>46279</v>
       </c>
-      <c r="D1102" s="8">
-        <v>0</v>
+      <c r="D1102" s="10">
+        <v>0.76079</v>
       </c>
       <c r="E1102" s="8">
-        <v>0</v>
+        <v>800146527</v>
       </c>
       <c r="F1102" s="9">
         <v>3574</v>
       </c>
       <c r="G1102" s="8">
-        <v>0</v>
+        <v>608743601.48</v>
       </c>
     </row>
     <row r="1103" spans="1:7" x14ac:dyDescent="0.25">
@@ -38025,17 +38025,17 @@
       <c r="C1103" s="6">
         <v>46279</v>
       </c>
-      <c r="D1103" s="8">
-        <v>0</v>
+      <c r="D1103" s="7">
+        <v>1.799282</v>
       </c>
       <c r="E1103" s="8">
-        <v>0</v>
+        <v>148250927</v>
       </c>
       <c r="F1103" s="9">
         <v>2708</v>
       </c>
       <c r="G1103" s="8">
-        <v>0</v>
+        <v>266745290.93</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.25">
@@ -38071,17 +38071,17 @@
       <c r="C1105" s="6">
         <v>46279</v>
       </c>
-      <c r="D1105" s="8">
-        <v>0</v>
+      <c r="D1105" s="7">
+        <v>12.098041</v>
       </c>
       <c r="E1105" s="8">
-        <v>0</v>
+        <v>636388485</v>
       </c>
       <c r="F1105" s="9">
         <v>40807</v>
       </c>
       <c r="G1105" s="8">
-        <v>0</v>
+        <v>7699054275.41</v>
       </c>
     </row>
     <row r="1106" spans="1:7" x14ac:dyDescent="0.25">
@@ -38094,17 +38094,17 @@
       <c r="C1106" s="6">
         <v>46279</v>
       </c>
-      <c r="D1106" s="8">
-        <v>0</v>
+      <c r="D1106" s="7">
+        <v>1.821668</v>
       </c>
       <c r="E1106" s="8">
-        <v>0</v>
+        <v>392570970</v>
       </c>
       <c r="F1106" s="9">
         <v>1</v>
       </c>
       <c r="G1106" s="8">
-        <v>0</v>
+        <v>715133860.92</v>
       </c>
     </row>
     <row r="1107" spans="1:7" x14ac:dyDescent="0.25">
@@ -38117,17 +38117,17 @@
       <c r="C1107" s="6">
         <v>46279</v>
       </c>
-      <c r="D1107" s="8">
-        <v>0</v>
+      <c r="D1107" s="7">
+        <v>1.298769</v>
       </c>
       <c r="E1107" s="8">
-        <v>0</v>
+        <v>668106186</v>
       </c>
       <c r="F1107" s="9">
         <v>132</v>
       </c>
       <c r="G1107" s="8">
-        <v>0</v>
+        <v>867715538.31</v>
       </c>
     </row>
     <row r="1108" spans="1:7" x14ac:dyDescent="0.25">
@@ -38209,17 +38209,17 @@
       <c r="C1111" s="6">
         <v>46279</v>
       </c>
-      <c r="D1111" s="8">
-        <v>0</v>
+      <c r="D1111" s="7">
+        <v>1.220582</v>
       </c>
       <c r="E1111" s="8">
-        <v>0</v>
+        <v>53069351</v>
       </c>
       <c r="F1111" s="9">
         <v>1498</v>
       </c>
       <c r="G1111" s="8">
-        <v>0</v>
+        <v>64775518.82</v>
       </c>
     </row>
     <row r="1112" spans="1:7" x14ac:dyDescent="0.25">
@@ -38255,17 +38255,17 @@
       <c r="C1113" s="6">
         <v>46279</v>
       </c>
-      <c r="D1113" s="8">
-        <v>0</v>
+      <c r="D1113" s="7">
+        <v>54.172706</v>
       </c>
       <c r="E1113" s="8">
-        <v>0</v>
+        <v>207100</v>
       </c>
       <c r="F1113" s="9">
         <v>18</v>
       </c>
       <c r="G1113" s="8">
-        <v>0</v>
+        <v>11219167.43</v>
       </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.25">
@@ -38278,17 +38278,17 @@
       <c r="C1114" s="6">
         <v>46279</v>
       </c>
-      <c r="D1114" s="8">
-        <v>0</v>
+      <c r="D1114" s="7">
+        <v>28.226447</v>
       </c>
       <c r="E1114" s="8">
-        <v>0</v>
+        <v>3135331109</v>
       </c>
       <c r="F1114" s="9">
         <v>65729</v>
       </c>
       <c r="G1114" s="8">
-        <v>0</v>
+        <v>88499257761.05</v>
       </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.25">
@@ -38324,17 +38324,17 @@
       <c r="C1116" s="6">
         <v>46279</v>
       </c>
-      <c r="D1116" s="8">
-        <v>0</v>
+      <c r="D1116" s="7">
+        <v>2.388089</v>
       </c>
       <c r="E1116" s="8">
-        <v>0</v>
+        <v>193997530</v>
       </c>
       <c r="F1116" s="9">
         <v>5759</v>
       </c>
       <c r="G1116" s="8">
-        <v>0</v>
+        <v>463283282.67</v>
       </c>
     </row>
     <row r="1117" spans="1:7" x14ac:dyDescent="0.25">
@@ -38601,7 +38601,7 @@
         <v>46279</v>
       </c>
       <c r="D1128" s="7">
-        <v>3.757465</v>
+        <v>3.758259</v>
       </c>
       <c r="E1128" s="8">
         <v>245457201</v>
@@ -38610,7 +38610,7 @@
         <v>12</v>
       </c>
       <c r="G1128" s="8">
-        <v>922296908.65</v>
+        <v>922491674.34</v>
       </c>
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.25">
@@ -38669,17 +38669,17 @@
       <c r="C1131" s="6">
         <v>46279</v>
       </c>
-      <c r="D1131" s="8">
-        <v>0</v>
+      <c r="D1131" s="7">
+        <v>4.403368</v>
       </c>
       <c r="E1131" s="8">
-        <v>0</v>
+        <v>553376235</v>
       </c>
       <c r="F1131" s="9">
         <v>13</v>
       </c>
       <c r="G1131" s="8">
-        <v>0</v>
+        <v>2436719296.97</v>
       </c>
     </row>
     <row r="1132" spans="1:7" x14ac:dyDescent="0.25">
@@ -38923,7 +38923,7 @@
         <v>46279</v>
       </c>
       <c r="D1142" s="7">
-        <v>1.347946</v>
+        <v>1.379348</v>
       </c>
       <c r="E1142" s="8">
         <v>391308413</v>
@@ -38932,7 +38932,7 @@
         <v>929</v>
       </c>
       <c r="G1142" s="8">
-        <v>527462603.05</v>
+        <v>539750484.36</v>
       </c>
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.25">
@@ -38946,16 +38946,16 @@
         <v>46279</v>
       </c>
       <c r="D1143" s="8">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="E1143" s="8">
-        <v>0</v>
+        <v>123667144</v>
       </c>
       <c r="F1143" s="9">
         <v>6536</v>
       </c>
       <c r="G1143" s="8">
-        <v>0</v>
+        <v>765499628.1</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.25">
@@ -39037,17 +39037,17 @@
       <c r="C1147" s="6">
         <v>46279</v>
       </c>
-      <c r="D1147" s="8">
-        <v>0</v>
+      <c r="D1147" s="7">
+        <v>2.268718</v>
       </c>
       <c r="E1147" s="8">
-        <v>0</v>
+        <v>213359272</v>
       </c>
       <c r="F1147" s="9">
         <v>737</v>
       </c>
       <c r="G1147" s="8">
-        <v>0</v>
+        <v>484051968.86</v>
       </c>
     </row>
     <row r="1148" spans="1:7" x14ac:dyDescent="0.25">
@@ -39176,7 +39176,7 @@
         <v>46279</v>
       </c>
       <c r="D1153" s="7">
-        <v>4.522053</v>
+        <v>4.563592</v>
       </c>
       <c r="E1153" s="8">
         <v>6335747</v>
@@ -39185,7 +39185,7 @@
         <v>35</v>
       </c>
       <c r="G1153" s="8">
-        <v>28650581.45</v>
+        <v>28913761.44</v>
       </c>
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.25">
@@ -39268,16 +39268,16 @@
         <v>46279</v>
       </c>
       <c r="D1157" s="7">
-        <v>17.742817</v>
+        <v>17.723678</v>
       </c>
       <c r="E1157" s="8">
-        <v>86862969</v>
+        <v>86794898</v>
       </c>
       <c r="F1157" s="9">
         <v>8068</v>
       </c>
       <c r="G1157" s="8">
-        <v>1541193801.08</v>
+        <v>1538324808.35</v>
       </c>
     </row>
     <row r="1158" spans="1:7" x14ac:dyDescent="0.25">
@@ -39681,17 +39681,17 @@
       <c r="C1175" s="6">
         <v>46279</v>
       </c>
-      <c r="D1175" s="8">
-        <v>0</v>
+      <c r="D1175" s="7">
+        <v>1.263353</v>
       </c>
       <c r="E1175" s="8">
-        <v>0</v>
+        <v>11025846</v>
       </c>
       <c r="F1175" s="9">
         <v>113</v>
       </c>
       <c r="G1175" s="8">
-        <v>0</v>
+        <v>13929534.05</v>
       </c>
     </row>
     <row r="1176" spans="1:7" x14ac:dyDescent="0.25">
@@ -39728,7 +39728,7 @@
         <v>46279</v>
       </c>
       <c r="D1177" s="7">
-        <v>59.900401</v>
+        <v>59.900333</v>
       </c>
       <c r="E1177" s="8">
         <v>8792690</v>
@@ -39737,7 +39737,7 @@
         <v>1</v>
       </c>
       <c r="G1177" s="8">
-        <v>526685658.93</v>
+        <v>526685058.95</v>
       </c>
     </row>
     <row r="1178" spans="1:7" x14ac:dyDescent="0.25">
@@ -40187,17 +40187,17 @@
       <c r="C1197" s="6">
         <v>46279</v>
       </c>
-      <c r="D1197" s="8">
-        <v>0</v>
+      <c r="D1197" s="7">
+        <v>5.416812</v>
       </c>
       <c r="E1197" s="8">
-        <v>0</v>
+        <v>15488274</v>
       </c>
       <c r="F1197" s="9">
         <v>2030</v>
       </c>
       <c r="G1197" s="8">
-        <v>0</v>
+        <v>83897073.98</v>
       </c>
     </row>
     <row r="1198" spans="1:7" x14ac:dyDescent="0.25">
@@ -40394,17 +40394,17 @@
       <c r="C1206" s="6">
         <v>46279</v>
       </c>
-      <c r="D1206" s="8">
-        <v>0</v>
+      <c r="D1206" s="7">
+        <v>1.551784</v>
       </c>
       <c r="E1206" s="8">
-        <v>0</v>
+        <v>1475011222</v>
       </c>
       <c r="F1206" s="9">
         <v>398</v>
       </c>
       <c r="G1206" s="8">
-        <v>0</v>
+        <v>2288898167.72</v>
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.25">
@@ -40601,17 +40601,17 @@
       <c r="C1215" s="6">
         <v>46279</v>
       </c>
-      <c r="D1215" s="8">
-        <v>0</v>
+      <c r="D1215" s="7">
+        <v>4.951774</v>
       </c>
       <c r="E1215" s="8">
-        <v>0</v>
+        <v>263482047</v>
       </c>
       <c r="F1215" s="9">
         <v>65</v>
       </c>
       <c r="G1215" s="8">
-        <v>0</v>
+        <v>1304703568.06</v>
       </c>
     </row>
     <row r="1216" spans="1:7" x14ac:dyDescent="0.25">
@@ -40717,7 +40717,7 @@
         <v>46279</v>
       </c>
       <c r="D1220" s="7">
-        <v>1.217673</v>
+        <v>1.224236</v>
       </c>
       <c r="E1220" s="8">
         <v>424626364</v>
@@ -40726,7 +40726,7 @@
         <v>15</v>
       </c>
       <c r="G1220" s="8">
-        <v>517056184.88</v>
+        <v>519842764.93</v>
       </c>
     </row>
     <row r="1221" spans="1:7" x14ac:dyDescent="0.25">
@@ -41084,17 +41084,17 @@
       <c r="C1236" s="6">
         <v>46279</v>
       </c>
-      <c r="D1236" s="8">
-        <v>0</v>
+      <c r="D1236" s="10">
+        <v>2.37236</v>
       </c>
       <c r="E1236" s="8">
-        <v>0</v>
+        <v>6866499553</v>
       </c>
       <c r="F1236" s="9">
         <v>1</v>
       </c>
       <c r="G1236" s="8">
-        <v>0</v>
+        <v>16289807210.69</v>
       </c>
     </row>
     <row r="1237" spans="1:7" x14ac:dyDescent="0.25">
@@ -41107,17 +41107,17 @@
       <c r="C1237" s="6">
         <v>46279</v>
       </c>
-      <c r="D1237" s="8">
-        <v>0</v>
+      <c r="D1237" s="7">
+        <v>51.526239</v>
       </c>
       <c r="E1237" s="8">
-        <v>0</v>
+        <v>3559908</v>
       </c>
       <c r="F1237" s="9">
         <v>19</v>
       </c>
       <c r="G1237" s="8">
-        <v>0</v>
+        <v>183428670.69</v>
       </c>
     </row>
     <row r="1238" spans="1:7" x14ac:dyDescent="0.25">
@@ -41314,17 +41314,17 @@
       <c r="C1246" s="6">
         <v>46279</v>
       </c>
-      <c r="D1246" s="8">
-        <v>0</v>
+      <c r="D1246" s="7">
+        <v>22.552931</v>
       </c>
       <c r="E1246" s="8">
-        <v>0</v>
+        <v>81255407</v>
       </c>
       <c r="F1246" s="9">
         <v>17470</v>
       </c>
       <c r="G1246" s="8">
-        <v>0</v>
+        <v>1832547582.01</v>
       </c>
     </row>
     <row r="1247" spans="1:7" x14ac:dyDescent="0.25">
@@ -41407,7 +41407,7 @@
         <v>46279</v>
       </c>
       <c r="D1250" s="7">
-        <v>5.410618</v>
+        <v>5.326236</v>
       </c>
       <c r="E1250" s="8">
         <v>280892491</v>
@@ -41416,7 +41416,7 @@
         <v>147</v>
       </c>
       <c r="G1250" s="8">
-        <v>1519801953.12</v>
+        <v>1496099776.57</v>
       </c>
     </row>
     <row r="1251" spans="1:7" x14ac:dyDescent="0.25">
@@ -41452,17 +41452,17 @@
       <c r="C1252" s="6">
         <v>46279</v>
       </c>
-      <c r="D1252" s="8">
-        <v>0</v>
+      <c r="D1252" s="7">
+        <v>1.616153</v>
       </c>
       <c r="E1252" s="8">
-        <v>0</v>
+        <v>592961232</v>
       </c>
       <c r="F1252" s="9">
         <v>1</v>
       </c>
       <c r="G1252" s="8">
-        <v>0</v>
+        <v>958316350.85</v>
       </c>
     </row>
     <row r="1253" spans="1:7" x14ac:dyDescent="0.25">
@@ -41614,7 +41614,7 @@
         <v>46279</v>
       </c>
       <c r="D1259" s="7">
-        <v>6.936375</v>
+        <v>6.933121</v>
       </c>
       <c r="E1259" s="8">
         <v>17984477</v>
@@ -41623,7 +41623,7 @@
         <v>83</v>
       </c>
       <c r="G1259" s="8">
-        <v>124747085.16</v>
+        <v>124688549.48</v>
       </c>
     </row>
     <row r="1260" spans="1:7" x14ac:dyDescent="0.25">
@@ -42097,7 +42097,7 @@
         <v>46279</v>
       </c>
       <c r="D1280" s="7">
-        <v>3.605938</v>
+        <v>3.594612</v>
       </c>
       <c r="E1280" s="8">
         <v>156713608</v>
@@ -42106,7 +42106,7 @@
         <v>300</v>
       </c>
       <c r="G1280" s="8">
-        <v>565099508.1</v>
+        <v>563324684.88</v>
       </c>
     </row>
     <row r="1281" spans="1:7" x14ac:dyDescent="0.25">
@@ -42189,7 +42189,7 @@
         <v>46279</v>
       </c>
       <c r="D1284" s="7">
-        <v>1.036918</v>
+        <v>1.036989</v>
       </c>
       <c r="E1284" s="8">
         <v>1648888925</v>
@@ -42198,7 +42198,7 @@
         <v>649</v>
       </c>
       <c r="G1284" s="8">
-        <v>1709763395.69</v>
+        <v>1709879626.22</v>
       </c>
     </row>
     <row r="1285" spans="1:7" x14ac:dyDescent="0.25">
@@ -42557,7 +42557,7 @@
         <v>46279</v>
       </c>
       <c r="D1300" s="7">
-        <v>4.124777</v>
+        <v>4.122455</v>
       </c>
       <c r="E1300" s="8">
         <v>38443737</v>
@@ -42566,7 +42566,7 @@
         <v>576</v>
       </c>
       <c r="G1300" s="8">
-        <v>158571828.66</v>
+        <v>158482567.56</v>
       </c>
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
@@ -42626,7 +42626,7 @@
         <v>46279</v>
       </c>
       <c r="D1303" s="7">
-        <v>8.426826</v>
+        <v>8.425962</v>
       </c>
       <c r="E1303" s="8">
         <v>22428570</v>
@@ -42635,7 +42635,7 @@
         <v>429</v>
       </c>
       <c r="G1303" s="8">
-        <v>189001666.7</v>
+        <v>188982288.59</v>
       </c>
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.25">
@@ -42648,8 +42648,8 @@
       <c r="C1304" s="6">
         <v>46279</v>
       </c>
-      <c r="D1304" s="7">
-        <v>11.679967</v>
+      <c r="D1304" s="10">
+        <v>11.67899</v>
       </c>
       <c r="E1304" s="8">
         <v>66864103</v>
@@ -42658,7 +42658,7 @@
         <v>3101</v>
       </c>
       <c r="G1304" s="8">
-        <v>780970544.03</v>
+        <v>780905172.27</v>
       </c>
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
@@ -43039,17 +43039,17 @@
       <c r="C1321" s="6">
         <v>46279</v>
       </c>
-      <c r="D1321" s="8">
-        <v>0</v>
+      <c r="D1321" s="7">
+        <v>6.620303</v>
       </c>
       <c r="E1321" s="8">
-        <v>0</v>
+        <v>11382509</v>
       </c>
       <c r="F1321" s="9">
         <v>435</v>
       </c>
       <c r="G1321" s="8">
-        <v>0</v>
+        <v>75355655.68</v>
       </c>
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
@@ -43155,7 +43155,7 @@
         <v>46279</v>
       </c>
       <c r="D1326" s="7">
-        <v>65.026629</v>
+        <v>65.026572</v>
       </c>
       <c r="E1326" s="8">
         <v>3513883</v>
@@ -43164,7 +43164,7 @@
         <v>3</v>
       </c>
       <c r="G1326" s="8">
-        <v>228495965.88</v>
+        <v>228495765.89</v>
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
@@ -43269,17 +43269,17 @@
       <c r="C1331" s="6">
         <v>46279</v>
       </c>
-      <c r="D1331" s="8">
-        <v>0</v>
+      <c r="D1331" s="7">
+        <v>53.221227</v>
       </c>
       <c r="E1331" s="8">
-        <v>0</v>
+        <v>100517909</v>
       </c>
       <c r="F1331" s="9">
         <v>564</v>
       </c>
       <c r="G1331" s="8">
-        <v>0</v>
+        <v>5349686456.92</v>
       </c>
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
@@ -43430,17 +43430,17 @@
       <c r="C1338" s="6">
         <v>46279</v>
       </c>
-      <c r="D1338" s="8">
-        <v>0</v>
+      <c r="D1338" s="10">
+        <v>53.60312</v>
       </c>
       <c r="E1338" s="8">
-        <v>0</v>
+        <v>91411125</v>
       </c>
       <c r="F1338" s="9">
         <v>374</v>
       </c>
       <c r="G1338" s="8">
-        <v>0</v>
+        <v>4899921486.77</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
@@ -43453,17 +43453,17 @@
       <c r="C1339" s="6">
         <v>46279</v>
       </c>
-      <c r="D1339" s="8">
-        <v>0</v>
+      <c r="D1339" s="7">
+        <v>67.384277</v>
       </c>
       <c r="E1339" s="8">
-        <v>0</v>
+        <v>35526381</v>
       </c>
       <c r="F1339" s="9">
         <v>745</v>
       </c>
       <c r="G1339" s="8">
-        <v>0</v>
+        <v>2393919483.94</v>
       </c>
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
@@ -43693,7 +43693,7 @@
         <v>56</v>
       </c>
       <c r="G1349" s="8">
-        <v>1374388602.66</v>
+        <v>1374388586.76</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
@@ -43890,17 +43890,17 @@
       <c r="C1358" s="6">
         <v>46279</v>
       </c>
-      <c r="D1358" s="8">
-        <v>0</v>
+      <c r="D1358" s="7">
+        <v>7.203744</v>
       </c>
       <c r="E1358" s="8">
-        <v>0</v>
+        <v>437230283</v>
       </c>
       <c r="F1358" s="9">
         <v>21515</v>
       </c>
       <c r="G1358" s="8">
-        <v>0</v>
+        <v>3149695062.69</v>
       </c>
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
@@ -44006,7 +44006,7 @@
         <v>46279</v>
       </c>
       <c r="D1363" s="7">
-        <v>67.701823</v>
+        <v>67.703714</v>
       </c>
       <c r="E1363" s="8">
         <v>2218226</v>
@@ -44015,7 +44015,7 @@
         <v>119</v>
       </c>
       <c r="G1363" s="8">
-        <v>150177944.74</v>
+        <v>150182138.09</v>
       </c>
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.25">
@@ -44143,17 +44143,17 @@
       <c r="C1369" s="6">
         <v>46279</v>
       </c>
-      <c r="D1369" s="8">
-        <v>0</v>
+      <c r="D1369" s="7">
+        <v>0.165708</v>
       </c>
       <c r="E1369" s="8">
-        <v>0</v>
+        <v>21109374150</v>
       </c>
       <c r="F1369" s="9">
         <v>8198</v>
       </c>
       <c r="G1369" s="8">
-        <v>0</v>
+        <v>3497990997.4</v>
       </c>
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.25">
@@ -44258,17 +44258,17 @@
       <c r="C1374" s="6">
         <v>46279</v>
       </c>
-      <c r="D1374" s="8">
-        <v>0</v>
+      <c r="D1374" s="7">
+        <v>1.094193</v>
       </c>
       <c r="E1374" s="8">
-        <v>0</v>
+        <v>33719577</v>
       </c>
       <c r="F1374" s="9">
         <v>464</v>
       </c>
       <c r="G1374" s="8">
-        <v>0</v>
+        <v>36895721.17</v>
       </c>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
@@ -44442,17 +44442,17 @@
       <c r="C1382" s="6">
         <v>46279</v>
       </c>
-      <c r="D1382" s="8">
-        <v>0</v>
+      <c r="D1382" s="7">
+        <v>6.429348</v>
       </c>
       <c r="E1382" s="8">
-        <v>0</v>
+        <v>7817036</v>
       </c>
       <c r="F1382" s="9">
         <v>11</v>
       </c>
       <c r="G1382" s="8">
-        <v>0</v>
+        <v>50258446.72</v>
       </c>
     </row>
     <row r="1383" spans="1:7" x14ac:dyDescent="0.25">
@@ -44488,17 +44488,17 @@
       <c r="C1384" s="6">
         <v>46279</v>
       </c>
-      <c r="D1384" s="8">
-        <v>0</v>
+      <c r="D1384" s="7">
+        <v>1.310539</v>
       </c>
       <c r="E1384" s="8">
-        <v>0</v>
+        <v>2398294516</v>
       </c>
       <c r="F1384" s="9">
         <v>12</v>
       </c>
       <c r="G1384" s="8">
-        <v>0</v>
+        <v>3143057511.02</v>
       </c>
     </row>
     <row r="1385" spans="1:7" x14ac:dyDescent="0.25">
@@ -44580,17 +44580,17 @@
       <c r="C1388" s="6">
         <v>46279</v>
       </c>
-      <c r="D1388" s="8">
-        <v>0</v>
+      <c r="D1388" s="7">
+        <v>1.285127</v>
       </c>
       <c r="E1388" s="8">
-        <v>0</v>
+        <v>953378632</v>
       </c>
       <c r="F1388" s="9">
         <v>17572</v>
       </c>
       <c r="G1388" s="8">
-        <v>0</v>
+        <v>1225212284.65</v>
       </c>
     </row>
     <row r="1389" spans="1:7" x14ac:dyDescent="0.25">
@@ -44696,7 +44696,7 @@
         <v>46279</v>
       </c>
       <c r="D1393" s="7">
-        <v>66.184849</v>
+        <v>66.167849</v>
       </c>
       <c r="E1393" s="8">
         <v>8605496</v>
@@ -44705,7 +44705,7 @@
         <v>12</v>
       </c>
       <c r="G1393" s="8">
-        <v>569553451.72</v>
+        <v>569407160.84</v>
       </c>
     </row>
     <row r="1394" spans="1:7" x14ac:dyDescent="0.25">
@@ -44741,17 +44741,17 @@
       <c r="C1395" s="6">
         <v>46279</v>
       </c>
-      <c r="D1395" s="8">
-        <v>0</v>
+      <c r="D1395" s="7">
+        <v>0.224794</v>
       </c>
       <c r="E1395" s="8">
-        <v>0</v>
+        <v>1084666311</v>
       </c>
       <c r="F1395" s="9">
         <v>15</v>
       </c>
       <c r="G1395" s="8">
-        <v>0</v>
+        <v>243826527.96</v>
       </c>
     </row>
     <row r="1396" spans="1:7" x14ac:dyDescent="0.25">
@@ -44787,17 +44787,17 @@
       <c r="C1397" s="6">
         <v>46279</v>
       </c>
-      <c r="D1397" s="8">
-        <v>0</v>
+      <c r="D1397" s="10">
+        <v>0.95142</v>
       </c>
       <c r="E1397" s="8">
-        <v>0</v>
+        <v>9682097247</v>
       </c>
       <c r="F1397" s="9">
         <v>14</v>
       </c>
       <c r="G1397" s="8">
-        <v>0</v>
+        <v>9211736423.48</v>
       </c>
     </row>
     <row r="1398" spans="1:7" x14ac:dyDescent="0.25">
@@ -44833,17 +44833,17 @@
       <c r="C1399" s="6">
         <v>46279</v>
       </c>
-      <c r="D1399" s="8">
-        <v>0</v>
+      <c r="D1399" s="7">
+        <v>0.436797</v>
       </c>
       <c r="E1399" s="8">
-        <v>0</v>
+        <v>525815645</v>
       </c>
       <c r="F1399" s="9">
         <v>11</v>
       </c>
       <c r="G1399" s="8">
-        <v>0</v>
+        <v>229674581.06</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.25">
@@ -44949,7 +44949,7 @@
         <v>46279</v>
       </c>
       <c r="D1404" s="7">
-        <v>2.425267</v>
+        <v>2.425979</v>
       </c>
       <c r="E1404" s="8">
         <v>32492167</v>
@@ -44958,7 +44958,7 @@
         <v>285</v>
       </c>
       <c r="G1404" s="8">
-        <v>78802179.71</v>
+        <v>78825318.54</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.25">
@@ -45040,17 +45040,17 @@
       <c r="C1408" s="6">
         <v>46279</v>
       </c>
-      <c r="D1408" s="8">
-        <v>0</v>
+      <c r="D1408" s="7">
+        <v>2.464451</v>
       </c>
       <c r="E1408" s="8">
-        <v>0</v>
+        <v>1328323644</v>
       </c>
       <c r="F1408" s="9">
         <v>12</v>
       </c>
       <c r="G1408" s="8">
-        <v>0</v>
+        <v>3273588348.39</v>
       </c>
     </row>
     <row r="1409" spans="1:7" x14ac:dyDescent="0.25">
@@ -45086,17 +45086,17 @@
       <c r="C1410" s="6">
         <v>46279</v>
       </c>
-      <c r="D1410" s="8">
-        <v>0</v>
+      <c r="D1410" s="7">
+        <v>1.077768</v>
       </c>
       <c r="E1410" s="8">
-        <v>0</v>
+        <v>5262810617</v>
       </c>
       <c r="F1410" s="9">
         <v>15</v>
       </c>
       <c r="G1410" s="8">
-        <v>0</v>
+        <v>5672086421.76</v>
       </c>
     </row>
     <row r="1411" spans="1:7" x14ac:dyDescent="0.25">
@@ -45109,17 +45109,17 @@
       <c r="C1411" s="6">
         <v>46279</v>
       </c>
-      <c r="D1411" s="8">
-        <v>0</v>
+      <c r="D1411" s="7">
+        <v>0.595014</v>
       </c>
       <c r="E1411" s="8">
-        <v>0</v>
+        <v>2804872883</v>
       </c>
       <c r="F1411" s="9">
         <v>51693</v>
       </c>
       <c r="G1411" s="8">
-        <v>0</v>
+        <v>1668939540.56</v>
       </c>
     </row>
     <row r="1412" spans="1:7" x14ac:dyDescent="0.25">
@@ -45201,17 +45201,17 @@
       <c r="C1415" s="6">
         <v>46279</v>
       </c>
-      <c r="D1415" s="8">
-        <v>0</v>
+      <c r="D1415" s="7">
+        <v>63.529678</v>
       </c>
       <c r="E1415" s="8">
-        <v>0</v>
+        <v>14064604</v>
       </c>
       <c r="F1415" s="9">
         <v>18</v>
       </c>
       <c r="G1415" s="8">
-        <v>0</v>
+        <v>893519761.59</v>
       </c>
     </row>
     <row r="1416" spans="1:7" x14ac:dyDescent="0.25">
@@ -45293,17 +45293,17 @@
       <c r="C1419" s="6">
         <v>46279</v>
       </c>
-      <c r="D1419" s="8">
-        <v>0</v>
+      <c r="D1419" s="7">
+        <v>3.913537</v>
       </c>
       <c r="E1419" s="8">
-        <v>0</v>
+        <v>109960272</v>
       </c>
       <c r="F1419" s="9">
         <v>7720</v>
       </c>
       <c r="G1419" s="8">
-        <v>0</v>
+        <v>430333635.69</v>
       </c>
     </row>
     <row r="1420" spans="1:7" x14ac:dyDescent="0.25">
@@ -45454,17 +45454,17 @@
       <c r="C1426" s="6">
         <v>46279</v>
       </c>
-      <c r="D1426" s="8">
-        <v>0</v>
+      <c r="D1426" s="7">
+        <v>0.945496</v>
       </c>
       <c r="E1426" s="8">
-        <v>0</v>
+        <v>7310581</v>
       </c>
       <c r="F1426" s="9">
         <v>104</v>
       </c>
       <c r="G1426" s="8">
-        <v>0</v>
+        <v>6912122.7</v>
       </c>
     </row>
     <row r="1427" spans="1:7" x14ac:dyDescent="0.25">
@@ -45523,17 +45523,17 @@
       <c r="C1429" s="6">
         <v>46279</v>
       </c>
-      <c r="D1429" s="8">
-        <v>0</v>
+      <c r="D1429" s="7">
+        <v>2.573749</v>
       </c>
       <c r="E1429" s="8">
-        <v>0</v>
+        <v>1552185490</v>
       </c>
       <c r="F1429" s="9">
         <v>14</v>
       </c>
       <c r="G1429" s="8">
-        <v>0</v>
+        <v>3994935189.33</v>
       </c>
     </row>
     <row r="1430" spans="1:7" x14ac:dyDescent="0.25">
@@ -45546,17 +45546,17 @@
       <c r="C1430" s="6">
         <v>46279</v>
       </c>
-      <c r="D1430" s="8">
-        <v>0</v>
+      <c r="D1430" s="10">
+        <v>1.09719</v>
       </c>
       <c r="E1430" s="8">
-        <v>0</v>
+        <v>377514662</v>
       </c>
       <c r="F1430" s="9">
         <v>508</v>
       </c>
       <c r="G1430" s="8">
-        <v>0</v>
+        <v>414205171.75</v>
       </c>
     </row>
     <row r="1431" spans="1:7" x14ac:dyDescent="0.25">
@@ -45707,17 +45707,17 @@
       <c r="C1437" s="6">
         <v>46279</v>
       </c>
-      <c r="D1437" s="8">
-        <v>0</v>
+      <c r="D1437" s="7">
+        <v>8.814468</v>
       </c>
       <c r="E1437" s="8">
-        <v>0</v>
+        <v>4258299761</v>
       </c>
       <c r="F1437" s="9">
         <v>16</v>
       </c>
       <c r="G1437" s="8">
-        <v>0</v>
+        <v>37534647528.59</v>
       </c>
     </row>
     <row r="1438" spans="1:7" x14ac:dyDescent="0.25">
@@ -45730,17 +45730,17 @@
       <c r="C1438" s="6">
         <v>46279</v>
       </c>
-      <c r="D1438" s="8">
-        <v>0</v>
+      <c r="D1438" s="7">
+        <v>1.293806</v>
       </c>
       <c r="E1438" s="8">
-        <v>0</v>
+        <v>545659</v>
       </c>
       <c r="F1438" s="9">
         <v>122</v>
       </c>
       <c r="G1438" s="8">
-        <v>0</v>
+        <v>705976.9</v>
       </c>
     </row>
     <row r="1439" spans="1:7" x14ac:dyDescent="0.25">
@@ -45868,17 +45868,17 @@
       <c r="C1444" s="6">
         <v>46279</v>
       </c>
-      <c r="D1444" s="8">
-        <v>0</v>
+      <c r="D1444" s="11">
+        <v>1.2797</v>
       </c>
       <c r="E1444" s="8">
-        <v>0</v>
+        <v>13469604237</v>
       </c>
       <c r="F1444" s="9">
         <v>20365</v>
       </c>
       <c r="G1444" s="8">
-        <v>0</v>
+        <v>17237048662.93</v>
       </c>
     </row>
     <row r="1445" spans="1:7" x14ac:dyDescent="0.25">
@@ -45914,17 +45914,17 @@
       <c r="C1446" s="6">
         <v>46279</v>
       </c>
-      <c r="D1446" s="8">
-        <v>0</v>
+      <c r="D1446" s="7">
+        <v>2.792591</v>
       </c>
       <c r="E1446" s="8">
-        <v>0</v>
+        <v>2947860</v>
       </c>
       <c r="F1446" s="9">
         <v>47</v>
       </c>
       <c r="G1446" s="8">
-        <v>0</v>
+        <v>8232165.97</v>
       </c>
     </row>
     <row r="1447" spans="1:7" x14ac:dyDescent="0.25">
@@ -46466,17 +46466,17 @@
       <c r="C1470" s="6">
         <v>46279</v>
       </c>
-      <c r="D1470" s="8">
-        <v>0</v>
+      <c r="D1470" s="7">
+        <v>3.370601</v>
       </c>
       <c r="E1470" s="8">
-        <v>0</v>
+        <v>791195694</v>
       </c>
       <c r="F1470" s="9">
         <v>3953</v>
       </c>
       <c r="G1470" s="8">
-        <v>0</v>
+        <v>2666805090.57</v>
       </c>
     </row>
     <row r="1471" spans="1:7" x14ac:dyDescent="0.25">
@@ -46696,17 +46696,17 @@
       <c r="C1480" s="6">
         <v>46279</v>
       </c>
-      <c r="D1480" s="8">
-        <v>0</v>
+      <c r="D1480" s="7">
+        <v>3.279813</v>
       </c>
       <c r="E1480" s="8">
-        <v>0</v>
+        <v>12876020137</v>
       </c>
       <c r="F1480" s="9">
         <v>39174</v>
       </c>
       <c r="G1480" s="8">
-        <v>0</v>
+        <v>42230936505.45</v>
       </c>
     </row>
     <row r="1481" spans="1:7" x14ac:dyDescent="0.25">
@@ -46742,17 +46742,17 @@
       <c r="C1482" s="6">
         <v>46279</v>
       </c>
-      <c r="D1482" s="8">
-        <v>0</v>
+      <c r="D1482" s="7">
+        <v>1.931446</v>
       </c>
       <c r="E1482" s="8">
-        <v>0</v>
+        <v>13142143770</v>
       </c>
       <c r="F1482" s="9">
         <v>5877</v>
       </c>
       <c r="G1482" s="8">
-        <v>0</v>
+        <v>25383346069.27</v>
       </c>
     </row>
     <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
@@ -47202,17 +47202,17 @@
       <c r="C1502" s="6">
         <v>46279</v>
       </c>
-      <c r="D1502" s="8">
-        <v>0</v>
+      <c r="D1502" s="10">
+        <v>1.65418</v>
       </c>
       <c r="E1502" s="8">
-        <v>0</v>
+        <v>132451627</v>
       </c>
       <c r="F1502" s="9">
         <v>5106</v>
       </c>
       <c r="G1502" s="8">
-        <v>0</v>
+        <v>219098862.21</v>
       </c>
     </row>
     <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
@@ -47340,17 +47340,17 @@
       <c r="C1508" s="6">
         <v>46279</v>
       </c>
-      <c r="D1508" s="8">
-        <v>0</v>
+      <c r="D1508" s="7">
+        <v>0.163558</v>
       </c>
       <c r="E1508" s="8">
-        <v>0</v>
+        <v>182529203</v>
       </c>
       <c r="F1508" s="9">
         <v>44</v>
       </c>
       <c r="G1508" s="8">
-        <v>0</v>
+        <v>29854155.02</v>
       </c>
     </row>
     <row r="1509" spans="1:7" x14ac:dyDescent="0.25">
@@ -47755,7 +47755,7 @@
         <v>46279</v>
       </c>
       <c r="D1526" s="7">
-        <v>8.933004</v>
+        <v>8.932063</v>
       </c>
       <c r="E1526" s="8">
         <v>4867612</v>
@@ -47764,7 +47764,7 @@
         <v>1134</v>
       </c>
       <c r="G1526" s="8">
-        <v>43482395.92</v>
+        <v>43477817.79</v>
       </c>
     </row>
     <row r="1527" spans="1:7" x14ac:dyDescent="0.25">
@@ -48076,8 +48076,8 @@
       <c r="C1540" s="6">
         <v>46279</v>
       </c>
-      <c r="D1540" s="10">
-        <v>22.70745</v>
+      <c r="D1540" s="7">
+        <v>22.700848</v>
       </c>
       <c r="E1540" s="8">
         <v>42798417</v>
@@ -48086,7 +48086,7 @@
         <v>11</v>
       </c>
       <c r="G1540" s="8">
-        <v>971842900.24</v>
+        <v>971560359.83</v>
       </c>
     </row>
     <row r="1541" spans="1:7" x14ac:dyDescent="0.25">
@@ -48329,17 +48329,17 @@
       <c r="C1551" s="6">
         <v>46279</v>
       </c>
-      <c r="D1551" s="8">
-        <v>0</v>
+      <c r="D1551" s="7">
+        <v>7.478353</v>
       </c>
       <c r="E1551" s="8">
-        <v>0</v>
+        <v>104500380</v>
       </c>
       <c r="F1551" s="9">
         <v>1452</v>
       </c>
       <c r="G1551" s="8">
-        <v>0</v>
+        <v>781490726.46</v>
       </c>
     </row>
     <row r="1552" spans="1:7" x14ac:dyDescent="0.25">
@@ -48675,7 +48675,7 @@
         <v>46279</v>
       </c>
       <c r="D1566" s="7">
-        <v>5.277708</v>
+        <v>5.275959</v>
       </c>
       <c r="E1566" s="8">
         <v>4599336</v>
@@ -48684,7 +48684,7 @@
         <v>565</v>
       </c>
       <c r="G1566" s="8">
-        <v>24273950.7</v>
+        <v>24265906.66</v>
       </c>
     </row>
     <row r="1567" spans="1:7" x14ac:dyDescent="0.25">
@@ -48743,17 +48743,17 @@
       <c r="C1569" s="6">
         <v>46279</v>
       </c>
-      <c r="D1569" s="8">
-        <v>0</v>
+      <c r="D1569" s="10">
+        <v>6.23939</v>
       </c>
       <c r="E1569" s="8">
-        <v>0</v>
+        <v>157081373</v>
       </c>
       <c r="F1569" s="9">
         <v>1665</v>
       </c>
       <c r="G1569" s="8">
-        <v>0</v>
+        <v>980091962.61</v>
       </c>
     </row>
     <row r="1570" spans="1:7" x14ac:dyDescent="0.25">
@@ -48813,7 +48813,7 @@
         <v>46279</v>
       </c>
       <c r="D1572" s="7">
-        <v>1.768402</v>
+        <v>1.768327</v>
       </c>
       <c r="E1572" s="8">
         <v>70047587</v>
@@ -48822,7 +48822,7 @@
         <v>15</v>
       </c>
       <c r="G1572" s="8">
-        <v>123872262.97</v>
+        <v>123867014.26</v>
       </c>
     </row>
     <row r="1573" spans="1:7" x14ac:dyDescent="0.25">
@@ -48836,7 +48836,7 @@
         <v>46279</v>
       </c>
       <c r="D1573" s="7">
-        <v>4.512173</v>
+        <v>4.511272</v>
       </c>
       <c r="E1573" s="8">
         <v>21420372</v>
@@ -48845,7 +48845,7 @@
         <v>3006</v>
       </c>
       <c r="G1573" s="8">
-        <v>96652416.41</v>
+        <v>96633130.11</v>
       </c>
     </row>
     <row r="1574" spans="1:7" x14ac:dyDescent="0.25">
@@ -48904,17 +48904,17 @@
       <c r="C1576" s="6">
         <v>46279</v>
       </c>
-      <c r="D1576" s="8">
-        <v>0</v>
+      <c r="D1576" s="7">
+        <v>5.086005</v>
       </c>
       <c r="E1576" s="8">
-        <v>0</v>
+        <v>1272396107</v>
       </c>
       <c r="F1576" s="9">
         <v>7561</v>
       </c>
       <c r="G1576" s="8">
-        <v>0</v>
+        <v>6471413596.95</v>
       </c>
     </row>
     <row r="1577" spans="1:7" x14ac:dyDescent="0.25">
@@ -48950,17 +48950,17 @@
       <c r="C1578" s="6">
         <v>46279</v>
       </c>
-      <c r="D1578" s="8">
-        <v>0</v>
+      <c r="D1578" s="7">
+        <v>5.267268</v>
       </c>
       <c r="E1578" s="8">
-        <v>0</v>
+        <v>233741731</v>
       </c>
       <c r="F1578" s="9">
         <v>166</v>
       </c>
       <c r="G1578" s="8">
-        <v>0</v>
+        <v>1231180398.79</v>
       </c>
     </row>
     <row r="1579" spans="1:7" x14ac:dyDescent="0.25">
@@ -48996,17 +48996,17 @@
       <c r="C1580" s="6">
         <v>46279</v>
       </c>
-      <c r="D1580" s="8">
-        <v>0</v>
+      <c r="D1580" s="7">
+        <v>63.883363</v>
       </c>
       <c r="E1580" s="8">
-        <v>0</v>
+        <v>9665783</v>
       </c>
       <c r="F1580" s="9">
         <v>122</v>
       </c>
       <c r="G1580" s="8">
-        <v>0</v>
+        <v>617482725.11</v>
       </c>
     </row>
     <row r="1581" spans="1:7" x14ac:dyDescent="0.25">
@@ -49019,17 +49019,17 @@
       <c r="C1581" s="6">
         <v>46279</v>
       </c>
-      <c r="D1581" s="8">
-        <v>0</v>
+      <c r="D1581" s="7">
+        <v>1.538286</v>
       </c>
       <c r="E1581" s="8">
-        <v>0</v>
+        <v>771102056</v>
       </c>
       <c r="F1581" s="9">
         <v>173</v>
       </c>
       <c r="G1581" s="8">
-        <v>0</v>
+        <v>1186175835.72</v>
       </c>
     </row>
     <row r="1582" spans="1:7" x14ac:dyDescent="0.25">
@@ -49065,17 +49065,17 @@
       <c r="C1583" s="6">
         <v>46279</v>
       </c>
-      <c r="D1583" s="8">
-        <v>0</v>
+      <c r="D1583" s="7">
+        <v>1.655488</v>
       </c>
       <c r="E1583" s="8">
-        <v>0</v>
+        <v>473291117</v>
       </c>
       <c r="F1583" s="9">
         <v>125</v>
       </c>
       <c r="G1583" s="8">
-        <v>0</v>
+        <v>783527735.52</v>
       </c>
     </row>
     <row r="1584" spans="1:7" x14ac:dyDescent="0.25">
@@ -49250,7 +49250,7 @@
         <v>46279</v>
       </c>
       <c r="D1591" s="7">
-        <v>5.832605</v>
+        <v>5.831249</v>
       </c>
       <c r="E1591" s="8">
         <v>41815120</v>
@@ -49259,7 +49259,7 @@
         <v>4724</v>
       </c>
       <c r="G1591" s="8">
-        <v>243891073.54</v>
+        <v>243834393.65</v>
       </c>
     </row>
     <row r="1592" spans="1:7" x14ac:dyDescent="0.25">
@@ -49433,17 +49433,17 @@
       <c r="C1599" s="6">
         <v>46279</v>
       </c>
-      <c r="D1599" s="8">
-        <v>0</v>
+      <c r="D1599" s="7">
+        <v>1.198813</v>
       </c>
       <c r="E1599" s="8">
-        <v>0</v>
+        <v>300623899</v>
       </c>
       <c r="F1599" s="9">
         <v>1</v>
       </c>
       <c r="G1599" s="8">
-        <v>0</v>
+        <v>360391766.22</v>
       </c>
     </row>
     <row r="1600" spans="1:7" x14ac:dyDescent="0.25">
@@ -49663,17 +49663,17 @@
       <c r="C1609" s="6">
         <v>46279</v>
       </c>
-      <c r="D1609" s="8">
-        <v>0</v>
+      <c r="D1609" s="7">
+        <v>1.795365</v>
       </c>
       <c r="E1609" s="8">
-        <v>0</v>
+        <v>190886564</v>
       </c>
       <c r="F1609" s="9">
         <v>605</v>
       </c>
       <c r="G1609" s="8">
-        <v>0</v>
+        <v>342711104.13</v>
       </c>
     </row>
     <row r="1610" spans="1:7" x14ac:dyDescent="0.25">
@@ -49778,17 +49778,17 @@
       <c r="C1614" s="6">
         <v>46279</v>
       </c>
-      <c r="D1614" s="8">
-        <v>0</v>
+      <c r="D1614" s="7">
+        <v>1.037674</v>
       </c>
       <c r="E1614" s="8">
-        <v>0</v>
+        <v>48027491</v>
       </c>
       <c r="F1614" s="9">
         <v>182</v>
       </c>
       <c r="G1614" s="8">
-        <v>0</v>
+        <v>49836896.76</v>
       </c>
     </row>
     <row r="1615" spans="1:7" x14ac:dyDescent="0.25">
@@ -49894,7 +49894,7 @@
         <v>46279</v>
       </c>
       <c r="D1619" s="7">
-        <v>1.429926</v>
+        <v>1.434496</v>
       </c>
       <c r="E1619" s="8">
         <v>22290746</v>
@@ -49903,7 +49903,7 @@
         <v>81</v>
       </c>
       <c r="G1619" s="8">
-        <v>31874111.94</v>
+        <v>31975978.35</v>
       </c>
     </row>
     <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
@@ -49939,17 +49939,17 @@
       <c r="C1621" s="6">
         <v>46279</v>
       </c>
-      <c r="D1621" s="8">
-        <v>0</v>
+      <c r="D1621" s="7">
+        <v>1.968323</v>
       </c>
       <c r="E1621" s="8">
-        <v>0</v>
+        <v>95597107</v>
       </c>
       <c r="F1621" s="9">
         <v>2690</v>
       </c>
       <c r="G1621" s="8">
-        <v>0</v>
+        <v>188166023.19</v>
       </c>
     </row>
     <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
@@ -49985,17 +49985,17 @@
       <c r="C1623" s="6">
         <v>46279</v>
       </c>
-      <c r="D1623" s="8">
-        <v>0</v>
+      <c r="D1623" s="7">
+        <v>3.605964</v>
       </c>
       <c r="E1623" s="8">
-        <v>0</v>
+        <v>15181913</v>
       </c>
       <c r="F1623" s="9">
         <v>631</v>
       </c>
       <c r="G1623" s="8">
-        <v>0</v>
+        <v>54745428.5</v>
       </c>
     </row>
     <row r="1624" spans="1:7" x14ac:dyDescent="0.25">
@@ -50031,17 +50031,17 @@
       <c r="C1625" s="6">
         <v>46279</v>
       </c>
-      <c r="D1625" s="8">
-        <v>0</v>
+      <c r="D1625" s="7">
+        <v>1.448968</v>
       </c>
       <c r="E1625" s="8">
-        <v>0</v>
+        <v>180771209</v>
       </c>
       <c r="F1625" s="9">
         <v>24</v>
       </c>
       <c r="G1625" s="8">
-        <v>0</v>
+        <v>261931702.02</v>
       </c>
     </row>
     <row r="1626" spans="1:7" x14ac:dyDescent="0.25">
@@ -50054,17 +50054,17 @@
       <c r="C1626" s="6">
         <v>46279</v>
       </c>
-      <c r="D1626" s="8">
-        <v>0</v>
+      <c r="D1626" s="7">
+        <v>0.894919</v>
       </c>
       <c r="E1626" s="8">
-        <v>0</v>
+        <v>1072723</v>
       </c>
       <c r="F1626" s="9">
         <v>5</v>
       </c>
       <c r="G1626" s="8">
-        <v>0</v>
+        <v>960000.57</v>
       </c>
     </row>
     <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
@@ -50077,17 +50077,17 @@
       <c r="C1627" s="6">
         <v>46279</v>
       </c>
-      <c r="D1627" s="8">
-        <v>0</v>
+      <c r="D1627" s="7">
+        <v>0.271909</v>
       </c>
       <c r="E1627" s="8">
-        <v>0</v>
+        <v>238794293</v>
       </c>
       <c r="F1627" s="9">
         <v>14</v>
       </c>
       <c r="G1627" s="8">
-        <v>0</v>
+        <v>64930252.03</v>
       </c>
     </row>
     <row r="1628" spans="1:7" x14ac:dyDescent="0.25">
@@ -50238,17 +50238,17 @@
       <c r="C1634" s="6">
         <v>46279</v>
       </c>
-      <c r="D1634" s="8">
-        <v>0</v>
+      <c r="D1634" s="7">
+        <v>11.586188</v>
       </c>
       <c r="E1634" s="8">
-        <v>0</v>
+        <v>138614870</v>
       </c>
       <c r="F1634" s="9">
         <v>6847</v>
       </c>
       <c r="G1634" s="8">
-        <v>0</v>
+        <v>1606017917.98</v>
       </c>
     </row>
     <row r="1635" spans="1:7" x14ac:dyDescent="0.25">
@@ -50376,17 +50376,17 @@
       <c r="C1640" s="6">
         <v>46279</v>
       </c>
-      <c r="D1640" s="8">
-        <v>0</v>
+      <c r="D1640" s="7">
+        <v>1.655675</v>
       </c>
       <c r="E1640" s="8">
-        <v>0</v>
+        <v>20871753</v>
       </c>
       <c r="F1640" s="9">
         <v>526</v>
       </c>
       <c r="G1640" s="8">
-        <v>0</v>
+        <v>34556838.58</v>
       </c>
     </row>
     <row r="1641" spans="1:7" x14ac:dyDescent="0.25">
@@ -50722,7 +50722,7 @@
         <v>46279</v>
       </c>
       <c r="D1655" s="7">
-        <v>1.757313</v>
+        <v>1.757134</v>
       </c>
       <c r="E1655" s="8">
         <v>27604338</v>
@@ -50731,7 +50731,7 @@
         <v>573</v>
       </c>
       <c r="G1655" s="8">
-        <v>48509470.28</v>
+        <v>48504510.93</v>
       </c>
     </row>
     <row r="1656" spans="1:7" x14ac:dyDescent="0.25">
@@ -50859,17 +50859,17 @@
       <c r="C1661" s="6">
         <v>46279</v>
       </c>
-      <c r="D1661" s="8">
-        <v>0</v>
+      <c r="D1661" s="7">
+        <v>1.455935</v>
       </c>
       <c r="E1661" s="8">
-        <v>0</v>
+        <v>11656773</v>
       </c>
       <c r="F1661" s="9">
         <v>136</v>
       </c>
       <c r="G1661" s="8">
-        <v>0</v>
+        <v>16971503.18</v>
       </c>
     </row>
     <row r="1662" spans="1:7" x14ac:dyDescent="0.25">
@@ -50952,7 +50952,7 @@
         <v>46279</v>
       </c>
       <c r="D1665" s="7">
-        <v>0.607161</v>
+        <v>0.606981</v>
       </c>
       <c r="E1665" s="8">
         <v>4159981554</v>
@@ -50961,7 +50961,7 @@
         <v>1176</v>
       </c>
       <c r="G1665" s="8">
-        <v>2525778295.54</v>
+        <v>2525029733.03</v>
       </c>
     </row>
     <row r="1666" spans="1:7" x14ac:dyDescent="0.25">
@@ -50998,7 +50998,7 @@
         <v>46279</v>
       </c>
       <c r="D1667" s="7">
-        <v>23.135519</v>
+        <v>23.100497</v>
       </c>
       <c r="E1667" s="8">
         <v>25753410</v>
@@ -51007,7 +51007,7 @@
         <v>516</v>
       </c>
       <c r="G1667" s="8">
-        <v>595818494.51</v>
+        <v>594916560.25</v>
       </c>
     </row>
     <row r="1668" spans="1:7" x14ac:dyDescent="0.25">
@@ -51250,17 +51250,17 @@
       <c r="C1678" s="6">
         <v>46279</v>
       </c>
-      <c r="D1678" s="8">
-        <v>0</v>
+      <c r="D1678" s="7">
+        <v>21.260738</v>
       </c>
       <c r="E1678" s="8">
-        <v>0</v>
+        <v>52856435</v>
       </c>
       <c r="F1678" s="9">
         <v>1</v>
       </c>
       <c r="G1678" s="8">
-        <v>0</v>
+        <v>1123766796.47</v>
       </c>
     </row>
     <row r="1679" spans="1:7" x14ac:dyDescent="0.25">
@@ -51342,17 +51342,17 @@
       <c r="C1682" s="6">
         <v>46279</v>
       </c>
-      <c r="D1682" s="8">
-        <v>0</v>
+      <c r="D1682" s="7">
+        <v>54.072281</v>
       </c>
       <c r="E1682" s="8">
-        <v>0</v>
+        <v>768351779</v>
       </c>
       <c r="F1682" s="9">
         <v>10628</v>
       </c>
       <c r="G1682" s="8">
-        <v>0</v>
+        <v>41546533376.23</v>
       </c>
     </row>
     <row r="1683" spans="1:7" x14ac:dyDescent="0.25">
@@ -51549,17 +51549,17 @@
       <c r="C1691" s="6">
         <v>46279</v>
       </c>
-      <c r="D1691" s="8">
-        <v>0</v>
+      <c r="D1691" s="7">
+        <v>1.333534</v>
       </c>
       <c r="E1691" s="8">
-        <v>0</v>
+        <v>141657132</v>
       </c>
       <c r="F1691" s="9">
         <v>1</v>
       </c>
       <c r="G1691" s="8">
-        <v>0</v>
+        <v>188904582.03</v>
       </c>
     </row>
     <row r="1692" spans="1:7" x14ac:dyDescent="0.25">
@@ -51664,17 +51664,17 @@
       <c r="C1696" s="6">
         <v>46279</v>
       </c>
-      <c r="D1696" s="8">
-        <v>0</v>
+      <c r="D1696" s="7">
+        <v>60.635551</v>
       </c>
       <c r="E1696" s="8">
-        <v>0</v>
+        <v>2355768</v>
       </c>
       <c r="F1696" s="9">
         <v>19</v>
       </c>
       <c r="G1696" s="8">
-        <v>0</v>
+        <v>142843290.67</v>
       </c>
     </row>
     <row r="1697" spans="1:7" x14ac:dyDescent="0.25">
@@ -51687,17 +51687,17 @@
       <c r="C1697" s="6">
         <v>46279</v>
       </c>
-      <c r="D1697" s="8">
-        <v>0</v>
+      <c r="D1697" s="7">
+        <v>42.076203</v>
       </c>
       <c r="E1697" s="8">
-        <v>0</v>
+        <v>27598727</v>
       </c>
       <c r="F1697" s="9">
         <v>2952</v>
       </c>
       <c r="G1697" s="8">
-        <v>0</v>
+        <v>1161249632.55</v>
       </c>
     </row>
     <row r="1698" spans="1:7" x14ac:dyDescent="0.25">
@@ -51710,17 +51710,17 @@
       <c r="C1698" s="6">
         <v>46279</v>
       </c>
-      <c r="D1698" s="8">
-        <v>0</v>
+      <c r="D1698" s="7">
+        <v>6.718037</v>
       </c>
       <c r="E1698" s="8">
-        <v>0</v>
+        <v>371021731</v>
       </c>
       <c r="F1698" s="9">
         <v>1519</v>
       </c>
       <c r="G1698" s="8">
-        <v>0</v>
+        <v>2492537677.22</v>
       </c>
     </row>
     <row r="1699" spans="1:7" x14ac:dyDescent="0.25">
@@ -51734,7 +51734,7 @@
         <v>46279</v>
       </c>
       <c r="D1699" s="7">
-        <v>2.784535</v>
+        <v>2.784446</v>
       </c>
       <c r="E1699" s="8">
         <v>259829445</v>
@@ -51743,7 +51743,7 @@
         <v>1311</v>
       </c>
       <c r="G1699" s="8">
-        <v>723504080.34</v>
+        <v>723481100.32</v>
       </c>
     </row>
     <row r="1700" spans="1:7" x14ac:dyDescent="0.25">
@@ -51779,17 +51779,17 @@
       <c r="C1701" s="6">
         <v>46279</v>
       </c>
-      <c r="D1701" s="8">
-        <v>0</v>
+      <c r="D1701" s="7">
+        <v>43.983548</v>
       </c>
       <c r="E1701" s="8">
-        <v>0</v>
+        <v>30686594</v>
       </c>
       <c r="F1701" s="9">
         <v>8995</v>
       </c>
       <c r="G1701" s="8">
-        <v>0</v>
+        <v>1349705292.99</v>
       </c>
     </row>
     <row r="1702" spans="1:7" x14ac:dyDescent="0.25">
@@ -52147,17 +52147,17 @@
       <c r="C1717" s="6">
         <v>46279</v>
       </c>
-      <c r="D1717" s="8">
-        <v>0</v>
+      <c r="D1717" s="7">
+        <v>47.668577</v>
       </c>
       <c r="E1717" s="8">
-        <v>0</v>
+        <v>45111410</v>
       </c>
       <c r="F1717" s="9">
         <v>16</v>
       </c>
       <c r="G1717" s="8">
-        <v>0</v>
+        <v>2150396722.07</v>
       </c>
     </row>
     <row r="1718" spans="1:7" x14ac:dyDescent="0.25">
@@ -52354,17 +52354,17 @@
       <c r="C1726" s="6">
         <v>46279</v>
       </c>
-      <c r="D1726" s="8">
-        <v>0</v>
+      <c r="D1726" s="7">
+        <v>50.685893</v>
       </c>
       <c r="E1726" s="8">
-        <v>0</v>
+        <v>17217749</v>
       </c>
       <c r="F1726" s="9">
         <v>85</v>
       </c>
       <c r="G1726" s="8">
-        <v>0</v>
+        <v>872696979.66</v>
       </c>
     </row>
     <row r="1727" spans="1:7" x14ac:dyDescent="0.25">
@@ -52492,17 +52492,17 @@
       <c r="C1732" s="6">
         <v>46279</v>
       </c>
-      <c r="D1732" s="8">
-        <v>0</v>
+      <c r="D1732" s="7">
+        <v>68.825419</v>
       </c>
       <c r="E1732" s="8">
-        <v>0</v>
+        <v>31992543</v>
       </c>
       <c r="F1732" s="9">
         <v>1827</v>
       </c>
       <c r="G1732" s="8">
-        <v>0</v>
+        <v>2201900170.5</v>
       </c>
     </row>
     <row r="1733" spans="1:7" x14ac:dyDescent="0.25">
@@ -52608,7 +52608,7 @@
         <v>46279</v>
       </c>
       <c r="D1737" s="7">
-        <v>1.081379</v>
+        <v>1.081446</v>
       </c>
       <c r="E1737" s="8">
         <v>640609274</v>
@@ -52617,7 +52617,7 @@
         <v>405</v>
       </c>
       <c r="G1737" s="8">
-        <v>692741168.44</v>
+        <v>692784282.51</v>
       </c>
     </row>
     <row r="1738" spans="1:7" x14ac:dyDescent="0.25">
@@ -52699,17 +52699,17 @@
       <c r="C1741" s="6">
         <v>46279</v>
       </c>
-      <c r="D1741" s="8">
-        <v>0</v>
+      <c r="D1741" s="7">
+        <v>71.935861</v>
       </c>
       <c r="E1741" s="8">
-        <v>0</v>
+        <v>5663669</v>
       </c>
       <c r="F1741" s="9">
         <v>1</v>
       </c>
       <c r="G1741" s="8">
-        <v>0</v>
+        <v>407420903.86</v>
       </c>
     </row>
     <row r="1742" spans="1:7" x14ac:dyDescent="0.25">
@@ -52722,17 +52722,17 @@
       <c r="C1742" s="6">
         <v>46279</v>
       </c>
-      <c r="D1742" s="8">
-        <v>0</v>
+      <c r="D1742" s="7">
+        <v>54.256043</v>
       </c>
       <c r="E1742" s="8">
-        <v>0</v>
+        <v>136039712</v>
       </c>
       <c r="F1742" s="9">
         <v>487</v>
       </c>
       <c r="G1742" s="8">
-        <v>0</v>
+        <v>7380976526.99</v>
       </c>
     </row>
     <row r="1743" spans="1:7" x14ac:dyDescent="0.25">
@@ -52906,17 +52906,17 @@
       <c r="C1750" s="6">
         <v>46279</v>
       </c>
-      <c r="D1750" s="8">
-        <v>0</v>
+      <c r="D1750" s="7">
+        <v>7.748697</v>
       </c>
       <c r="E1750" s="8">
-        <v>0</v>
+        <v>1187525000</v>
       </c>
       <c r="F1750" s="9">
         <v>1</v>
       </c>
       <c r="G1750" s="8">
-        <v>0</v>
+        <v>9201771636.05</v>
       </c>
     </row>
     <row r="1751" spans="1:7" x14ac:dyDescent="0.25">
@@ -52953,7 +52953,7 @@
         <v>46279</v>
       </c>
       <c r="D1752" s="7">
-        <v>1.454209</v>
+        <v>1.459321</v>
       </c>
       <c r="E1752" s="8">
         <v>39222039</v>
@@ -52962,7 +52962,7 @@
         <v>93</v>
       </c>
       <c r="G1752" s="8">
-        <v>57037030.4</v>
+        <v>57237540.99</v>
       </c>
     </row>
     <row r="1753" spans="1:7" x14ac:dyDescent="0.25">
@@ -53021,17 +53021,17 @@
       <c r="C1755" s="6">
         <v>46279</v>
       </c>
-      <c r="D1755" s="8">
-        <v>0</v>
+      <c r="D1755" s="7">
+        <v>50.535696</v>
       </c>
       <c r="E1755" s="8">
-        <v>0</v>
+        <v>13268799</v>
       </c>
       <c r="F1755" s="9">
         <v>80</v>
       </c>
       <c r="G1755" s="8">
-        <v>0</v>
+        <v>670547994.78</v>
       </c>
     </row>
     <row r="1756" spans="1:7" x14ac:dyDescent="0.25">
@@ -53067,17 +53067,17 @@
       <c r="C1757" s="6">
         <v>46279</v>
       </c>
-      <c r="D1757" s="8">
-        <v>0</v>
+      <c r="D1757" s="7">
+        <v>4.361543</v>
       </c>
       <c r="E1757" s="8">
-        <v>0</v>
+        <v>1216123947</v>
       </c>
       <c r="F1757" s="9">
         <v>3</v>
       </c>
       <c r="G1757" s="8">
-        <v>0</v>
+        <v>5304176893.22</v>
       </c>
     </row>
     <row r="1758" spans="1:7" x14ac:dyDescent="0.25">
@@ -53113,17 +53113,17 @@
       <c r="C1759" s="6">
         <v>46279</v>
       </c>
-      <c r="D1759" s="8">
-        <v>0</v>
+      <c r="D1759" s="7">
+        <v>11.643779</v>
       </c>
       <c r="E1759" s="8">
-        <v>0</v>
+        <v>763032608</v>
       </c>
       <c r="F1759" s="9">
         <v>3023</v>
       </c>
       <c r="G1759" s="8">
-        <v>0</v>
+        <v>8884583181.89</v>
       </c>
     </row>
     <row r="1760" spans="1:7" x14ac:dyDescent="0.25">
@@ -53182,17 +53182,17 @@
       <c r="C1762" s="6">
         <v>46279</v>
       </c>
-      <c r="D1762" s="8">
-        <v>0</v>
+      <c r="D1762" s="7">
+        <v>57.388308</v>
       </c>
       <c r="E1762" s="8">
-        <v>0</v>
+        <v>12799131</v>
       </c>
       <c r="F1762" s="9">
         <v>101</v>
       </c>
       <c r="G1762" s="8">
-        <v>0</v>
+        <v>734520471.4</v>
       </c>
     </row>
     <row r="1763" spans="1:7" x14ac:dyDescent="0.25">
@@ -53205,17 +53205,17 @@
       <c r="C1763" s="6">
         <v>46279</v>
       </c>
-      <c r="D1763" s="8">
-        <v>0</v>
+      <c r="D1763" s="7">
+        <v>59.881314</v>
       </c>
       <c r="E1763" s="8">
-        <v>0</v>
+        <v>405103931</v>
       </c>
       <c r="F1763" s="9">
         <v>6914</v>
       </c>
       <c r="G1763" s="8">
-        <v>0</v>
+        <v>24258155817.68</v>
       </c>
     </row>
     <row r="1764" spans="1:7" x14ac:dyDescent="0.25">
@@ -53251,17 +53251,17 @@
       <c r="C1765" s="6">
         <v>46279</v>
       </c>
-      <c r="D1765" s="8">
-        <v>0</v>
+      <c r="D1765" s="7">
+        <v>68.886027</v>
       </c>
       <c r="E1765" s="8">
-        <v>0</v>
+        <v>5611179</v>
       </c>
       <c r="F1765" s="9">
         <v>1</v>
       </c>
       <c r="G1765" s="8">
-        <v>0</v>
+        <v>386531827.8</v>
       </c>
     </row>
     <row r="1766" spans="1:7" x14ac:dyDescent="0.25">
@@ -53366,17 +53366,17 @@
       <c r="C1770" s="6">
         <v>46279</v>
       </c>
-      <c r="D1770" s="8">
-        <v>0</v>
+      <c r="D1770" s="7">
+        <v>79.506022</v>
       </c>
       <c r="E1770" s="8">
-        <v>0</v>
+        <v>30166787</v>
       </c>
       <c r="F1770" s="9">
         <v>1490</v>
       </c>
       <c r="G1770" s="8">
-        <v>0</v>
+        <v>2398441243.24</v>
       </c>
     </row>
     <row r="1771" spans="1:7" x14ac:dyDescent="0.25">
@@ -53389,17 +53389,17 @@
       <c r="C1771" s="6">
         <v>46279</v>
       </c>
-      <c r="D1771" s="8">
-        <v>0</v>
+      <c r="D1771" s="7">
+        <v>21.310439</v>
       </c>
       <c r="E1771" s="8">
-        <v>0</v>
+        <v>23469429.01</v>
       </c>
       <c r="F1771" s="9">
         <v>1527</v>
       </c>
       <c r="G1771" s="8">
-        <v>0</v>
+        <v>500143840.35</v>
       </c>
     </row>
     <row r="1772" spans="1:7" x14ac:dyDescent="0.25">
@@ -53435,17 +53435,17 @@
       <c r="C1773" s="6">
         <v>46279</v>
       </c>
-      <c r="D1773" s="8">
-        <v>0</v>
+      <c r="D1773" s="7">
+        <v>78.750273</v>
       </c>
       <c r="E1773" s="8">
-        <v>0</v>
+        <v>23960000</v>
       </c>
       <c r="F1773" s="9">
         <v>387</v>
       </c>
       <c r="G1773" s="8">
-        <v>0</v>
+        <v>1886856542.51</v>
       </c>
     </row>
     <row r="1774" spans="1:7" x14ac:dyDescent="0.25">
@@ -53504,17 +53504,17 @@
       <c r="C1776" s="6">
         <v>46279</v>
       </c>
-      <c r="D1776" s="8">
-        <v>0</v>
+      <c r="D1776" s="7">
+        <v>28.849357</v>
       </c>
       <c r="E1776" s="8">
-        <v>0</v>
+        <v>5390303</v>
       </c>
       <c r="F1776" s="9">
         <v>1504</v>
       </c>
       <c r="G1776" s="8">
-        <v>0</v>
+        <v>155506777.04</v>
       </c>
     </row>
     <row r="1777" spans="1:7" x14ac:dyDescent="0.25">
@@ -53757,17 +53757,17 @@
       <c r="C1787" s="6">
         <v>46279</v>
       </c>
-      <c r="D1787" s="8">
-        <v>0</v>
+      <c r="D1787" s="10">
+        <v>52.19267</v>
       </c>
       <c r="E1787" s="8">
-        <v>0</v>
+        <v>17213905</v>
       </c>
       <c r="F1787" s="9">
         <v>105</v>
       </c>
       <c r="G1787" s="8">
-        <v>0</v>
+        <v>898439668.11</v>
       </c>
     </row>
     <row r="1788" spans="1:7" x14ac:dyDescent="0.25">
@@ -53780,17 +53780,17 @@
       <c r="C1788" s="6">
         <v>46279</v>
       </c>
-      <c r="D1788" s="8">
-        <v>0</v>
+      <c r="D1788" s="7">
+        <v>71.092645</v>
       </c>
       <c r="E1788" s="8">
-        <v>0</v>
+        <v>31086506</v>
       </c>
       <c r="F1788" s="9">
         <v>1</v>
       </c>
       <c r="G1788" s="8">
-        <v>0</v>
+        <v>2210021942.74</v>
       </c>
     </row>
     <row r="1789" spans="1:7" x14ac:dyDescent="0.25">
@@ -53827,7 +53827,7 @@
         <v>46279</v>
       </c>
       <c r="D1790" s="7">
-        <v>3.809974</v>
+        <v>3.810034</v>
       </c>
       <c r="E1790" s="8">
         <v>64074841</v>
@@ -53836,7 +53836,7 @@
         <v>7</v>
       </c>
       <c r="G1790" s="8">
-        <v>244123485.85</v>
+        <v>244127320.84</v>
       </c>
     </row>
     <row r="1791" spans="1:7" x14ac:dyDescent="0.25">
@@ -53850,7 +53850,7 @@
         <v>46279</v>
       </c>
       <c r="D1791" s="7">
-        <v>1.463668</v>
+        <v>1.463674</v>
       </c>
       <c r="E1791" s="8">
         <v>10289851567.21</v>
@@ -53859,7 +53859,7 @@
         <v>31074</v>
       </c>
       <c r="G1791" s="8">
-        <v>15060923252.63</v>
+        <v>15060990642.68</v>
       </c>
     </row>
     <row r="1792" spans="1:7" x14ac:dyDescent="0.25">
@@ -53895,8 +53895,8 @@
       <c r="C1793" s="6">
         <v>46279</v>
       </c>
-      <c r="D1793" s="7">
-        <v>3.019866</v>
+      <c r="D1793" s="10">
+        <v>3.02397</v>
       </c>
       <c r="E1793" s="8">
         <v>4052228</v>
@@ -53905,7 +53905,7 @@
         <v>530</v>
       </c>
       <c r="G1793" s="8">
-        <v>12237187.26</v>
+        <v>12253815.85</v>
       </c>
     </row>
     <row r="1794" spans="1:7" x14ac:dyDescent="0.25">
@@ -54033,17 +54033,17 @@
       <c r="C1799" s="6">
         <v>46279</v>
       </c>
-      <c r="D1799" s="8">
-        <v>0</v>
+      <c r="D1799" s="7">
+        <v>14.587824</v>
       </c>
       <c r="E1799" s="8">
-        <v>0</v>
+        <v>78955112</v>
       </c>
       <c r="F1799" s="9">
         <v>14</v>
       </c>
       <c r="G1799" s="8">
-        <v>0</v>
+        <v>1151783256.21</v>
       </c>
     </row>
     <row r="1800" spans="1:7" x14ac:dyDescent="0.25">
@@ -54103,7 +54103,7 @@
         <v>46279</v>
       </c>
       <c r="D1802" s="7">
-        <v>5.471019</v>
+        <v>5.470706</v>
       </c>
       <c r="E1802" s="8">
         <v>118042548</v>
@@ -54112,7 +54112,7 @@
         <v>2</v>
       </c>
       <c r="G1802" s="8">
-        <v>645813075.98</v>
+        <v>645776047.84</v>
       </c>
     </row>
     <row r="1803" spans="1:7" x14ac:dyDescent="0.25">
@@ -54264,7 +54264,7 @@
         <v>46279</v>
       </c>
       <c r="D1809" s="7">
-        <v>6.679229</v>
+        <v>6.652912</v>
       </c>
       <c r="E1809" s="8">
         <v>193160614</v>
@@ -54273,7 +54273,7 @@
         <v>236</v>
       </c>
       <c r="G1809" s="8">
-        <v>1290164056.72</v>
+        <v>1285080574.17</v>
       </c>
     </row>
     <row r="1810" spans="1:7" x14ac:dyDescent="0.25">
@@ -54379,7 +54379,7 @@
         <v>46279</v>
       </c>
       <c r="D1814" s="7">
-        <v>22.255002</v>
+        <v>22.250795</v>
       </c>
       <c r="E1814" s="8">
         <v>110149985</v>
@@ -54388,7 +54388,7 @@
         <v>252</v>
       </c>
       <c r="G1814" s="8">
-        <v>2451388150.72</v>
+        <v>2450924745.6</v>
       </c>
     </row>
     <row r="1815" spans="1:7" x14ac:dyDescent="0.25">
@@ -54448,7 +54448,7 @@
         <v>46279</v>
       </c>
       <c r="D1817" s="7">
-        <v>5.036761</v>
+        <v>5.035903</v>
       </c>
       <c r="E1817" s="8">
         <v>211105000</v>
@@ -54457,7 +54457,7 @@
         <v>1</v>
       </c>
       <c r="G1817" s="8">
-        <v>1063285376.91</v>
+        <v>1063104294.47</v>
       </c>
     </row>
     <row r="1818" spans="1:7" x14ac:dyDescent="0.25">
@@ -54471,7 +54471,7 @@
         <v>46279</v>
       </c>
       <c r="D1818" s="7">
-        <v>1.921314</v>
+        <v>1.886783</v>
       </c>
       <c r="E1818" s="8">
         <v>328509863</v>
@@ -54480,7 +54480,7 @@
         <v>8869</v>
       </c>
       <c r="G1818" s="8">
-        <v>631170676.46</v>
+        <v>619826942.04</v>
       </c>
     </row>
     <row r="1819" spans="1:7" x14ac:dyDescent="0.25">
@@ -54517,7 +54517,7 @@
         <v>46279</v>
       </c>
       <c r="D1820" s="7">
-        <v>50.922156</v>
+        <v>50.920365</v>
       </c>
       <c r="E1820" s="8">
         <v>220705597</v>
@@ -54526,7 +54526,7 @@
         <v>14</v>
       </c>
       <c r="G1820" s="8">
-        <v>11238804898.32</v>
+        <v>11238409620.26</v>
       </c>
     </row>
     <row r="1821" spans="1:7" x14ac:dyDescent="0.25">
@@ -54586,7 +54586,7 @@
         <v>46279</v>
       </c>
       <c r="D1823" s="7">
-        <v>4.027486</v>
+        <v>4.027495</v>
       </c>
       <c r="E1823" s="8">
         <v>262089128</v>
@@ -54595,7 +54595,7 @@
         <v>1</v>
       </c>
       <c r="G1823" s="8">
-        <v>1055560250.49</v>
+        <v>1055562647.93</v>
       </c>
     </row>
     <row r="1824" spans="1:7" x14ac:dyDescent="0.25">
@@ -54678,7 +54678,7 @@
         <v>46279</v>
       </c>
       <c r="D1827" s="7">
-        <v>0.265251</v>
+        <v>0.265189</v>
       </c>
       <c r="E1827" s="8">
         <v>5152114150</v>
@@ -54687,7 +54687,7 @@
         <v>389</v>
       </c>
       <c r="G1827" s="8">
-        <v>1366602099.22</v>
+        <v>1366285972.4</v>
       </c>
     </row>
     <row r="1828" spans="1:7" x14ac:dyDescent="0.25">
@@ -54724,7 +54724,7 @@
         <v>46279</v>
       </c>
       <c r="D1829" s="7">
-        <v>9.434346</v>
+        <v>9.432948</v>
       </c>
       <c r="E1829" s="8">
         <v>35392468</v>
@@ -54733,7 +54733,7 @@
         <v>43</v>
       </c>
       <c r="G1829" s="8">
-        <v>333904805.84</v>
+        <v>333855327.93</v>
       </c>
     </row>
     <row r="1830" spans="1:7" x14ac:dyDescent="0.25">
@@ -54861,17 +54861,17 @@
       <c r="C1835" s="6">
         <v>46279</v>
       </c>
-      <c r="D1835" s="8">
-        <v>0</v>
+      <c r="D1835" s="7">
+        <v>1.007771</v>
       </c>
       <c r="E1835" s="8">
-        <v>0</v>
+        <v>412425812</v>
       </c>
       <c r="F1835" s="9">
         <v>8581</v>
       </c>
       <c r="G1835" s="8">
-        <v>0</v>
+        <v>415630634.81</v>
       </c>
     </row>
     <row r="1836" spans="1:7" x14ac:dyDescent="0.25">
@@ -54907,17 +54907,17 @@
       <c r="C1837" s="6">
         <v>46279</v>
       </c>
-      <c r="D1837" s="8">
-        <v>0</v>
+      <c r="D1837" s="10">
+        <v>1.01529</v>
       </c>
       <c r="E1837" s="8">
-        <v>0</v>
+        <v>16782449</v>
       </c>
       <c r="F1837" s="9">
         <v>660</v>
       </c>
       <c r="G1837" s="8">
-        <v>0</v>
+        <v>17039059.98</v>
       </c>
     </row>
     <row r="1838" spans="1:7" x14ac:dyDescent="0.25">
@@ -55114,17 +55114,17 @@
       <c r="C1846" s="6">
         <v>46279</v>
       </c>
-      <c r="D1846" s="8">
-        <v>0</v>
+      <c r="D1846" s="7">
+        <v>2.855744</v>
       </c>
       <c r="E1846" s="8">
-        <v>0</v>
+        <v>2579794157</v>
       </c>
       <c r="F1846" s="9">
         <v>141</v>
       </c>
       <c r="G1846" s="8">
-        <v>0</v>
+        <v>7367232195.68</v>
       </c>
     </row>
     <row r="1847" spans="1:7" x14ac:dyDescent="0.25">
@@ -55137,17 +55137,17 @@
       <c r="C1847" s="6">
         <v>46279</v>
       </c>
-      <c r="D1847" s="8">
-        <v>0</v>
+      <c r="D1847" s="7">
+        <v>2.456866</v>
       </c>
       <c r="E1847" s="8">
-        <v>0</v>
+        <v>1547563800</v>
       </c>
       <c r="F1847" s="9">
         <v>225</v>
       </c>
       <c r="G1847" s="8">
-        <v>0</v>
+        <v>3802157058.29</v>
       </c>
     </row>
     <row r="1848" spans="1:7" x14ac:dyDescent="0.25">
@@ -55183,17 +55183,17 @@
       <c r="C1849" s="6">
         <v>46279</v>
       </c>
-      <c r="D1849" s="8">
-        <v>0</v>
+      <c r="D1849" s="7">
+        <v>1.006519</v>
       </c>
       <c r="E1849" s="8">
-        <v>0</v>
+        <v>8460350</v>
       </c>
       <c r="F1849" s="9">
         <v>155</v>
       </c>
       <c r="G1849" s="8">
-        <v>0</v>
+        <v>8515503.05</v>
       </c>
     </row>
     <row r="1850" spans="1:7" x14ac:dyDescent="0.25">
@@ -55206,17 +55206,17 @@
       <c r="C1850" s="6">
         <v>46279</v>
       </c>
-      <c r="D1850" s="8">
-        <v>0</v>
+      <c r="D1850" s="7">
+        <v>1.006126</v>
       </c>
       <c r="E1850" s="8">
-        <v>0</v>
+        <v>7685398</v>
       </c>
       <c r="F1850" s="9">
         <v>129</v>
       </c>
       <c r="G1850" s="8">
-        <v>0</v>
+        <v>7732479</v>
       </c>
     </row>
     <row r="1851" spans="1:7" x14ac:dyDescent="0.25">
@@ -55229,17 +55229,17 @@
       <c r="C1851" s="6">
         <v>46279</v>
       </c>
-      <c r="D1851" s="8">
-        <v>0</v>
+      <c r="D1851" s="7">
+        <v>1.038576</v>
       </c>
       <c r="E1851" s="8">
-        <v>0</v>
+        <v>34334855</v>
       </c>
       <c r="F1851" s="9">
         <v>681</v>
       </c>
       <c r="G1851" s="8">
-        <v>0</v>
+        <v>35659370.35</v>
       </c>
     </row>
     <row r="1852" spans="1:7" x14ac:dyDescent="0.25">
@@ -55252,17 +55252,17 @@
       <c r="C1852" s="6">
         <v>46279</v>
       </c>
-      <c r="D1852" s="8">
-        <v>0</v>
+      <c r="D1852" s="7">
+        <v>54.896335</v>
       </c>
       <c r="E1852" s="8">
-        <v>0</v>
+        <v>27904271</v>
       </c>
       <c r="F1852" s="9">
         <v>571</v>
       </c>
       <c r="G1852" s="8">
-        <v>0</v>
+        <v>1531842202.26</v>
       </c>
     </row>
     <row r="1853" spans="1:7" x14ac:dyDescent="0.25">
@@ -55275,17 +55275,17 @@
       <c r="C1853" s="6">
         <v>46279</v>
       </c>
-      <c r="D1853" s="8">
-        <v>0</v>
+      <c r="D1853" s="7">
+        <v>0.850104</v>
       </c>
       <c r="E1853" s="8">
-        <v>0</v>
+        <v>1119944015</v>
       </c>
       <c r="F1853" s="9">
         <v>5344</v>
       </c>
       <c r="G1853" s="8">
-        <v>0</v>
+        <v>952068600.92</v>
       </c>
     </row>
     <row r="1854" spans="1:7" x14ac:dyDescent="0.25">
@@ -55390,17 +55390,17 @@
       <c r="C1858" s="6">
         <v>46279</v>
       </c>
-      <c r="D1858" s="8">
-        <v>0</v>
+      <c r="D1858" s="7">
+        <v>14.957397</v>
       </c>
       <c r="E1858" s="8">
-        <v>0</v>
+        <v>367076691</v>
       </c>
       <c r="F1858" s="9">
         <v>9781</v>
       </c>
       <c r="G1858" s="8">
-        <v>0</v>
+        <v>5490511834.35</v>
       </c>
     </row>
     <row r="1859" spans="1:7" x14ac:dyDescent="0.25">
@@ -55459,17 +55459,17 @@
       <c r="C1861" s="6">
         <v>46279</v>
       </c>
-      <c r="D1861" s="8">
-        <v>0</v>
+      <c r="D1861" s="7">
+        <v>14.883567</v>
       </c>
       <c r="E1861" s="8">
-        <v>0</v>
+        <v>126809017</v>
       </c>
       <c r="F1861" s="9">
         <v>3603</v>
       </c>
       <c r="G1861" s="8">
-        <v>0</v>
+        <v>1887370497.42</v>
       </c>
     </row>
     <row r="1862" spans="1:7" x14ac:dyDescent="0.25">
@@ -55712,17 +55712,17 @@
       <c r="C1872" s="6">
         <v>46279</v>
       </c>
-      <c r="D1872" s="8">
-        <v>0</v>
+      <c r="D1872" s="7">
+        <v>2.745809</v>
       </c>
       <c r="E1872" s="8">
-        <v>0</v>
+        <v>39643052</v>
       </c>
       <c r="F1872" s="9">
         <v>113</v>
       </c>
       <c r="G1872" s="8">
-        <v>0</v>
+        <v>108852259.26</v>
       </c>
     </row>
     <row r="1873" spans="1:7" x14ac:dyDescent="0.25">
@@ -56287,17 +56287,17 @@
       <c r="C1897" s="6">
         <v>46279</v>
       </c>
-      <c r="D1897" s="8">
-        <v>0</v>
+      <c r="D1897" s="7">
+        <v>2.696477</v>
       </c>
       <c r="E1897" s="8">
-        <v>0</v>
+        <v>799929846</v>
       </c>
       <c r="F1897" s="9">
         <v>15907</v>
       </c>
       <c r="G1897" s="8">
-        <v>0</v>
+        <v>2156992560.61</v>
       </c>
     </row>
     <row r="1898" spans="1:7" x14ac:dyDescent="0.25">
@@ -56379,17 +56379,17 @@
       <c r="C1901" s="6">
         <v>46279</v>
       </c>
-      <c r="D1901" s="8">
-        <v>0</v>
+      <c r="D1901" s="7">
+        <v>5.729753</v>
       </c>
       <c r="E1901" s="8">
-        <v>0</v>
+        <v>177836251</v>
       </c>
       <c r="F1901" s="9">
         <v>13989</v>
       </c>
       <c r="G1901" s="8">
-        <v>0</v>
+        <v>1018957772.58</v>
       </c>
     </row>
     <row r="1902" spans="1:7" x14ac:dyDescent="0.25">
@@ -56517,8 +56517,8 @@
       <c r="C1907" s="6">
         <v>46279</v>
       </c>
-      <c r="D1907" s="7">
-        <v>4.011021</v>
+      <c r="D1907" s="10">
+        <v>4.00471</v>
       </c>
       <c r="E1907" s="8">
         <v>19673207</v>
@@ -56527,7 +56527,7 @@
         <v>1355</v>
       </c>
       <c r="G1907" s="8">
-        <v>78909649.3</v>
+        <v>78785479.21</v>
       </c>
     </row>
     <row r="1908" spans="1:7" x14ac:dyDescent="0.25">
@@ -57207,17 +57207,17 @@
       <c r="C1937" s="6">
         <v>46279</v>
       </c>
-      <c r="D1937" s="8">
-        <v>0</v>
+      <c r="D1937" s="7">
+        <v>8.061244</v>
       </c>
       <c r="E1937" s="8">
-        <v>0</v>
+        <v>689992066</v>
       </c>
       <c r="F1937" s="9">
         <v>3339</v>
       </c>
       <c r="G1937" s="8">
-        <v>0</v>
+        <v>5562194154.75</v>
       </c>
     </row>
     <row r="1938" spans="1:7" x14ac:dyDescent="0.25">
@@ -57368,17 +57368,17 @@
       <c r="C1944" s="6">
         <v>46279</v>
       </c>
-      <c r="D1944" s="8">
-        <v>0</v>
+      <c r="D1944" s="7">
+        <v>0.973715</v>
       </c>
       <c r="E1944" s="8">
-        <v>0</v>
+        <v>1841392039</v>
       </c>
       <c r="F1944" s="9">
         <v>14965</v>
       </c>
       <c r="G1944" s="8">
-        <v>0</v>
+        <v>1792990372.04</v>
       </c>
     </row>
     <row r="1945" spans="1:7" x14ac:dyDescent="0.25">
@@ -57828,17 +57828,17 @@
       <c r="C1964" s="6">
         <v>46279</v>
       </c>
-      <c r="D1964" s="8">
-        <v>0</v>
+      <c r="D1964" s="7">
+        <v>13.120693</v>
       </c>
       <c r="E1964" s="8">
-        <v>0</v>
+        <v>812736846</v>
       </c>
       <c r="F1964" s="9">
         <v>59582</v>
       </c>
       <c r="G1964" s="8">
-        <v>0</v>
+        <v>10663670375.1</v>
       </c>
     </row>
     <row r="1965" spans="1:7" x14ac:dyDescent="0.25">
@@ -57943,17 +57943,17 @@
       <c r="C1969" s="6">
         <v>46279</v>
       </c>
-      <c r="D1969" s="8">
-        <v>0</v>
+      <c r="D1969" s="7">
+        <v>2.106633</v>
       </c>
       <c r="E1969" s="8">
-        <v>0</v>
+        <v>1874064246</v>
       </c>
       <c r="F1969" s="9">
         <v>526</v>
       </c>
       <c r="G1969" s="8">
-        <v>0</v>
+        <v>3947965502.69</v>
       </c>
     </row>
     <row r="1970" spans="1:7" x14ac:dyDescent="0.25">
@@ -57966,17 +57966,17 @@
       <c r="C1970" s="6">
         <v>46279</v>
       </c>
-      <c r="D1970" s="8">
-        <v>0</v>
+      <c r="D1970" s="7">
+        <v>46.793477</v>
       </c>
       <c r="E1970" s="8">
-        <v>0</v>
+        <v>296277</v>
       </c>
       <c r="F1970" s="9">
         <v>51</v>
       </c>
       <c r="G1970" s="8">
-        <v>0</v>
+        <v>13863830.99</v>
       </c>
     </row>
     <row r="1971" spans="1:7" x14ac:dyDescent="0.25">
@@ -58012,17 +58012,17 @@
       <c r="C1972" s="6">
         <v>46279</v>
       </c>
-      <c r="D1972" s="8">
-        <v>0</v>
+      <c r="D1972" s="7">
+        <v>6.547088</v>
       </c>
       <c r="E1972" s="8">
-        <v>0</v>
+        <v>174428236</v>
       </c>
       <c r="F1972" s="9">
         <v>3270</v>
       </c>
       <c r="G1972" s="8">
-        <v>0</v>
+        <v>1141997010.62</v>
       </c>
     </row>
     <row r="1973" spans="1:7" x14ac:dyDescent="0.25">
@@ -58357,8 +58357,8 @@
       <c r="C1987" s="6">
         <v>46279</v>
       </c>
-      <c r="D1987" s="10">
-        <v>4.14867</v>
+      <c r="D1987" s="7">
+        <v>4.134442</v>
       </c>
       <c r="E1987" s="8">
         <v>148263900</v>
@@ -58367,7 +58367,7 @@
         <v>6465</v>
       </c>
       <c r="G1987" s="8">
-        <v>615097923.96</v>
+        <v>612988442.25</v>
       </c>
     </row>
     <row r="1988" spans="1:7" x14ac:dyDescent="0.25">
@@ -58702,17 +58702,17 @@
       <c r="C2002" s="6">
         <v>46279</v>
       </c>
-      <c r="D2002" s="8">
-        <v>0</v>
+      <c r="D2002" s="7">
+        <v>51.102933</v>
       </c>
       <c r="E2002" s="8">
-        <v>0</v>
+        <v>9657151</v>
       </c>
       <c r="F2002" s="9">
         <v>46</v>
       </c>
       <c r="G2002" s="8">
-        <v>0</v>
+        <v>493508743.82</v>
       </c>
     </row>
     <row r="2003" spans="1:7" x14ac:dyDescent="0.25">
@@ -58841,7 +58841,7 @@
         <v>46279</v>
       </c>
       <c r="D2008" s="7">
-        <v>1.902646</v>
+        <v>1.901704</v>
       </c>
       <c r="E2008" s="8">
         <v>306521428</v>
@@ -58850,7 +58850,7 @@
         <v>11</v>
       </c>
       <c r="G2008" s="8">
-        <v>583201675.04</v>
+        <v>582912929.77</v>
       </c>
     </row>
     <row r="2009" spans="1:7" x14ac:dyDescent="0.25">
@@ -58887,7 +58887,7 @@
         <v>46279</v>
       </c>
       <c r="D2010" s="7">
-        <v>5.899496</v>
+        <v>5.896391</v>
       </c>
       <c r="E2010" s="8">
         <v>106786382</v>
@@ -58896,7 +58896,7 @@
         <v>1</v>
       </c>
       <c r="G2010" s="8">
-        <v>629985884.05</v>
+        <v>629654270.96</v>
       </c>
     </row>
     <row r="2011" spans="1:7" x14ac:dyDescent="0.25">
@@ -59047,8 +59047,8 @@
       <c r="C2017" s="6">
         <v>46279</v>
       </c>
-      <c r="D2017" s="7">
-        <v>20.066862</v>
+      <c r="D2017" s="10">
+        <v>20.06701</v>
       </c>
       <c r="E2017" s="8">
         <v>164961199</v>
@@ -59057,7 +59057,7 @@
         <v>2805</v>
       </c>
       <c r="G2017" s="8">
-        <v>3310253661.95</v>
+        <v>3310277959.19</v>
       </c>
     </row>
     <row r="2018" spans="1:7" x14ac:dyDescent="0.25">
@@ -59324,7 +59324,7 @@
         <v>46279</v>
       </c>
       <c r="D2029" s="7">
-        <v>12.556178</v>
+        <v>12.553517</v>
       </c>
       <c r="E2029" s="8">
         <v>216588410</v>
@@ -59333,7 +59333,7 @@
         <v>25</v>
       </c>
       <c r="G2029" s="8">
-        <v>2719522641.78</v>
+        <v>2718946277.88</v>
       </c>
     </row>
     <row r="2030" spans="1:7" x14ac:dyDescent="0.25">
@@ -59370,7 +59370,7 @@
         <v>46279</v>
       </c>
       <c r="D2031" s="7">
-        <v>4.425745</v>
+        <v>4.430587</v>
       </c>
       <c r="E2031" s="8">
         <v>11572300</v>
@@ -59379,7 +59379,7 @@
         <v>908</v>
       </c>
       <c r="G2031" s="8">
-        <v>51216049.44</v>
+        <v>51272079.25</v>
       </c>
     </row>
     <row r="2032" spans="1:7" x14ac:dyDescent="0.25">
@@ -59416,7 +59416,7 @@
         <v>46279</v>
       </c>
       <c r="D2033" s="7">
-        <v>7.732461</v>
+        <v>7.735035</v>
       </c>
       <c r="E2033" s="8">
         <v>274862095</v>
@@ -59425,7 +59425,7 @@
         <v>1</v>
       </c>
       <c r="G2033" s="8">
-        <v>2125360530.92</v>
+        <v>2126067888.25</v>
       </c>
     </row>
     <row r="2034" spans="1:7" x14ac:dyDescent="0.25">
@@ -59439,7 +59439,7 @@
         <v>46279</v>
       </c>
       <c r="D2034" s="7">
-        <v>1.375355</v>
+        <v>1.369293</v>
       </c>
       <c r="E2034" s="8">
         <v>34061587</v>
@@ -59448,7 +59448,7 @@
         <v>1136</v>
       </c>
       <c r="G2034" s="8">
-        <v>46846766.81</v>
+        <v>46640276.46</v>
       </c>
     </row>
     <row r="2035" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>17.09.2026 10:05:46</t>
+    <t>17.09.2026 10:21:11</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -13140,7 +13140,7 @@
         <v>46282</v>
       </c>
       <c r="D21" s="7">
-        <v>5.900515</v>
+        <v>5.900514</v>
       </c>
       <c r="E21" s="8">
         <v>57504795.77</v>
@@ -13149,7 +13149,7 @@
         <v>1487</v>
       </c>
       <c r="G21" s="8">
-        <v>339307888.11</v>
+        <v>339307869.36</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -16484,7 +16484,7 @@
         <v>15</v>
       </c>
       <c r="G166" s="8">
-        <v>3969896549.86</v>
+        <v>3969896486.39</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -19004,17 +19004,17 @@
       <c r="C276" s="6">
         <v>46282</v>
       </c>
-      <c r="D276" s="8">
-        <v>0</v>
+      <c r="D276" s="7">
+        <v>6.085683</v>
       </c>
       <c r="E276" s="8">
-        <v>0</v>
+        <v>4694438254</v>
       </c>
       <c r="F276" s="9">
         <v>47595</v>
       </c>
       <c r="G276" s="8">
-        <v>0</v>
+        <v>28568862830.56</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -19487,8 +19487,8 @@
       <c r="C297" s="6">
         <v>46282</v>
       </c>
-      <c r="D297" s="7">
-        <v>48.855597</v>
+      <c r="D297" s="10">
+        <v>48.74303</v>
       </c>
       <c r="E297" s="8">
         <v>86130000</v>
@@ -19497,7 +19497,7 @@
         <v>628</v>
       </c>
       <c r="G297" s="8">
-        <v>4207932529.41</v>
+        <v>4198237138.75</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -19856,7 +19856,7 @@
         <v>46282</v>
       </c>
       <c r="D313" s="7">
-        <v>1.590209</v>
+        <v>1.590212</v>
       </c>
       <c r="E313" s="8">
         <v>378647601</v>
@@ -19865,7 +19865,7 @@
         <v>127</v>
       </c>
       <c r="G313" s="8">
-        <v>602128937.12</v>
+        <v>602130003.1</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -22708,7 +22708,7 @@
         <v>46282</v>
       </c>
       <c r="D437" s="7">
-        <v>48.767745</v>
+        <v>48.616298</v>
       </c>
       <c r="E437" s="8">
         <v>91240000</v>
@@ -22717,7 +22717,7 @@
         <v>879</v>
       </c>
       <c r="G437" s="8">
-        <v>4449569027.21</v>
+        <v>4435751008.82</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
@@ -22915,7 +22915,7 @@
         <v>46282</v>
       </c>
       <c r="D446" s="7">
-        <v>7.794823</v>
+        <v>7.732235</v>
       </c>
       <c r="E446" s="8">
         <v>253410939</v>
@@ -22924,7 +22924,7 @@
         <v>2384</v>
       </c>
       <c r="G446" s="8">
-        <v>1975293430.61</v>
+        <v>1959432808.74</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
@@ -23283,7 +23283,7 @@
         <v>46282</v>
       </c>
       <c r="D462" s="7">
-        <v>48.850779</v>
+        <v>48.674606</v>
       </c>
       <c r="E462" s="8">
         <v>47840000.01</v>
@@ -23292,7 +23292,7 @@
         <v>474</v>
       </c>
       <c r="G462" s="8">
-        <v>2337021263.24</v>
+        <v>2328593142.58</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
@@ -23651,7 +23651,7 @@
         <v>46282</v>
       </c>
       <c r="D478" s="7">
-        <v>70.341642</v>
+        <v>70.331181</v>
       </c>
       <c r="E478" s="8">
         <v>1940857862</v>
@@ -23660,7 +23660,7 @@
         <v>19510</v>
       </c>
       <c r="G478" s="8">
-        <v>136523129638.67</v>
+        <v>136502824799.33</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
@@ -24088,7 +24088,7 @@
         <v>46282</v>
       </c>
       <c r="D497" s="7">
-        <v>56.278725</v>
+        <v>56.149054</v>
       </c>
       <c r="E497" s="8">
         <v>183610000.01</v>
@@ -24097,7 +24097,7 @@
         <v>1650</v>
       </c>
       <c r="G497" s="8">
-        <v>10333336769.23</v>
+        <v>10309527716.11</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
@@ -24157,7 +24157,7 @@
         <v>46282</v>
       </c>
       <c r="D500" s="7">
-        <v>48.744074</v>
+        <v>48.587817</v>
       </c>
       <c r="E500" s="8">
         <v>165470000</v>
@@ -24166,7 +24166,7 @@
         <v>1239</v>
       </c>
       <c r="G500" s="8">
-        <v>8065681947.16</v>
+        <v>8039825998.62</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
@@ -24318,7 +24318,7 @@
         <v>46282</v>
       </c>
       <c r="D507" s="7">
-        <v>0.054809</v>
+        <v>0.054808</v>
       </c>
       <c r="E507" s="8">
         <v>24880006007.69</v>
@@ -24327,7 +24327,7 @@
         <v>142</v>
       </c>
       <c r="G507" s="8">
-        <v>1363638942.44</v>
+        <v>1363635242.26</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
@@ -26135,7 +26135,7 @@
         <v>46282</v>
       </c>
       <c r="D586" s="7">
-        <v>1425.995191</v>
+        <v>1425.996242</v>
       </c>
       <c r="E586" s="8">
         <v>1060036</v>
@@ -26144,7 +26144,7 @@
         <v>985</v>
       </c>
       <c r="G586" s="8">
-        <v>1511606238.44</v>
+        <v>1511607352.36</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
@@ -28871,17 +28871,17 @@
       <c r="C705" s="6">
         <v>46282</v>
       </c>
-      <c r="D705" s="8">
-        <v>0</v>
+      <c r="D705" s="10">
+        <v>4.34279</v>
       </c>
       <c r="E705" s="8">
-        <v>0</v>
+        <v>121799199</v>
       </c>
       <c r="F705" s="9">
         <v>1057</v>
       </c>
       <c r="G705" s="8">
-        <v>0</v>
+        <v>528948301.7</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.25">
@@ -29723,7 +29723,7 @@
         <v>46282</v>
       </c>
       <c r="D742" s="7">
-        <v>1.459103</v>
+        <v>1.462375</v>
       </c>
       <c r="E742" s="8">
         <v>27506142</v>
@@ -29732,7 +29732,7 @@
         <v>1161</v>
       </c>
       <c r="G742" s="8">
-        <v>40134295.63</v>
+        <v>40224289.54</v>
       </c>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.25">
@@ -30182,8 +30182,8 @@
       <c r="C762" s="6">
         <v>46282</v>
       </c>
-      <c r="D762" s="10">
-        <v>0.36663</v>
+      <c r="D762" s="7">
+        <v>0.366618</v>
       </c>
       <c r="E762" s="8">
         <v>3633329777</v>
@@ -30192,7 +30192,7 @@
         <v>2528</v>
       </c>
       <c r="G762" s="8">
-        <v>1332087366.51</v>
+        <v>1332043150.36</v>
       </c>
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.25">
@@ -30643,7 +30643,7 @@
         <v>46282</v>
       </c>
       <c r="D782" s="7">
-        <v>0.990159</v>
+        <v>0.986528</v>
       </c>
       <c r="E782" s="8">
         <v>98746276</v>
@@ -30652,7 +30652,7 @@
         <v>797</v>
       </c>
       <c r="G782" s="8">
-        <v>97774561.95</v>
+        <v>97415934.96</v>
       </c>
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.25">
@@ -31195,7 +31195,7 @@
         <v>46282</v>
       </c>
       <c r="D806" s="7">
-        <v>2.070015</v>
+        <v>2.070008</v>
       </c>
       <c r="E806" s="8">
         <v>126701562</v>
@@ -31204,7 +31204,7 @@
         <v>445</v>
       </c>
       <c r="G806" s="8">
-        <v>262274171.99</v>
+        <v>262273246.77</v>
       </c>
     </row>
     <row r="807" spans="1:7" x14ac:dyDescent="0.25">
@@ -31907,17 +31907,17 @@
       <c r="C837" s="6">
         <v>46282</v>
       </c>
-      <c r="D837" s="8">
-        <v>0</v>
+      <c r="D837" s="10">
+        <v>78.15591</v>
       </c>
       <c r="E837" s="8">
-        <v>0</v>
+        <v>164153273</v>
       </c>
       <c r="F837" s="9">
         <v>4305</v>
       </c>
       <c r="G837" s="8">
-        <v>0</v>
+        <v>12829548385.24</v>
       </c>
     </row>
     <row r="838" spans="1:7" x14ac:dyDescent="0.25">
@@ -32460,7 +32460,7 @@
         <v>46282</v>
       </c>
       <c r="D861" s="7">
-        <v>1.603873</v>
+        <v>1.603846</v>
       </c>
       <c r="E861" s="8">
         <v>38641205</v>
@@ -32469,7 +32469,7 @@
         <v>246</v>
       </c>
       <c r="G861" s="8">
-        <v>61975604.21</v>
+        <v>61974555.49</v>
       </c>
     </row>
     <row r="862" spans="1:7" x14ac:dyDescent="0.25">
@@ -32584,7 +32584,7 @@
         <v>11</v>
       </c>
       <c r="G866" s="8">
-        <v>1395363005.66</v>
+        <v>1395362893.8</v>
       </c>
     </row>
     <row r="867" spans="1:7" x14ac:dyDescent="0.25">
@@ -32874,7 +32874,7 @@
         <v>46282</v>
       </c>
       <c r="D879" s="10">
-        <v>9.59976</v>
+        <v>9.59972</v>
       </c>
       <c r="E879" s="8">
         <v>20335938</v>
@@ -32883,7 +32883,7 @@
         <v>258</v>
       </c>
       <c r="G879" s="8">
-        <v>195220124.22</v>
+        <v>195219303.24</v>
       </c>
     </row>
     <row r="880" spans="1:7" x14ac:dyDescent="0.25">
@@ -32988,8 +32988,8 @@
       <c r="C884" s="6">
         <v>46282</v>
       </c>
-      <c r="D884" s="10">
-        <v>5.79564</v>
+      <c r="D884" s="7">
+        <v>5.795675</v>
       </c>
       <c r="E884" s="8">
         <v>612152094</v>
@@ -32998,7 +32998,7 @@
         <v>2779</v>
       </c>
       <c r="G884" s="8">
-        <v>3547812865.25</v>
+        <v>3547834566.58</v>
       </c>
     </row>
     <row r="885" spans="1:7" x14ac:dyDescent="0.25">
@@ -33080,8 +33080,8 @@
       <c r="C888" s="6">
         <v>46282</v>
       </c>
-      <c r="D888" s="7">
-        <v>9.016187</v>
+      <c r="D888" s="10">
+        <v>9.01657</v>
       </c>
       <c r="E888" s="8">
         <v>106388614</v>
@@ -33090,7 +33090,7 @@
         <v>12542</v>
       </c>
       <c r="G888" s="8">
-        <v>959219649.09</v>
+        <v>959260418.71</v>
       </c>
     </row>
     <row r="889" spans="1:7" x14ac:dyDescent="0.25">
@@ -33219,7 +33219,7 @@
         <v>46282</v>
       </c>
       <c r="D894" s="7">
-        <v>6.829567</v>
+        <v>6.829565</v>
       </c>
       <c r="E894" s="8">
         <v>43526148</v>
@@ -33228,7 +33228,7 @@
         <v>13</v>
       </c>
       <c r="G894" s="8">
-        <v>297264727.42</v>
+        <v>297264650.94</v>
       </c>
     </row>
     <row r="895" spans="1:7" x14ac:dyDescent="0.25">
@@ -33872,7 +33872,7 @@
         <v>14598</v>
       </c>
       <c r="G922" s="8">
-        <v>928470033.3</v>
+        <v>928469960.99</v>
       </c>
     </row>
     <row r="923" spans="1:7" x14ac:dyDescent="0.25">
@@ -34208,7 +34208,7 @@
         <v>46282</v>
       </c>
       <c r="D937" s="7">
-        <v>17.495417</v>
+        <v>17.495332</v>
       </c>
       <c r="E937" s="8">
         <v>12924189</v>
@@ -34217,7 +34217,7 @@
         <v>15</v>
       </c>
       <c r="G937" s="8">
-        <v>226114081.76</v>
+        <v>226112979.27</v>
       </c>
     </row>
     <row r="938" spans="1:7" x14ac:dyDescent="0.25">
@@ -34277,7 +34277,7 @@
         <v>46282</v>
       </c>
       <c r="D940" s="7">
-        <v>7.188824</v>
+        <v>7.188869</v>
       </c>
       <c r="E940" s="8">
         <v>60355372</v>
@@ -34286,7 +34286,7 @@
         <v>78</v>
       </c>
       <c r="G940" s="8">
-        <v>433884173.07</v>
+        <v>433886885.55</v>
       </c>
     </row>
     <row r="941" spans="1:7" x14ac:dyDescent="0.25">
@@ -34378,7 +34378,7 @@
         <v>3066</v>
       </c>
       <c r="G944" s="8">
-        <v>1864255547.18</v>
+        <v>1864254444.73</v>
       </c>
     </row>
     <row r="945" spans="1:7" x14ac:dyDescent="0.25">
@@ -34599,16 +34599,16 @@
         <v>46282</v>
       </c>
       <c r="D954" s="7">
-        <v>67.898861</v>
+        <v>67.898863</v>
       </c>
       <c r="E954" s="8">
-        <v>6132109</v>
+        <v>6132134</v>
       </c>
       <c r="F954" s="9">
         <v>51</v>
       </c>
       <c r="G954" s="8">
-        <v>416363215.15</v>
+        <v>416364924.55</v>
       </c>
     </row>
     <row r="955" spans="1:7" x14ac:dyDescent="0.25">
@@ -35105,7 +35105,7 @@
         <v>46282</v>
       </c>
       <c r="D976" s="7">
-        <v>11.159984</v>
+        <v>11.165047</v>
       </c>
       <c r="E976" s="8">
         <v>17436801</v>
@@ -35114,7 +35114,7 @@
         <v>81</v>
       </c>
       <c r="G976" s="8">
-        <v>194594428.76</v>
+        <v>194682700.04</v>
       </c>
     </row>
     <row r="977" spans="1:7" x14ac:dyDescent="0.25">
@@ -35174,7 +35174,7 @@
         <v>46282</v>
       </c>
       <c r="D979" s="7">
-        <v>10.706351</v>
+        <v>10.706325</v>
       </c>
       <c r="E979" s="8">
         <v>13361600</v>
@@ -35183,7 +35183,7 @@
         <v>104</v>
       </c>
       <c r="G979" s="8">
-        <v>143053977.84</v>
+        <v>143053627.55</v>
       </c>
     </row>
     <row r="980" spans="1:7" x14ac:dyDescent="0.25">
@@ -35496,7 +35496,7 @@
         <v>46282</v>
       </c>
       <c r="D993" s="7">
-        <v>5.239643</v>
+        <v>5.239472</v>
       </c>
       <c r="E993" s="8">
         <v>565097692</v>
@@ -35505,7 +35505,7 @@
         <v>13534</v>
       </c>
       <c r="G993" s="8">
-        <v>2960910010.08</v>
+        <v>2960813638.13</v>
       </c>
     </row>
     <row r="994" spans="1:7" x14ac:dyDescent="0.25">
@@ -36599,8 +36599,8 @@
       <c r="C1041" s="6">
         <v>46282</v>
       </c>
-      <c r="D1041" s="7">
-        <v>3.457657</v>
+      <c r="D1041" s="10">
+        <v>3.45786</v>
       </c>
       <c r="E1041" s="8">
         <v>509463026</v>
@@ -36609,7 +36609,7 @@
         <v>2225</v>
       </c>
       <c r="G1041" s="8">
-        <v>1761548223.74</v>
+        <v>1761651564.75</v>
       </c>
     </row>
     <row r="1042" spans="1:7" x14ac:dyDescent="0.25">
@@ -36876,7 +36876,7 @@
         <v>46282</v>
       </c>
       <c r="D1053" s="7">
-        <v>56.332454</v>
+        <v>56.236518</v>
       </c>
       <c r="E1053" s="8">
         <v>82040000</v>
@@ -36885,7 +36885,7 @@
         <v>853</v>
       </c>
       <c r="G1053" s="8">
-        <v>4621514555.51</v>
+        <v>4613643954.29</v>
       </c>
     </row>
     <row r="1054" spans="1:7" x14ac:dyDescent="0.25">
@@ -37290,7 +37290,7 @@
         <v>46282</v>
       </c>
       <c r="D1071" s="7">
-        <v>48.777124</v>
+        <v>48.606102</v>
       </c>
       <c r="E1071" s="8">
         <v>485020000</v>
@@ -37299,7 +37299,7 @@
         <v>3270</v>
       </c>
       <c r="G1071" s="8">
-        <v>23657880531.71</v>
+        <v>23574931641.12</v>
       </c>
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.25">
@@ -37497,7 +37497,7 @@
         <v>46282</v>
       </c>
       <c r="D1080" s="7">
-        <v>48.877852</v>
+        <v>48.755442</v>
       </c>
       <c r="E1080" s="8">
         <v>115710000.01</v>
@@ -37506,7 +37506,7 @@
         <v>1020</v>
       </c>
       <c r="G1080" s="8">
-        <v>5655656296.91</v>
+        <v>5641492182.04</v>
       </c>
     </row>
     <row r="1081" spans="1:7" x14ac:dyDescent="0.25">
@@ -37566,7 +37566,7 @@
         <v>46282</v>
       </c>
       <c r="D1083" s="7">
-        <v>3.007376</v>
+        <v>3.007491</v>
       </c>
       <c r="E1083" s="8">
         <v>1589097860</v>
@@ -37575,7 +37575,7 @@
         <v>680</v>
       </c>
       <c r="G1083" s="8">
-        <v>4779014317.68</v>
+        <v>4779197310.64</v>
       </c>
     </row>
     <row r="1084" spans="1:7" x14ac:dyDescent="0.25">
@@ -37635,7 +37635,7 @@
         <v>46282</v>
       </c>
       <c r="D1086" s="7">
-        <v>65.518943</v>
+        <v>65.327955</v>
       </c>
       <c r="E1086" s="8">
         <v>25325000</v>
@@ -37644,7 +37644,7 @@
         <v>360</v>
       </c>
       <c r="G1086" s="8">
-        <v>1659267232.67</v>
+        <v>1654430459.94</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.25">
@@ -38187,7 +38187,7 @@
         <v>46282</v>
       </c>
       <c r="D1110" s="7">
-        <v>3.924328</v>
+        <v>3.924401</v>
       </c>
       <c r="E1110" s="8">
         <v>6268103218</v>
@@ -38196,7 +38196,7 @@
         <v>2364</v>
       </c>
       <c r="G1110" s="8">
-        <v>24598090499.28</v>
+        <v>24598553357.03</v>
       </c>
     </row>
     <row r="1111" spans="1:7" x14ac:dyDescent="0.25">
@@ -40394,17 +40394,17 @@
       <c r="C1206" s="6">
         <v>46282</v>
       </c>
-      <c r="D1206" s="8">
-        <v>0</v>
+      <c r="D1206" s="7">
+        <v>1.554958</v>
       </c>
       <c r="E1206" s="8">
-        <v>0</v>
+        <v>1617874751</v>
       </c>
       <c r="F1206" s="9">
         <v>395</v>
       </c>
       <c r="G1206" s="8">
-        <v>0</v>
+        <v>2515728088.55</v>
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.25">
@@ -41370,7 +41370,7 @@
         <v>14</v>
       </c>
       <c r="G1248" s="8">
-        <v>1354742545.22</v>
+        <v>1354742424.88</v>
       </c>
     </row>
     <row r="1249" spans="1:7" x14ac:dyDescent="0.25">
@@ -41452,17 +41452,17 @@
       <c r="C1252" s="6">
         <v>46282</v>
       </c>
-      <c r="D1252" s="8">
-        <v>0</v>
+      <c r="D1252" s="7">
+        <v>1.589136</v>
       </c>
       <c r="E1252" s="8">
-        <v>0</v>
+        <v>592961232</v>
       </c>
       <c r="F1252" s="9">
         <v>1</v>
       </c>
       <c r="G1252" s="8">
-        <v>0</v>
+        <v>942296314.41</v>
       </c>
     </row>
     <row r="1253" spans="1:7" x14ac:dyDescent="0.25">
@@ -42925,7 +42925,7 @@
         <v>46282</v>
       </c>
       <c r="D1316" s="7">
-        <v>12.789965</v>
+        <v>12.760349</v>
       </c>
       <c r="E1316" s="8">
         <v>355154436</v>
@@ -42934,7 +42934,7 @@
         <v>11017</v>
       </c>
       <c r="G1316" s="8">
-        <v>4542412966.2</v>
+        <v>4531894663.73</v>
       </c>
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
@@ -43293,7 +43293,7 @@
         <v>46282</v>
       </c>
       <c r="D1332" s="7">
-        <v>48.778491</v>
+        <v>48.666101</v>
       </c>
       <c r="E1332" s="8">
         <v>71770000.01</v>
@@ -43302,7 +43302,7 @@
         <v>624</v>
       </c>
       <c r="G1332" s="8">
-        <v>3500832294.62</v>
+        <v>3492766079.58</v>
       </c>
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
@@ -44098,7 +44098,7 @@
         <v>46282</v>
       </c>
       <c r="D1367" s="7">
-        <v>3.636696</v>
+        <v>3.638105</v>
       </c>
       <c r="E1367" s="8">
         <v>257705095</v>
@@ -44107,7 +44107,7 @@
         <v>3310</v>
       </c>
       <c r="G1367" s="8">
-        <v>937195013.68</v>
+        <v>937558105.48</v>
       </c>
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.25">
@@ -44949,7 +44949,7 @@
         <v>46282</v>
       </c>
       <c r="D1404" s="7">
-        <v>2.398401</v>
+        <v>2.364078</v>
       </c>
       <c r="E1404" s="8">
         <v>32513983</v>
@@ -44958,7 +44958,7 @@
         <v>282</v>
       </c>
       <c r="G1404" s="8">
-        <v>77981577.24</v>
+        <v>76865577.38</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.25">
@@ -45063,8 +45063,8 @@
       <c r="C1409" s="6">
         <v>46282</v>
       </c>
-      <c r="D1409" s="7">
-        <v>1.224306</v>
+      <c r="D1409" s="10">
+        <v>1.22347</v>
       </c>
       <c r="E1409" s="8">
         <v>123627809</v>
@@ -45073,7 +45073,7 @@
         <v>417</v>
       </c>
       <c r="G1409" s="8">
-        <v>151358311.64</v>
+        <v>151254972.48</v>
       </c>
     </row>
     <row r="1410" spans="1:7" x14ac:dyDescent="0.25">
@@ -45179,16 +45179,16 @@
         <v>46282</v>
       </c>
       <c r="D1414" s="7">
-        <v>1.515373</v>
+        <v>1.515372</v>
       </c>
       <c r="E1414" s="8">
-        <v>51965135</v>
+        <v>51964135</v>
       </c>
       <c r="F1414" s="9">
         <v>356</v>
       </c>
       <c r="G1414" s="8">
-        <v>78746567.5</v>
+        <v>78744971.45</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.25">
@@ -46444,16 +46444,16 @@
         <v>46282</v>
       </c>
       <c r="D1469" s="7">
-        <v>4.227384</v>
+        <v>4.227381</v>
       </c>
       <c r="E1469" s="8">
-        <v>266659260</v>
+        <v>266641668</v>
       </c>
       <c r="F1469" s="9">
         <v>2207</v>
       </c>
       <c r="G1469" s="8">
-        <v>1127271012.86</v>
+        <v>1127196024.55</v>
       </c>
     </row>
     <row r="1470" spans="1:7" x14ac:dyDescent="0.25">
@@ -48628,17 +48628,17 @@
       <c r="C1564" s="6">
         <v>46282</v>
       </c>
-      <c r="D1564" s="8">
-        <v>0</v>
+      <c r="D1564" s="7">
+        <v>3.100501</v>
       </c>
       <c r="E1564" s="8">
-        <v>0</v>
+        <v>152853655</v>
       </c>
       <c r="F1564" s="9">
         <v>372</v>
       </c>
       <c r="G1564" s="8">
-        <v>0</v>
+        <v>473922849.98</v>
       </c>
     </row>
     <row r="1565" spans="1:7" x14ac:dyDescent="0.25">
@@ -50722,7 +50722,7 @@
         <v>46282</v>
       </c>
       <c r="D1655" s="7">
-        <v>1.753516</v>
+        <v>1.753241</v>
       </c>
       <c r="E1655" s="8">
         <v>25690857</v>
@@ -50731,7 +50731,7 @@
         <v>573</v>
       </c>
       <c r="G1655" s="8">
-        <v>45049328.18</v>
+        <v>45042267.8</v>
       </c>
     </row>
     <row r="1656" spans="1:7" x14ac:dyDescent="0.25">
@@ -51467,7 +51467,7 @@
         <v>4606</v>
       </c>
       <c r="G1687" s="8">
-        <v>3011886308.98</v>
+        <v>3011886405.31</v>
       </c>
     </row>
     <row r="1688" spans="1:7" x14ac:dyDescent="0.25">
@@ -51973,7 +51973,7 @@
         <v>29</v>
       </c>
       <c r="G1709" s="8">
-        <v>1147417353.14</v>
+        <v>1147417326.57</v>
       </c>
     </row>
     <row r="1710" spans="1:7" x14ac:dyDescent="0.25">
@@ -52033,7 +52033,7 @@
         <v>46282</v>
       </c>
       <c r="D1712" s="7">
-        <v>7.370437</v>
+        <v>7.370426</v>
       </c>
       <c r="E1712" s="8">
         <v>24050230</v>
@@ -52042,7 +52042,7 @@
         <v>175</v>
       </c>
       <c r="G1712" s="8">
-        <v>177260698.5</v>
+        <v>177260447.92</v>
       </c>
     </row>
     <row r="1713" spans="1:7" x14ac:dyDescent="0.25">
@@ -52562,7 +52562,7 @@
         <v>46282</v>
       </c>
       <c r="D1735" s="7">
-        <v>1.741148</v>
+        <v>1.741149</v>
       </c>
       <c r="E1735" s="8">
         <v>1014422750</v>
@@ -52571,7 +52571,7 @@
         <v>112605</v>
       </c>
       <c r="G1735" s="8">
-        <v>1766259987.76</v>
+        <v>1766260977.07</v>
       </c>
     </row>
     <row r="1736" spans="1:7" x14ac:dyDescent="0.25">
@@ -52930,7 +52930,7 @@
         <v>46282</v>
       </c>
       <c r="D1751" s="7">
-        <v>2.085836</v>
+        <v>2.085837</v>
       </c>
       <c r="E1751" s="8">
         <v>197520041</v>
@@ -52939,7 +52939,7 @@
         <v>85</v>
       </c>
       <c r="G1751" s="8">
-        <v>411994472</v>
+        <v>411994567.46</v>
       </c>
     </row>
     <row r="1752" spans="1:7" x14ac:dyDescent="0.25">
@@ -52999,7 +52999,7 @@
         <v>46282</v>
       </c>
       <c r="D1754" s="7">
-        <v>1.977686</v>
+        <v>1.977697</v>
       </c>
       <c r="E1754" s="8">
         <v>27015300</v>
@@ -53008,7 +53008,7 @@
         <v>2589</v>
       </c>
       <c r="G1754" s="8">
-        <v>53427774.5</v>
+        <v>53428074.55</v>
       </c>
     </row>
     <row r="1755" spans="1:7" x14ac:dyDescent="0.25">
@@ -53159,8 +53159,8 @@
       <c r="C1761" s="6">
         <v>46282</v>
       </c>
-      <c r="D1761" s="7">
-        <v>12.533519</v>
+      <c r="D1761" s="10">
+        <v>12.53353</v>
       </c>
       <c r="E1761" s="8">
         <v>7255694</v>
@@ -53169,7 +53169,7 @@
         <v>16</v>
       </c>
       <c r="G1761" s="8">
-        <v>90939381.35</v>
+        <v>90939455.89</v>
       </c>
     </row>
     <row r="1762" spans="1:7" x14ac:dyDescent="0.25">
@@ -53735,7 +53735,7 @@
         <v>46282</v>
       </c>
       <c r="D1786" s="7">
-        <v>37.271572</v>
+        <v>37.272493</v>
       </c>
       <c r="E1786" s="8">
         <v>7850603</v>
@@ -53744,7 +53744,7 @@
         <v>339</v>
       </c>
       <c r="G1786" s="8">
-        <v>292604313</v>
+        <v>292611544.83</v>
       </c>
     </row>
     <row r="1787" spans="1:7" x14ac:dyDescent="0.25">
@@ -58035,8 +58035,8 @@
       <c r="C1973" s="6">
         <v>46282</v>
       </c>
-      <c r="D1973" s="7">
-        <v>661.771407</v>
+      <c r="D1973" s="10">
+        <v>661.90198</v>
       </c>
       <c r="E1973" s="8">
         <v>1378453.39</v>
@@ -58045,7 +58045,7 @@
         <v>2084</v>
       </c>
       <c r="G1973" s="8">
-        <v>912221046.6</v>
+        <v>912401034.44</v>
       </c>
     </row>
     <row r="1974" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>01.10.2026 08:50:52</t>
+    <t>01.10.2026 10:18:00</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -11431,7 +11431,7 @@
     <t>YLR</t>
   </si>
   <si>
-    <t>YAPI KREDİ PORTFÖY AKATLAR SERBEST (DÖVİZ) ÖZEL FON</t>
+    <t>YAPI KREDİ PORTFÖY AKATLAR KAR PAYI ÖDEYEN SERBEST (DÖVİZ) FON</t>
   </si>
   <si>
     <t>YLY</t>
@@ -12788,7 +12788,7 @@
         <v>46296</v>
       </c>
       <c r="D7" s="7">
-        <v>13.089539</v>
+        <v>13.089445</v>
       </c>
       <c r="E7" s="8">
         <v>1297510</v>
@@ -12797,7 +12797,7 @@
         <v>123</v>
       </c>
       <c r="G7" s="8">
-        <v>16983808</v>
+        <v>16983686.39</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -12994,17 +12994,17 @@
       <c r="C16" s="6">
         <v>46296</v>
       </c>
-      <c r="D16" s="8">
-        <v>0</v>
+      <c r="D16" s="7">
+        <v>3.881557</v>
       </c>
       <c r="E16" s="8">
-        <v>0</v>
+        <v>6190256</v>
       </c>
       <c r="F16" s="9">
         <v>142</v>
       </c>
       <c r="G16" s="8">
-        <v>0</v>
+        <v>24027832.52</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -13063,17 +13063,17 @@
       <c r="C19" s="6">
         <v>46296</v>
       </c>
-      <c r="D19" s="8">
-        <v>0</v>
+      <c r="D19" s="7">
+        <v>94.266755</v>
       </c>
       <c r="E19" s="8">
-        <v>0</v>
+        <v>15143517</v>
       </c>
       <c r="F19" s="9">
         <v>96</v>
       </c>
       <c r="G19" s="8">
-        <v>0</v>
+        <v>1427530202.72</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -13086,17 +13086,17 @@
       <c r="C20" s="6">
         <v>46296</v>
       </c>
-      <c r="D20" s="8">
-        <v>0</v>
+      <c r="D20" s="10">
+        <v>40.85805</v>
       </c>
       <c r="E20" s="8">
-        <v>0</v>
+        <v>1777779</v>
       </c>
       <c r="F20" s="9">
         <v>1085</v>
       </c>
       <c r="G20" s="8">
-        <v>0</v>
+        <v>72636582.93</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -13132,17 +13132,17 @@
       <c r="C22" s="6">
         <v>46296</v>
       </c>
-      <c r="D22" s="8">
-        <v>0</v>
+      <c r="D22" s="7">
+        <v>12.867647</v>
       </c>
       <c r="E22" s="8">
-        <v>0</v>
+        <v>51041566</v>
       </c>
       <c r="F22" s="9">
         <v>16</v>
       </c>
       <c r="G22" s="8">
-        <v>0</v>
+        <v>656784871.03</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -13155,17 +13155,17 @@
       <c r="C23" s="6">
         <v>46296</v>
       </c>
-      <c r="D23" s="8">
-        <v>0</v>
+      <c r="D23" s="7">
+        <v>58.531066</v>
       </c>
       <c r="E23" s="8">
-        <v>0</v>
+        <v>24913852</v>
       </c>
       <c r="F23" s="9">
         <v>131</v>
       </c>
       <c r="G23" s="8">
-        <v>0</v>
+        <v>1458234314.34</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -13661,17 +13661,17 @@
       <c r="C45" s="6">
         <v>46296</v>
       </c>
-      <c r="D45" s="8">
-        <v>0</v>
+      <c r="D45" s="7">
+        <v>1.375224</v>
       </c>
       <c r="E45" s="8">
-        <v>0</v>
+        <v>7567639</v>
       </c>
       <c r="F45" s="9">
         <v>81</v>
       </c>
       <c r="G45" s="8">
-        <v>0</v>
+        <v>10407196.07</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -14213,17 +14213,17 @@
       <c r="C69" s="6">
         <v>46296</v>
       </c>
-      <c r="D69" s="8">
-        <v>0</v>
+      <c r="D69" s="7">
+        <v>2.765268</v>
       </c>
       <c r="E69" s="8">
-        <v>0</v>
+        <v>71018601</v>
       </c>
       <c r="F69" s="9">
         <v>399</v>
       </c>
       <c r="G69" s="8">
-        <v>0</v>
+        <v>196385493.24</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -14489,17 +14489,17 @@
       <c r="C81" s="6">
         <v>46296</v>
       </c>
-      <c r="D81" s="8">
-        <v>0</v>
+      <c r="D81" s="7">
+        <v>1.158977</v>
       </c>
       <c r="E81" s="8">
-        <v>0</v>
+        <v>41368028</v>
       </c>
       <c r="F81" s="9">
         <v>831</v>
       </c>
       <c r="G81" s="8">
-        <v>0</v>
+        <v>47944586.48</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -15179,17 +15179,17 @@
       <c r="C111" s="6">
         <v>46296</v>
       </c>
-      <c r="D111" s="8">
-        <v>0</v>
+      <c r="D111" s="7">
+        <v>9.129052</v>
       </c>
       <c r="E111" s="8">
-        <v>0</v>
+        <v>31195515</v>
       </c>
       <c r="F111" s="9">
         <v>25</v>
       </c>
       <c r="G111" s="8">
-        <v>0</v>
+        <v>284785464.57</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -16122,17 +16122,17 @@
       <c r="C152" s="6">
         <v>46296</v>
       </c>
-      <c r="D152" s="8">
-        <v>0</v>
+      <c r="D152" s="11">
+        <v>1.4573</v>
       </c>
       <c r="E152" s="8">
-        <v>0</v>
+        <v>46896124</v>
       </c>
       <c r="F152" s="9">
         <v>435</v>
       </c>
       <c r="G152" s="8">
-        <v>0</v>
+        <v>68341715.67</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -16241,7 +16241,7 @@
         <v>1.015648</v>
       </c>
       <c r="E157" s="8">
-        <v>83248869</v>
+        <v>83330584</v>
       </c>
       <c r="F157" s="9">
         <v>76</v>
@@ -16444,17 +16444,17 @@
       <c r="C166" s="6">
         <v>46296</v>
       </c>
-      <c r="D166" s="8">
-        <v>0</v>
+      <c r="D166" s="7">
+        <v>55.510512</v>
       </c>
       <c r="E166" s="8">
-        <v>0</v>
+        <v>28212700</v>
       </c>
       <c r="F166" s="9">
         <v>5</v>
       </c>
       <c r="G166" s="8">
-        <v>0</v>
+        <v>1566101418.84</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -16513,17 +16513,17 @@
       <c r="C169" s="6">
         <v>46296</v>
       </c>
-      <c r="D169" s="8">
-        <v>0</v>
+      <c r="D169" s="7">
+        <v>0.003331</v>
       </c>
       <c r="E169" s="8">
-        <v>0</v>
+        <v>957330904</v>
       </c>
       <c r="F169" s="9">
         <v>41</v>
       </c>
       <c r="G169" s="8">
-        <v>0</v>
+        <v>3189008.5</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -16675,7 +16675,7 @@
         <v>46296</v>
       </c>
       <c r="D176" s="7">
-        <v>10.165892</v>
+        <v>10.165779</v>
       </c>
       <c r="E176" s="8">
         <v>3431148</v>
@@ -16684,7 +16684,7 @@
         <v>525</v>
       </c>
       <c r="G176" s="8">
-        <v>34880679.8</v>
+        <v>34880293.08</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -16973,8 +16973,8 @@
       <c r="C189" s="6">
         <v>46296</v>
       </c>
-      <c r="D189" s="10">
-        <v>1.48963</v>
+      <c r="D189" s="7">
+        <v>1.489629</v>
       </c>
       <c r="E189" s="8">
         <v>29914281</v>
@@ -16983,7 +16983,7 @@
         <v>337</v>
       </c>
       <c r="G189" s="8">
-        <v>44561202.45</v>
+        <v>44561184.45</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -17019,8 +17019,8 @@
       <c r="C191" s="6">
         <v>46296</v>
       </c>
-      <c r="D191" s="10">
-        <v>4.52574</v>
+      <c r="D191" s="11">
+        <v>4.5205</v>
       </c>
       <c r="E191" s="8">
         <v>1621342207</v>
@@ -17029,7 +17029,7 @@
         <v>1</v>
       </c>
       <c r="G191" s="8">
-        <v>7337773246.74</v>
+        <v>7329276776.33</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -17387,17 +17387,17 @@
       <c r="C207" s="6">
         <v>46296</v>
       </c>
-      <c r="D207" s="8">
-        <v>0</v>
+      <c r="D207" s="7">
+        <v>2.623315</v>
       </c>
       <c r="E207" s="8">
-        <v>0</v>
+        <v>623404352</v>
       </c>
       <c r="F207" s="9">
         <v>348</v>
       </c>
       <c r="G207" s="8">
-        <v>0</v>
+        <v>1635386088.34</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -18054,17 +18054,17 @@
       <c r="C236" s="6">
         <v>46296</v>
       </c>
-      <c r="D236" s="8">
-        <v>0</v>
+      <c r="D236" s="7">
+        <v>1.542757</v>
       </c>
       <c r="E236" s="8">
-        <v>0</v>
+        <v>84841893</v>
       </c>
       <c r="F236" s="9">
         <v>1914</v>
       </c>
       <c r="G236" s="8">
-        <v>0</v>
+        <v>130890386.49</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -18262,7 +18262,7 @@
         <v>46296</v>
       </c>
       <c r="D245" s="7">
-        <v>56.641764</v>
+        <v>56.641821</v>
       </c>
       <c r="E245" s="8">
         <v>1855904392.31</v>
@@ -18271,7 +18271,7 @@
         <v>24231</v>
       </c>
       <c r="G245" s="8">
-        <v>105121698453.04</v>
+        <v>105121804950.06</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -18676,7 +18676,7 @@
         <v>46296</v>
       </c>
       <c r="D263" s="10">
-        <v>12.00543</v>
+        <v>12.00557</v>
       </c>
       <c r="E263" s="8">
         <v>17224481</v>
@@ -18685,7 +18685,7 @@
         <v>925</v>
       </c>
       <c r="G263" s="8">
-        <v>206787307.58</v>
+        <v>206789705.51</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -19780,7 +19780,7 @@
         <v>46296</v>
       </c>
       <c r="D311" s="7">
-        <v>56.627985</v>
+        <v>56.656902</v>
       </c>
       <c r="E311" s="8">
         <v>3786622</v>
@@ -19789,7 +19789,7 @@
         <v>1</v>
       </c>
       <c r="G311" s="8">
-        <v>214428773.49</v>
+        <v>214538273.09</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -19802,8 +19802,8 @@
       <c r="C312" s="6">
         <v>46296</v>
       </c>
-      <c r="D312" s="7">
-        <v>52.952417</v>
+      <c r="D312" s="10">
+        <v>52.89253</v>
       </c>
       <c r="E312" s="8">
         <v>25854210</v>
@@ -19812,7 +19812,7 @@
         <v>980</v>
       </c>
       <c r="G312" s="8">
-        <v>1369042917.9</v>
+        <v>1367494586</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -20654,7 +20654,7 @@
         <v>46296</v>
       </c>
       <c r="D349" s="7">
-        <v>1.136465</v>
+        <v>1.137305</v>
       </c>
       <c r="E349" s="8">
         <v>159096701</v>
@@ -20663,7 +20663,7 @@
         <v>162</v>
       </c>
       <c r="G349" s="8">
-        <v>180807840.86</v>
+        <v>180941476.61</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -20837,17 +20837,17 @@
       <c r="C357" s="6">
         <v>46296</v>
       </c>
-      <c r="D357" s="8">
-        <v>0</v>
+      <c r="D357" s="7">
+        <v>1.056359</v>
       </c>
       <c r="E357" s="8">
-        <v>0</v>
+        <v>116371024</v>
       </c>
       <c r="F357" s="9">
         <v>356</v>
       </c>
       <c r="G357" s="8">
-        <v>0</v>
+        <v>122929528.33</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -21597,7 +21597,7 @@
         <v>46296</v>
       </c>
       <c r="D390" s="7">
-        <v>0.980407</v>
+        <v>0.980371</v>
       </c>
       <c r="E390" s="8">
         <v>10884803</v>
@@ -21606,7 +21606,7 @@
         <v>95</v>
       </c>
       <c r="G390" s="8">
-        <v>10671535.68</v>
+        <v>10671142.17</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -21643,7 +21643,7 @@
         <v>46296</v>
       </c>
       <c r="D392" s="7">
-        <v>1.001966</v>
+        <v>1.002026</v>
       </c>
       <c r="E392" s="8">
         <v>286048584</v>
@@ -21652,7 +21652,7 @@
         <v>80</v>
       </c>
       <c r="G392" s="8">
-        <v>286610944.22</v>
+        <v>286627976.31</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -21803,17 +21803,17 @@
       <c r="C399" s="6">
         <v>46296</v>
       </c>
-      <c r="D399" s="7">
-        <v>1.896044</v>
+      <c r="D399" s="10">
+        <v>1.89605</v>
       </c>
       <c r="E399" s="8">
-        <v>923445097</v>
+        <v>920770323</v>
       </c>
       <c r="F399" s="9">
         <v>1206</v>
       </c>
       <c r="G399" s="8">
-        <v>1750892707.38</v>
+        <v>1745826929.16</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
@@ -22057,7 +22057,7 @@
         <v>46296</v>
       </c>
       <c r="D410" s="7">
-        <v>1.019985</v>
+        <v>1.020613</v>
       </c>
       <c r="E410" s="8">
         <v>250462766</v>
@@ -22066,7 +22066,7 @@
         <v>277</v>
       </c>
       <c r="G410" s="8">
-        <v>255468274.39</v>
+        <v>255625611.8</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
@@ -22080,7 +22080,7 @@
         <v>46296</v>
       </c>
       <c r="D411" s="7">
-        <v>1.304055</v>
+        <v>1.304123</v>
       </c>
       <c r="E411" s="8">
         <v>157105155</v>
@@ -22089,7 +22089,7 @@
         <v>1219</v>
       </c>
       <c r="G411" s="8">
-        <v>204873750.6</v>
+        <v>204884519.41</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
@@ -22540,7 +22540,7 @@
         <v>46296</v>
       </c>
       <c r="D431" s="7">
-        <v>4.888225</v>
+        <v>4.888228</v>
       </c>
       <c r="E431" s="8">
         <v>54677390</v>
@@ -22549,7 +22549,7 @@
         <v>363</v>
       </c>
       <c r="G431" s="8">
-        <v>267275404.06</v>
+        <v>267275532.74</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
@@ -22838,8 +22838,8 @@
       <c r="C444" s="6">
         <v>46296</v>
       </c>
-      <c r="D444" s="10">
-        <v>7.75618</v>
+      <c r="D444" s="7">
+        <v>7.737438</v>
       </c>
       <c r="E444" s="8">
         <v>241880880</v>
@@ -22848,7 +22848,7 @@
         <v>2258</v>
       </c>
       <c r="G444" s="8">
-        <v>1876071699.48</v>
+        <v>1871538347.78</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
@@ -23262,7 +23262,7 @@
         <v>9562</v>
       </c>
       <c r="G462" s="8">
-        <v>11408687701.34</v>
+        <v>11408687709.34</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
@@ -23345,7 +23345,7 @@
         <v>46296</v>
       </c>
       <c r="D466" s="7">
-        <v>0.204291</v>
+        <v>0.204172</v>
       </c>
       <c r="E466" s="8">
         <v>49635403546.04</v>
@@ -23354,7 +23354,7 @@
         <v>6243</v>
       </c>
       <c r="G466" s="8">
-        <v>10140069752.83</v>
+        <v>10134171411.53</v>
       </c>
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.25">
@@ -23367,17 +23367,17 @@
       <c r="C467" s="6">
         <v>46296</v>
       </c>
-      <c r="D467" s="8">
-        <v>0</v>
+      <c r="D467" s="10">
+        <v>1.74443</v>
       </c>
       <c r="E467" s="8">
-        <v>0</v>
+        <v>142765590</v>
       </c>
       <c r="F467" s="9">
         <v>1547</v>
       </c>
       <c r="G467" s="8">
-        <v>0</v>
+        <v>249044520.79</v>
       </c>
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.25">
@@ -23670,7 +23670,7 @@
         <v>1.225748</v>
       </c>
       <c r="E480" s="8">
-        <v>83358587</v>
+        <v>83116349</v>
       </c>
       <c r="F480" s="9">
         <v>205</v>
@@ -23785,7 +23785,7 @@
         <v>1.961233</v>
       </c>
       <c r="E485" s="8">
-        <v>105635453</v>
+        <v>105605453</v>
       </c>
       <c r="F485" s="9">
         <v>243</v>
@@ -23896,17 +23896,17 @@
       <c r="C490" s="6">
         <v>46296</v>
       </c>
-      <c r="D490" s="8">
-        <v>0</v>
+      <c r="D490" s="10">
+        <v>0.48482</v>
       </c>
       <c r="E490" s="8">
-        <v>0</v>
+        <v>277378063</v>
       </c>
       <c r="F490" s="9">
         <v>19</v>
       </c>
       <c r="G490" s="8">
-        <v>0</v>
+        <v>134478467.9</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
@@ -24011,17 +24011,17 @@
       <c r="C495" s="6">
         <v>46296</v>
       </c>
-      <c r="D495" s="8">
-        <v>0</v>
+      <c r="D495" s="7">
+        <v>1.595653</v>
       </c>
       <c r="E495" s="8">
-        <v>0</v>
+        <v>120993741.85</v>
       </c>
       <c r="F495" s="9">
         <v>572</v>
       </c>
       <c r="G495" s="8">
-        <v>0</v>
+        <v>193063967.11</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
@@ -24540,17 +24540,17 @@
       <c r="C518" s="6">
         <v>46296</v>
       </c>
-      <c r="D518" s="8">
-        <v>0</v>
+      <c r="D518" s="7">
+        <v>78.532965</v>
       </c>
       <c r="E518" s="8">
-        <v>0</v>
+        <v>5527677</v>
       </c>
       <c r="F518" s="9">
         <v>1</v>
       </c>
       <c r="G518" s="8">
-        <v>0</v>
+        <v>434104865.28</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
@@ -24655,17 +24655,17 @@
       <c r="C523" s="6">
         <v>46296</v>
       </c>
-      <c r="D523" s="8">
-        <v>0</v>
+      <c r="D523" s="7">
+        <v>64.084328</v>
       </c>
       <c r="E523" s="8">
-        <v>0</v>
+        <v>7935068</v>
       </c>
       <c r="F523" s="9">
         <v>1</v>
       </c>
       <c r="G523" s="8">
-        <v>0</v>
+        <v>508513497.42</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
@@ -24747,17 +24747,17 @@
       <c r="C527" s="6">
         <v>46296</v>
       </c>
-      <c r="D527" s="8">
-        <v>0</v>
+      <c r="D527" s="7">
+        <v>67.727404</v>
       </c>
       <c r="E527" s="8">
-        <v>0</v>
+        <v>32360328</v>
       </c>
       <c r="F527" s="9">
         <v>5</v>
       </c>
       <c r="G527" s="8">
-        <v>0</v>
+        <v>2191681011.54</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
@@ -24931,17 +24931,17 @@
       <c r="C535" s="6">
         <v>46296</v>
       </c>
-      <c r="D535" s="8">
-        <v>0</v>
+      <c r="D535" s="10">
+        <v>69.70706</v>
       </c>
       <c r="E535" s="8">
-        <v>0</v>
+        <v>53983981</v>
       </c>
       <c r="F535" s="9">
         <v>2</v>
       </c>
       <c r="G535" s="8">
-        <v>0</v>
+        <v>3763064613.55</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
@@ -25000,17 +25000,17 @@
       <c r="C538" s="6">
         <v>46296</v>
       </c>
-      <c r="D538" s="8">
-        <v>0</v>
+      <c r="D538" s="10">
+        <v>71.18456</v>
       </c>
       <c r="E538" s="8">
-        <v>0</v>
+        <v>11517383</v>
       </c>
       <c r="F538" s="9">
         <v>2</v>
       </c>
       <c r="G538" s="8">
-        <v>0</v>
+        <v>819859837.05</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
@@ -25069,17 +25069,17 @@
       <c r="C541" s="6">
         <v>46296</v>
       </c>
-      <c r="D541" s="8">
-        <v>0</v>
+      <c r="D541" s="7">
+        <v>64.952331</v>
       </c>
       <c r="E541" s="8">
-        <v>0</v>
+        <v>3425896</v>
       </c>
       <c r="F541" s="9">
         <v>3</v>
       </c>
       <c r="G541" s="8">
-        <v>0</v>
+        <v>222519930.5</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
@@ -25115,17 +25115,17 @@
       <c r="C543" s="6">
         <v>46296</v>
       </c>
-      <c r="D543" s="8">
-        <v>0</v>
+      <c r="D543" s="7">
+        <v>62.786723</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F543" s="9">
         <v>4</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>508662115.41</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25138,17 +25138,17 @@
       <c r="C544" s="6">
         <v>46296</v>
       </c>
-      <c r="D544" s="8">
-        <v>0</v>
+      <c r="D544" s="7">
+        <v>67.330925</v>
       </c>
       <c r="E544" s="8">
-        <v>0</v>
+        <v>23236050</v>
       </c>
       <c r="F544" s="9">
         <v>1</v>
       </c>
       <c r="G544" s="8">
-        <v>0</v>
+        <v>1564504730.02</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -25161,17 +25161,17 @@
       <c r="C545" s="6">
         <v>46296</v>
       </c>
-      <c r="D545" s="8">
-        <v>0</v>
+      <c r="D545" s="7">
+        <v>76.256642</v>
       </c>
       <c r="E545" s="8">
-        <v>0</v>
+        <v>2362495</v>
       </c>
       <c r="F545" s="9">
         <v>2</v>
       </c>
       <c r="G545" s="8">
-        <v>0</v>
+        <v>180155935.36</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -25207,17 +25207,17 @@
       <c r="C547" s="6">
         <v>46296</v>
       </c>
-      <c r="D547" s="8">
-        <v>0</v>
+      <c r="D547" s="7">
+        <v>62.317547</v>
       </c>
       <c r="E547" s="8">
-        <v>0</v>
+        <v>6554750</v>
       </c>
       <c r="F547" s="9">
         <v>1</v>
       </c>
       <c r="G547" s="8">
-        <v>0</v>
+        <v>408475938.41</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -25230,17 +25230,17 @@
       <c r="C548" s="6">
         <v>46296</v>
       </c>
-      <c r="D548" s="8">
-        <v>0</v>
+      <c r="D548" s="10">
+        <v>70.64404</v>
       </c>
       <c r="E548" s="8">
-        <v>0</v>
+        <v>5851512</v>
       </c>
       <c r="F548" s="9">
         <v>4</v>
       </c>
       <c r="G548" s="8">
-        <v>0</v>
+        <v>413374446.38</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
@@ -25253,17 +25253,17 @@
       <c r="C549" s="6">
         <v>46296</v>
       </c>
-      <c r="D549" s="8">
-        <v>0</v>
+      <c r="D549" s="10">
+        <v>70.93009</v>
       </c>
       <c r="E549" s="8">
-        <v>0</v>
+        <v>1533442</v>
       </c>
       <c r="F549" s="9">
         <v>2</v>
       </c>
       <c r="G549" s="8">
-        <v>0</v>
+        <v>108767178.41</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -25276,17 +25276,17 @@
       <c r="C550" s="6">
         <v>46296</v>
       </c>
-      <c r="D550" s="8">
-        <v>0</v>
+      <c r="D550" s="7">
+        <v>54.240389</v>
       </c>
       <c r="E550" s="8">
-        <v>0</v>
+        <v>30698413</v>
       </c>
       <c r="F550" s="9">
         <v>3</v>
       </c>
       <c r="G550" s="8">
-        <v>0</v>
+        <v>1665093857.55</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
@@ -25299,17 +25299,17 @@
       <c r="C551" s="6">
         <v>46296</v>
       </c>
-      <c r="D551" s="8">
-        <v>0</v>
+      <c r="D551" s="7">
+        <v>11.982175</v>
       </c>
       <c r="E551" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F551" s="9">
         <v>1</v>
       </c>
       <c r="G551" s="8">
-        <v>0</v>
+        <v>353317505.13</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -25322,17 +25322,17 @@
       <c r="C552" s="6">
         <v>46296</v>
       </c>
-      <c r="D552" s="8">
-        <v>0</v>
+      <c r="D552" s="7">
+        <v>79.486508</v>
       </c>
       <c r="E552" s="8">
-        <v>0</v>
+        <v>11573436</v>
       </c>
       <c r="F552" s="9">
         <v>3</v>
       </c>
       <c r="G552" s="8">
-        <v>0</v>
+        <v>919932014.23</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -25368,17 +25368,17 @@
       <c r="C554" s="6">
         <v>46296</v>
       </c>
-      <c r="D554" s="8">
-        <v>0</v>
+      <c r="D554" s="7">
+        <v>67.679523</v>
       </c>
       <c r="E554" s="8">
-        <v>0</v>
+        <v>121942198</v>
       </c>
       <c r="F554" s="9">
         <v>3</v>
       </c>
       <c r="G554" s="8">
-        <v>0</v>
+        <v>8252989792.62</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -25414,17 +25414,17 @@
       <c r="C556" s="6">
         <v>46296</v>
       </c>
-      <c r="D556" s="8">
-        <v>0</v>
+      <c r="D556" s="7">
+        <v>66.653739</v>
       </c>
       <c r="E556" s="8">
-        <v>0</v>
+        <v>90240169</v>
       </c>
       <c r="F556" s="9">
         <v>2</v>
       </c>
       <c r="G556" s="8">
-        <v>0</v>
+        <v>6014844696.25</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
@@ -25460,17 +25460,17 @@
       <c r="C558" s="6">
         <v>46296</v>
       </c>
-      <c r="D558" s="8">
-        <v>0</v>
+      <c r="D558" s="7">
+        <v>8.834888</v>
       </c>
       <c r="E558" s="8">
-        <v>0</v>
+        <v>342290935</v>
       </c>
       <c r="F558" s="9">
         <v>1</v>
       </c>
       <c r="G558" s="8">
-        <v>0</v>
+        <v>3024101909.29</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -25483,17 +25483,17 @@
       <c r="C559" s="6">
         <v>46296</v>
       </c>
-      <c r="D559" s="8">
-        <v>0</v>
+      <c r="D559" s="7">
+        <v>70.572998</v>
       </c>
       <c r="E559" s="8">
-        <v>0</v>
+        <v>6963426</v>
       </c>
       <c r="F559" s="9">
         <v>4</v>
       </c>
       <c r="G559" s="8">
-        <v>0</v>
+        <v>491429850.74</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
@@ -25644,17 +25644,17 @@
       <c r="C566" s="6">
         <v>46296</v>
       </c>
-      <c r="D566" s="8">
-        <v>0</v>
+      <c r="D566" s="7">
+        <v>67.175123</v>
       </c>
       <c r="E566" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F566" s="9">
         <v>3</v>
       </c>
       <c r="G566" s="8">
-        <v>0</v>
+        <v>958142699.24</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.25">
@@ -25690,17 +25690,17 @@
       <c r="C568" s="6">
         <v>46296</v>
       </c>
-      <c r="D568" s="8">
-        <v>0</v>
+      <c r="D568" s="7">
+        <v>65.224449</v>
       </c>
       <c r="E568" s="8">
-        <v>0</v>
+        <v>6256592</v>
       </c>
       <c r="F568" s="9">
         <v>3</v>
       </c>
       <c r="G568" s="8">
-        <v>0</v>
+        <v>408082766.62</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
@@ -25713,17 +25713,17 @@
       <c r="C569" s="6">
         <v>46296</v>
       </c>
-      <c r="D569" s="8">
-        <v>0</v>
+      <c r="D569" s="7">
+        <v>64.305816</v>
       </c>
       <c r="E569" s="8">
-        <v>0</v>
+        <v>2316713</v>
       </c>
       <c r="F569" s="9">
         <v>2</v>
       </c>
       <c r="G569" s="8">
-        <v>0</v>
+        <v>148978120.72</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
@@ -25920,17 +25920,17 @@
       <c r="C578" s="6">
         <v>46296</v>
       </c>
-      <c r="D578" s="8">
-        <v>0</v>
+      <c r="D578" s="7">
+        <v>66.144433</v>
       </c>
       <c r="E578" s="8">
-        <v>0</v>
+        <v>30617607</v>
       </c>
       <c r="F578" s="9">
         <v>2</v>
       </c>
       <c r="G578" s="8">
-        <v>0</v>
+        <v>2025184258.36</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.25">
@@ -26104,17 +26104,17 @@
       <c r="C586" s="6">
         <v>46296</v>
       </c>
-      <c r="D586" s="8">
-        <v>0</v>
+      <c r="D586" s="7">
+        <v>0.986446</v>
       </c>
       <c r="E586" s="8">
-        <v>0</v>
+        <v>8570148</v>
       </c>
       <c r="F586" s="9">
         <v>37</v>
       </c>
       <c r="G586" s="8">
-        <v>0</v>
+        <v>8453989.93</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
@@ -26150,17 +26150,17 @@
       <c r="C588" s="6">
         <v>46296</v>
       </c>
-      <c r="D588" s="8">
-        <v>0</v>
+      <c r="D588" s="7">
+        <v>69.593597</v>
       </c>
       <c r="E588" s="8">
-        <v>0</v>
+        <v>8202021</v>
       </c>
       <c r="F588" s="9">
         <v>4</v>
       </c>
       <c r="G588" s="8">
-        <v>0</v>
+        <v>570808140.86</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -26242,17 +26242,17 @@
       <c r="C592" s="6">
         <v>46296</v>
       </c>
-      <c r="D592" s="8">
-        <v>0</v>
+      <c r="D592" s="7">
+        <v>7.336896</v>
       </c>
       <c r="E592" s="8">
-        <v>0</v>
+        <v>479242280</v>
       </c>
       <c r="F592" s="9">
         <v>19259</v>
       </c>
       <c r="G592" s="8">
-        <v>0</v>
+        <v>3516150932.7</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
@@ -26403,17 +26403,17 @@
       <c r="C599" s="6">
         <v>46296</v>
       </c>
-      <c r="D599" s="8">
-        <v>0</v>
+      <c r="D599" s="7">
+        <v>61.845953</v>
       </c>
       <c r="E599" s="8">
-        <v>0</v>
+        <v>25439462</v>
       </c>
       <c r="F599" s="9">
         <v>1</v>
       </c>
       <c r="G599" s="8">
-        <v>0</v>
+        <v>1573327774.49</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
@@ -26541,17 +26541,17 @@
       <c r="C605" s="6">
         <v>46296</v>
       </c>
-      <c r="D605" s="8">
-        <v>0</v>
+      <c r="D605" s="7">
+        <v>62.332636</v>
       </c>
       <c r="E605" s="8">
-        <v>0</v>
+        <v>28454944</v>
       </c>
       <c r="F605" s="9">
         <v>3</v>
       </c>
       <c r="G605" s="8">
-        <v>0</v>
+        <v>1773671672.6</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
@@ -26702,17 +26702,17 @@
       <c r="C612" s="6">
         <v>46296</v>
       </c>
-      <c r="D612" s="8">
-        <v>0</v>
+      <c r="D612" s="7">
+        <v>4.423603</v>
       </c>
       <c r="E612" s="8">
-        <v>0</v>
+        <v>308721583</v>
       </c>
       <c r="F612" s="9">
         <v>2278</v>
       </c>
       <c r="G612" s="8">
-        <v>0</v>
+        <v>1365661622.44</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
@@ -26725,17 +26725,17 @@
       <c r="C613" s="6">
         <v>46296</v>
       </c>
-      <c r="D613" s="8">
-        <v>0</v>
+      <c r="D613" s="7">
+        <v>2.409233</v>
       </c>
       <c r="E613" s="8">
-        <v>0</v>
+        <v>69569617</v>
       </c>
       <c r="F613" s="9">
         <v>1162</v>
       </c>
       <c r="G613" s="8">
-        <v>0</v>
+        <v>167609385.16</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
@@ -26794,17 +26794,17 @@
       <c r="C616" s="6">
         <v>46296</v>
       </c>
-      <c r="D616" s="8">
-        <v>0</v>
+      <c r="D616" s="7">
+        <v>1.031048</v>
       </c>
       <c r="E616" s="8">
-        <v>0</v>
+        <v>52198444</v>
       </c>
       <c r="F616" s="9">
         <v>14</v>
       </c>
       <c r="G616" s="8">
-        <v>0</v>
+        <v>53819084.2</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
@@ -26840,17 +26840,17 @@
       <c r="C618" s="6">
         <v>46296</v>
       </c>
-      <c r="D618" s="8">
-        <v>0</v>
+      <c r="D618" s="10">
+        <v>1.28199</v>
       </c>
       <c r="E618" s="8">
-        <v>0</v>
+        <v>184581943</v>
       </c>
       <c r="F618" s="9">
         <v>1051</v>
       </c>
       <c r="G618" s="8">
-        <v>0</v>
+        <v>236632150.38</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
@@ -26932,17 +26932,17 @@
       <c r="C622" s="6">
         <v>46296</v>
       </c>
-      <c r="D622" s="8">
-        <v>0</v>
+      <c r="D622" s="7">
+        <v>12.456369</v>
       </c>
       <c r="E622" s="8">
-        <v>0</v>
+        <v>100048115</v>
       </c>
       <c r="F622" s="9">
         <v>9426</v>
       </c>
       <c r="G622" s="8">
-        <v>0</v>
+        <v>1246236217.9</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
@@ -26955,17 +26955,17 @@
       <c r="C623" s="6">
         <v>46296</v>
       </c>
-      <c r="D623" s="8">
-        <v>0</v>
+      <c r="D623" s="7">
+        <v>72.233283</v>
       </c>
       <c r="E623" s="8">
-        <v>0</v>
+        <v>85163084</v>
       </c>
       <c r="F623" s="9">
         <v>3340</v>
       </c>
       <c r="G623" s="8">
-        <v>0</v>
+        <v>6151609137.16</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
@@ -27070,17 +27070,17 @@
       <c r="C628" s="6">
         <v>46296</v>
       </c>
-      <c r="D628" s="8">
-        <v>0</v>
+      <c r="D628" s="7">
+        <v>58.802097</v>
       </c>
       <c r="E628" s="8">
-        <v>0</v>
+        <v>14627030</v>
       </c>
       <c r="F628" s="9">
         <v>2</v>
       </c>
       <c r="G628" s="8">
-        <v>0</v>
+        <v>860100031.53</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
@@ -27116,17 +27116,17 @@
       <c r="C630" s="6">
         <v>46296</v>
       </c>
-      <c r="D630" s="8">
-        <v>0</v>
+      <c r="D630" s="7">
+        <v>62.833436</v>
       </c>
       <c r="E630" s="8">
-        <v>0</v>
+        <v>20837078</v>
       </c>
       <c r="F630" s="9">
         <v>2</v>
       </c>
       <c r="G630" s="8">
-        <v>0</v>
+        <v>1309265213.3</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -27255,7 +27255,7 @@
         <v>46296</v>
       </c>
       <c r="D636" s="7">
-        <v>1.732996</v>
+        <v>1.741778</v>
       </c>
       <c r="E636" s="8">
         <v>160496776</v>
@@ -27264,7 +27264,7 @@
         <v>257</v>
       </c>
       <c r="G636" s="8">
-        <v>278140245</v>
+        <v>279549805.72</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
@@ -27369,17 +27369,17 @@
       <c r="C641" s="6">
         <v>46296</v>
       </c>
-      <c r="D641" s="8">
-        <v>0</v>
+      <c r="D641" s="7">
+        <v>15.953193</v>
       </c>
       <c r="E641" s="8">
-        <v>0</v>
+        <v>257896262</v>
       </c>
       <c r="F641" s="9">
         <v>6</v>
       </c>
       <c r="G641" s="8">
-        <v>0</v>
+        <v>4114268828.06</v>
       </c>
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.25">
@@ -27415,17 +27415,17 @@
       <c r="C643" s="6">
         <v>46296</v>
       </c>
-      <c r="D643" s="8">
-        <v>0</v>
+      <c r="D643" s="7">
+        <v>58.100884</v>
       </c>
       <c r="E643" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F643" s="9">
         <v>2</v>
       </c>
       <c r="G643" s="8">
-        <v>0</v>
+        <v>269771700.78</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.25">
@@ -27599,17 +27599,17 @@
       <c r="C651" s="6">
         <v>46296</v>
       </c>
-      <c r="D651" s="8">
-        <v>0</v>
+      <c r="D651" s="7">
+        <v>52.779682</v>
       </c>
       <c r="E651" s="8">
-        <v>0</v>
+        <v>28012535</v>
       </c>
       <c r="F651" s="9">
         <v>2</v>
       </c>
       <c r="G651" s="8">
-        <v>0</v>
+        <v>1478492691.94</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
@@ -27668,17 +27668,17 @@
       <c r="C654" s="6">
         <v>46296</v>
       </c>
-      <c r="D654" s="8">
-        <v>0</v>
+      <c r="D654" s="7">
+        <v>6.108638</v>
       </c>
       <c r="E654" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F654" s="9">
         <v>1</v>
       </c>
       <c r="G654" s="8">
-        <v>0</v>
+        <v>2088303857.1</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
@@ -27875,17 +27875,17 @@
       <c r="C663" s="6">
         <v>46296</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="7">
+        <v>68.265723</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>52499640</v>
       </c>
       <c r="F663" s="9">
         <v>3</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>3583925876.78</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -27898,17 +27898,17 @@
       <c r="C664" s="6">
         <v>46296</v>
       </c>
-      <c r="D664" s="8">
-        <v>0</v>
+      <c r="D664" s="7">
+        <v>64.846227</v>
       </c>
       <c r="E664" s="8">
-        <v>0</v>
+        <v>4739268</v>
       </c>
       <c r="F664" s="9">
         <v>1</v>
       </c>
       <c r="G664" s="8">
-        <v>0</v>
+        <v>307323650.25</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
@@ -27967,17 +27967,17 @@
       <c r="C667" s="6">
         <v>46296</v>
       </c>
-      <c r="D667" s="8">
-        <v>0</v>
+      <c r="D667" s="7">
+        <v>67.416882</v>
       </c>
       <c r="E667" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F667" s="9">
         <v>3</v>
       </c>
       <c r="G667" s="8">
-        <v>0</v>
+        <v>530713382.95</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -27990,17 +27990,17 @@
       <c r="C668" s="6">
         <v>46296</v>
       </c>
-      <c r="D668" s="8">
-        <v>0</v>
+      <c r="D668" s="7">
+        <v>72.742236</v>
       </c>
       <c r="E668" s="8">
-        <v>0</v>
+        <v>5533354</v>
       </c>
       <c r="F668" s="9">
         <v>2</v>
       </c>
       <c r="G668" s="8">
-        <v>0</v>
+        <v>402508544.43</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -28036,17 +28036,17 @@
       <c r="C670" s="6">
         <v>46296</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="7">
+        <v>70.778061</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>7036272</v>
       </c>
       <c r="F670" s="9">
         <v>4</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>498013688.21</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28105,17 +28105,17 @@
       <c r="C673" s="6">
         <v>46296</v>
       </c>
-      <c r="D673" s="8">
-        <v>0</v>
+      <c r="D673" s="7">
+        <v>69.415856</v>
       </c>
       <c r="E673" s="8">
-        <v>0</v>
+        <v>20613565</v>
       </c>
       <c r="F673" s="9">
         <v>1</v>
       </c>
       <c r="G673" s="8">
-        <v>0</v>
+        <v>1430908250.25</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -28128,17 +28128,17 @@
       <c r="C674" s="6">
         <v>46296</v>
       </c>
-      <c r="D674" s="8">
-        <v>0</v>
+      <c r="D674" s="10">
+        <v>63.48269</v>
       </c>
       <c r="E674" s="8">
-        <v>0</v>
+        <v>9307247</v>
       </c>
       <c r="F674" s="9">
         <v>5</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>590849071.44</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -28174,17 +28174,17 @@
       <c r="C676" s="6">
         <v>46296</v>
       </c>
-      <c r="D676" s="8">
-        <v>0</v>
+      <c r="D676" s="7">
+        <v>62.388231</v>
       </c>
       <c r="E676" s="8">
-        <v>0</v>
+        <v>876698</v>
       </c>
       <c r="F676" s="9">
         <v>3</v>
       </c>
       <c r="G676" s="8">
-        <v>0</v>
+        <v>54695637.03</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
@@ -28358,17 +28358,17 @@
       <c r="C684" s="6">
         <v>46296</v>
       </c>
-      <c r="D684" s="8">
-        <v>0</v>
+      <c r="D684" s="7">
+        <v>68.567603</v>
       </c>
       <c r="E684" s="8">
-        <v>0</v>
+        <v>1210798</v>
       </c>
       <c r="F684" s="9">
         <v>1</v>
       </c>
       <c r="G684" s="8">
-        <v>0</v>
+        <v>83021517.12</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -28427,17 +28427,17 @@
       <c r="C687" s="6">
         <v>46296</v>
       </c>
-      <c r="D687" s="8">
-        <v>0</v>
+      <c r="D687" s="7">
+        <v>68.398729</v>
       </c>
       <c r="E687" s="8">
-        <v>0</v>
+        <v>6829649</v>
       </c>
       <c r="F687" s="9">
         <v>2</v>
       </c>
       <c r="G687" s="8">
-        <v>0</v>
+        <v>467139310.13</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.25">
@@ -28588,17 +28588,17 @@
       <c r="C694" s="6">
         <v>46296</v>
       </c>
-      <c r="D694" s="8">
-        <v>0</v>
+      <c r="D694" s="7">
+        <v>3.049108</v>
       </c>
       <c r="E694" s="8">
-        <v>0</v>
+        <v>291416302</v>
       </c>
       <c r="F694" s="9">
         <v>7269</v>
       </c>
       <c r="G694" s="8">
-        <v>0</v>
+        <v>888559814.07</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
@@ -28634,17 +28634,17 @@
       <c r="C696" s="6">
         <v>46296</v>
       </c>
-      <c r="D696" s="8">
-        <v>0</v>
+      <c r="D696" s="7">
+        <v>1.868338</v>
       </c>
       <c r="E696" s="8">
-        <v>0</v>
+        <v>1455430</v>
       </c>
       <c r="F696" s="9">
         <v>73</v>
       </c>
       <c r="G696" s="8">
-        <v>0</v>
+        <v>2719235.83</v>
       </c>
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.25">
@@ -28795,17 +28795,17 @@
       <c r="C703" s="6">
         <v>46296</v>
       </c>
-      <c r="D703" s="8">
-        <v>0</v>
+      <c r="D703" s="10">
+        <v>17.64741</v>
       </c>
       <c r="E703" s="8">
-        <v>0</v>
+        <v>57550088</v>
       </c>
       <c r="F703" s="9">
         <v>17</v>
       </c>
       <c r="G703" s="8">
-        <v>0</v>
+        <v>1015609988.65</v>
       </c>
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.25">
@@ -28818,17 +28818,17 @@
       <c r="C704" s="6">
         <v>46296</v>
       </c>
-      <c r="D704" s="8">
-        <v>0</v>
+      <c r="D704" s="7">
+        <v>0.987129</v>
       </c>
       <c r="E704" s="8">
-        <v>0</v>
+        <v>136715077</v>
       </c>
       <c r="F704" s="9">
         <v>541</v>
       </c>
       <c r="G704" s="8">
-        <v>0</v>
+        <v>134955395.35</v>
       </c>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.25">
@@ -28841,17 +28841,17 @@
       <c r="C705" s="6">
         <v>46296</v>
       </c>
-      <c r="D705" s="8">
-        <v>0</v>
+      <c r="D705" s="7">
+        <v>3.213702</v>
       </c>
       <c r="E705" s="8">
-        <v>0</v>
+        <v>24211612</v>
       </c>
       <c r="F705" s="9">
         <v>480</v>
       </c>
       <c r="G705" s="8">
-        <v>0</v>
+        <v>77808896.51</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.25">
@@ -28910,17 +28910,17 @@
       <c r="C708" s="6">
         <v>46296</v>
       </c>
-      <c r="D708" s="8">
-        <v>0</v>
+      <c r="D708" s="7">
+        <v>1155.560083</v>
       </c>
       <c r="E708" s="8">
-        <v>0</v>
+        <v>2988390</v>
       </c>
       <c r="F708" s="9">
         <v>16</v>
       </c>
       <c r="G708" s="8">
-        <v>0</v>
+        <v>3453264196.56</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.25">
@@ -28933,17 +28933,17 @@
       <c r="C709" s="6">
         <v>46296</v>
       </c>
-      <c r="D709" s="8">
-        <v>0</v>
+      <c r="D709" s="7">
+        <v>6.883663</v>
       </c>
       <c r="E709" s="8">
-        <v>0</v>
+        <v>14877895</v>
       </c>
       <c r="F709" s="9">
         <v>13</v>
       </c>
       <c r="G709" s="8">
-        <v>0</v>
+        <v>102414418.67</v>
       </c>
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.25">
@@ -28956,17 +28956,17 @@
       <c r="C710" s="6">
         <v>46296</v>
       </c>
-      <c r="D710" s="8">
-        <v>0</v>
+      <c r="D710" s="7">
+        <v>3.065827</v>
       </c>
       <c r="E710" s="8">
-        <v>0</v>
+        <v>3734881</v>
       </c>
       <c r="F710" s="9">
         <v>120</v>
       </c>
       <c r="G710" s="8">
-        <v>0</v>
+        <v>11450498.09</v>
       </c>
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.25">
@@ -28979,17 +28979,17 @@
       <c r="C711" s="6">
         <v>46296</v>
       </c>
-      <c r="D711" s="8">
-        <v>0</v>
+      <c r="D711" s="7">
+        <v>17.435974</v>
       </c>
       <c r="E711" s="8">
-        <v>0</v>
+        <v>91221799</v>
       </c>
       <c r="F711" s="9">
         <v>13</v>
       </c>
       <c r="G711" s="8">
-        <v>0</v>
+        <v>1590540872.15</v>
       </c>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.25">
@@ -29003,7 +29003,7 @@
         <v>46296</v>
       </c>
       <c r="D712" s="7">
-        <v>66.677359</v>
+        <v>66.681737</v>
       </c>
       <c r="E712" s="8">
         <v>76215710</v>
@@ -29012,7 +29012,7 @@
         <v>2215</v>
       </c>
       <c r="G712" s="8">
-        <v>5081862283.49</v>
+        <v>5082195939.73</v>
       </c>
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.25">
@@ -29025,17 +29025,17 @@
       <c r="C713" s="6">
         <v>46296</v>
       </c>
-      <c r="D713" s="8">
-        <v>0</v>
+      <c r="D713" s="7">
+        <v>3.387368</v>
       </c>
       <c r="E713" s="8">
-        <v>0</v>
+        <v>109831779</v>
       </c>
       <c r="F713" s="9">
         <v>1316</v>
       </c>
       <c r="G713" s="8">
-        <v>0</v>
+        <v>372040684.23</v>
       </c>
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.25">
@@ -29071,17 +29071,17 @@
       <c r="C715" s="6">
         <v>46296</v>
       </c>
-      <c r="D715" s="8">
-        <v>0</v>
+      <c r="D715" s="10">
+        <v>1.61672</v>
       </c>
       <c r="E715" s="8">
-        <v>0</v>
+        <v>34323339</v>
       </c>
       <c r="F715" s="9">
         <v>125</v>
       </c>
       <c r="G715" s="8">
-        <v>0</v>
+        <v>55491213.38</v>
       </c>
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.25">
@@ -29209,17 +29209,17 @@
       <c r="C721" s="6">
         <v>46296</v>
       </c>
-      <c r="D721" s="8">
-        <v>0</v>
+      <c r="D721" s="7">
+        <v>1.725925</v>
       </c>
       <c r="E721" s="8">
-        <v>0</v>
+        <v>572445</v>
       </c>
       <c r="F721" s="9">
         <v>19</v>
       </c>
       <c r="G721" s="8">
-        <v>0</v>
+        <v>987996.86</v>
       </c>
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.25">
@@ -29255,17 +29255,17 @@
       <c r="C723" s="6">
         <v>46296</v>
       </c>
-      <c r="D723" s="8">
-        <v>0</v>
+      <c r="D723" s="7">
+        <v>3.750734</v>
       </c>
       <c r="E723" s="8">
-        <v>0</v>
+        <v>34579119.35</v>
       </c>
       <c r="F723" s="9">
         <v>1682</v>
       </c>
       <c r="G723" s="8">
-        <v>0</v>
+        <v>129697079.82</v>
       </c>
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.25">
@@ -29278,17 +29278,17 @@
       <c r="C724" s="6">
         <v>46296</v>
       </c>
-      <c r="D724" s="8">
-        <v>0</v>
+      <c r="D724" s="7">
+        <v>1.398042</v>
       </c>
       <c r="E724" s="8">
-        <v>0</v>
+        <v>21549033</v>
       </c>
       <c r="F724" s="9">
         <v>132</v>
       </c>
       <c r="G724" s="8">
-        <v>0</v>
+        <v>30126448.51</v>
       </c>
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.25">
@@ -29347,17 +29347,17 @@
       <c r="C727" s="6">
         <v>46296</v>
       </c>
-      <c r="D727" s="8">
-        <v>0</v>
+      <c r="D727" s="7">
+        <v>4.237938</v>
       </c>
       <c r="E727" s="8">
-        <v>0</v>
+        <v>4091835</v>
       </c>
       <c r="F727" s="9">
         <v>333</v>
       </c>
       <c r="G727" s="8">
-        <v>0</v>
+        <v>17340943.24</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.25">
@@ -29370,17 +29370,17 @@
       <c r="C728" s="6">
         <v>46296</v>
       </c>
-      <c r="D728" s="8">
-        <v>0</v>
+      <c r="D728" s="7">
+        <v>1.602629</v>
       </c>
       <c r="E728" s="8">
-        <v>0</v>
+        <v>541543387</v>
       </c>
       <c r="F728" s="9">
         <v>230</v>
       </c>
       <c r="G728" s="8">
-        <v>0</v>
+        <v>867893259.56</v>
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.25">
@@ -29393,17 +29393,17 @@
       <c r="C729" s="6">
         <v>46296</v>
       </c>
-      <c r="D729" s="8">
-        <v>0</v>
+      <c r="D729" s="10">
+        <v>0.49514</v>
       </c>
       <c r="E729" s="8">
-        <v>0</v>
+        <v>20924497</v>
       </c>
       <c r="F729" s="9">
         <v>43</v>
       </c>
       <c r="G729" s="8">
-        <v>0</v>
+        <v>10360563.12</v>
       </c>
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.25">
@@ -29462,17 +29462,17 @@
       <c r="C732" s="6">
         <v>46296</v>
       </c>
-      <c r="D732" s="8">
-        <v>0</v>
+      <c r="D732" s="7">
+        <v>4.112668</v>
       </c>
       <c r="E732" s="8">
-        <v>0</v>
+        <v>67520750</v>
       </c>
       <c r="F732" s="9">
         <v>186</v>
       </c>
       <c r="G732" s="8">
-        <v>0</v>
+        <v>277690426.51</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.25">
@@ -29508,17 +29508,17 @@
       <c r="C734" s="6">
         <v>46296</v>
       </c>
-      <c r="D734" s="8">
-        <v>0</v>
+      <c r="D734" s="7">
+        <v>2.946199</v>
       </c>
       <c r="E734" s="8">
-        <v>0</v>
+        <v>440177</v>
       </c>
       <c r="F734" s="9">
         <v>13</v>
       </c>
       <c r="G734" s="8">
-        <v>0</v>
+        <v>1296849.09</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.25">
@@ -29577,17 +29577,17 @@
       <c r="C737" s="6">
         <v>46296</v>
       </c>
-      <c r="D737" s="8">
-        <v>0</v>
+      <c r="D737" s="7">
+        <v>4.526455</v>
       </c>
       <c r="E737" s="8">
-        <v>0</v>
+        <v>21338570</v>
       </c>
       <c r="F737" s="9">
         <v>1448</v>
       </c>
       <c r="G737" s="8">
-        <v>0</v>
+        <v>96588084.83</v>
       </c>
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.25">
@@ -29623,17 +29623,17 @@
       <c r="C739" s="6">
         <v>46296</v>
       </c>
-      <c r="D739" s="8">
-        <v>0</v>
+      <c r="D739" s="7">
+        <v>7.974845</v>
       </c>
       <c r="E739" s="8">
-        <v>0</v>
+        <v>85020805</v>
       </c>
       <c r="F739" s="9">
         <v>12921</v>
       </c>
       <c r="G739" s="8">
-        <v>0</v>
+        <v>678027739.22</v>
       </c>
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.25">
@@ -29646,17 +29646,17 @@
       <c r="C740" s="6">
         <v>46296</v>
       </c>
-      <c r="D740" s="8">
-        <v>0</v>
+      <c r="D740" s="7">
+        <v>1.455374</v>
       </c>
       <c r="E740" s="8">
-        <v>0</v>
+        <v>4967923952</v>
       </c>
       <c r="F740" s="9">
         <v>1813</v>
       </c>
       <c r="G740" s="8">
-        <v>0</v>
+        <v>7230184986.11</v>
       </c>
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.25">
@@ -29669,17 +29669,17 @@
       <c r="C741" s="6">
         <v>46296</v>
       </c>
-      <c r="D741" s="8">
-        <v>0</v>
+      <c r="D741" s="7">
+        <v>2.624464</v>
       </c>
       <c r="E741" s="8">
-        <v>0</v>
+        <v>10793247</v>
       </c>
       <c r="F741" s="9">
         <v>809</v>
       </c>
       <c r="G741" s="8">
-        <v>0</v>
+        <v>28326486.75</v>
       </c>
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.25">
@@ -29692,17 +29692,17 @@
       <c r="C742" s="6">
         <v>46296</v>
       </c>
-      <c r="D742" s="8">
-        <v>0</v>
+      <c r="D742" s="7">
+        <v>5.289613</v>
       </c>
       <c r="E742" s="8">
-        <v>0</v>
+        <v>24185590</v>
       </c>
       <c r="F742" s="9">
         <v>65</v>
       </c>
       <c r="G742" s="8">
-        <v>0</v>
+        <v>127932412.69</v>
       </c>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.25">
@@ -29807,17 +29807,17 @@
       <c r="C747" s="6">
         <v>46296</v>
       </c>
-      <c r="D747" s="8">
-        <v>0</v>
+      <c r="D747" s="7">
+        <v>36.998406</v>
       </c>
       <c r="E747" s="8">
-        <v>0</v>
+        <v>20523635</v>
       </c>
       <c r="F747" s="9">
         <v>13</v>
       </c>
       <c r="G747" s="8">
-        <v>0</v>
+        <v>759341770.8</v>
       </c>
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.25">
@@ -29830,17 +29830,17 @@
       <c r="C748" s="6">
         <v>46296</v>
       </c>
-      <c r="D748" s="8">
-        <v>0</v>
+      <c r="D748" s="7">
+        <v>9.081837</v>
       </c>
       <c r="E748" s="8">
-        <v>0</v>
+        <v>819965</v>
       </c>
       <c r="F748" s="9">
         <v>130</v>
       </c>
       <c r="G748" s="8">
-        <v>0</v>
+        <v>7446788.22</v>
       </c>
     </row>
     <row r="749" spans="1:7" x14ac:dyDescent="0.25">
@@ -29899,17 +29899,17 @@
       <c r="C751" s="6">
         <v>46296</v>
       </c>
-      <c r="D751" s="8">
-        <v>0</v>
+      <c r="D751" s="7">
+        <v>190.762796</v>
       </c>
       <c r="E751" s="8">
-        <v>0</v>
+        <v>226039</v>
       </c>
       <c r="F751" s="9">
         <v>37</v>
       </c>
       <c r="G751" s="8">
-        <v>0</v>
+        <v>43119831.6</v>
       </c>
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.25">
@@ -29922,17 +29922,17 @@
       <c r="C752" s="6">
         <v>46296</v>
       </c>
-      <c r="D752" s="8">
-        <v>0</v>
+      <c r="D752" s="7">
+        <v>49.000756</v>
       </c>
       <c r="E752" s="8">
-        <v>0</v>
+        <v>1624487</v>
       </c>
       <c r="F752" s="9">
         <v>39</v>
       </c>
       <c r="G752" s="8">
-        <v>0</v>
+        <v>79601091.79</v>
       </c>
     </row>
     <row r="753" spans="1:7" x14ac:dyDescent="0.25">
@@ -29991,17 +29991,17 @@
       <c r="C755" s="6">
         <v>46296</v>
       </c>
-      <c r="D755" s="8">
-        <v>0</v>
+      <c r="D755" s="7">
+        <v>4.494898</v>
       </c>
       <c r="E755" s="8">
-        <v>0</v>
+        <v>887234531</v>
       </c>
       <c r="F755" s="9">
         <v>13</v>
       </c>
       <c r="G755" s="8">
-        <v>0</v>
+        <v>3988028325.29</v>
       </c>
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.25">
@@ -30083,17 +30083,17 @@
       <c r="C759" s="6">
         <v>46296</v>
       </c>
-      <c r="D759" s="8">
-        <v>0</v>
+      <c r="D759" s="7">
+        <v>60.252181</v>
       </c>
       <c r="E759" s="8">
-        <v>0</v>
+        <v>12214544</v>
       </c>
       <c r="F759" s="9">
         <v>163</v>
       </c>
       <c r="G759" s="8">
-        <v>0</v>
+        <v>735952914.7</v>
       </c>
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.25">
@@ -30175,17 +30175,17 @@
       <c r="C763" s="6">
         <v>46296</v>
       </c>
-      <c r="D763" s="8">
-        <v>0</v>
+      <c r="D763" s="7">
+        <v>2.453659</v>
       </c>
       <c r="E763" s="8">
-        <v>0</v>
+        <v>1650591181</v>
       </c>
       <c r="F763" s="9">
         <v>6593</v>
       </c>
       <c r="G763" s="8">
-        <v>0</v>
+        <v>4049987304.64</v>
       </c>
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.25">
@@ -30198,17 +30198,17 @@
       <c r="C764" s="6">
         <v>46296</v>
       </c>
-      <c r="D764" s="8">
-        <v>0</v>
+      <c r="D764" s="7">
+        <v>1.328175</v>
       </c>
       <c r="E764" s="8">
-        <v>0</v>
+        <v>34414080</v>
       </c>
       <c r="F764" s="9">
         <v>14</v>
       </c>
       <c r="G764" s="8">
-        <v>0</v>
+        <v>45707927.94</v>
       </c>
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.25">
@@ -30244,17 +30244,17 @@
       <c r="C766" s="6">
         <v>46296</v>
       </c>
-      <c r="D766" s="8">
-        <v>0</v>
+      <c r="D766" s="7">
+        <v>0.071406</v>
       </c>
       <c r="E766" s="8">
-        <v>0</v>
+        <v>291815213</v>
       </c>
       <c r="F766" s="9">
         <v>24</v>
       </c>
       <c r="G766" s="8">
-        <v>0</v>
+        <v>20837289.83</v>
       </c>
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.25">
@@ -30336,17 +30336,17 @@
       <c r="C770" s="6">
         <v>46296</v>
       </c>
-      <c r="D770" s="8">
-        <v>0</v>
+      <c r="D770" s="7">
+        <v>509.640129</v>
       </c>
       <c r="E770" s="8">
-        <v>0</v>
+        <v>9674</v>
       </c>
       <c r="F770" s="9">
         <v>18</v>
       </c>
       <c r="G770" s="8">
-        <v>0</v>
+        <v>4930258.61</v>
       </c>
     </row>
     <row r="771" spans="1:7" x14ac:dyDescent="0.25">
@@ -30497,17 +30497,17 @@
       <c r="C777" s="6">
         <v>46296</v>
       </c>
-      <c r="D777" s="8">
-        <v>0</v>
+      <c r="D777" s="10">
+        <v>2.03213</v>
       </c>
       <c r="E777" s="8">
-        <v>0</v>
+        <v>21411893</v>
       </c>
       <c r="F777" s="9">
         <v>234</v>
       </c>
       <c r="G777" s="8">
-        <v>0</v>
+        <v>43511755.05</v>
       </c>
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.25">
@@ -30521,7 +30521,7 @@
         <v>46296</v>
       </c>
       <c r="D778" s="7">
-        <v>0.957285</v>
+        <v>0.955911</v>
       </c>
       <c r="E778" s="8">
         <v>88592774</v>
@@ -30530,7 +30530,7 @@
         <v>695</v>
       </c>
       <c r="G778" s="8">
-        <v>84808502</v>
+        <v>84686764.96</v>
       </c>
     </row>
     <row r="779" spans="1:7" x14ac:dyDescent="0.25">
@@ -30566,17 +30566,17 @@
       <c r="C780" s="6">
         <v>46296</v>
       </c>
-      <c r="D780" s="8">
-        <v>0</v>
+      <c r="D780" s="7">
+        <v>8.813394</v>
       </c>
       <c r="E780" s="8">
-        <v>0</v>
+        <v>6936066</v>
       </c>
       <c r="F780" s="9">
         <v>13</v>
       </c>
       <c r="G780" s="8">
-        <v>0</v>
+        <v>61130285.47</v>
       </c>
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.25">
@@ -30612,17 +30612,17 @@
       <c r="C782" s="6">
         <v>46296</v>
       </c>
-      <c r="D782" s="8">
-        <v>0</v>
+      <c r="D782" s="7">
+        <v>0.003478</v>
       </c>
       <c r="E782" s="8">
-        <v>0</v>
+        <v>568993837</v>
       </c>
       <c r="F782" s="9">
         <v>12</v>
       </c>
       <c r="G782" s="8">
-        <v>0</v>
+        <v>1979122</v>
       </c>
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.25">
@@ -30658,17 +30658,17 @@
       <c r="C784" s="6">
         <v>46296</v>
       </c>
-      <c r="D784" s="8">
-        <v>0</v>
+      <c r="D784" s="7">
+        <v>0.396787</v>
       </c>
       <c r="E784" s="8">
-        <v>0</v>
+        <v>1151128347</v>
       </c>
       <c r="F784" s="9">
         <v>13</v>
       </c>
       <c r="G784" s="8">
-        <v>0</v>
+        <v>456752626.41</v>
       </c>
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.25">
@@ -30681,17 +30681,17 @@
       <c r="C785" s="6">
         <v>46296</v>
       </c>
-      <c r="D785" s="8">
-        <v>0</v>
+      <c r="D785" s="7">
+        <v>22.424022</v>
       </c>
       <c r="E785" s="8">
-        <v>0</v>
+        <v>2727730</v>
       </c>
       <c r="F785" s="9">
         <v>16</v>
       </c>
       <c r="G785" s="8">
-        <v>0</v>
+        <v>61166676.65</v>
       </c>
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.25">
@@ -30727,17 +30727,17 @@
       <c r="C787" s="6">
         <v>46296</v>
       </c>
-      <c r="D787" s="8">
-        <v>0</v>
+      <c r="D787" s="7">
+        <v>5.030688</v>
       </c>
       <c r="E787" s="8">
-        <v>0</v>
+        <v>77031628</v>
       </c>
       <c r="F787" s="9">
         <v>1190</v>
       </c>
       <c r="G787" s="8">
-        <v>0</v>
+        <v>387522064.21</v>
       </c>
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.25">
@@ -30750,17 +30750,17 @@
       <c r="C788" s="6">
         <v>46296</v>
       </c>
-      <c r="D788" s="8">
-        <v>0</v>
+      <c r="D788" s="7">
+        <v>20.169115</v>
       </c>
       <c r="E788" s="8">
-        <v>0</v>
+        <v>52526</v>
       </c>
       <c r="F788" s="9">
         <v>11</v>
       </c>
       <c r="G788" s="8">
-        <v>0</v>
+        <v>1059402.91</v>
       </c>
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.25">
@@ -30773,17 +30773,17 @@
       <c r="C789" s="6">
         <v>46296</v>
       </c>
-      <c r="D789" s="8">
-        <v>0</v>
+      <c r="D789" s="7">
+        <v>5.884513</v>
       </c>
       <c r="E789" s="8">
-        <v>0</v>
+        <v>325196</v>
       </c>
       <c r="F789" s="9">
         <v>12</v>
       </c>
       <c r="G789" s="8">
-        <v>0</v>
+        <v>1913620</v>
       </c>
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.25">
@@ -30911,17 +30911,17 @@
       <c r="C795" s="6">
         <v>46296</v>
       </c>
-      <c r="D795" s="8">
-        <v>0</v>
+      <c r="D795" s="7">
+        <v>11.422529</v>
       </c>
       <c r="E795" s="8">
-        <v>0</v>
+        <v>18395521</v>
       </c>
       <c r="F795" s="9">
         <v>41</v>
       </c>
       <c r="G795" s="8">
-        <v>0</v>
+        <v>210123365.79</v>
       </c>
     </row>
     <row r="796" spans="1:7" x14ac:dyDescent="0.25">
@@ -30980,17 +30980,17 @@
       <c r="C798" s="6">
         <v>46296</v>
       </c>
-      <c r="D798" s="8">
-        <v>0</v>
+      <c r="D798" s="7">
+        <v>6.563332</v>
       </c>
       <c r="E798" s="8">
-        <v>0</v>
+        <v>926146311</v>
       </c>
       <c r="F798" s="9">
         <v>6244</v>
       </c>
       <c r="G798" s="8">
-        <v>0</v>
+        <v>6078605400.5</v>
       </c>
     </row>
     <row r="799" spans="1:7" x14ac:dyDescent="0.25">
@@ -31234,7 +31234,7 @@
         <v>46296</v>
       </c>
       <c r="D809" s="7">
-        <v>2.742896</v>
+        <v>2.742873</v>
       </c>
       <c r="E809" s="8">
         <v>7094208</v>
@@ -31243,7 +31243,7 @@
         <v>188</v>
       </c>
       <c r="G809" s="8">
-        <v>19458674.82</v>
+        <v>19458511.54</v>
       </c>
     </row>
     <row r="810" spans="1:7" x14ac:dyDescent="0.25">
@@ -31486,17 +31486,17 @@
       <c r="C820" s="6">
         <v>46296</v>
       </c>
-      <c r="D820" s="8">
-        <v>0</v>
+      <c r="D820" s="7">
+        <v>0.539106</v>
       </c>
       <c r="E820" s="8">
-        <v>0</v>
+        <v>1064121231</v>
       </c>
       <c r="F820" s="9">
         <v>2642</v>
       </c>
       <c r="G820" s="8">
-        <v>0</v>
+        <v>573674276.2</v>
       </c>
     </row>
     <row r="821" spans="1:7" x14ac:dyDescent="0.25">
@@ -31509,17 +31509,17 @@
       <c r="C821" s="6">
         <v>46296</v>
       </c>
-      <c r="D821" s="8">
-        <v>0</v>
+      <c r="D821" s="7">
+        <v>1.305731</v>
       </c>
       <c r="E821" s="8">
-        <v>0</v>
+        <v>16801847</v>
       </c>
       <c r="F821" s="9">
         <v>267</v>
       </c>
       <c r="G821" s="8">
-        <v>0</v>
+        <v>21938694.2</v>
       </c>
     </row>
     <row r="822" spans="1:7" x14ac:dyDescent="0.25">
@@ -31532,17 +31532,17 @@
       <c r="C822" s="6">
         <v>46296</v>
       </c>
-      <c r="D822" s="8">
-        <v>0</v>
+      <c r="D822" s="7">
+        <v>139.180973</v>
       </c>
       <c r="E822" s="8">
-        <v>0</v>
+        <v>247637</v>
       </c>
       <c r="F822" s="9">
         <v>187</v>
       </c>
       <c r="G822" s="8">
-        <v>0</v>
+        <v>34466358.53</v>
       </c>
     </row>
     <row r="823" spans="1:7" x14ac:dyDescent="0.25">
@@ -31578,17 +31578,17 @@
       <c r="C824" s="6">
         <v>46296</v>
       </c>
-      <c r="D824" s="8">
-        <v>0</v>
+      <c r="D824" s="7">
+        <v>179.232802</v>
       </c>
       <c r="E824" s="8">
-        <v>0</v>
+        <v>95118</v>
       </c>
       <c r="F824" s="9">
         <v>520</v>
       </c>
       <c r="G824" s="8">
-        <v>0</v>
+        <v>17048265.65</v>
       </c>
     </row>
     <row r="825" spans="1:7" x14ac:dyDescent="0.25">
@@ -31693,17 +31693,17 @@
       <c r="C829" s="6">
         <v>46296</v>
       </c>
-      <c r="D829" s="8">
-        <v>0</v>
+      <c r="D829" s="7">
+        <v>50.370025</v>
       </c>
       <c r="E829" s="8">
-        <v>0</v>
+        <v>152577</v>
       </c>
       <c r="F829" s="9">
         <v>53</v>
       </c>
       <c r="G829" s="8">
-        <v>0</v>
+        <v>7685307.26</v>
       </c>
     </row>
     <row r="830" spans="1:7" x14ac:dyDescent="0.25">
@@ -31716,17 +31716,17 @@
       <c r="C830" s="6">
         <v>46296</v>
       </c>
-      <c r="D830" s="8">
-        <v>0</v>
+      <c r="D830" s="7">
+        <v>6.152651</v>
       </c>
       <c r="E830" s="8">
-        <v>0</v>
+        <v>941900</v>
       </c>
       <c r="F830" s="9">
         <v>43</v>
       </c>
       <c r="G830" s="8">
-        <v>0</v>
+        <v>5795181.98</v>
       </c>
     </row>
     <row r="831" spans="1:7" x14ac:dyDescent="0.25">
@@ -31946,17 +31946,17 @@
       <c r="C840" s="6">
         <v>46296</v>
       </c>
-      <c r="D840" s="8">
-        <v>0</v>
+      <c r="D840" s="7">
+        <v>0.240593</v>
       </c>
       <c r="E840" s="8">
-        <v>0</v>
+        <v>2246994841.13</v>
       </c>
       <c r="F840" s="9">
         <v>2324</v>
       </c>
       <c r="G840" s="8">
-        <v>0</v>
+        <v>540611079.3</v>
       </c>
     </row>
     <row r="841" spans="1:7" x14ac:dyDescent="0.25">
@@ -32084,17 +32084,17 @@
       <c r="C846" s="6">
         <v>46296</v>
       </c>
-      <c r="D846" s="8">
-        <v>0</v>
+      <c r="D846" s="7">
+        <v>8.565755</v>
       </c>
       <c r="E846" s="8">
-        <v>0</v>
+        <v>406846</v>
       </c>
       <c r="F846" s="9">
         <v>394</v>
       </c>
       <c r="G846" s="8">
-        <v>0</v>
+        <v>3484943.25</v>
       </c>
     </row>
     <row r="847" spans="1:7" x14ac:dyDescent="0.25">
@@ -33211,17 +33211,17 @@
       <c r="C895" s="6">
         <v>46296</v>
       </c>
-      <c r="D895" s="8">
-        <v>0</v>
+      <c r="D895" s="7">
+        <v>5.642057</v>
       </c>
       <c r="E895" s="8">
-        <v>0</v>
+        <v>66550045</v>
       </c>
       <c r="F895" s="9">
         <v>19</v>
       </c>
       <c r="G895" s="8">
-        <v>0</v>
+        <v>375479143.02</v>
       </c>
     </row>
     <row r="896" spans="1:7" x14ac:dyDescent="0.25">
@@ -33810,7 +33810,7 @@
         <v>46296</v>
       </c>
       <c r="D921" s="7">
-        <v>0.125827</v>
+        <v>0.125663</v>
       </c>
       <c r="E921" s="8">
         <v>1127043729</v>
@@ -33819,7 +33819,7 @@
         <v>56</v>
       </c>
       <c r="G921" s="8">
-        <v>141812907.6</v>
+        <v>141627944.72</v>
       </c>
     </row>
     <row r="922" spans="1:7" x14ac:dyDescent="0.25">
@@ -33925,7 +33925,7 @@
         <v>46296</v>
       </c>
       <c r="D926" s="7">
-        <v>0.187991</v>
+        <v>0.188151</v>
       </c>
       <c r="E926" s="8">
         <v>35241410409</v>
@@ -33934,7 +33934,7 @@
         <v>150</v>
       </c>
       <c r="G926" s="8">
-        <v>6625067599.12</v>
+        <v>6630711069.23</v>
       </c>
     </row>
     <row r="927" spans="1:7" x14ac:dyDescent="0.25">
@@ -34062,17 +34062,17 @@
       <c r="C932" s="6">
         <v>46296</v>
       </c>
-      <c r="D932" s="8">
-        <v>0</v>
+      <c r="D932" s="7">
+        <v>7.661774</v>
       </c>
       <c r="E932" s="8">
-        <v>0</v>
+        <v>49337491</v>
       </c>
       <c r="F932" s="9">
         <v>1496</v>
       </c>
       <c r="G932" s="8">
-        <v>0</v>
+        <v>378012688.66</v>
       </c>
     </row>
     <row r="933" spans="1:7" x14ac:dyDescent="0.25">
@@ -35304,17 +35304,17 @@
       <c r="C986" s="6">
         <v>46296</v>
       </c>
-      <c r="D986" s="8">
-        <v>0</v>
+      <c r="D986" s="7">
+        <v>1.677996</v>
       </c>
       <c r="E986" s="8">
-        <v>0</v>
+        <v>6030240</v>
       </c>
       <c r="F986" s="9">
         <v>134</v>
       </c>
       <c r="G986" s="8">
-        <v>0</v>
+        <v>10118716.66</v>
       </c>
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.25">
@@ -35396,17 +35396,17 @@
       <c r="C990" s="6">
         <v>46296</v>
       </c>
-      <c r="D990" s="8">
-        <v>0</v>
+      <c r="D990" s="7">
+        <v>59.236076</v>
       </c>
       <c r="E990" s="8">
-        <v>0</v>
+        <v>248988</v>
       </c>
       <c r="F990" s="9">
         <v>12</v>
       </c>
       <c r="G990" s="8">
-        <v>0</v>
+        <v>14749072.18</v>
       </c>
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
@@ -35673,7 +35673,7 @@
         <v>46296</v>
       </c>
       <c r="D1002" s="7">
-        <v>2.821362</v>
+        <v>2.821372</v>
       </c>
       <c r="E1002" s="8">
         <v>942497355</v>
@@ -35682,7 +35682,7 @@
         <v>29112</v>
       </c>
       <c r="G1002" s="8">
-        <v>2659125848.99</v>
+        <v>2659135383.84</v>
       </c>
     </row>
     <row r="1003" spans="1:7" x14ac:dyDescent="0.25">
@@ -35741,17 +35741,17 @@
       <c r="C1005" s="6">
         <v>46296</v>
       </c>
-      <c r="D1005" s="8">
-        <v>0</v>
+      <c r="D1005" s="7">
+        <v>1.263059</v>
       </c>
       <c r="E1005" s="8">
-        <v>0</v>
+        <v>8372118</v>
       </c>
       <c r="F1005" s="9">
         <v>173</v>
       </c>
       <c r="G1005" s="8">
-        <v>0</v>
+        <v>10574477.92</v>
       </c>
     </row>
     <row r="1006" spans="1:7" x14ac:dyDescent="0.25">
@@ -35972,16 +35972,16 @@
         <v>46296</v>
       </c>
       <c r="D1015" s="7">
-        <v>4.861269</v>
+        <v>4.861271</v>
       </c>
       <c r="E1015" s="8">
-        <v>41490694</v>
+        <v>45608821</v>
       </c>
       <c r="F1015" s="9">
         <v>832</v>
       </c>
       <c r="G1015" s="8">
-        <v>221716745.35</v>
+        <v>221716834.9</v>
       </c>
     </row>
     <row r="1016" spans="1:7" x14ac:dyDescent="0.25">
@@ -35994,17 +35994,17 @@
       <c r="C1016" s="6">
         <v>46296</v>
       </c>
-      <c r="D1016" s="8">
-        <v>0</v>
+      <c r="D1016" s="7">
+        <v>1.594776</v>
       </c>
       <c r="E1016" s="8">
-        <v>0</v>
+        <v>38675606</v>
       </c>
       <c r="F1016" s="9">
         <v>20</v>
       </c>
       <c r="G1016" s="8">
-        <v>0</v>
+        <v>61678914.41</v>
       </c>
     </row>
     <row r="1017" spans="1:7" x14ac:dyDescent="0.25">
@@ -36109,17 +36109,17 @@
       <c r="C1021" s="6">
         <v>46296</v>
       </c>
-      <c r="D1021" s="8">
-        <v>0</v>
+      <c r="D1021" s="7">
+        <v>57.692633</v>
       </c>
       <c r="E1021" s="8">
-        <v>0</v>
+        <v>617027</v>
       </c>
       <c r="F1021" s="9">
         <v>34</v>
       </c>
       <c r="G1021" s="8">
-        <v>0</v>
+        <v>35597911.96</v>
       </c>
     </row>
     <row r="1022" spans="1:7" x14ac:dyDescent="0.25">
@@ -36570,7 +36570,7 @@
         <v>46296</v>
       </c>
       <c r="D1041" s="7">
-        <v>2.008649</v>
+        <v>2.008251</v>
       </c>
       <c r="E1041" s="8">
         <v>511425354</v>
@@ -36579,7 +36579,7 @@
         <v>15085</v>
       </c>
       <c r="G1041" s="8">
-        <v>1027273966.08</v>
+        <v>1027070238.57</v>
       </c>
     </row>
     <row r="1042" spans="1:7" x14ac:dyDescent="0.25">
@@ -36868,17 +36868,17 @@
       <c r="C1054" s="6">
         <v>46296</v>
       </c>
-      <c r="D1054" s="8">
-        <v>0</v>
+      <c r="D1054" s="7">
+        <v>53.029105</v>
       </c>
       <c r="E1054" s="8">
-        <v>0</v>
+        <v>262119</v>
       </c>
       <c r="F1054" s="9">
         <v>5</v>
       </c>
       <c r="G1054" s="8">
-        <v>0</v>
+        <v>13899935.93</v>
       </c>
     </row>
     <row r="1055" spans="1:7" x14ac:dyDescent="0.25">
@@ -37075,17 +37075,17 @@
       <c r="C1063" s="6">
         <v>46296</v>
       </c>
-      <c r="D1063" s="8">
-        <v>0</v>
+      <c r="D1063" s="7">
+        <v>0.928783</v>
       </c>
       <c r="E1063" s="8">
-        <v>0</v>
+        <v>1508400</v>
       </c>
       <c r="F1063" s="9">
         <v>16</v>
       </c>
       <c r="G1063" s="8">
-        <v>0</v>
+        <v>1400975.54</v>
       </c>
     </row>
     <row r="1064" spans="1:7" x14ac:dyDescent="0.25">
@@ -37099,7 +37099,7 @@
         <v>46296</v>
       </c>
       <c r="D1064" s="7">
-        <v>3.294512</v>
+        <v>3.294405</v>
       </c>
       <c r="E1064" s="8">
         <v>110311411</v>
@@ -37108,7 +37108,7 @@
         <v>541</v>
       </c>
       <c r="G1064" s="8">
-        <v>363422267.75</v>
+        <v>363410423.69</v>
       </c>
     </row>
     <row r="1065" spans="1:7" x14ac:dyDescent="0.25">
@@ -37213,17 +37213,17 @@
       <c r="C1069" s="6">
         <v>46296</v>
       </c>
-      <c r="D1069" s="8">
-        <v>0</v>
+      <c r="D1069" s="7">
+        <v>21.288678</v>
       </c>
       <c r="E1069" s="8">
-        <v>0</v>
+        <v>1779644</v>
       </c>
       <c r="F1069" s="9">
         <v>514</v>
       </c>
       <c r="G1069" s="8">
-        <v>0</v>
+        <v>37886267.79</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.25">
@@ -37236,17 +37236,17 @@
       <c r="C1070" s="6">
         <v>46296</v>
       </c>
-      <c r="D1070" s="8">
-        <v>0</v>
+      <c r="D1070" s="7">
+        <v>1.361327</v>
       </c>
       <c r="E1070" s="8">
-        <v>0</v>
+        <v>1303124471</v>
       </c>
       <c r="F1070" s="9">
         <v>41</v>
       </c>
       <c r="G1070" s="8">
-        <v>0</v>
+        <v>1773977877.5</v>
       </c>
     </row>
     <row r="1071" spans="1:7" x14ac:dyDescent="0.25">
@@ -37305,17 +37305,17 @@
       <c r="C1073" s="6">
         <v>46296</v>
       </c>
-      <c r="D1073" s="8">
-        <v>0</v>
+      <c r="D1073" s="10">
+        <v>0.52832</v>
       </c>
       <c r="E1073" s="8">
-        <v>0</v>
+        <v>2311372720</v>
       </c>
       <c r="F1073" s="9">
         <v>866</v>
       </c>
       <c r="G1073" s="8">
-        <v>0</v>
+        <v>1221144522.92</v>
       </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.25">
@@ -37328,17 +37328,17 @@
       <c r="C1074" s="6">
         <v>46296</v>
       </c>
-      <c r="D1074" s="8">
-        <v>0</v>
+      <c r="D1074" s="7">
+        <v>75.917782</v>
       </c>
       <c r="E1074" s="8">
-        <v>0</v>
+        <v>9758952</v>
       </c>
       <c r="F1074" s="9">
         <v>133</v>
       </c>
       <c r="G1074" s="8">
-        <v>0</v>
+        <v>740877992.99</v>
       </c>
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.25">
@@ -37374,17 +37374,17 @@
       <c r="C1076" s="6">
         <v>46296</v>
       </c>
-      <c r="D1076" s="8">
-        <v>0</v>
+      <c r="D1076" s="11">
+        <v>4.2752</v>
       </c>
       <c r="E1076" s="8">
-        <v>0</v>
+        <v>2956653121</v>
       </c>
       <c r="F1076" s="9">
         <v>3896</v>
       </c>
       <c r="G1076" s="8">
-        <v>0</v>
+        <v>12640283380.84</v>
       </c>
     </row>
     <row r="1077" spans="1:7" x14ac:dyDescent="0.25">
@@ -37651,7 +37651,7 @@
         <v>46296</v>
       </c>
       <c r="D1088" s="7">
-        <v>2.802049</v>
+        <v>2.801346</v>
       </c>
       <c r="E1088" s="8">
         <v>534965854</v>
@@ -37660,7 +37660,7 @@
         <v>20775</v>
       </c>
       <c r="G1088" s="8">
-        <v>1499000747.11</v>
+        <v>1498624325.88</v>
       </c>
     </row>
     <row r="1089" spans="1:7" x14ac:dyDescent="0.25">
@@ -37880,17 +37880,17 @@
       <c r="C1098" s="6">
         <v>46296</v>
       </c>
-      <c r="D1098" s="8">
-        <v>0</v>
+      <c r="D1098" s="7">
+        <v>0.761759</v>
       </c>
       <c r="E1098" s="8">
-        <v>0</v>
+        <v>695182316</v>
       </c>
       <c r="F1098" s="9">
         <v>3170</v>
       </c>
       <c r="G1098" s="8">
-        <v>0</v>
+        <v>529561205.09</v>
       </c>
     </row>
     <row r="1099" spans="1:7" x14ac:dyDescent="0.25">
@@ -37949,8 +37949,8 @@
       <c r="C1101" s="6">
         <v>46296</v>
       </c>
-      <c r="D1101" s="7">
-        <v>11.765322</v>
+      <c r="D1101" s="10">
+        <v>11.76514</v>
       </c>
       <c r="E1101" s="8">
         <v>601671166</v>
@@ -37959,7 +37959,7 @@
         <v>38305</v>
       </c>
       <c r="G1101" s="8">
-        <v>7078855090.12</v>
+        <v>7078745455.31</v>
       </c>
     </row>
     <row r="1102" spans="1:7" x14ac:dyDescent="0.25">
@@ -37995,17 +37995,17 @@
       <c r="C1103" s="6">
         <v>46296</v>
       </c>
-      <c r="D1103" s="8">
-        <v>0</v>
+      <c r="D1103" s="7">
+        <v>1.315826</v>
       </c>
       <c r="E1103" s="8">
-        <v>0</v>
+        <v>662730892</v>
       </c>
       <c r="F1103" s="9">
         <v>127</v>
       </c>
       <c r="G1103" s="8">
-        <v>0</v>
+        <v>872038255.2</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.25">
@@ -38087,17 +38087,17 @@
       <c r="C1107" s="6">
         <v>46296</v>
       </c>
-      <c r="D1107" s="8">
-        <v>0</v>
+      <c r="D1107" s="7">
+        <v>1.075959</v>
       </c>
       <c r="E1107" s="8">
-        <v>0</v>
+        <v>49280751</v>
       </c>
       <c r="F1107" s="9">
         <v>1311</v>
       </c>
       <c r="G1107" s="8">
-        <v>0</v>
+        <v>53024071.42</v>
       </c>
     </row>
     <row r="1108" spans="1:7" x14ac:dyDescent="0.25">
@@ -38133,17 +38133,17 @@
       <c r="C1109" s="6">
         <v>46296</v>
       </c>
-      <c r="D1109" s="8">
-        <v>0</v>
+      <c r="D1109" s="7">
+        <v>54.243798</v>
       </c>
       <c r="E1109" s="8">
-        <v>0</v>
+        <v>207100</v>
       </c>
       <c r="F1109" s="9">
         <v>18</v>
       </c>
       <c r="G1109" s="8">
-        <v>0</v>
+        <v>11233890.52</v>
       </c>
     </row>
     <row r="1110" spans="1:7" x14ac:dyDescent="0.25">
@@ -38524,17 +38524,17 @@
       <c r="C1126" s="6">
         <v>46296</v>
       </c>
-      <c r="D1126" s="8">
-        <v>0</v>
+      <c r="D1126" s="7">
+        <v>3.923325</v>
       </c>
       <c r="E1126" s="8">
-        <v>0</v>
+        <v>553376235</v>
       </c>
       <c r="F1126" s="9">
         <v>13</v>
       </c>
       <c r="G1126" s="8">
-        <v>0</v>
+        <v>2171074974.3</v>
       </c>
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.25">
@@ -38603,7 +38603,7 @@
         <v>318</v>
       </c>
       <c r="G1129" s="8">
-        <v>22050432.81</v>
+        <v>22050432.8</v>
       </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.25">
@@ -38778,7 +38778,7 @@
         <v>46296</v>
       </c>
       <c r="D1137" s="7">
-        <v>1.363217</v>
+        <v>1.364483</v>
       </c>
       <c r="E1137" s="8">
         <v>357413416</v>
@@ -38787,7 +38787,7 @@
         <v>866</v>
       </c>
       <c r="G1137" s="8">
-        <v>487231914.41</v>
+        <v>487684442.91</v>
       </c>
     </row>
     <row r="1138" spans="1:7" x14ac:dyDescent="0.25">
@@ -38892,17 +38892,17 @@
       <c r="C1142" s="6">
         <v>46296</v>
       </c>
-      <c r="D1142" s="8">
-        <v>0</v>
+      <c r="D1142" s="7">
+        <v>2.307324</v>
       </c>
       <c r="E1142" s="8">
-        <v>0</v>
+        <v>201385491</v>
       </c>
       <c r="F1142" s="9">
         <v>689</v>
       </c>
       <c r="G1142" s="8">
-        <v>0</v>
+        <v>464661546.24</v>
       </c>
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.25">
@@ -39053,8 +39053,8 @@
       <c r="C1149" s="6">
         <v>46296</v>
       </c>
-      <c r="D1149" s="7">
-        <v>33.866392</v>
+      <c r="D1149" s="10">
+        <v>33.86666</v>
       </c>
       <c r="E1149" s="8">
         <v>48447180</v>
@@ -39063,7 +39063,7 @@
         <v>381</v>
       </c>
       <c r="G1149" s="8">
-        <v>1640731203.29</v>
+        <v>1640744177.38</v>
       </c>
     </row>
     <row r="1150" spans="1:7" x14ac:dyDescent="0.25">
@@ -39399,7 +39399,7 @@
         <v>46296</v>
       </c>
       <c r="D1164" s="7">
-        <v>3.222513</v>
+        <v>3.222514</v>
       </c>
       <c r="E1164" s="8">
         <v>23228404</v>
@@ -39408,7 +39408,7 @@
         <v>33</v>
       </c>
       <c r="G1164" s="8">
-        <v>74853824.94</v>
+        <v>74853847.54</v>
       </c>
     </row>
     <row r="1165" spans="1:7" x14ac:dyDescent="0.25">
@@ -39491,7 +39491,7 @@
         <v>46296</v>
       </c>
       <c r="D1168" s="7">
-        <v>22.299805</v>
+        <v>22.300102</v>
       </c>
       <c r="E1168" s="8">
         <v>13934348</v>
@@ -39500,7 +39500,7 @@
         <v>1014</v>
       </c>
       <c r="G1168" s="8">
-        <v>310733238.42</v>
+        <v>310737374.96</v>
       </c>
     </row>
     <row r="1169" spans="1:7" x14ac:dyDescent="0.25">
@@ -39536,17 +39536,17 @@
       <c r="C1170" s="6">
         <v>46296</v>
       </c>
-      <c r="D1170" s="8">
-        <v>0</v>
+      <c r="D1170" s="7">
+        <v>1.220991</v>
       </c>
       <c r="E1170" s="8">
-        <v>0</v>
+        <v>10880003</v>
       </c>
       <c r="F1170" s="9">
         <v>97</v>
       </c>
       <c r="G1170" s="8">
-        <v>0</v>
+        <v>13284380.52</v>
       </c>
     </row>
     <row r="1171" spans="1:7" x14ac:dyDescent="0.25">
@@ -39606,7 +39606,7 @@
         <v>46296</v>
       </c>
       <c r="D1173" s="7">
-        <v>2.088477</v>
+        <v>2.088508</v>
       </c>
       <c r="E1173" s="8">
         <v>11771490</v>
@@ -39615,7 +39615,7 @@
         <v>14</v>
       </c>
       <c r="G1173" s="8">
-        <v>24584483.51</v>
+        <v>24584853.84</v>
       </c>
     </row>
     <row r="1174" spans="1:7" x14ac:dyDescent="0.25">
@@ -39882,7 +39882,7 @@
         <v>46296</v>
       </c>
       <c r="D1185" s="7">
-        <v>1.806172</v>
+        <v>1.806173</v>
       </c>
       <c r="E1185" s="8">
         <v>62530177</v>
@@ -39891,7 +39891,7 @@
         <v>1876</v>
       </c>
       <c r="G1185" s="8">
-        <v>112940242.66</v>
+        <v>112940343.27</v>
       </c>
     </row>
     <row r="1186" spans="1:7" x14ac:dyDescent="0.25">
@@ -40042,17 +40042,17 @@
       <c r="C1192" s="6">
         <v>46296</v>
       </c>
-      <c r="D1192" s="8">
-        <v>0</v>
+      <c r="D1192" s="7">
+        <v>5.288329</v>
       </c>
       <c r="E1192" s="8">
-        <v>0</v>
+        <v>13942841</v>
       </c>
       <c r="F1192" s="9">
         <v>1917</v>
       </c>
       <c r="G1192" s="8">
-        <v>0</v>
+        <v>73734334.19</v>
       </c>
     </row>
     <row r="1193" spans="1:7" x14ac:dyDescent="0.25">
@@ -40181,7 +40181,7 @@
         <v>46296</v>
       </c>
       <c r="D1198" s="7">
-        <v>1.070875</v>
+        <v>1.071147</v>
       </c>
       <c r="E1198" s="8">
         <v>58874427</v>
@@ -40190,7 +40190,7 @@
         <v>15</v>
       </c>
       <c r="G1198" s="8">
-        <v>63047131.37</v>
+        <v>63063190.5</v>
       </c>
     </row>
     <row r="1199" spans="1:7" x14ac:dyDescent="0.25">
@@ -40456,17 +40456,17 @@
       <c r="C1210" s="6">
         <v>46296</v>
       </c>
-      <c r="D1210" s="8">
-        <v>0</v>
+      <c r="D1210" s="7">
+        <v>4.134289</v>
       </c>
       <c r="E1210" s="8">
-        <v>0</v>
+        <v>250768612</v>
       </c>
       <c r="F1210" s="9">
         <v>60</v>
       </c>
       <c r="G1210" s="8">
-        <v>0</v>
+        <v>1036749829.72</v>
       </c>
     </row>
     <row r="1211" spans="1:7" x14ac:dyDescent="0.25">
@@ -40917,7 +40917,7 @@
         <v>46296</v>
       </c>
       <c r="D1230" s="7">
-        <v>1.437199</v>
+        <v>1.438487</v>
       </c>
       <c r="E1230" s="8">
         <v>52188774</v>
@@ -40926,7 +40926,7 @@
         <v>646</v>
       </c>
       <c r="G1230" s="8">
-        <v>75005658.4</v>
+        <v>75072852.15</v>
       </c>
     </row>
     <row r="1231" spans="1:7" x14ac:dyDescent="0.25">
@@ -40962,17 +40962,17 @@
       <c r="C1232" s="6">
         <v>46296</v>
       </c>
-      <c r="D1232" s="8">
-        <v>0</v>
+      <c r="D1232" s="7">
+        <v>51.973236</v>
       </c>
       <c r="E1232" s="8">
-        <v>0</v>
+        <v>3559908</v>
       </c>
       <c r="F1232" s="9">
         <v>19</v>
       </c>
       <c r="G1232" s="8">
-        <v>0</v>
+        <v>185019936.97</v>
       </c>
     </row>
     <row r="1233" spans="1:7" x14ac:dyDescent="0.25">
@@ -41009,7 +41009,7 @@
         <v>46296</v>
       </c>
       <c r="D1234" s="7">
-        <v>1.496152</v>
+        <v>1.498099</v>
       </c>
       <c r="E1234" s="8">
         <v>166295122</v>
@@ -41018,7 +41018,7 @@
         <v>6912</v>
       </c>
       <c r="G1234" s="8">
-        <v>248802838.42</v>
+        <v>249126551.66</v>
       </c>
     </row>
     <row r="1235" spans="1:7" x14ac:dyDescent="0.25">
@@ -41146,8 +41146,8 @@
       <c r="C1240" s="6">
         <v>46296</v>
       </c>
-      <c r="D1240" s="8">
-        <v>0</v>
+      <c r="D1240" s="11">
+        <v>1.2213</v>
       </c>
       <c r="E1240" s="8">
         <v>610784820</v>
@@ -41156,7 +41156,7 @@
         <v>250</v>
       </c>
       <c r="G1240" s="8">
-        <v>0</v>
+        <v>745951522.45</v>
       </c>
     </row>
     <row r="1241" spans="1:7" x14ac:dyDescent="0.25">
@@ -41169,17 +41169,17 @@
       <c r="C1241" s="6">
         <v>46296</v>
       </c>
-      <c r="D1241" s="8">
-        <v>0</v>
+      <c r="D1241" s="7">
+        <v>19.158756</v>
       </c>
       <c r="E1241" s="8">
-        <v>0</v>
+        <v>77294940</v>
       </c>
       <c r="F1241" s="9">
         <v>16982</v>
       </c>
       <c r="G1241" s="8">
-        <v>0</v>
+        <v>1480874901.34</v>
       </c>
     </row>
     <row r="1242" spans="1:7" x14ac:dyDescent="0.25">
@@ -41285,7 +41285,7 @@
         <v>46296</v>
       </c>
       <c r="D1246" s="7">
-        <v>1.427354</v>
+        <v>1.427903</v>
       </c>
       <c r="E1246" s="8">
         <v>90933762</v>
@@ -41294,7 +41294,7 @@
         <v>568</v>
       </c>
       <c r="G1246" s="8">
-        <v>129794685.29</v>
+        <v>129844549.82</v>
       </c>
     </row>
     <row r="1247" spans="1:7" x14ac:dyDescent="0.25">
@@ -41445,8 +41445,8 @@
       <c r="C1253" s="6">
         <v>46296</v>
       </c>
-      <c r="D1253" s="8">
-        <v>0</v>
+      <c r="D1253" s="7">
+        <v>2.256871</v>
       </c>
       <c r="E1253" s="8">
         <v>968105257</v>
@@ -41455,7 +41455,7 @@
         <v>1063</v>
       </c>
       <c r="G1253" s="8">
-        <v>0</v>
+        <v>2184888611.87</v>
       </c>
     </row>
     <row r="1254" spans="1:7" x14ac:dyDescent="0.25">
@@ -42043,17 +42043,17 @@
       <c r="C1279" s="6">
         <v>46296</v>
       </c>
-      <c r="D1279" s="8">
-        <v>0</v>
+      <c r="D1279" s="10">
+        <v>1.04868</v>
       </c>
       <c r="E1279" s="8">
-        <v>0</v>
+        <v>1263740037</v>
       </c>
       <c r="F1279" s="9">
         <v>514</v>
       </c>
       <c r="G1279" s="8">
-        <v>0</v>
+        <v>1325259308.76</v>
       </c>
     </row>
     <row r="1280" spans="1:7" x14ac:dyDescent="0.25">
@@ -42365,17 +42365,17 @@
       <c r="C1293" s="6">
         <v>46296</v>
       </c>
-      <c r="D1293" s="8">
-        <v>0</v>
+      <c r="D1293" s="7">
+        <v>57.573763</v>
       </c>
       <c r="E1293" s="8">
-        <v>0</v>
+        <v>3303149</v>
       </c>
       <c r="F1293" s="9">
         <v>113</v>
       </c>
       <c r="G1293" s="8">
-        <v>0</v>
+        <v>190174718.23</v>
       </c>
     </row>
     <row r="1294" spans="1:7" x14ac:dyDescent="0.25">
@@ -42411,17 +42411,17 @@
       <c r="C1295" s="6">
         <v>46296</v>
       </c>
-      <c r="D1295" s="8">
-        <v>0</v>
+      <c r="D1295" s="7">
+        <v>4.005312</v>
       </c>
       <c r="E1295" s="8">
-        <v>0</v>
+        <v>38141733</v>
       </c>
       <c r="F1295" s="9">
         <v>503</v>
       </c>
       <c r="G1295" s="8">
-        <v>0</v>
+        <v>152769541.11</v>
       </c>
     </row>
     <row r="1296" spans="1:7" x14ac:dyDescent="0.25">
@@ -42480,17 +42480,17 @@
       <c r="C1298" s="6">
         <v>46296</v>
       </c>
-      <c r="D1298" s="8">
-        <v>0</v>
+      <c r="D1298" s="7">
+        <v>8.176063</v>
       </c>
       <c r="E1298" s="8">
-        <v>0</v>
+        <v>22710778</v>
       </c>
       <c r="F1298" s="9">
         <v>393</v>
       </c>
       <c r="G1298" s="8">
-        <v>0</v>
+        <v>185684744.11</v>
       </c>
     </row>
     <row r="1299" spans="1:7" x14ac:dyDescent="0.25">
@@ -42766,7 +42766,7 @@
         <v>26733</v>
       </c>
       <c r="G1310" s="8">
-        <v>44949544712.89</v>
+        <v>44949544453.24</v>
       </c>
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
@@ -42780,7 +42780,7 @@
         <v>46296</v>
       </c>
       <c r="D1311" s="7">
-        <v>13.221059</v>
+        <v>13.214083</v>
       </c>
       <c r="E1311" s="8">
         <v>317937782</v>
@@ -42789,7 +42789,7 @@
         <v>10335</v>
       </c>
       <c r="G1311" s="8">
-        <v>4203474216.7</v>
+        <v>4201256165.13</v>
       </c>
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
@@ -43124,17 +43124,17 @@
       <c r="C1326" s="6">
         <v>46296</v>
       </c>
-      <c r="D1326" s="8">
-        <v>0</v>
+      <c r="D1326" s="7">
+        <v>53.850751</v>
       </c>
       <c r="E1326" s="8">
-        <v>0</v>
+        <v>75339807</v>
       </c>
       <c r="F1326" s="9">
         <v>513</v>
       </c>
       <c r="G1326" s="8">
-        <v>0</v>
+        <v>4057105223.35</v>
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
@@ -43285,17 +43285,17 @@
       <c r="C1333" s="6">
         <v>46296</v>
       </c>
-      <c r="D1333" s="8">
-        <v>0</v>
+      <c r="D1333" s="7">
+        <v>54.234441</v>
       </c>
       <c r="E1333" s="8">
-        <v>0</v>
+        <v>85907830</v>
       </c>
       <c r="F1333" s="9">
         <v>350</v>
       </c>
       <c r="G1333" s="8">
-        <v>0</v>
+        <v>4659163120.71</v>
       </c>
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
@@ -43308,17 +43308,17 @@
       <c r="C1334" s="6">
         <v>46296</v>
       </c>
-      <c r="D1334" s="8">
-        <v>0</v>
+      <c r="D1334" s="7">
+        <v>66.960735</v>
       </c>
       <c r="E1334" s="8">
-        <v>0</v>
+        <v>35120229</v>
       </c>
       <c r="F1334" s="9">
         <v>719</v>
       </c>
       <c r="G1334" s="8">
-        <v>0</v>
+        <v>2351676344.62</v>
       </c>
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
@@ -43745,17 +43745,17 @@
       <c r="C1353" s="6">
         <v>46296</v>
       </c>
-      <c r="D1353" s="8">
-        <v>0</v>
+      <c r="D1353" s="7">
+        <v>6.928897</v>
       </c>
       <c r="E1353" s="8">
-        <v>0</v>
+        <v>415180102</v>
       </c>
       <c r="F1353" s="9">
         <v>19471</v>
       </c>
       <c r="G1353" s="8">
-        <v>0</v>
+        <v>2876740313.29</v>
       </c>
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
@@ -43998,17 +43998,17 @@
       <c r="C1364" s="6">
         <v>46296</v>
       </c>
-      <c r="D1364" s="8">
-        <v>0</v>
+      <c r="D1364" s="7">
+        <v>0.168391</v>
       </c>
       <c r="E1364" s="8">
-        <v>0</v>
+        <v>19602512670</v>
       </c>
       <c r="F1364" s="9">
         <v>7820</v>
       </c>
       <c r="G1364" s="8">
-        <v>0</v>
+        <v>3300881904.35</v>
       </c>
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.25">
@@ -44113,17 +44113,17 @@
       <c r="C1369" s="6">
         <v>46296</v>
       </c>
-      <c r="D1369" s="8">
-        <v>0</v>
+      <c r="D1369" s="7">
+        <v>1.065129</v>
       </c>
       <c r="E1369" s="8">
-        <v>0</v>
+        <v>28725759</v>
       </c>
       <c r="F1369" s="9">
         <v>377</v>
       </c>
       <c r="G1369" s="8">
-        <v>0</v>
+        <v>30596639.8</v>
       </c>
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.25">
@@ -44297,17 +44297,17 @@
       <c r="C1377" s="6">
         <v>46296</v>
       </c>
-      <c r="D1377" s="8">
-        <v>0</v>
+      <c r="D1377" s="7">
+        <v>6.762084</v>
       </c>
       <c r="E1377" s="8">
-        <v>0</v>
+        <v>3829036</v>
       </c>
       <c r="F1377" s="9">
         <v>11</v>
       </c>
       <c r="G1377" s="8">
-        <v>0</v>
+        <v>25892262.16</v>
       </c>
     </row>
     <row r="1378" spans="1:7" x14ac:dyDescent="0.25">
@@ -44343,17 +44343,17 @@
       <c r="C1379" s="6">
         <v>46296</v>
       </c>
-      <c r="D1379" s="8">
-        <v>0</v>
+      <c r="D1379" s="7">
+        <v>0.975712</v>
       </c>
       <c r="E1379" s="8">
-        <v>0</v>
+        <v>2398294516</v>
       </c>
       <c r="F1379" s="9">
         <v>12</v>
       </c>
       <c r="G1379" s="8">
-        <v>0</v>
+        <v>2340045225.18</v>
       </c>
     </row>
     <row r="1380" spans="1:7" x14ac:dyDescent="0.25">
@@ -44642,17 +44642,17 @@
       <c r="C1392" s="6">
         <v>46296</v>
       </c>
-      <c r="D1392" s="8">
-        <v>0</v>
+      <c r="D1392" s="7">
+        <v>0.255044</v>
       </c>
       <c r="E1392" s="8">
-        <v>0</v>
+        <v>9682097247</v>
       </c>
       <c r="F1392" s="9">
         <v>14</v>
       </c>
       <c r="G1392" s="8">
-        <v>0</v>
+        <v>2469357823.58</v>
       </c>
     </row>
     <row r="1393" spans="1:7" x14ac:dyDescent="0.25">
@@ -44688,17 +44688,17 @@
       <c r="C1394" s="6">
         <v>46296</v>
       </c>
-      <c r="D1394" s="8">
-        <v>0</v>
+      <c r="D1394" s="11">
+        <v>0.1315</v>
       </c>
       <c r="E1394" s="8">
-        <v>0</v>
+        <v>525815645</v>
       </c>
       <c r="F1394" s="9">
         <v>11</v>
       </c>
       <c r="G1394" s="8">
-        <v>0</v>
+        <v>69145016.15</v>
       </c>
     </row>
     <row r="1395" spans="1:7" x14ac:dyDescent="0.25">
@@ -44872,17 +44872,17 @@
       <c r="C1402" s="6">
         <v>46296</v>
       </c>
-      <c r="D1402" s="8">
-        <v>0</v>
+      <c r="D1402" s="7">
+        <v>23.960228</v>
       </c>
       <c r="E1402" s="8">
-        <v>0</v>
+        <v>403827399</v>
       </c>
       <c r="F1402" s="9">
         <v>45</v>
       </c>
       <c r="G1402" s="8">
-        <v>0</v>
+        <v>9675796492.2</v>
       </c>
     </row>
     <row r="1403" spans="1:7" x14ac:dyDescent="0.25">
@@ -44895,17 +44895,17 @@
       <c r="C1403" s="6">
         <v>46296</v>
       </c>
-      <c r="D1403" s="8">
-        <v>0</v>
+      <c r="D1403" s="7">
+        <v>0.612834</v>
       </c>
       <c r="E1403" s="8">
-        <v>0</v>
+        <v>1328323644</v>
       </c>
       <c r="F1403" s="9">
         <v>12</v>
       </c>
       <c r="G1403" s="8">
-        <v>0</v>
+        <v>814042005.22</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.25">
@@ -44941,17 +44941,17 @@
       <c r="C1405" s="6">
         <v>46296</v>
       </c>
-      <c r="D1405" s="8">
-        <v>0</v>
+      <c r="D1405" s="10">
+        <v>0.26606</v>
       </c>
       <c r="E1405" s="8">
-        <v>0</v>
+        <v>5262810617</v>
       </c>
       <c r="F1405" s="9">
         <v>15</v>
       </c>
       <c r="G1405" s="8">
-        <v>0</v>
+        <v>1400220809.74</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.25">
@@ -45217,17 +45217,17 @@
       <c r="C1417" s="6">
         <v>46296</v>
       </c>
-      <c r="D1417" s="8">
-        <v>0</v>
+      <c r="D1417" s="7">
+        <v>1.529863</v>
       </c>
       <c r="E1417" s="8">
-        <v>0</v>
+        <v>851521280</v>
       </c>
       <c r="F1417" s="9">
         <v>187</v>
       </c>
       <c r="G1417" s="8">
-        <v>0</v>
+        <v>1302710599.61</v>
       </c>
     </row>
     <row r="1418" spans="1:7" x14ac:dyDescent="0.25">
@@ -45309,17 +45309,17 @@
       <c r="C1421" s="6">
         <v>46296</v>
       </c>
-      <c r="D1421" s="8">
-        <v>0</v>
+      <c r="D1421" s="7">
+        <v>0.842999</v>
       </c>
       <c r="E1421" s="8">
-        <v>0</v>
+        <v>2968702</v>
       </c>
       <c r="F1421" s="9">
         <v>91</v>
       </c>
       <c r="G1421" s="8">
-        <v>0</v>
+        <v>2502612.66</v>
       </c>
     </row>
     <row r="1422" spans="1:7" x14ac:dyDescent="0.25">
@@ -45378,17 +45378,17 @@
       <c r="C1424" s="6">
         <v>46296</v>
       </c>
-      <c r="D1424" s="8">
-        <v>0</v>
+      <c r="D1424" s="7">
+        <v>2.591261</v>
       </c>
       <c r="E1424" s="8">
-        <v>0</v>
+        <v>1552185490</v>
       </c>
       <c r="F1424" s="9">
         <v>14</v>
       </c>
       <c r="G1424" s="8">
-        <v>0</v>
+        <v>4022118447.24</v>
       </c>
     </row>
     <row r="1425" spans="1:7" x14ac:dyDescent="0.25">
@@ -45401,17 +45401,17 @@
       <c r="C1425" s="6">
         <v>46296</v>
       </c>
-      <c r="D1425" s="8">
-        <v>0</v>
+      <c r="D1425" s="7">
+        <v>1.110855</v>
       </c>
       <c r="E1425" s="8">
-        <v>0</v>
+        <v>312395595</v>
       </c>
       <c r="F1425" s="9">
         <v>348</v>
       </c>
       <c r="G1425" s="8">
-        <v>0</v>
+        <v>347026346.45</v>
       </c>
     </row>
     <row r="1426" spans="1:7" x14ac:dyDescent="0.25">
@@ -45539,17 +45539,17 @@
       <c r="C1431" s="6">
         <v>46296</v>
       </c>
-      <c r="D1431" s="8">
-        <v>0</v>
+      <c r="D1431" s="7">
+        <v>2.156998</v>
       </c>
       <c r="E1431" s="8">
-        <v>0</v>
+        <v>5883206417</v>
       </c>
       <c r="F1431" s="9">
         <v>2632</v>
       </c>
       <c r="G1431" s="8">
-        <v>0</v>
+        <v>12690062724.14</v>
       </c>
     </row>
     <row r="1432" spans="1:7" x14ac:dyDescent="0.25">
@@ -45562,17 +45562,17 @@
       <c r="C1432" s="6">
         <v>46296</v>
       </c>
-      <c r="D1432" s="8">
-        <v>0</v>
+      <c r="D1432" s="7">
+        <v>0.319752</v>
       </c>
       <c r="E1432" s="8">
-        <v>0</v>
+        <v>4258299901</v>
       </c>
       <c r="F1432" s="9">
         <v>17</v>
       </c>
       <c r="G1432" s="8">
-        <v>0</v>
+        <v>1361598660.71</v>
       </c>
     </row>
     <row r="1433" spans="1:7" x14ac:dyDescent="0.25">
@@ -45585,17 +45585,17 @@
       <c r="C1433" s="6">
         <v>46296</v>
       </c>
-      <c r="D1433" s="8">
-        <v>0</v>
+      <c r="D1433" s="7">
+        <v>1.321498</v>
       </c>
       <c r="E1433" s="8">
-        <v>0</v>
+        <v>492804</v>
       </c>
       <c r="F1433" s="9">
         <v>120</v>
       </c>
       <c r="G1433" s="8">
-        <v>0</v>
+        <v>651239.38</v>
       </c>
     </row>
     <row r="1434" spans="1:7" x14ac:dyDescent="0.25">
@@ -45723,17 +45723,17 @@
       <c r="C1439" s="6">
         <v>46296</v>
       </c>
-      <c r="D1439" s="8">
-        <v>0</v>
+      <c r="D1439" s="7">
+        <v>1.284401</v>
       </c>
       <c r="E1439" s="8">
-        <v>0</v>
+        <v>5451818052</v>
       </c>
       <c r="F1439" s="9">
         <v>20164</v>
       </c>
       <c r="G1439" s="8">
-        <v>0</v>
+        <v>7002322889.8</v>
       </c>
     </row>
     <row r="1440" spans="1:7" x14ac:dyDescent="0.25">
@@ -45746,17 +45746,17 @@
       <c r="C1440" s="6">
         <v>46296</v>
       </c>
-      <c r="D1440" s="8">
-        <v>0</v>
+      <c r="D1440" s="7">
+        <v>1.046964</v>
       </c>
       <c r="E1440" s="8">
-        <v>0</v>
+        <v>1513476425</v>
       </c>
       <c r="F1440" s="9">
         <v>43</v>
       </c>
       <c r="G1440" s="8">
-        <v>0</v>
+        <v>1584555602.31</v>
       </c>
     </row>
     <row r="1441" spans="1:7" x14ac:dyDescent="0.25">
@@ -46551,17 +46551,17 @@
       <c r="C1475" s="6">
         <v>46296</v>
       </c>
-      <c r="D1475" s="8">
-        <v>0</v>
+      <c r="D1475" s="7">
+        <v>3.281222</v>
       </c>
       <c r="E1475" s="8">
-        <v>0</v>
+        <v>5754582499</v>
       </c>
       <c r="F1475" s="9">
         <v>38751</v>
       </c>
       <c r="G1475" s="8">
-        <v>0</v>
+        <v>18882061125.11</v>
       </c>
     </row>
     <row r="1476" spans="1:7" x14ac:dyDescent="0.25">
@@ -47057,17 +47057,17 @@
       <c r="C1497" s="6">
         <v>46296</v>
       </c>
-      <c r="D1497" s="8">
-        <v>0</v>
+      <c r="D1497" s="7">
+        <v>1.245032</v>
       </c>
       <c r="E1497" s="8">
-        <v>0</v>
+        <v>271451753</v>
       </c>
       <c r="F1497" s="9">
         <v>4481</v>
       </c>
       <c r="G1497" s="8">
-        <v>0</v>
+        <v>337966164.33</v>
       </c>
     </row>
     <row r="1498" spans="1:7" x14ac:dyDescent="0.25">
@@ -48713,17 +48713,17 @@
       <c r="C1569" s="6">
         <v>46296</v>
       </c>
-      <c r="D1569" s="8">
-        <v>0</v>
+      <c r="D1569" s="7">
+        <v>5.170086</v>
       </c>
       <c r="E1569" s="8">
-        <v>0</v>
+        <v>915843207</v>
       </c>
       <c r="F1569" s="9">
         <v>5851</v>
       </c>
       <c r="G1569" s="8">
-        <v>0</v>
+        <v>4734988053.35</v>
       </c>
     </row>
     <row r="1570" spans="1:7" x14ac:dyDescent="0.25">
@@ -48759,17 +48759,17 @@
       <c r="C1571" s="6">
         <v>46296</v>
       </c>
-      <c r="D1571" s="8">
-        <v>0</v>
+      <c r="D1571" s="7">
+        <v>5.357024</v>
       </c>
       <c r="E1571" s="8">
-        <v>0</v>
+        <v>217990165</v>
       </c>
       <c r="F1571" s="9">
         <v>131</v>
       </c>
       <c r="G1571" s="8">
-        <v>0</v>
+        <v>1167778595.43</v>
       </c>
     </row>
     <row r="1572" spans="1:7" x14ac:dyDescent="0.25">
@@ -48805,17 +48805,17 @@
       <c r="C1573" s="6">
         <v>46296</v>
       </c>
-      <c r="D1573" s="8">
-        <v>0</v>
+      <c r="D1573" s="7">
+        <v>64.471607</v>
       </c>
       <c r="E1573" s="8">
-        <v>0</v>
+        <v>9272181</v>
       </c>
       <c r="F1573" s="9">
         <v>98</v>
       </c>
       <c r="G1573" s="8">
-        <v>0</v>
+        <v>597792412.15</v>
       </c>
     </row>
     <row r="1574" spans="1:7" x14ac:dyDescent="0.25">
@@ -48874,17 +48874,17 @@
       <c r="C1576" s="6">
         <v>46296</v>
       </c>
-      <c r="D1576" s="8">
-        <v>0</v>
+      <c r="D1576" s="7">
+        <v>1.684954</v>
       </c>
       <c r="E1576" s="8">
-        <v>0</v>
+        <v>583927818</v>
       </c>
       <c r="F1576" s="9">
         <v>126</v>
       </c>
       <c r="G1576" s="8">
-        <v>0</v>
+        <v>983891586.89</v>
       </c>
     </row>
     <row r="1577" spans="1:7" x14ac:dyDescent="0.25">
@@ -49242,17 +49242,17 @@
       <c r="C1592" s="6">
         <v>46296</v>
       </c>
-      <c r="D1592" s="8">
-        <v>0</v>
+      <c r="D1592" s="7">
+        <v>0.943674</v>
       </c>
       <c r="E1592" s="8">
-        <v>0</v>
+        <v>300623899</v>
       </c>
       <c r="F1592" s="9">
         <v>1</v>
       </c>
       <c r="G1592" s="8">
-        <v>0</v>
+        <v>283690912.26</v>
       </c>
     </row>
     <row r="1593" spans="1:7" x14ac:dyDescent="0.25">
@@ -49472,17 +49472,17 @@
       <c r="C1602" s="6">
         <v>46296</v>
       </c>
-      <c r="D1602" s="8">
-        <v>0</v>
+      <c r="D1602" s="7">
+        <v>1.563267</v>
       </c>
       <c r="E1602" s="8">
-        <v>0</v>
+        <v>142114018</v>
       </c>
       <c r="F1602" s="9">
         <v>422</v>
       </c>
       <c r="G1602" s="8">
-        <v>0</v>
+        <v>222162185</v>
       </c>
     </row>
     <row r="1603" spans="1:7" x14ac:dyDescent="0.25">
@@ -49587,17 +49587,17 @@
       <c r="C1607" s="6">
         <v>46296</v>
       </c>
-      <c r="D1607" s="8">
-        <v>0</v>
+      <c r="D1607" s="7">
+        <v>0.955926</v>
       </c>
       <c r="E1607" s="8">
-        <v>0</v>
+        <v>17941127</v>
       </c>
       <c r="F1607" s="9">
         <v>110</v>
       </c>
       <c r="G1607" s="8">
-        <v>0</v>
+        <v>17150398.2</v>
       </c>
     </row>
     <row r="1608" spans="1:7" x14ac:dyDescent="0.25">
@@ -49726,7 +49726,7 @@
         <v>46296</v>
       </c>
       <c r="D1613" s="7">
-        <v>0.941036</v>
+        <v>0.941027</v>
       </c>
       <c r="E1613" s="8">
         <v>200254832</v>
@@ -49735,7 +49735,7 @@
         <v>60</v>
       </c>
       <c r="G1613" s="8">
-        <v>188447098.41</v>
+        <v>188445119.58</v>
       </c>
     </row>
     <row r="1614" spans="1:7" x14ac:dyDescent="0.25">
@@ -49781,7 +49781,7 @@
         <v>125</v>
       </c>
       <c r="G1615" s="8">
-        <v>75418859.91</v>
+        <v>75418860.06</v>
       </c>
     </row>
     <row r="1616" spans="1:7" x14ac:dyDescent="0.25">
@@ -49794,17 +49794,17 @@
       <c r="C1616" s="6">
         <v>46296</v>
       </c>
-      <c r="D1616" s="8">
-        <v>0</v>
+      <c r="D1616" s="7">
+        <v>3.280771</v>
       </c>
       <c r="E1616" s="8">
-        <v>0</v>
+        <v>14782189</v>
       </c>
       <c r="F1616" s="9">
         <v>589</v>
       </c>
       <c r="G1616" s="8">
-        <v>0</v>
+        <v>48496969.77</v>
       </c>
     </row>
     <row r="1617" spans="1:7" x14ac:dyDescent="0.25">
@@ -49840,17 +49840,17 @@
       <c r="C1618" s="6">
         <v>46296</v>
       </c>
-      <c r="D1618" s="8">
-        <v>0</v>
+      <c r="D1618" s="7">
+        <v>1.026203</v>
       </c>
       <c r="E1618" s="8">
-        <v>0</v>
+        <v>2900073</v>
       </c>
       <c r="F1618" s="9">
         <v>3</v>
       </c>
       <c r="G1618" s="8">
-        <v>0</v>
+        <v>2976062.61</v>
       </c>
     </row>
     <row r="1619" spans="1:7" x14ac:dyDescent="0.25">
@@ -49863,17 +49863,17 @@
       <c r="C1619" s="6">
         <v>46296</v>
       </c>
-      <c r="D1619" s="8">
-        <v>0</v>
+      <c r="D1619" s="7">
+        <v>0.792829</v>
       </c>
       <c r="E1619" s="8">
-        <v>0</v>
+        <v>1181522</v>
       </c>
       <c r="F1619" s="9">
         <v>5</v>
       </c>
       <c r="G1619" s="8">
-        <v>0</v>
+        <v>936744.97</v>
       </c>
     </row>
     <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
@@ -49886,17 +49886,17 @@
       <c r="C1620" s="6">
         <v>46296</v>
       </c>
-      <c r="D1620" s="8">
-        <v>0</v>
+      <c r="D1620" s="7">
+        <v>0.237523</v>
       </c>
       <c r="E1620" s="8">
-        <v>0</v>
+        <v>133057489</v>
       </c>
       <c r="F1620" s="9">
         <v>13</v>
       </c>
       <c r="G1620" s="8">
-        <v>0</v>
+        <v>31604241.67</v>
       </c>
     </row>
     <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
@@ -50140,7 +50140,7 @@
         <v>46296</v>
       </c>
       <c r="D1631" s="7">
-        <v>1.071139</v>
+        <v>1.071086</v>
       </c>
       <c r="E1631" s="8">
         <v>1400000000</v>
@@ -50149,7 +50149,7 @@
         <v>1</v>
       </c>
       <c r="G1631" s="8">
-        <v>1499594809.82</v>
+        <v>1499519833.83</v>
       </c>
     </row>
     <row r="1632" spans="1:7" x14ac:dyDescent="0.25">
@@ -50185,17 +50185,17 @@
       <c r="C1633" s="6">
         <v>46296</v>
       </c>
-      <c r="D1633" s="8">
-        <v>0</v>
+      <c r="D1633" s="7">
+        <v>1.549441</v>
       </c>
       <c r="E1633" s="8">
-        <v>0</v>
+        <v>14437699</v>
       </c>
       <c r="F1633" s="9">
         <v>433</v>
       </c>
       <c r="G1633" s="8">
-        <v>0</v>
+        <v>22370367.83</v>
       </c>
     </row>
     <row r="1634" spans="1:7" x14ac:dyDescent="0.25">
@@ -50669,7 +50669,7 @@
         <v>46296</v>
       </c>
       <c r="D1654" s="7">
-        <v>1.420495</v>
+        <v>1.419645</v>
       </c>
       <c r="E1654" s="8">
         <v>10658118</v>
@@ -50678,7 +50678,7 @@
         <v>155</v>
       </c>
       <c r="G1654" s="8">
-        <v>15139799.32</v>
+        <v>15130748.55</v>
       </c>
     </row>
     <row r="1655" spans="1:7" x14ac:dyDescent="0.25">
@@ -50784,7 +50784,7 @@
         <v>46296</v>
       </c>
       <c r="D1659" s="7">
-        <v>0.370024</v>
+        <v>0.370006</v>
       </c>
       <c r="E1659" s="8">
         <v>268845275</v>
@@ -50793,7 +50793,7 @@
         <v>661</v>
       </c>
       <c r="G1659" s="8">
-        <v>99479321.37</v>
+        <v>99474346.92</v>
       </c>
     </row>
     <row r="1660" spans="1:7" x14ac:dyDescent="0.25">
@@ -50807,7 +50807,7 @@
         <v>46296</v>
       </c>
       <c r="D1660" s="7">
-        <v>23.452912</v>
+        <v>23.458174</v>
       </c>
       <c r="E1660" s="8">
         <v>26129387</v>
@@ -50816,7 +50816,7 @@
         <v>454</v>
       </c>
       <c r="G1660" s="8">
-        <v>612810217.38</v>
+        <v>612947714.18</v>
       </c>
     </row>
     <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
@@ -51059,17 +51059,17 @@
       <c r="C1671" s="6">
         <v>46296</v>
       </c>
-      <c r="D1671" s="8">
-        <v>0</v>
+      <c r="D1671" s="7">
+        <v>21.643572</v>
       </c>
       <c r="E1671" s="8">
-        <v>0</v>
+        <v>52856435</v>
       </c>
       <c r="F1671" s="9">
         <v>1</v>
       </c>
       <c r="G1671" s="8">
-        <v>0</v>
+        <v>1144002049.01</v>
       </c>
     </row>
     <row r="1672" spans="1:7" x14ac:dyDescent="0.25">
@@ -51151,17 +51151,17 @@
       <c r="C1675" s="6">
         <v>46296</v>
       </c>
-      <c r="D1675" s="8">
-        <v>0</v>
+      <c r="D1675" s="7">
+        <v>54.713208</v>
       </c>
       <c r="E1675" s="8">
-        <v>0</v>
+        <v>749228592</v>
       </c>
       <c r="F1675" s="9">
         <v>10322</v>
       </c>
       <c r="G1675" s="8">
-        <v>0</v>
+        <v>40992699931.54</v>
       </c>
     </row>
     <row r="1676" spans="1:7" x14ac:dyDescent="0.25">
@@ -51197,17 +51197,17 @@
       <c r="C1677" s="6">
         <v>46296</v>
       </c>
-      <c r="D1677" s="8">
-        <v>0</v>
+      <c r="D1677" s="7">
+        <v>54.499486</v>
       </c>
       <c r="E1677" s="8">
-        <v>0</v>
+        <v>8357711.52</v>
       </c>
       <c r="F1677" s="9">
         <v>2313</v>
       </c>
       <c r="G1677" s="8">
-        <v>0</v>
+        <v>455490980.37</v>
       </c>
     </row>
     <row r="1678" spans="1:7" x14ac:dyDescent="0.25">
@@ -51358,17 +51358,17 @@
       <c r="C1684" s="6">
         <v>46296</v>
       </c>
-      <c r="D1684" s="8">
-        <v>0</v>
+      <c r="D1684" s="7">
+        <v>1.264049</v>
       </c>
       <c r="E1684" s="8">
-        <v>0</v>
+        <v>141657132</v>
       </c>
       <c r="F1684" s="9">
         <v>1</v>
       </c>
       <c r="G1684" s="8">
-        <v>0</v>
+        <v>179061611.34</v>
       </c>
     </row>
     <row r="1685" spans="1:7" x14ac:dyDescent="0.25">
@@ -51473,17 +51473,17 @@
       <c r="C1689" s="6">
         <v>46296</v>
       </c>
-      <c r="D1689" s="8">
-        <v>0</v>
+      <c r="D1689" s="7">
+        <v>61.184907</v>
       </c>
       <c r="E1689" s="8">
-        <v>0</v>
+        <v>2355768</v>
       </c>
       <c r="F1689" s="9">
         <v>19</v>
       </c>
       <c r="G1689" s="8">
-        <v>0</v>
+        <v>144137445.8</v>
       </c>
     </row>
     <row r="1690" spans="1:7" x14ac:dyDescent="0.25">
@@ -51496,17 +51496,17 @@
       <c r="C1690" s="6">
         <v>46296</v>
       </c>
-      <c r="D1690" s="8">
-        <v>0</v>
+      <c r="D1690" s="7">
+        <v>39.753844</v>
       </c>
       <c r="E1690" s="8">
-        <v>0</v>
+        <v>26213523</v>
       </c>
       <c r="F1690" s="9">
         <v>2722</v>
       </c>
       <c r="G1690" s="8">
-        <v>0</v>
+        <v>1042088311.57</v>
       </c>
     </row>
     <row r="1691" spans="1:7" x14ac:dyDescent="0.25">
@@ -51519,17 +51519,17 @@
       <c r="C1691" s="6">
         <v>46296</v>
       </c>
-      <c r="D1691" s="8">
-        <v>0</v>
+      <c r="D1691" s="7">
+        <v>6.793701</v>
       </c>
       <c r="E1691" s="8">
-        <v>0</v>
+        <v>345602582</v>
       </c>
       <c r="F1691" s="9">
         <v>1425</v>
       </c>
       <c r="G1691" s="8">
-        <v>0</v>
+        <v>2347920451.84</v>
       </c>
     </row>
     <row r="1692" spans="1:7" x14ac:dyDescent="0.25">
@@ -51588,17 +51588,17 @@
       <c r="C1694" s="6">
         <v>46296</v>
       </c>
-      <c r="D1694" s="8">
-        <v>0</v>
+      <c r="D1694" s="7">
+        <v>46.400886</v>
       </c>
       <c r="E1694" s="8">
-        <v>0</v>
+        <v>29704413</v>
       </c>
       <c r="F1694" s="9">
         <v>8605</v>
       </c>
       <c r="G1694" s="8">
-        <v>0</v>
+        <v>1378311086.07</v>
       </c>
     </row>
     <row r="1695" spans="1:7" x14ac:dyDescent="0.25">
@@ -52163,17 +52163,17 @@
       <c r="C1719" s="6">
         <v>46296</v>
       </c>
-      <c r="D1719" s="8">
-        <v>0</v>
+      <c r="D1719" s="7">
+        <v>51.356033</v>
       </c>
       <c r="E1719" s="8">
-        <v>0</v>
+        <v>19646399</v>
       </c>
       <c r="F1719" s="9">
         <v>106</v>
       </c>
       <c r="G1719" s="8">
-        <v>0</v>
+        <v>1008961122.31</v>
       </c>
     </row>
     <row r="1720" spans="1:7" x14ac:dyDescent="0.25">
@@ -52301,17 +52301,17 @@
       <c r="C1725" s="6">
         <v>46296</v>
       </c>
-      <c r="D1725" s="8">
-        <v>0</v>
+      <c r="D1725" s="10">
+        <v>67.74072</v>
       </c>
       <c r="E1725" s="8">
-        <v>0</v>
+        <v>29538426</v>
       </c>
       <c r="F1725" s="9">
         <v>1718</v>
       </c>
       <c r="G1725" s="8">
-        <v>0</v>
+        <v>2000954238.36</v>
       </c>
     </row>
     <row r="1726" spans="1:7" x14ac:dyDescent="0.25">
@@ -52416,17 +52416,17 @@
       <c r="C1730" s="6">
         <v>46296</v>
       </c>
-      <c r="D1730" s="8">
-        <v>0</v>
+      <c r="D1730" s="7">
+        <v>1.093904</v>
       </c>
       <c r="E1730" s="8">
-        <v>0</v>
+        <v>580742412</v>
       </c>
       <c r="F1730" s="9">
         <v>381</v>
       </c>
       <c r="G1730" s="8">
-        <v>0</v>
+        <v>635276715.91</v>
       </c>
     </row>
     <row r="1731" spans="1:7" x14ac:dyDescent="0.25">
@@ -52508,17 +52508,17 @@
       <c r="C1734" s="6">
         <v>46296</v>
       </c>
-      <c r="D1734" s="8">
-        <v>0</v>
+      <c r="D1734" s="7">
+        <v>71.947754</v>
       </c>
       <c r="E1734" s="8">
-        <v>0</v>
+        <v>5663669</v>
       </c>
       <c r="F1734" s="9">
         <v>1</v>
       </c>
       <c r="G1734" s="8">
-        <v>0</v>
+        <v>407488265.14</v>
       </c>
     </row>
     <row r="1735" spans="1:7" x14ac:dyDescent="0.25">
@@ -52531,17 +52531,17 @@
       <c r="C1735" s="6">
         <v>46296</v>
       </c>
-      <c r="D1735" s="8">
-        <v>0</v>
+      <c r="D1735" s="7">
+        <v>54.896158</v>
       </c>
       <c r="E1735" s="8">
-        <v>0</v>
+        <v>136039712</v>
       </c>
       <c r="F1735" s="9">
         <v>487</v>
       </c>
       <c r="G1735" s="8">
-        <v>0</v>
+        <v>7468057581.33</v>
       </c>
     </row>
     <row r="1736" spans="1:7" x14ac:dyDescent="0.25">
@@ -52554,17 +52554,17 @@
       <c r="C1736" s="6">
         <v>46296</v>
       </c>
-      <c r="D1736" s="8">
-        <v>0</v>
+      <c r="D1736" s="7">
+        <v>1.397008</v>
       </c>
       <c r="E1736" s="8">
-        <v>0</v>
+        <v>2601491042</v>
       </c>
       <c r="F1736" s="9">
         <v>12177</v>
       </c>
       <c r="G1736" s="8">
-        <v>0</v>
+        <v>3634303048.01</v>
       </c>
     </row>
     <row r="1737" spans="1:7" x14ac:dyDescent="0.25">
@@ -52715,17 +52715,17 @@
       <c r="C1743" s="6">
         <v>46296</v>
       </c>
-      <c r="D1743" s="8">
-        <v>0</v>
+      <c r="D1743" s="7">
+        <v>7.768161</v>
       </c>
       <c r="E1743" s="8">
-        <v>0</v>
+        <v>1168550000</v>
       </c>
       <c r="F1743" s="9">
         <v>1</v>
       </c>
       <c r="G1743" s="8">
-        <v>0</v>
+        <v>9077484314.86</v>
       </c>
     </row>
     <row r="1744" spans="1:7" x14ac:dyDescent="0.25">
@@ -52830,17 +52830,17 @@
       <c r="C1748" s="6">
         <v>46296</v>
       </c>
-      <c r="D1748" s="8">
-        <v>0</v>
+      <c r="D1748" s="10">
+        <v>50.80996</v>
       </c>
       <c r="E1748" s="8">
-        <v>0</v>
+        <v>12235569</v>
       </c>
       <c r="F1748" s="9">
         <v>78</v>
       </c>
       <c r="G1748" s="8">
-        <v>0</v>
+        <v>621688767.81</v>
       </c>
     </row>
     <row r="1749" spans="1:7" x14ac:dyDescent="0.25">
@@ -52876,17 +52876,17 @@
       <c r="C1750" s="6">
         <v>46296</v>
       </c>
-      <c r="D1750" s="8">
-        <v>0</v>
+      <c r="D1750" s="10">
+        <v>4.43656</v>
       </c>
       <c r="E1750" s="8">
-        <v>0</v>
+        <v>1216123947</v>
       </c>
       <c r="F1750" s="9">
         <v>3</v>
       </c>
       <c r="G1750" s="8">
-        <v>0</v>
+        <v>5395407200.87</v>
       </c>
     </row>
     <row r="1751" spans="1:7" x14ac:dyDescent="0.25">
@@ -52922,17 +52922,17 @@
       <c r="C1752" s="6">
         <v>46296</v>
       </c>
-      <c r="D1752" s="8">
-        <v>0</v>
+      <c r="D1752" s="7">
+        <v>11.771871</v>
       </c>
       <c r="E1752" s="8">
-        <v>0</v>
+        <v>706520242</v>
       </c>
       <c r="F1752" s="9">
         <v>2760</v>
       </c>
       <c r="G1752" s="8">
-        <v>0</v>
+        <v>8317065174.81</v>
       </c>
     </row>
     <row r="1753" spans="1:7" x14ac:dyDescent="0.25">
@@ -52991,17 +52991,17 @@
       <c r="C1755" s="6">
         <v>46296</v>
       </c>
-      <c r="D1755" s="8">
-        <v>0</v>
+      <c r="D1755" s="7">
+        <v>56.824246</v>
       </c>
       <c r="E1755" s="8">
-        <v>0</v>
+        <v>12799131</v>
       </c>
       <c r="F1755" s="9">
         <v>101</v>
       </c>
       <c r="G1755" s="8">
-        <v>0</v>
+        <v>727300967.77</v>
       </c>
     </row>
     <row r="1756" spans="1:7" x14ac:dyDescent="0.25">
@@ -53014,17 +53014,17 @@
       <c r="C1756" s="6">
         <v>46296</v>
       </c>
-      <c r="D1756" s="8">
-        <v>0</v>
+      <c r="D1756" s="7">
+        <v>59.262578</v>
       </c>
       <c r="E1756" s="8">
-        <v>0</v>
+        <v>398825187</v>
       </c>
       <c r="F1756" s="9">
         <v>6705</v>
       </c>
       <c r="G1756" s="8">
-        <v>0</v>
+        <v>23635408882.94</v>
       </c>
     </row>
     <row r="1757" spans="1:7" x14ac:dyDescent="0.25">
@@ -53037,17 +53037,17 @@
       <c r="C1757" s="6">
         <v>46296</v>
       </c>
-      <c r="D1757" s="8">
-        <v>0</v>
+      <c r="D1757" s="7">
+        <v>991.106416</v>
       </c>
       <c r="E1757" s="8">
-        <v>0</v>
+        <v>111995</v>
       </c>
       <c r="F1757" s="9">
         <v>623</v>
       </c>
       <c r="G1757" s="8">
-        <v>0</v>
+        <v>110998963.08</v>
       </c>
     </row>
     <row r="1758" spans="1:7" x14ac:dyDescent="0.25">
@@ -53060,17 +53060,17 @@
       <c r="C1758" s="6">
         <v>46296</v>
       </c>
-      <c r="D1758" s="8">
-        <v>0</v>
+      <c r="D1758" s="7">
+        <v>69.073912</v>
       </c>
       <c r="E1758" s="8">
-        <v>0</v>
+        <v>5611179</v>
       </c>
       <c r="F1758" s="9">
         <v>1</v>
       </c>
       <c r="G1758" s="8">
-        <v>0</v>
+        <v>387586082.45</v>
       </c>
     </row>
     <row r="1759" spans="1:7" x14ac:dyDescent="0.25">
@@ -53106,17 +53106,17 @@
       <c r="C1760" s="6">
         <v>46296</v>
       </c>
-      <c r="D1760" s="8">
-        <v>0</v>
+      <c r="D1760" s="7">
+        <v>12.519466</v>
       </c>
       <c r="E1760" s="8">
-        <v>0</v>
+        <v>418559328</v>
       </c>
       <c r="F1760" s="9">
         <v>10907</v>
       </c>
       <c r="G1760" s="8">
-        <v>0</v>
+        <v>5240139383.53</v>
       </c>
     </row>
     <row r="1761" spans="1:7" x14ac:dyDescent="0.25">
@@ -53175,17 +53175,17 @@
       <c r="C1763" s="6">
         <v>46296</v>
       </c>
-      <c r="D1763" s="8">
-        <v>0</v>
+      <c r="D1763" s="7">
+        <v>80.100602</v>
       </c>
       <c r="E1763" s="8">
-        <v>0</v>
+        <v>28781496</v>
       </c>
       <c r="F1763" s="9">
         <v>1406</v>
       </c>
       <c r="G1763" s="8">
-        <v>0</v>
+        <v>2305415164.68</v>
       </c>
     </row>
     <row r="1764" spans="1:7" x14ac:dyDescent="0.25">
@@ -53198,17 +53198,17 @@
       <c r="C1764" s="6">
         <v>46296</v>
       </c>
-      <c r="D1764" s="8">
-        <v>0</v>
+      <c r="D1764" s="7">
+        <v>21.232912</v>
       </c>
       <c r="E1764" s="8">
-        <v>0</v>
+        <v>23371034.01</v>
       </c>
       <c r="F1764" s="9">
         <v>1459</v>
       </c>
       <c r="G1764" s="8">
-        <v>0</v>
+        <v>496235097.67</v>
       </c>
     </row>
     <row r="1765" spans="1:7" x14ac:dyDescent="0.25">
@@ -53244,17 +53244,17 @@
       <c r="C1766" s="6">
         <v>46296</v>
       </c>
-      <c r="D1766" s="8">
-        <v>0</v>
+      <c r="D1766" s="7">
+        <v>76.783957</v>
       </c>
       <c r="E1766" s="8">
-        <v>0</v>
+        <v>22458000</v>
       </c>
       <c r="F1766" s="9">
         <v>357</v>
       </c>
       <c r="G1766" s="8">
-        <v>0</v>
+        <v>1724414116.41</v>
       </c>
     </row>
     <row r="1767" spans="1:7" x14ac:dyDescent="0.25">
@@ -53313,17 +53313,17 @@
       <c r="C1769" s="6">
         <v>46296</v>
       </c>
-      <c r="D1769" s="8">
-        <v>0</v>
+      <c r="D1769" s="7">
+        <v>29.023641</v>
       </c>
       <c r="E1769" s="8">
-        <v>0</v>
+        <v>5070361</v>
       </c>
       <c r="F1769" s="9">
         <v>1427</v>
       </c>
       <c r="G1769" s="8">
-        <v>0</v>
+        <v>147160338.09</v>
       </c>
     </row>
     <row r="1770" spans="1:7" x14ac:dyDescent="0.25">
@@ -53405,17 +53405,17 @@
       <c r="C1773" s="6">
         <v>46296</v>
       </c>
-      <c r="D1773" s="8">
-        <v>0</v>
+      <c r="D1773" s="7">
+        <v>6.703478</v>
       </c>
       <c r="E1773" s="8">
-        <v>0</v>
+        <v>403625836</v>
       </c>
       <c r="F1773" s="9">
         <v>457</v>
       </c>
       <c r="G1773" s="8">
-        <v>0</v>
+        <v>2705696831.29</v>
       </c>
     </row>
     <row r="1774" spans="1:7" x14ac:dyDescent="0.25">
@@ -53566,17 +53566,17 @@
       <c r="C1780" s="6">
         <v>46296</v>
       </c>
-      <c r="D1780" s="8">
-        <v>0</v>
+      <c r="D1780" s="7">
+        <v>52.891229</v>
       </c>
       <c r="E1780" s="8">
-        <v>0</v>
+        <v>17212505</v>
       </c>
       <c r="F1780" s="9">
         <v>105</v>
       </c>
       <c r="G1780" s="8">
-        <v>0</v>
+        <v>910390539.62</v>
       </c>
     </row>
     <row r="1781" spans="1:7" x14ac:dyDescent="0.25">
@@ -53589,17 +53589,17 @@
       <c r="C1781" s="6">
         <v>46296</v>
       </c>
-      <c r="D1781" s="8">
-        <v>0</v>
+      <c r="D1781" s="7">
+        <v>71.031345</v>
       </c>
       <c r="E1781" s="8">
-        <v>0</v>
+        <v>31086506</v>
       </c>
       <c r="F1781" s="9">
         <v>1</v>
       </c>
       <c r="G1781" s="8">
-        <v>0</v>
+        <v>2208116319.01</v>
       </c>
     </row>
     <row r="1782" spans="1:7" x14ac:dyDescent="0.25">
@@ -53658,17 +53658,17 @@
       <c r="C1784" s="6">
         <v>46296</v>
       </c>
-      <c r="D1784" s="8">
-        <v>0</v>
+      <c r="D1784" s="7">
+        <v>1.425066</v>
       </c>
       <c r="E1784" s="8">
-        <v>0</v>
+        <v>9999068263.21</v>
       </c>
       <c r="F1784" s="9">
         <v>29833</v>
       </c>
       <c r="G1784" s="8">
-        <v>0</v>
+        <v>14249337079.89</v>
       </c>
     </row>
     <row r="1785" spans="1:7" x14ac:dyDescent="0.25">
@@ -53682,7 +53682,7 @@
         <v>46296</v>
       </c>
       <c r="D1785" s="7">
-        <v>1.020192</v>
+        <v>1.020229</v>
       </c>
       <c r="E1785" s="8">
         <v>237908266</v>
@@ -53691,7 +53691,7 @@
         <v>297</v>
       </c>
       <c r="G1785" s="8">
-        <v>242712043.31</v>
+        <v>242720975.53</v>
       </c>
     </row>
     <row r="1786" spans="1:7" x14ac:dyDescent="0.25">
@@ -53727,17 +53727,17 @@
       <c r="C1787" s="6">
         <v>46296</v>
       </c>
-      <c r="D1787" s="8">
-        <v>0</v>
+      <c r="D1787" s="7">
+        <v>1.908445</v>
       </c>
       <c r="E1787" s="8">
-        <v>0</v>
+        <v>469376058.29</v>
       </c>
       <c r="F1787" s="9">
         <v>5883</v>
       </c>
       <c r="G1787" s="8">
-        <v>0</v>
+        <v>895778212.6</v>
       </c>
     </row>
     <row r="1788" spans="1:7" x14ac:dyDescent="0.25">
@@ -54073,7 +54073,7 @@
         <v>46296</v>
       </c>
       <c r="D1802" s="7">
-        <v>6.889821</v>
+        <v>6.891547</v>
       </c>
       <c r="E1802" s="8">
         <v>188235121</v>
@@ -54082,7 +54082,7 @@
         <v>221</v>
       </c>
       <c r="G1802" s="8">
-        <v>1296906198.9</v>
+        <v>1297231180.2</v>
       </c>
     </row>
     <row r="1803" spans="1:7" x14ac:dyDescent="0.25">
@@ -54533,7 +54533,7 @@
         <v>46296</v>
       </c>
       <c r="D1822" s="7">
-        <v>9.409261</v>
+        <v>9.410602</v>
       </c>
       <c r="E1822" s="8">
         <v>35492249</v>
@@ -54542,7 +54542,7 @@
         <v>44</v>
       </c>
       <c r="G1822" s="8">
-        <v>333955820.61</v>
+        <v>334003445.17</v>
       </c>
     </row>
     <row r="1823" spans="1:7" x14ac:dyDescent="0.25">
@@ -54670,17 +54670,17 @@
       <c r="C1828" s="6">
         <v>46296</v>
       </c>
-      <c r="D1828" s="8">
-        <v>0</v>
+      <c r="D1828" s="7">
+        <v>0.982122</v>
       </c>
       <c r="E1828" s="8">
-        <v>0</v>
+        <v>362078657</v>
       </c>
       <c r="F1828" s="9">
         <v>7208</v>
       </c>
       <c r="G1828" s="8">
-        <v>0</v>
+        <v>355605399.39</v>
       </c>
     </row>
     <row r="1829" spans="1:7" x14ac:dyDescent="0.25">
@@ -54716,17 +54716,17 @@
       <c r="C1830" s="6">
         <v>46296</v>
       </c>
-      <c r="D1830" s="8">
-        <v>0</v>
+      <c r="D1830" s="7">
+        <v>0.862247</v>
       </c>
       <c r="E1830" s="8">
-        <v>0</v>
+        <v>12373179</v>
       </c>
       <c r="F1830" s="9">
         <v>649</v>
       </c>
       <c r="G1830" s="8">
-        <v>0</v>
+        <v>10668730.58</v>
       </c>
     </row>
     <row r="1831" spans="1:7" x14ac:dyDescent="0.25">
@@ -54923,17 +54923,17 @@
       <c r="C1839" s="6">
         <v>46296</v>
       </c>
-      <c r="D1839" s="8">
-        <v>0</v>
+      <c r="D1839" s="7">
+        <v>2.903127</v>
       </c>
       <c r="E1839" s="8">
-        <v>0</v>
+        <v>2599151050</v>
       </c>
       <c r="F1839" s="9">
         <v>107</v>
       </c>
       <c r="G1839" s="8">
-        <v>0</v>
+        <v>7545666439.33</v>
       </c>
     </row>
     <row r="1840" spans="1:7" x14ac:dyDescent="0.25">
@@ -54946,17 +54946,17 @@
       <c r="C1840" s="6">
         <v>46296</v>
       </c>
-      <c r="D1840" s="8">
-        <v>0</v>
+      <c r="D1840" s="7">
+        <v>2.501375</v>
       </c>
       <c r="E1840" s="8">
-        <v>0</v>
+        <v>1458611965</v>
       </c>
       <c r="F1840" s="9">
         <v>181</v>
       </c>
       <c r="G1840" s="8">
-        <v>0</v>
+        <v>3648535260.06</v>
       </c>
     </row>
     <row r="1841" spans="1:7" x14ac:dyDescent="0.25">
@@ -54992,17 +54992,17 @@
       <c r="C1842" s="6">
         <v>46296</v>
       </c>
-      <c r="D1842" s="8">
-        <v>0</v>
+      <c r="D1842" s="7">
+        <v>1.019988</v>
       </c>
       <c r="E1842" s="8">
-        <v>0</v>
+        <v>5385921</v>
       </c>
       <c r="F1842" s="9">
         <v>206</v>
       </c>
       <c r="G1842" s="8">
-        <v>0</v>
+        <v>5493575.16</v>
       </c>
     </row>
     <row r="1843" spans="1:7" x14ac:dyDescent="0.25">
@@ -55015,17 +55015,17 @@
       <c r="C1843" s="6">
         <v>46296</v>
       </c>
-      <c r="D1843" s="8">
-        <v>0</v>
+      <c r="D1843" s="7">
+        <v>1.022753</v>
       </c>
       <c r="E1843" s="8">
-        <v>0</v>
+        <v>5929994</v>
       </c>
       <c r="F1843" s="9">
         <v>147</v>
       </c>
       <c r="G1843" s="8">
-        <v>0</v>
+        <v>6064916.55</v>
       </c>
     </row>
     <row r="1844" spans="1:7" x14ac:dyDescent="0.25">
@@ -55038,17 +55038,17 @@
       <c r="C1844" s="6">
         <v>46296</v>
       </c>
-      <c r="D1844" s="8">
-        <v>0</v>
+      <c r="D1844" s="7">
+        <v>0.919328</v>
       </c>
       <c r="E1844" s="8">
-        <v>0</v>
+        <v>21643461</v>
       </c>
       <c r="F1844" s="9">
         <v>618</v>
       </c>
       <c r="G1844" s="8">
-        <v>0</v>
+        <v>19897440.65</v>
       </c>
     </row>
     <row r="1845" spans="1:7" x14ac:dyDescent="0.25">
@@ -55061,17 +55061,17 @@
       <c r="C1845" s="6">
         <v>46296</v>
       </c>
-      <c r="D1845" s="8">
-        <v>0</v>
+      <c r="D1845" s="7">
+        <v>56.210938</v>
       </c>
       <c r="E1845" s="8">
-        <v>0</v>
+        <v>20163107</v>
       </c>
       <c r="F1845" s="9">
         <v>326</v>
       </c>
       <c r="G1845" s="8">
-        <v>0</v>
+        <v>1133387156.41</v>
       </c>
     </row>
     <row r="1846" spans="1:7" x14ac:dyDescent="0.25">
@@ -55084,17 +55084,17 @@
       <c r="C1846" s="6">
         <v>46296</v>
       </c>
-      <c r="D1846" s="8">
-        <v>0</v>
+      <c r="D1846" s="10">
+        <v>0.72415</v>
       </c>
       <c r="E1846" s="8">
-        <v>0</v>
+        <v>918454762</v>
       </c>
       <c r="F1846" s="9">
         <v>4468</v>
       </c>
       <c r="G1846" s="8">
-        <v>0</v>
+        <v>665099060.4</v>
       </c>
     </row>
     <row r="1847" spans="1:7" x14ac:dyDescent="0.25">
@@ -55199,17 +55199,17 @@
       <c r="C1851" s="6">
         <v>46296</v>
       </c>
-      <c r="D1851" s="8">
-        <v>0</v>
+      <c r="D1851" s="7">
+        <v>14.758893</v>
       </c>
       <c r="E1851" s="8">
-        <v>0</v>
+        <v>364802224</v>
       </c>
       <c r="F1851" s="9">
         <v>9625</v>
       </c>
       <c r="G1851" s="8">
-        <v>0</v>
+        <v>5384076998.08</v>
       </c>
     </row>
     <row r="1852" spans="1:7" x14ac:dyDescent="0.25">
@@ -55268,17 +55268,17 @@
       <c r="C1854" s="6">
         <v>46296</v>
       </c>
-      <c r="D1854" s="8">
-        <v>0</v>
+      <c r="D1854" s="7">
+        <v>15.069612</v>
       </c>
       <c r="E1854" s="8">
-        <v>0</v>
+        <v>125673235</v>
       </c>
       <c r="F1854" s="9">
         <v>3511</v>
       </c>
       <c r="G1854" s="8">
-        <v>0</v>
+        <v>1893846876.17</v>
       </c>
     </row>
     <row r="1855" spans="1:7" x14ac:dyDescent="0.25">
@@ -55521,17 +55521,17 @@
       <c r="C1865" s="6">
         <v>46296</v>
       </c>
-      <c r="D1865" s="8">
-        <v>0</v>
+      <c r="D1865" s="7">
+        <v>2.735245</v>
       </c>
       <c r="E1865" s="8">
-        <v>0</v>
+        <v>38406886</v>
       </c>
       <c r="F1865" s="9">
         <v>109</v>
       </c>
       <c r="G1865" s="8">
-        <v>0</v>
+        <v>105052224.76</v>
       </c>
     </row>
     <row r="1866" spans="1:7" x14ac:dyDescent="0.25">
@@ -55613,17 +55613,17 @@
       <c r="C1869" s="6">
         <v>46296</v>
       </c>
-      <c r="D1869" s="8">
-        <v>0</v>
+      <c r="D1869" s="7">
+        <v>4.180432</v>
       </c>
       <c r="E1869" s="8">
-        <v>0</v>
+        <v>95834351</v>
       </c>
       <c r="F1869" s="9">
         <v>240</v>
       </c>
       <c r="G1869" s="8">
-        <v>0</v>
+        <v>400628967</v>
       </c>
     </row>
     <row r="1870" spans="1:7" x14ac:dyDescent="0.25">
@@ -56096,17 +56096,17 @@
       <c r="C1890" s="6">
         <v>46296</v>
       </c>
-      <c r="D1890" s="8">
-        <v>0</v>
+      <c r="D1890" s="7">
+        <v>2.719572</v>
       </c>
       <c r="E1890" s="8">
-        <v>0</v>
+        <v>698327496</v>
       </c>
       <c r="F1890" s="9">
         <v>14207</v>
       </c>
       <c r="G1890" s="8">
-        <v>0</v>
+        <v>1899152198.92</v>
       </c>
     </row>
     <row r="1891" spans="1:7" x14ac:dyDescent="0.25">
@@ -56188,17 +56188,17 @@
       <c r="C1894" s="6">
         <v>46296</v>
       </c>
-      <c r="D1894" s="8">
-        <v>0</v>
+      <c r="D1894" s="7">
+        <v>5.760861</v>
       </c>
       <c r="E1894" s="8">
-        <v>0</v>
+        <v>167456209</v>
       </c>
       <c r="F1894" s="9">
         <v>12997</v>
       </c>
       <c r="G1894" s="8">
-        <v>0</v>
+        <v>964691895.31</v>
       </c>
     </row>
     <row r="1895" spans="1:7" x14ac:dyDescent="0.25">
@@ -57016,17 +57016,17 @@
       <c r="C1930" s="6">
         <v>46296</v>
       </c>
-      <c r="D1930" s="8">
-        <v>0</v>
+      <c r="D1930" s="7">
+        <v>7.845131</v>
       </c>
       <c r="E1930" s="8">
-        <v>0</v>
+        <v>681690349</v>
       </c>
       <c r="F1930" s="9">
         <v>3253</v>
       </c>
       <c r="G1930" s="8">
-        <v>0</v>
+        <v>5347949768.22</v>
       </c>
     </row>
     <row r="1931" spans="1:7" x14ac:dyDescent="0.25">
@@ -57177,17 +57177,17 @@
       <c r="C1937" s="6">
         <v>46296</v>
       </c>
-      <c r="D1937" s="8">
-        <v>0</v>
+      <c r="D1937" s="7">
+        <v>1.012141</v>
       </c>
       <c r="E1937" s="8">
-        <v>0</v>
+        <v>1806306558</v>
       </c>
       <c r="F1937" s="9">
         <v>14456</v>
       </c>
       <c r="G1937" s="8">
-        <v>0</v>
+        <v>1828236239.94</v>
       </c>
     </row>
     <row r="1938" spans="1:7" x14ac:dyDescent="0.25">
@@ -57637,17 +57637,17 @@
       <c r="C1957" s="6">
         <v>46296</v>
       </c>
-      <c r="D1957" s="8">
-        <v>0</v>
+      <c r="D1957" s="10">
+        <v>12.41964</v>
       </c>
       <c r="E1957" s="8">
-        <v>0</v>
+        <v>787129037</v>
       </c>
       <c r="F1957" s="9">
         <v>56825</v>
       </c>
       <c r="G1957" s="8">
-        <v>0</v>
+        <v>9775859143.8</v>
       </c>
     </row>
     <row r="1958" spans="1:7" x14ac:dyDescent="0.25">
@@ -57660,17 +57660,17 @@
       <c r="C1958" s="6">
         <v>46296</v>
       </c>
-      <c r="D1958" s="8">
-        <v>0</v>
+      <c r="D1958" s="7">
+        <v>10.292416</v>
       </c>
       <c r="E1958" s="8">
-        <v>0</v>
+        <v>52919979</v>
       </c>
       <c r="F1958" s="9">
         <v>5035</v>
       </c>
       <c r="G1958" s="8">
-        <v>0</v>
+        <v>544674440.66</v>
       </c>
     </row>
     <row r="1959" spans="1:7" x14ac:dyDescent="0.25">
@@ -58327,8 +58327,8 @@
       <c r="C1987" s="6">
         <v>46296</v>
       </c>
-      <c r="D1987" s="10">
-        <v>9.45508</v>
+      <c r="D1987" s="7">
+        <v>9.454937</v>
       </c>
       <c r="E1987" s="8">
         <v>804765378</v>
@@ -58337,7 +58337,7 @@
         <v>1513</v>
       </c>
       <c r="G1987" s="8">
-        <v>7609120957.16</v>
+        <v>7609005618.59</v>
       </c>
     </row>
     <row r="1988" spans="1:7" x14ac:dyDescent="0.25">
@@ -58511,17 +58511,17 @@
       <c r="C1995" s="6">
         <v>46296</v>
       </c>
-      <c r="D1995" s="8">
-        <v>0</v>
+      <c r="D1995" s="7">
+        <v>51.299808</v>
       </c>
       <c r="E1995" s="8">
-        <v>0</v>
+        <v>9016463</v>
       </c>
       <c r="F1995" s="9">
         <v>46</v>
       </c>
       <c r="G1995" s="8">
-        <v>0</v>
+        <v>462542823.33</v>
       </c>
     </row>
     <row r="1996" spans="1:7" x14ac:dyDescent="0.25">
@@ -58673,7 +58673,7 @@
         <v>46296</v>
       </c>
       <c r="D2002" s="7">
-        <v>1.864687</v>
+        <v>1.864345</v>
       </c>
       <c r="E2002" s="8">
         <v>306521428</v>
@@ -58682,7 +58682,7 @@
         <v>11</v>
       </c>
       <c r="G2002" s="8">
-        <v>571566639.75</v>
+        <v>571461804.03</v>
       </c>
     </row>
     <row r="2003" spans="1:7" x14ac:dyDescent="0.25">
@@ -58719,7 +58719,7 @@
         <v>46296</v>
       </c>
       <c r="D2004" s="7">
-        <v>6.147473</v>
+        <v>6.146307</v>
       </c>
       <c r="E2004" s="8">
         <v>106786382</v>
@@ -58728,7 +58728,7 @@
         <v>1</v>
       </c>
       <c r="G2004" s="8">
-        <v>656466433.65</v>
+        <v>656341877.42</v>
       </c>
     </row>
     <row r="2005" spans="1:7" x14ac:dyDescent="0.25">
@@ -59156,7 +59156,7 @@
         <v>46296</v>
       </c>
       <c r="D2023" s="7">
-        <v>12.942766</v>
+        <v>12.944136</v>
       </c>
       <c r="E2023" s="8">
         <v>216588410</v>
@@ -59165,7 +59165,7 @@
         <v>25</v>
       </c>
       <c r="G2023" s="8">
-        <v>2803253127.66</v>
+        <v>2803549907.13</v>
       </c>
     </row>
     <row r="2024" spans="1:7" x14ac:dyDescent="0.25">
@@ -59247,8 +59247,8 @@
       <c r="C2027" s="6">
         <v>46296</v>
       </c>
-      <c r="D2027" s="10">
-        <v>7.85292</v>
+      <c r="D2027" s="7">
+        <v>7.851966</v>
       </c>
       <c r="E2027" s="8">
         <v>274862095</v>
@@ -59257,7 +59257,7 @@
         <v>1</v>
       </c>
       <c r="G2027" s="8">
-        <v>2158469944.02</v>
+        <v>2158207836.16</v>
       </c>
     </row>
     <row r="2028" spans="1:7" x14ac:dyDescent="0.25">
